--- a/顶奢_整站资料批量编辑.xlsx
+++ b/顶奢_整站资料批量编辑.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2924" uniqueCount="1592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2924" uniqueCount="1574">
   <si>
     <t>顶奢 · 整站资料批量编辑</t>
   </si>
@@ -1783,16 +1783,16 @@
     <t>beijing</t>
   </si>
   <si>
-    <t>北京澄光雅集</t>
+    <t>北京外围模特</t>
   </si>
   <si>
     <t>北京外围｜北京商务模特｜北京外围模特</t>
   </si>
   <si>
-    <t>浏览北京澄光雅集的独立资料、图片说明、内容介绍与相关推荐。</t>
-  </si>
-  <si>
-    <t>北京澄光雅集主题资料展示页，内容、图片和视频可按实际资料独立更新。</t>
+    <t>浏览北京外围模特的独立资料、图片说明、内容介绍与相关推荐。</t>
+  </si>
+  <si>
+    <t>北京外围模特资料展示页，内容、图片和视频可按实际资料独立更新。</t>
   </si>
   <si>
     <t>北京澄光雅集拥有独立内容区域，图片说明与页面文字围绕同一资料主题设置。</t>
@@ -1840,15 +1840,9 @@
     <t>北京澄光雅集资料展示</t>
   </si>
   <si>
-    <t>北京鎏金映像</t>
-  </si>
-  <si>
     <t>北京外围 ｜北京外围女｜北京外围女联系方式</t>
   </si>
   <si>
-    <t>浏览北京鎏金映像的独立资料、图片说明、内容介绍与相关推荐。</t>
-  </si>
-  <si>
     <t>北京鎏金映像主题资料展示页，内容、图片和视频可按实际资料独立更新。</t>
   </si>
   <si>
@@ -1891,15 +1885,9 @@
     <t>北京鎏金映像资料展示</t>
   </si>
   <si>
-    <t>北京云端风尚</t>
-  </si>
-  <si>
     <t>北京外围｜北京朝阳区外围｜北京外围上门</t>
   </si>
   <si>
-    <t>浏览北京云端风尚的独立资料、图片说明、内容介绍与相关推荐。</t>
-  </si>
-  <si>
     <t>北京云端风尚主题资料展示页，内容、图片和视频可按实际资料独立更新。</t>
   </si>
   <si>
@@ -1942,15 +1930,9 @@
     <t>北京云端风尚资料展示</t>
   </si>
   <si>
-    <t>北京星河雅韵</t>
-  </si>
-  <si>
     <t>北京外围｜北京朝阳区外围上门｜北京上门服务</t>
   </si>
   <si>
-    <t>浏览北京星河雅韵的独立资料、图片说明、内容介绍与相关推荐。</t>
-  </si>
-  <si>
     <t>北京星河雅韵主题资料展示页，内容、图片和视频可按实际资料独立更新。</t>
   </si>
   <si>
@@ -1993,15 +1975,9 @@
     <t>北京星河雅韵资料展示</t>
   </si>
   <si>
-    <t>北京绮境轻奢</t>
-  </si>
-  <si>
     <t>北京外围｜北京怎么找外围｜北京外围资源</t>
   </si>
   <si>
-    <t>浏览北京绮境轻奢的独立资料、图片说明、内容介绍与相关推荐。</t>
-  </si>
-  <si>
     <t>北京绮境轻奢主题资料展示页，内容、图片和视频可按实际资料独立更新。</t>
   </si>
   <si>
@@ -2044,15 +2020,9 @@
     <t>北京绮境轻奢资料展示</t>
   </si>
   <si>
-    <t>北京摩登画境</t>
-  </si>
-  <si>
     <t>北京外围｜北京上门服务｜北京网红外围</t>
   </si>
   <si>
-    <t>浏览北京摩登画境的独立资料、图片说明、内容介绍与相关推荐。</t>
-  </si>
-  <si>
     <t>北京摩登画境主题资料展示页，内容、图片和视频可按实际资料独立更新。</t>
   </si>
   <si>
@@ -2095,15 +2065,9 @@
     <t>北京摩登画境资料展示</t>
   </si>
   <si>
-    <t>北京静雅臻选</t>
-  </si>
-  <si>
     <t>北京外围｜北京外围女｜北京高端模特预约</t>
   </si>
   <si>
-    <t>浏览北京静雅臻选的独立资料、图片说明、内容介绍与相关推荐。</t>
-  </si>
-  <si>
     <t>北京静雅臻选主题资料展示页，内容、图片和视频可按实际资料独立更新。</t>
   </si>
   <si>
@@ -2146,15 +2110,9 @@
     <t>北京静雅臻选资料展示</t>
   </si>
   <si>
-    <t>北京璀璨华章</t>
-  </si>
-  <si>
     <t>北京外围｜北京外围模特预约｜北京学生外围</t>
   </si>
   <si>
-    <t>浏览北京璀璨华章的独立资料、图片说明、内容介绍与相关推荐。</t>
-  </si>
-  <si>
     <t>北京璀璨华章主题资料展示页，内容、图片和视频可按实际资料独立更新。</t>
   </si>
   <si>
@@ -2197,15 +2155,9 @@
     <t>北京璀璨华章资料展示</t>
   </si>
   <si>
-    <t>北京高定风格</t>
-  </si>
-  <si>
     <t>北京外围｜北京外围经纪｜北京外围资源</t>
   </si>
   <si>
-    <t>浏览北京高定风格的独立资料、图片说明、内容介绍与相关推荐。</t>
-  </si>
-  <si>
     <t>北京高定风格主题资料展示页，内容、图片和视频可按实际资料独立更新。</t>
   </si>
   <si>
@@ -2248,15 +2200,9 @@
     <t>北京高定风格资料展示</t>
   </si>
   <si>
-    <t>北京城市绮梦</t>
-  </si>
-  <si>
     <t>北京外围｜北京女大学生外围｜北京高端外围</t>
   </si>
   <si>
-    <t>浏览北京城市绮梦的独立资料、图片说明、内容介绍与相关推荐。</t>
-  </si>
-  <si>
     <t>北京城市绮梦主题资料展示页，内容、图片和视频可按实际资料独立更新。</t>
   </si>
   <si>
@@ -3676,7 +3622,7 @@
     <t>海派格调与都会精选</t>
   </si>
   <si>
-    <t>上海精选资料与城市资源库｜顶奢</t>
+    <t>上海外围｜上海模特预约｜顶奢</t>
   </si>
   <si>
     <t>顶奢上海资源库，集中展示上海城市精选资料、独立图片、视频、风格介绍与相关推荐。</t>
@@ -3685,7 +3631,7 @@
     <t>CITY COLLECTION</t>
   </si>
   <si>
-    <t>上海精选资料与城市浏览指南</t>
+    <t>上海精选资料</t>
   </si>
   <si>
     <t>欢迎您来到顶奢上海精选，网页只展示部分女孩资料，进入独立详情页查看照片、视频与完整介绍，更多资源请联系客服加入会员后解锁！</t>
@@ -3697,7 +3643,7 @@
     <t>CITY GUIDE</t>
   </si>
   <si>
-    <t>上海城市资料浏览指南</t>
+    <t>上海资料浏览指南</t>
   </si>
   <si>
     <t>上海兼具都会节奏与精致审美，资料库收录不同风格的城市精选内容。你可以从个人气质、形象特点和展示风格入手，进入独立详情页查看照片、视频与完整介绍。</t>
@@ -3736,7 +3682,7 @@
     <t>ALL PROFILES</t>
   </si>
   <si>
-    <t>上海全部资料</t>
+    <t>上海部分资料展示</t>
   </si>
   <si>
     <t>当前共 {count} 个可直接访问的独立详情页。</t>
@@ -3745,7 +3691,7 @@
     <t>上海资源常见问题</t>
   </si>
   <si>
-    <t>关于页面浏览、媒体更新和站内跳转的简要说明。</t>
+    <t>关于流程与价格的简要说明。</t>
   </si>
   <si>
     <t>怎样查看上海全部资料？</t>
@@ -3775,7 +3721,7 @@
     <t>岭南风尚与城市精选</t>
   </si>
   <si>
-    <t>广州精选资料与城市资源库｜顶奢</t>
+    <t>广州外围｜广州模特预约｜顶奢</t>
   </si>
   <si>
     <t>顶奢广州资源库，浏览广州城市精选资料、专属图片、视频介绍及相关城市内容。</t>
@@ -3787,7 +3733,7 @@
     <t>欢迎您来到顶奢广州精选，网页只展示部分女孩资料，更多资源请联系客服加入会员后解锁！</t>
   </si>
   <si>
-    <t>广州城市资料浏览指南</t>
+    <t>广州资料浏览指南</t>
   </si>
   <si>
     <t>广州城市资料注重自然气质与多样风格，每套资料均有独立页面，可查看图片、视频和详细介绍。</t>
@@ -3805,7 +3751,7 @@
     <t>广州精选入口</t>
   </si>
   <si>
-    <t>广州全部资料</t>
+    <t>广州部分资料展示</t>
   </si>
   <si>
     <t>广州资源常见问题</t>
@@ -3817,7 +3763,7 @@
     <t>湾区新锐与现代精选</t>
   </si>
   <si>
-    <t>深圳精选资料与城市资源库｜顶奢</t>
+    <t>深圳外围｜深圳模特预约｜顶奢</t>
   </si>
   <si>
     <t>顶奢深圳资源库，查看深圳现代城市精选资料、图片展示、视频位置与相关推荐。</t>
@@ -3829,7 +3775,7 @@
     <t>欢迎您来到顶奢深圳精选，网页只展示部分女孩资料，更多资源请联系客服加入会员后解锁！</t>
   </si>
   <si>
-    <t>深圳城市资料浏览指南</t>
+    <t>深圳资料浏览指南</t>
   </si>
   <si>
     <t>深圳资料库以现代、时尚和年轻化风格为主，收录不同气质的城市精选资料。你可以通过资料卡快速了解基本特点，再进入详情页查看完整图片、视频与介绍。</t>
@@ -3850,7 +3796,7 @@
     <t>深圳精选入口</t>
   </si>
   <si>
-    <t>深圳全部资料</t>
+    <t>深圳部分资料展示</t>
   </si>
   <si>
     <t>深圳资源常见问题</t>
@@ -3862,7 +3808,7 @@
     <t>京华气韵与城市精选</t>
   </si>
   <si>
-    <t>北京精选资料与城市资源库｜顶奢</t>
+    <t>北京外围｜北京模特预约｜顶奢</t>
   </si>
   <si>
     <t>顶奢北京资源库，汇总北京城市精选资料、独立图片、视频、专题说明和相关推荐。</t>
@@ -3874,7 +3820,7 @@
     <t>欢迎您来到顶奢北京精选，网页只展示部分女孩资料，更多资源请联系客服加入会员后解锁！</t>
   </si>
   <si>
-    <t>北京城市资料浏览指南</t>
+    <t>北京资料浏览指南</t>
   </si>
   <si>
     <t>朝阳、海淀、东城等区域都有工作室，也可以上门，具体要求请在咨询时说明。</t>
@@ -3889,7 +3835,7 @@
     <t>北京精选入口</t>
   </si>
   <si>
-    <t>北京全部资料</t>
+    <t>北京部分资料展示</t>
   </si>
   <si>
     <t>北京资源常见问题</t>
@@ -3901,7 +3847,7 @@
     <t>江南雅意与城市精选</t>
   </si>
   <si>
-    <t>杭州精选资料与城市资源库｜顶奢</t>
+    <t>杭州外围｜杭州模特预约｜顶奢</t>
   </si>
   <si>
     <t>顶奢杭州资源库，浏览杭州城市精选资料、独立图片说明、视频信息、独立说明与站内推荐。</t>
@@ -3913,7 +3859,7 @@
     <t>欢迎您来到顶奢杭州精选，网页只展示部分女孩资料，更多资源请联系客服加入会员后解锁！</t>
   </si>
   <si>
-    <t>杭州城市资料浏览指南</t>
+    <t>杭州资料浏览指南</t>
   </si>
   <si>
     <t>杭州城市资料以雅致和精致风格为主，适合按照个人气质、形象特点喜好和展示内容进行浏览。每套资料都有独立页面，便于查看照片、视频和详细说明。</t>
@@ -3928,7 +3874,7 @@
     <t>杭州精选入口</t>
   </si>
   <si>
-    <t>杭州全部资料</t>
+    <t>杭州部分资料展示</t>
   </si>
   <si>
     <t>杭州资源常见问题</t>
@@ -5473,7 +5419,7 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -9597,16 +9543,16 @@
       <c r="D35" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="16" t="s">
         <v>583</v>
       </c>
       <c r="F35" s="21" t="s">
         <v>584</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G35" s="16" t="s">
         <v>585</v>
       </c>
-      <c r="H35" s="4" t="s">
+      <c r="H35" s="16" t="s">
         <v>586</v>
       </c>
       <c r="I35" s="4" t="s">
@@ -9699,17 +9645,17 @@
       <c r="D36" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="16" t="s">
+        <v>583</v>
+      </c>
+      <c r="F36" s="21" t="s">
         <v>602</v>
       </c>
-      <c r="F36" s="21" t="s">
+      <c r="G36" s="16" t="s">
+        <v>585</v>
+      </c>
+      <c r="H36" s="4" t="s">
         <v>603</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>605</v>
       </c>
       <c r="I36" s="4" t="s">
         <v>74</v>
@@ -9718,7 +9664,7 @@
         <v>49</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="L36" s="4" t="s">
         <v>241</v>
@@ -9727,25 +9673,25 @@
         <v>588</v>
       </c>
       <c r="N36" s="20" t="s">
+        <v>605</v>
+      </c>
+      <c r="O36" s="20" t="s">
+        <v>606</v>
+      </c>
+      <c r="P36" s="20" t="s">
         <v>607</v>
       </c>
-      <c r="O36" s="20" t="s">
+      <c r="Q36" s="20" t="s">
         <v>608</v>
       </c>
-      <c r="P36" s="20" t="s">
+      <c r="R36" s="20" t="s">
         <v>609</v>
-      </c>
-      <c r="Q36" s="20" t="s">
-        <v>610</v>
-      </c>
-      <c r="R36" s="20" t="s">
-        <v>611</v>
       </c>
       <c r="S36" s="22" t="s">
         <v>594</v>
       </c>
       <c r="T36" s="20" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="U36" s="4" t="s">
         <v>60</v>
@@ -9762,22 +9708,22 @@
       <c r="Y36" s="17"/>
       <c r="Z36" s="17"/>
       <c r="AA36" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="AB36" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="AC36" s="4" t="s">
         <v>613</v>
       </c>
-      <c r="AB36" s="4" t="s">
+      <c r="AD36" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="AC36" s="4" t="s">
+      <c r="AE36" s="4" t="s">
         <v>615</v>
       </c>
-      <c r="AD36" s="4" t="s">
+      <c r="AF36" s="4" t="s">
         <v>616</v>
-      </c>
-      <c r="AE36" s="4" t="s">
-        <v>617</v>
-      </c>
-      <c r="AF36" s="4" t="s">
-        <v>618</v>
       </c>
       <c r="AG36" s="4"/>
       <c r="AH36" s="4"/>
@@ -9801,17 +9747,17 @@
       <c r="D37" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="E37" s="4" t="s">
-        <v>619</v>
+      <c r="E37" s="16" t="s">
+        <v>583</v>
       </c>
       <c r="F37" s="21" t="s">
-        <v>620</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>621</v>
+        <v>617</v>
+      </c>
+      <c r="G37" s="16" t="s">
+        <v>585</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="I37" s="4" t="s">
         <v>93</v>
@@ -9820,7 +9766,7 @@
         <v>49</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="L37" s="4" t="s">
         <v>241</v>
@@ -9829,25 +9775,25 @@
         <v>588</v>
       </c>
       <c r="N37" s="20" t="s">
+        <v>620</v>
+      </c>
+      <c r="O37" s="20" t="s">
+        <v>621</v>
+      </c>
+      <c r="P37" s="20" t="s">
+        <v>622</v>
+      </c>
+      <c r="Q37" s="20" t="s">
+        <v>623</v>
+      </c>
+      <c r="R37" s="20" t="s">
         <v>624</v>
-      </c>
-      <c r="O37" s="20" t="s">
-        <v>625</v>
-      </c>
-      <c r="P37" s="20" t="s">
-        <v>626</v>
-      </c>
-      <c r="Q37" s="20" t="s">
-        <v>627</v>
-      </c>
-      <c r="R37" s="20" t="s">
-        <v>628</v>
       </c>
       <c r="S37" s="22" t="s">
         <v>594</v>
       </c>
       <c r="T37" s="20" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="U37" s="4" t="s">
         <v>60</v>
@@ -9864,22 +9810,22 @@
       <c r="Y37" s="17"/>
       <c r="Z37" s="17"/>
       <c r="AA37" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="AB37" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="AC37" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="AD37" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="AE37" s="4" t="s">
         <v>630</v>
       </c>
-      <c r="AB37" s="4" t="s">
+      <c r="AF37" s="4" t="s">
         <v>631</v>
-      </c>
-      <c r="AC37" s="4" t="s">
-        <v>632</v>
-      </c>
-      <c r="AD37" s="4" t="s">
-        <v>633</v>
-      </c>
-      <c r="AE37" s="4" t="s">
-        <v>634</v>
-      </c>
-      <c r="AF37" s="4" t="s">
-        <v>635</v>
       </c>
       <c r="AG37" s="4"/>
       <c r="AH37" s="4"/>
@@ -9903,17 +9849,17 @@
       <c r="D38" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="E38" s="4" t="s">
-        <v>636</v>
+      <c r="E38" s="16" t="s">
+        <v>583</v>
       </c>
       <c r="F38" s="21" t="s">
-        <v>637</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>638</v>
+        <v>632</v>
+      </c>
+      <c r="G38" s="16" t="s">
+        <v>585</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="I38" s="4" t="s">
         <v>112</v>
@@ -9922,7 +9868,7 @@
         <v>49</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="L38" s="4" t="s">
         <v>241</v>
@@ -9931,25 +9877,25 @@
         <v>588</v>
       </c>
       <c r="N38" s="20" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="O38" s="20" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="P38" s="20" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="Q38" s="20" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="R38" s="20" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="S38" s="22" t="s">
         <v>594</v>
       </c>
       <c r="T38" s="20" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="U38" s="4" t="s">
         <v>60</v>
@@ -9966,22 +9912,22 @@
       <c r="Y38" s="17"/>
       <c r="Z38" s="17"/>
       <c r="AA38" s="4" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="AB38" s="4" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="AC38" s="4" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="AD38" s="4" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="AE38" s="4" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="AF38" s="4" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="AG38" s="4"/>
       <c r="AH38" s="4"/>
@@ -10005,17 +9951,17 @@
       <c r="D39" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="E39" s="4" t="s">
-        <v>653</v>
+      <c r="E39" s="16" t="s">
+        <v>583</v>
       </c>
       <c r="F39" s="21" t="s">
-        <v>654</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>655</v>
+        <v>647</v>
+      </c>
+      <c r="G39" s="16" t="s">
+        <v>585</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="I39" s="4" t="s">
         <v>131</v>
@@ -10024,7 +9970,7 @@
         <v>49</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="L39" s="4" t="s">
         <v>241</v>
@@ -10033,25 +9979,25 @@
         <v>588</v>
       </c>
       <c r="N39" s="20" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="O39" s="20" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="P39" s="20" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="Q39" s="20" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="R39" s="20" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="S39" s="22" t="s">
         <v>594</v>
       </c>
       <c r="T39" s="20" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="U39" s="4" t="s">
         <v>60</v>
@@ -10068,22 +10014,22 @@
       <c r="Y39" s="17"/>
       <c r="Z39" s="17"/>
       <c r="AA39" s="4" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="AB39" s="4" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="AC39" s="4" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="AD39" s="4" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="AE39" s="4" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="AF39" s="4" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="AG39" s="4"/>
       <c r="AH39" s="4"/>
@@ -10107,17 +10053,17 @@
       <c r="D40" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="E40" s="4" t="s">
-        <v>670</v>
+      <c r="E40" s="16" t="s">
+        <v>583</v>
       </c>
       <c r="F40" s="21" t="s">
-        <v>671</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>672</v>
+        <v>662</v>
+      </c>
+      <c r="G40" s="16" t="s">
+        <v>585</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="I40" s="4" t="s">
         <v>48</v>
@@ -10126,7 +10072,7 @@
         <v>49</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="L40" s="4" t="s">
         <v>241</v>
@@ -10135,25 +10081,25 @@
         <v>588</v>
       </c>
       <c r="N40" s="20" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="O40" s="20" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="P40" s="20" t="s">
-        <v>677</v>
+        <v>667</v>
       </c>
       <c r="Q40" s="20" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="R40" s="20" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="S40" s="22" t="s">
         <v>594</v>
       </c>
       <c r="T40" s="20" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="U40" s="4" t="s">
         <v>60</v>
@@ -10170,22 +10116,22 @@
       <c r="Y40" s="17"/>
       <c r="Z40" s="17"/>
       <c r="AA40" s="4" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="AB40" s="4" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="AC40" s="4" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="AD40" s="4" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="AE40" s="4" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="AF40" s="4" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="AG40" s="4"/>
       <c r="AH40" s="4"/>
@@ -10209,17 +10155,17 @@
       <c r="D41" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="E41" s="4" t="s">
-        <v>687</v>
+      <c r="E41" s="16" t="s">
+        <v>583</v>
       </c>
       <c r="F41" s="21" t="s">
-        <v>688</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>689</v>
+        <v>677</v>
+      </c>
+      <c r="G41" s="16" t="s">
+        <v>585</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>690</v>
+        <v>678</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>74</v>
@@ -10228,7 +10174,7 @@
         <v>49</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>691</v>
+        <v>679</v>
       </c>
       <c r="L41" s="4" t="s">
         <v>241</v>
@@ -10237,25 +10183,25 @@
         <v>588</v>
       </c>
       <c r="N41" s="20" t="s">
-        <v>692</v>
+        <v>680</v>
       </c>
       <c r="O41" s="20" t="s">
-        <v>693</v>
+        <v>681</v>
       </c>
       <c r="P41" s="20" t="s">
-        <v>694</v>
+        <v>682</v>
       </c>
       <c r="Q41" s="20" t="s">
-        <v>695</v>
+        <v>683</v>
       </c>
       <c r="R41" s="20" t="s">
-        <v>696</v>
+        <v>684</v>
       </c>
       <c r="S41" s="22" t="s">
         <v>594</v>
       </c>
       <c r="T41" s="20" t="s">
-        <v>697</v>
+        <v>685</v>
       </c>
       <c r="U41" s="4" t="s">
         <v>60</v>
@@ -10272,22 +10218,22 @@
       <c r="Y41" s="17"/>
       <c r="Z41" s="17"/>
       <c r="AA41" s="4" t="s">
-        <v>698</v>
+        <v>686</v>
       </c>
       <c r="AB41" s="4" t="s">
-        <v>699</v>
+        <v>687</v>
       </c>
       <c r="AC41" s="4" t="s">
-        <v>700</v>
+        <v>688</v>
       </c>
       <c r="AD41" s="4" t="s">
-        <v>701</v>
+        <v>689</v>
       </c>
       <c r="AE41" s="4" t="s">
-        <v>702</v>
+        <v>690</v>
       </c>
       <c r="AF41" s="4" t="s">
-        <v>703</v>
+        <v>691</v>
       </c>
       <c r="AG41" s="4"/>
       <c r="AH41" s="4"/>
@@ -10311,17 +10257,17 @@
       <c r="D42" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="E42" s="4" t="s">
-        <v>704</v>
+      <c r="E42" s="16" t="s">
+        <v>583</v>
       </c>
       <c r="F42" s="21" t="s">
-        <v>705</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>706</v>
+        <v>692</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>585</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="I42" s="4" t="s">
         <v>93</v>
@@ -10330,7 +10276,7 @@
         <v>49</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="L42" s="4" t="s">
         <v>241</v>
@@ -10339,25 +10285,25 @@
         <v>588</v>
       </c>
       <c r="N42" s="20" t="s">
-        <v>709</v>
+        <v>695</v>
       </c>
       <c r="O42" s="20" t="s">
-        <v>710</v>
+        <v>696</v>
       </c>
       <c r="P42" s="20" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="Q42" s="20" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="R42" s="20" t="s">
-        <v>713</v>
+        <v>699</v>
       </c>
       <c r="S42" s="22" t="s">
         <v>594</v>
       </c>
       <c r="T42" s="20" t="s">
-        <v>714</v>
+        <v>700</v>
       </c>
       <c r="U42" s="4" t="s">
         <v>60</v>
@@ -10374,22 +10320,22 @@
       <c r="Y42" s="17"/>
       <c r="Z42" s="17"/>
       <c r="AA42" s="4" t="s">
-        <v>715</v>
+        <v>701</v>
       </c>
       <c r="AB42" s="4" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="AC42" s="4" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="AD42" s="4" t="s">
-        <v>718</v>
+        <v>704</v>
       </c>
       <c r="AE42" s="4" t="s">
-        <v>719</v>
+        <v>705</v>
       </c>
       <c r="AF42" s="4" t="s">
-        <v>720</v>
+        <v>706</v>
       </c>
       <c r="AG42" s="4"/>
       <c r="AH42" s="4"/>
@@ -10413,17 +10359,17 @@
       <c r="D43" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="E43" s="4" t="s">
-        <v>721</v>
+      <c r="E43" s="16" t="s">
+        <v>583</v>
       </c>
       <c r="F43" s="21" t="s">
-        <v>722</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>723</v>
+        <v>707</v>
+      </c>
+      <c r="G43" s="16" t="s">
+        <v>585</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>724</v>
+        <v>708</v>
       </c>
       <c r="I43" s="4" t="s">
         <v>112</v>
@@ -10432,7 +10378,7 @@
         <v>49</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>725</v>
+        <v>709</v>
       </c>
       <c r="L43" s="4" t="s">
         <v>241</v>
@@ -10441,25 +10387,25 @@
         <v>588</v>
       </c>
       <c r="N43" s="20" t="s">
-        <v>726</v>
+        <v>710</v>
       </c>
       <c r="O43" s="20" t="s">
-        <v>727</v>
+        <v>711</v>
       </c>
       <c r="P43" s="20" t="s">
-        <v>728</v>
+        <v>712</v>
       </c>
       <c r="Q43" s="20" t="s">
-        <v>729</v>
+        <v>713</v>
       </c>
       <c r="R43" s="20" t="s">
-        <v>730</v>
+        <v>714</v>
       </c>
       <c r="S43" s="22" t="s">
         <v>594</v>
       </c>
       <c r="T43" s="20" t="s">
-        <v>731</v>
+        <v>715</v>
       </c>
       <c r="U43" s="4" t="s">
         <v>60</v>
@@ -10476,22 +10422,22 @@
       <c r="Y43" s="17"/>
       <c r="Z43" s="17"/>
       <c r="AA43" s="4" t="s">
-        <v>732</v>
+        <v>716</v>
       </c>
       <c r="AB43" s="4" t="s">
-        <v>733</v>
+        <v>717</v>
       </c>
       <c r="AC43" s="4" t="s">
-        <v>734</v>
+        <v>718</v>
       </c>
       <c r="AD43" s="4" t="s">
-        <v>735</v>
+        <v>719</v>
       </c>
       <c r="AE43" s="4" t="s">
-        <v>736</v>
+        <v>720</v>
       </c>
       <c r="AF43" s="4" t="s">
-        <v>737</v>
+        <v>721</v>
       </c>
       <c r="AG43" s="4"/>
       <c r="AH43" s="4"/>
@@ -10515,17 +10461,17 @@
       <c r="D44" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="E44" s="4" t="s">
-        <v>738</v>
+      <c r="E44" s="16" t="s">
+        <v>583</v>
       </c>
       <c r="F44" s="21" t="s">
-        <v>739</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>740</v>
+        <v>722</v>
+      </c>
+      <c r="G44" s="16" t="s">
+        <v>585</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>741</v>
+        <v>723</v>
       </c>
       <c r="I44" s="4" t="s">
         <v>131</v>
@@ -10534,7 +10480,7 @@
         <v>49</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>742</v>
+        <v>724</v>
       </c>
       <c r="L44" s="4" t="s">
         <v>241</v>
@@ -10543,25 +10489,25 @@
         <v>588</v>
       </c>
       <c r="N44" s="20" t="s">
-        <v>743</v>
+        <v>725</v>
       </c>
       <c r="O44" s="20" t="s">
-        <v>744</v>
+        <v>726</v>
       </c>
       <c r="P44" s="20" t="s">
-        <v>745</v>
+        <v>727</v>
       </c>
       <c r="Q44" s="20" t="s">
-        <v>746</v>
+        <v>728</v>
       </c>
       <c r="R44" s="20" t="s">
-        <v>747</v>
+        <v>729</v>
       </c>
       <c r="S44" s="22" t="s">
         <v>594</v>
       </c>
       <c r="T44" s="20" t="s">
-        <v>748</v>
+        <v>730</v>
       </c>
       <c r="U44" s="4" t="s">
         <v>60</v>
@@ -10578,22 +10524,22 @@
       <c r="Y44" s="17"/>
       <c r="Z44" s="17"/>
       <c r="AA44" s="4" t="s">
-        <v>749</v>
+        <v>731</v>
       </c>
       <c r="AB44" s="4" t="s">
-        <v>750</v>
+        <v>732</v>
       </c>
       <c r="AC44" s="4" t="s">
-        <v>751</v>
+        <v>733</v>
       </c>
       <c r="AD44" s="4" t="s">
-        <v>752</v>
+        <v>734</v>
       </c>
       <c r="AE44" s="4" t="s">
-        <v>753</v>
+        <v>735</v>
       </c>
       <c r="AF44" s="4" t="s">
-        <v>754</v>
+        <v>736</v>
       </c>
       <c r="AG44" s="4"/>
       <c r="AH44" s="4"/>
@@ -10606,10 +10552,10 @@
     </row>
     <row r="45" ht="42" customHeight="1" spans="1:38">
       <c r="A45" s="19" t="s">
-        <v>755</v>
+        <v>737</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>756</v>
+        <v>738</v>
       </c>
       <c r="C45" s="20" t="s">
         <v>42</v>
@@ -10618,16 +10564,16 @@
         <v>43</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>757</v>
+        <v>739</v>
       </c>
       <c r="F45" s="21" t="s">
-        <v>758</v>
+        <v>740</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>759</v>
+        <v>741</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>760</v>
+        <v>742</v>
       </c>
       <c r="I45" s="4" t="s">
         <v>48</v>
@@ -10636,34 +10582,34 @@
         <v>49</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>761</v>
+        <v>743</v>
       </c>
       <c r="L45" s="4" t="s">
         <v>241</v>
       </c>
       <c r="M45" s="4" t="s">
-        <v>762</v>
+        <v>744</v>
       </c>
       <c r="N45" s="20" t="s">
-        <v>763</v>
+        <v>745</v>
       </c>
       <c r="O45" s="20" t="s">
-        <v>764</v>
+        <v>746</v>
       </c>
       <c r="P45" s="20" t="s">
-        <v>765</v>
+        <v>747</v>
       </c>
       <c r="Q45" s="20" t="s">
-        <v>766</v>
+        <v>748</v>
       </c>
       <c r="R45" s="20" t="s">
-        <v>767</v>
+        <v>749</v>
       </c>
       <c r="S45" s="19" t="s">
         <v>58</v>
       </c>
       <c r="T45" s="20" t="s">
-        <v>768</v>
+        <v>750</v>
       </c>
       <c r="U45" s="4" t="s">
         <v>60</v>
@@ -10680,22 +10626,22 @@
       <c r="Y45" s="17"/>
       <c r="Z45" s="17"/>
       <c r="AA45" s="4" t="s">
-        <v>769</v>
+        <v>751</v>
       </c>
       <c r="AB45" s="4" t="s">
-        <v>770</v>
+        <v>752</v>
       </c>
       <c r="AC45" s="4" t="s">
-        <v>771</v>
+        <v>753</v>
       </c>
       <c r="AD45" s="4" t="s">
-        <v>772</v>
+        <v>754</v>
       </c>
       <c r="AE45" s="4" t="s">
-        <v>773</v>
+        <v>755</v>
       </c>
       <c r="AF45" s="4" t="s">
-        <v>774</v>
+        <v>756</v>
       </c>
       <c r="AG45" s="4"/>
       <c r="AH45" s="4"/>
@@ -10708,10 +10654,10 @@
     </row>
     <row r="46" ht="42" customHeight="1" spans="1:38">
       <c r="A46" s="19" t="s">
-        <v>755</v>
+        <v>737</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>756</v>
+        <v>738</v>
       </c>
       <c r="C46" s="20" t="s">
         <v>68</v>
@@ -10720,16 +10666,16 @@
         <v>69</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>775</v>
+        <v>757</v>
       </c>
       <c r="F46" s="21" t="s">
-        <v>776</v>
+        <v>758</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>777</v>
+        <v>759</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>778</v>
+        <v>760</v>
       </c>
       <c r="I46" s="4" t="s">
         <v>74</v>
@@ -10738,34 +10684,34 @@
         <v>49</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>779</v>
+        <v>761</v>
       </c>
       <c r="L46" s="4" t="s">
         <v>241</v>
       </c>
       <c r="M46" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="N46" s="20" t="s">
         <v>762</v>
       </c>
-      <c r="N46" s="20" t="s">
-        <v>780</v>
-      </c>
       <c r="O46" s="20" t="s">
-        <v>781</v>
+        <v>763</v>
       </c>
       <c r="P46" s="20" t="s">
-        <v>782</v>
+        <v>764</v>
       </c>
       <c r="Q46" s="20" t="s">
-        <v>783</v>
+        <v>765</v>
       </c>
       <c r="R46" s="20" t="s">
-        <v>784</v>
+        <v>766</v>
       </c>
       <c r="S46" s="19" t="s">
         <v>58</v>
       </c>
       <c r="T46" s="20" t="s">
-        <v>785</v>
+        <v>767</v>
       </c>
       <c r="U46" s="4" t="s">
         <v>60</v>
@@ -10782,22 +10728,22 @@
       <c r="Y46" s="17"/>
       <c r="Z46" s="17"/>
       <c r="AA46" s="4" t="s">
-        <v>786</v>
+        <v>768</v>
       </c>
       <c r="AB46" s="4" t="s">
-        <v>787</v>
+        <v>769</v>
       </c>
       <c r="AC46" s="4" t="s">
-        <v>788</v>
+        <v>770</v>
       </c>
       <c r="AD46" s="4" t="s">
-        <v>789</v>
+        <v>771</v>
       </c>
       <c r="AE46" s="4" t="s">
-        <v>790</v>
+        <v>772</v>
       </c>
       <c r="AF46" s="4" t="s">
-        <v>791</v>
+        <v>773</v>
       </c>
       <c r="AG46" s="4"/>
       <c r="AH46" s="4"/>
@@ -10810,10 +10756,10 @@
     </row>
     <row r="47" ht="42" customHeight="1" spans="1:38">
       <c r="A47" s="19" t="s">
-        <v>755</v>
+        <v>737</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>756</v>
+        <v>738</v>
       </c>
       <c r="C47" s="20" t="s">
         <v>87</v>
@@ -10822,16 +10768,16 @@
         <v>88</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>792</v>
+        <v>774</v>
       </c>
       <c r="F47" s="21" t="s">
-        <v>793</v>
+        <v>775</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>794</v>
+        <v>776</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>795</v>
+        <v>777</v>
       </c>
       <c r="I47" s="4" t="s">
         <v>93</v>
@@ -10840,34 +10786,34 @@
         <v>49</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>796</v>
+        <v>778</v>
       </c>
       <c r="L47" s="4" t="s">
         <v>241</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>762</v>
+        <v>744</v>
       </c>
       <c r="N47" s="20" t="s">
-        <v>797</v>
+        <v>779</v>
       </c>
       <c r="O47" s="20" t="s">
-        <v>798</v>
+        <v>780</v>
       </c>
       <c r="P47" s="20" t="s">
-        <v>799</v>
+        <v>781</v>
       </c>
       <c r="Q47" s="20" t="s">
-        <v>800</v>
+        <v>782</v>
       </c>
       <c r="R47" s="20" t="s">
-        <v>801</v>
+        <v>783</v>
       </c>
       <c r="S47" s="19" t="s">
         <v>58</v>
       </c>
       <c r="T47" s="20" t="s">
-        <v>802</v>
+        <v>784</v>
       </c>
       <c r="U47" s="4" t="s">
         <v>60</v>
@@ -10884,22 +10830,22 @@
       <c r="Y47" s="17"/>
       <c r="Z47" s="17"/>
       <c r="AA47" s="4" t="s">
-        <v>803</v>
+        <v>785</v>
       </c>
       <c r="AB47" s="4" t="s">
-        <v>804</v>
+        <v>786</v>
       </c>
       <c r="AC47" s="4" t="s">
-        <v>805</v>
+        <v>787</v>
       </c>
       <c r="AD47" s="4" t="s">
-        <v>806</v>
+        <v>788</v>
       </c>
       <c r="AE47" s="4" t="s">
-        <v>807</v>
+        <v>789</v>
       </c>
       <c r="AF47" s="4" t="s">
-        <v>808</v>
+        <v>790</v>
       </c>
       <c r="AG47" s="4"/>
       <c r="AH47" s="4"/>
@@ -10912,10 +10858,10 @@
     </row>
     <row r="48" ht="42" customHeight="1" spans="1:38">
       <c r="A48" s="19" t="s">
-        <v>755</v>
+        <v>737</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>756</v>
+        <v>738</v>
       </c>
       <c r="C48" s="20" t="s">
         <v>106</v>
@@ -10924,16 +10870,16 @@
         <v>107</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>809</v>
+        <v>791</v>
       </c>
       <c r="F48" s="21" t="s">
-        <v>810</v>
+        <v>792</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>811</v>
+        <v>793</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>812</v>
+        <v>794</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>112</v>
@@ -10942,34 +10888,34 @@
         <v>49</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>813</v>
+        <v>795</v>
       </c>
       <c r="L48" s="4" t="s">
         <v>241</v>
       </c>
       <c r="M48" s="4" t="s">
-        <v>762</v>
+        <v>744</v>
       </c>
       <c r="N48" s="20" t="s">
-        <v>814</v>
+        <v>796</v>
       </c>
       <c r="O48" s="20" t="s">
-        <v>815</v>
+        <v>797</v>
       </c>
       <c r="P48" s="20" t="s">
-        <v>816</v>
+        <v>798</v>
       </c>
       <c r="Q48" s="20" t="s">
-        <v>817</v>
+        <v>799</v>
       </c>
       <c r="R48" s="20" t="s">
-        <v>818</v>
+        <v>800</v>
       </c>
       <c r="S48" s="19" t="s">
         <v>58</v>
       </c>
       <c r="T48" s="20" t="s">
-        <v>819</v>
+        <v>801</v>
       </c>
       <c r="U48" s="4" t="s">
         <v>60</v>
@@ -10986,22 +10932,22 @@
       <c r="Y48" s="17"/>
       <c r="Z48" s="17"/>
       <c r="AA48" s="4" t="s">
-        <v>820</v>
+        <v>802</v>
       </c>
       <c r="AB48" s="4" t="s">
-        <v>821</v>
+        <v>803</v>
       </c>
       <c r="AC48" s="4" t="s">
-        <v>822</v>
+        <v>804</v>
       </c>
       <c r="AD48" s="4" t="s">
-        <v>823</v>
+        <v>805</v>
       </c>
       <c r="AE48" s="4" t="s">
-        <v>824</v>
+        <v>806</v>
       </c>
       <c r="AF48" s="4" t="s">
-        <v>825</v>
+        <v>807</v>
       </c>
       <c r="AG48" s="4"/>
       <c r="AH48" s="4"/>
@@ -11014,10 +10960,10 @@
     </row>
     <row r="49" ht="42" customHeight="1" spans="1:38">
       <c r="A49" s="19" t="s">
-        <v>755</v>
+        <v>737</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>756</v>
+        <v>738</v>
       </c>
       <c r="C49" s="20" t="s">
         <v>125</v>
@@ -11026,16 +10972,16 @@
         <v>126</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>826</v>
+        <v>808</v>
       </c>
       <c r="F49" s="21" t="s">
-        <v>827</v>
+        <v>809</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>828</v>
+        <v>810</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>829</v>
+        <v>811</v>
       </c>
       <c r="I49" s="4" t="s">
         <v>131</v>
@@ -11044,34 +10990,34 @@
         <v>49</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>830</v>
+        <v>812</v>
       </c>
       <c r="L49" s="4" t="s">
         <v>241</v>
       </c>
       <c r="M49" s="4" t="s">
-        <v>762</v>
+        <v>744</v>
       </c>
       <c r="N49" s="20" t="s">
-        <v>831</v>
+        <v>813</v>
       </c>
       <c r="O49" s="20" t="s">
-        <v>832</v>
+        <v>814</v>
       </c>
       <c r="P49" s="20" t="s">
-        <v>833</v>
+        <v>815</v>
       </c>
       <c r="Q49" s="20" t="s">
-        <v>834</v>
+        <v>816</v>
       </c>
       <c r="R49" s="20" t="s">
-        <v>835</v>
+        <v>817</v>
       </c>
       <c r="S49" s="19" t="s">
         <v>58</v>
       </c>
       <c r="T49" s="20" t="s">
-        <v>836</v>
+        <v>818</v>
       </c>
       <c r="U49" s="4" t="s">
         <v>60</v>
@@ -11088,22 +11034,22 @@
       <c r="Y49" s="17"/>
       <c r="Z49" s="17"/>
       <c r="AA49" s="4" t="s">
-        <v>837</v>
+        <v>819</v>
       </c>
       <c r="AB49" s="4" t="s">
-        <v>838</v>
+        <v>820</v>
       </c>
       <c r="AC49" s="4" t="s">
-        <v>839</v>
+        <v>821</v>
       </c>
       <c r="AD49" s="4" t="s">
-        <v>840</v>
+        <v>822</v>
       </c>
       <c r="AE49" s="4" t="s">
-        <v>841</v>
+        <v>823</v>
       </c>
       <c r="AF49" s="4" t="s">
-        <v>842</v>
+        <v>824</v>
       </c>
       <c r="AG49" s="4"/>
       <c r="AH49" s="4"/>
@@ -11116,10 +11062,10 @@
     </row>
     <row r="50" ht="42" customHeight="1" spans="1:38">
       <c r="A50" s="19" t="s">
-        <v>755</v>
+        <v>737</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>756</v>
+        <v>738</v>
       </c>
       <c r="C50" s="20" t="s">
         <v>144</v>
@@ -11128,16 +11074,16 @@
         <v>145</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>843</v>
+        <v>825</v>
       </c>
       <c r="F50" s="21" t="s">
-        <v>844</v>
+        <v>826</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>845</v>
+        <v>827</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>846</v>
+        <v>828</v>
       </c>
       <c r="I50" s="4" t="s">
         <v>48</v>
@@ -11146,34 +11092,34 @@
         <v>49</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>847</v>
+        <v>829</v>
       </c>
       <c r="L50" s="4" t="s">
         <v>241</v>
       </c>
       <c r="M50" s="4" t="s">
-        <v>762</v>
+        <v>744</v>
       </c>
       <c r="N50" s="20" t="s">
-        <v>848</v>
+        <v>830</v>
       </c>
       <c r="O50" s="20" t="s">
-        <v>849</v>
+        <v>831</v>
       </c>
       <c r="P50" s="20" t="s">
-        <v>850</v>
+        <v>832</v>
       </c>
       <c r="Q50" s="20" t="s">
-        <v>851</v>
+        <v>833</v>
       </c>
       <c r="R50" s="20" t="s">
-        <v>852</v>
+        <v>834</v>
       </c>
       <c r="S50" s="19" t="s">
         <v>58</v>
       </c>
       <c r="T50" s="20" t="s">
-        <v>853</v>
+        <v>835</v>
       </c>
       <c r="U50" s="4" t="s">
         <v>60</v>
@@ -11190,22 +11136,22 @@
       <c r="Y50" s="17"/>
       <c r="Z50" s="17"/>
       <c r="AA50" s="4" t="s">
-        <v>854</v>
+        <v>836</v>
       </c>
       <c r="AB50" s="4" t="s">
-        <v>855</v>
+        <v>837</v>
       </c>
       <c r="AC50" s="4" t="s">
-        <v>856</v>
+        <v>838</v>
       </c>
       <c r="AD50" s="4" t="s">
-        <v>857</v>
+        <v>839</v>
       </c>
       <c r="AE50" s="4" t="s">
-        <v>858</v>
+        <v>840</v>
       </c>
       <c r="AF50" s="4" t="s">
-        <v>859</v>
+        <v>841</v>
       </c>
       <c r="AG50" s="4"/>
       <c r="AH50" s="4"/>
@@ -11218,10 +11164,10 @@
     </row>
     <row r="51" ht="42" customHeight="1" spans="1:38">
       <c r="A51" s="19" t="s">
-        <v>755</v>
+        <v>737</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>756</v>
+        <v>738</v>
       </c>
       <c r="C51" s="20" t="s">
         <v>162</v>
@@ -11230,16 +11176,16 @@
         <v>163</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>860</v>
+        <v>842</v>
       </c>
       <c r="F51" s="21" t="s">
-        <v>861</v>
+        <v>843</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>862</v>
+        <v>844</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>863</v>
+        <v>845</v>
       </c>
       <c r="I51" s="4" t="s">
         <v>74</v>
@@ -11248,34 +11194,34 @@
         <v>49</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>864</v>
+        <v>846</v>
       </c>
       <c r="L51" s="4" t="s">
         <v>241</v>
       </c>
       <c r="M51" s="4" t="s">
-        <v>762</v>
+        <v>744</v>
       </c>
       <c r="N51" s="20" t="s">
-        <v>865</v>
+        <v>847</v>
       </c>
       <c r="O51" s="20" t="s">
-        <v>866</v>
+        <v>848</v>
       </c>
       <c r="P51" s="20" t="s">
-        <v>867</v>
+        <v>849</v>
       </c>
       <c r="Q51" s="20" t="s">
-        <v>868</v>
+        <v>850</v>
       </c>
       <c r="R51" s="20" t="s">
-        <v>869</v>
+        <v>851</v>
       </c>
       <c r="S51" s="19" t="s">
         <v>58</v>
       </c>
       <c r="T51" s="20" t="s">
-        <v>870</v>
+        <v>852</v>
       </c>
       <c r="U51" s="4" t="s">
         <v>60</v>
@@ -11292,22 +11238,22 @@
       <c r="Y51" s="17"/>
       <c r="Z51" s="17"/>
       <c r="AA51" s="4" t="s">
-        <v>871</v>
+        <v>853</v>
       </c>
       <c r="AB51" s="4" t="s">
-        <v>872</v>
+        <v>854</v>
       </c>
       <c r="AC51" s="4" t="s">
-        <v>873</v>
+        <v>855</v>
       </c>
       <c r="AD51" s="4" t="s">
-        <v>874</v>
+        <v>856</v>
       </c>
       <c r="AE51" s="4" t="s">
-        <v>875</v>
+        <v>857</v>
       </c>
       <c r="AF51" s="4" t="s">
-        <v>876</v>
+        <v>858</v>
       </c>
       <c r="AG51" s="4"/>
       <c r="AH51" s="4"/>
@@ -11320,10 +11266,10 @@
     </row>
     <row r="52" ht="42" customHeight="1" spans="1:38">
       <c r="A52" s="19" t="s">
-        <v>755</v>
+        <v>737</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>756</v>
+        <v>738</v>
       </c>
       <c r="C52" s="20" t="s">
         <v>180</v>
@@ -11332,16 +11278,16 @@
         <v>181</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>877</v>
+        <v>859</v>
       </c>
       <c r="F52" s="21" t="s">
-        <v>878</v>
+        <v>860</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>879</v>
+        <v>861</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>880</v>
+        <v>862</v>
       </c>
       <c r="I52" s="4" t="s">
         <v>93</v>
@@ -11350,34 +11296,34 @@
         <v>49</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>881</v>
+        <v>863</v>
       </c>
       <c r="L52" s="4" t="s">
         <v>241</v>
       </c>
       <c r="M52" s="4" t="s">
-        <v>762</v>
+        <v>744</v>
       </c>
       <c r="N52" s="20" t="s">
-        <v>882</v>
+        <v>864</v>
       </c>
       <c r="O52" s="20" t="s">
-        <v>883</v>
+        <v>865</v>
       </c>
       <c r="P52" s="20" t="s">
-        <v>884</v>
+        <v>866</v>
       </c>
       <c r="Q52" s="20" t="s">
-        <v>885</v>
+        <v>867</v>
       </c>
       <c r="R52" s="20" t="s">
-        <v>886</v>
+        <v>868</v>
       </c>
       <c r="S52" s="19" t="s">
         <v>58</v>
       </c>
       <c r="T52" s="20" t="s">
-        <v>887</v>
+        <v>869</v>
       </c>
       <c r="U52" s="4" t="s">
         <v>60</v>
@@ -11394,22 +11340,22 @@
       <c r="Y52" s="17"/>
       <c r="Z52" s="17"/>
       <c r="AA52" s="4" t="s">
-        <v>888</v>
+        <v>870</v>
       </c>
       <c r="AB52" s="4" t="s">
-        <v>889</v>
+        <v>871</v>
       </c>
       <c r="AC52" s="4" t="s">
-        <v>890</v>
+        <v>872</v>
       </c>
       <c r="AD52" s="4" t="s">
-        <v>891</v>
+        <v>873</v>
       </c>
       <c r="AE52" s="4" t="s">
-        <v>892</v>
+        <v>874</v>
       </c>
       <c r="AF52" s="4" t="s">
-        <v>893</v>
+        <v>875</v>
       </c>
       <c r="AG52" s="4"/>
       <c r="AH52" s="4"/>
@@ -11422,10 +11368,10 @@
     </row>
     <row r="53" ht="42" customHeight="1" spans="1:38">
       <c r="A53" s="19" t="s">
-        <v>755</v>
+        <v>737</v>
       </c>
       <c r="B53" s="20" t="s">
-        <v>756</v>
+        <v>738</v>
       </c>
       <c r="C53" s="20" t="s">
         <v>198</v>
@@ -11434,16 +11380,16 @@
         <v>199</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>894</v>
+        <v>876</v>
       </c>
       <c r="F53" s="21" t="s">
-        <v>895</v>
+        <v>877</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>896</v>
+        <v>878</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>897</v>
+        <v>879</v>
       </c>
       <c r="I53" s="4" t="s">
         <v>112</v>
@@ -11452,34 +11398,34 @@
         <v>49</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>898</v>
+        <v>880</v>
       </c>
       <c r="L53" s="4" t="s">
         <v>241</v>
       </c>
       <c r="M53" s="4" t="s">
-        <v>762</v>
+        <v>744</v>
       </c>
       <c r="N53" s="20" t="s">
-        <v>899</v>
+        <v>881</v>
       </c>
       <c r="O53" s="20" t="s">
-        <v>900</v>
+        <v>882</v>
       </c>
       <c r="P53" s="20" t="s">
-        <v>901</v>
+        <v>883</v>
       </c>
       <c r="Q53" s="20" t="s">
-        <v>902</v>
+        <v>884</v>
       </c>
       <c r="R53" s="20" t="s">
-        <v>903</v>
+        <v>885</v>
       </c>
       <c r="S53" s="19" t="s">
         <v>58</v>
       </c>
       <c r="T53" s="20" t="s">
-        <v>904</v>
+        <v>886</v>
       </c>
       <c r="U53" s="4" t="s">
         <v>60</v>
@@ -11496,22 +11442,22 @@
       <c r="Y53" s="17"/>
       <c r="Z53" s="17"/>
       <c r="AA53" s="4" t="s">
-        <v>905</v>
+        <v>887</v>
       </c>
       <c r="AB53" s="4" t="s">
-        <v>906</v>
+        <v>888</v>
       </c>
       <c r="AC53" s="4" t="s">
-        <v>907</v>
+        <v>889</v>
       </c>
       <c r="AD53" s="4" t="s">
-        <v>908</v>
+        <v>890</v>
       </c>
       <c r="AE53" s="4" t="s">
-        <v>909</v>
+        <v>891</v>
       </c>
       <c r="AF53" s="4" t="s">
-        <v>910</v>
+        <v>892</v>
       </c>
       <c r="AG53" s="4"/>
       <c r="AH53" s="4"/>
@@ -11524,10 +11470,10 @@
     </row>
     <row r="54" ht="42" customHeight="1" spans="1:38">
       <c r="A54" s="19" t="s">
-        <v>755</v>
+        <v>737</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>756</v>
+        <v>738</v>
       </c>
       <c r="C54" s="20" t="s">
         <v>216</v>
@@ -11536,16 +11482,16 @@
         <v>217</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>911</v>
+        <v>893</v>
       </c>
       <c r="F54" s="21" t="s">
-        <v>912</v>
+        <v>894</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>913</v>
+        <v>895</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>914</v>
+        <v>896</v>
       </c>
       <c r="I54" s="4" t="s">
         <v>131</v>
@@ -11554,34 +11500,34 @@
         <v>49</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>915</v>
+        <v>897</v>
       </c>
       <c r="L54" s="4" t="s">
         <v>241</v>
       </c>
       <c r="M54" s="4" t="s">
-        <v>762</v>
+        <v>744</v>
       </c>
       <c r="N54" s="20" t="s">
-        <v>916</v>
+        <v>898</v>
       </c>
       <c r="O54" s="20" t="s">
-        <v>917</v>
+        <v>899</v>
       </c>
       <c r="P54" s="20" t="s">
-        <v>918</v>
+        <v>900</v>
       </c>
       <c r="Q54" s="20" t="s">
-        <v>919</v>
+        <v>901</v>
       </c>
       <c r="R54" s="20" t="s">
-        <v>920</v>
+        <v>902</v>
       </c>
       <c r="S54" s="19" t="s">
         <v>58</v>
       </c>
       <c r="T54" s="20" t="s">
-        <v>921</v>
+        <v>903</v>
       </c>
       <c r="U54" s="4" t="s">
         <v>60</v>
@@ -11598,22 +11544,22 @@
       <c r="Y54" s="17"/>
       <c r="Z54" s="17"/>
       <c r="AA54" s="4" t="s">
-        <v>922</v>
+        <v>904</v>
       </c>
       <c r="AB54" s="4" t="s">
-        <v>923</v>
+        <v>905</v>
       </c>
       <c r="AC54" s="4" t="s">
-        <v>924</v>
+        <v>906</v>
       </c>
       <c r="AD54" s="4" t="s">
-        <v>925</v>
+        <v>907</v>
       </c>
       <c r="AE54" s="4" t="s">
-        <v>926</v>
+        <v>908</v>
       </c>
       <c r="AF54" s="4" t="s">
-        <v>927</v>
+        <v>909</v>
       </c>
       <c r="AG54" s="4"/>
       <c r="AH54" s="4"/>
@@ -15675,7 +15621,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>928</v>
+        <v>910</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -15684,7 +15630,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:5">
       <c r="A2" s="8" t="s">
-        <v>929</v>
+        <v>911</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -15700,1141 +15646,1141 @@
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:5">
       <c r="A4" s="10" t="s">
-        <v>930</v>
+        <v>912</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>931</v>
+        <v>913</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>932</v>
+        <v>914</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>933</v>
+        <v>915</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>934</v>
+        <v>916</v>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1" spans="1:5">
       <c r="A5" s="11" t="s">
-        <v>935</v>
+        <v>917</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>936</v>
+        <v>918</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>937</v>
+        <v>919</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>938</v>
+        <v>920</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>939</v>
+        <v>921</v>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1" spans="1:5">
       <c r="A6" s="11" t="s">
-        <v>935</v>
+        <v>917</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>940</v>
+        <v>922</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>941</v>
+        <v>923</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>942</v>
+        <v>924</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>943</v>
+        <v>925</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1" spans="1:5">
       <c r="A7" s="11" t="s">
-        <v>935</v>
+        <v>917</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>944</v>
+        <v>926</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>945</v>
+        <v>927</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>946</v>
+        <v>928</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>947</v>
+        <v>929</v>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1" spans="1:5">
       <c r="A8" s="11" t="s">
-        <v>935</v>
+        <v>917</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>948</v>
+        <v>930</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>949</v>
+        <v>931</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>950</v>
+        <v>932</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>951</v>
+        <v>933</v>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1" spans="1:5">
       <c r="A9" s="11" t="s">
+        <v>917</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>934</v>
+      </c>
+      <c r="C9" s="11" t="s">
         <v>935</v>
       </c>
-      <c r="B9" s="11" t="s">
-        <v>952</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>953</v>
-      </c>
       <c r="D9" s="12" t="s">
-        <v>954</v>
+        <v>936</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>955</v>
+        <v>937</v>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1" spans="1:5">
       <c r="A10" s="11" t="s">
-        <v>935</v>
+        <v>917</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>956</v>
+        <v>938</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>957</v>
+        <v>939</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>958</v>
+        <v>940</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>959</v>
+        <v>941</v>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1" spans="1:5">
       <c r="A11" s="11" t="s">
-        <v>935</v>
+        <v>917</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>960</v>
+        <v>942</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>961</v>
+        <v>943</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>962</v>
+        <v>944</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>947</v>
+        <v>929</v>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:5">
       <c r="A12" s="11" t="s">
-        <v>935</v>
+        <v>917</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>963</v>
+        <v>945</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>964</v>
+        <v>946</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>965</v>
+        <v>947</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>947</v>
+        <v>929</v>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1" spans="1:5">
       <c r="A13" s="11" t="s">
-        <v>966</v>
+        <v>948</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>967</v>
+        <v>949</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>7</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>968</v>
+        <v>950</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>969</v>
+        <v>951</v>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1" spans="1:5">
       <c r="A14" s="11" t="s">
-        <v>966</v>
+        <v>948</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>970</v>
+        <v>952</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>971</v>
+        <v>953</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>972</v>
+        <v>954</v>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1" spans="1:5">
       <c r="A15" s="11" t="s">
-        <v>973</v>
+        <v>955</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>974</v>
+        <v>956</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>975</v>
+        <v>957</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>976</v>
+        <v>958</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>977</v>
+        <v>959</v>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1" spans="1:5">
       <c r="A16" s="11" t="s">
-        <v>973</v>
+        <v>955</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>978</v>
+        <v>960</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>979</v>
+        <v>961</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>980</v>
+        <v>962</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>981</v>
+        <v>963</v>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1" spans="1:5">
       <c r="A17" s="11" t="s">
-        <v>982</v>
+        <v>964</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>983</v>
+        <v>965</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>984</v>
+        <v>966</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>985</v>
+        <v>967</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>986</v>
+        <v>968</v>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1" spans="1:5">
       <c r="A18" s="11" t="s">
-        <v>982</v>
+        <v>964</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>987</v>
+        <v>969</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>988</v>
+        <v>970</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>989</v>
+        <v>971</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>990</v>
+        <v>972</v>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1" spans="1:5">
       <c r="A19" s="11" t="s">
-        <v>982</v>
+        <v>964</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>991</v>
+        <v>973</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>992</v>
+        <v>974</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>993</v>
+        <v>975</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>994</v>
+        <v>976</v>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1" spans="1:5">
       <c r="A20" s="11" t="s">
-        <v>982</v>
+        <v>964</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>995</v>
+        <v>977</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>996</v>
+        <v>978</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>997</v>
+        <v>979</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>998</v>
+        <v>980</v>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1" spans="1:5">
       <c r="A21" s="11" t="s">
-        <v>999</v>
+        <v>981</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>1000</v>
+        <v>982</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>1001</v>
+        <v>983</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>1002</v>
+        <v>984</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>1003</v>
+        <v>985</v>
       </c>
     </row>
     <row r="22" ht="42" customHeight="1" spans="1:5">
       <c r="A22" s="11" t="s">
-        <v>999</v>
+        <v>981</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>1004</v>
+        <v>986</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>1005</v>
+        <v>987</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>1006</v>
+        <v>988</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>1003</v>
+        <v>985</v>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1" spans="1:5">
       <c r="A23" s="11" t="s">
-        <v>999</v>
+        <v>981</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>1007</v>
+        <v>989</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>1008</v>
+        <v>990</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>1009</v>
+        <v>991</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>1010</v>
+        <v>992</v>
       </c>
     </row>
     <row r="24" ht="42" customHeight="1" spans="1:5">
       <c r="A24" s="11" t="s">
-        <v>999</v>
+        <v>981</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>1011</v>
+        <v>993</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>1012</v>
+        <v>994</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>1013</v>
+        <v>995</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>1014</v>
+        <v>996</v>
       </c>
     </row>
     <row r="25" ht="42" customHeight="1" spans="1:5">
       <c r="A25" s="11" t="s">
-        <v>1015</v>
+        <v>997</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>1016</v>
+        <v>998</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>1017</v>
+        <v>999</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>1018</v>
+        <v>1000</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>1019</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="26" ht="42" customHeight="1" spans="1:5">
       <c r="A26" s="11" t="s">
-        <v>1015</v>
+        <v>997</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>1020</v>
+        <v>1002</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>1021</v>
+        <v>1003</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>1022</v>
+        <v>1004</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>1023</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="27" ht="42" customHeight="1" spans="1:5">
       <c r="A27" s="11" t="s">
-        <v>1015</v>
+        <v>997</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>1024</v>
+        <v>1006</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>1025</v>
+        <v>1007</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>1026</v>
+        <v>1008</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>1023</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="28" ht="42" customHeight="1" spans="1:5">
       <c r="A28" s="11" t="s">
-        <v>1015</v>
+        <v>997</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>1027</v>
+        <v>1009</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>1028</v>
+        <v>1010</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>1029</v>
+        <v>1011</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>1030</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="29" ht="42" customHeight="1" spans="1:5">
       <c r="A29" s="11" t="s">
-        <v>1031</v>
+        <v>1013</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>1032</v>
+        <v>1014</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>1033</v>
+        <v>1015</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>1034</v>
+        <v>1016</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>1023</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="30" ht="42" customHeight="1" spans="1:5">
       <c r="A30" s="11" t="s">
-        <v>1031</v>
+        <v>1013</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>1035</v>
+        <v>1017</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>1036</v>
+        <v>1018</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>1037</v>
+        <v>1019</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>1023</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="31" ht="42" customHeight="1" spans="1:5">
       <c r="A31" s="11" t="s">
-        <v>1038</v>
+        <v>1020</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>1039</v>
+        <v>1021</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>1040</v>
+        <v>1022</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>1041</v>
+        <v>1023</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>1042</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="32" ht="42" customHeight="1" spans="1:5">
       <c r="A32" s="11" t="s">
-        <v>1038</v>
+        <v>1020</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>1043</v>
+        <v>1025</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>1044</v>
+        <v>1026</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>993</v>
+        <v>975</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>1042</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="33" ht="42" customHeight="1" spans="1:5">
       <c r="A33" s="11" t="s">
-        <v>1038</v>
+        <v>1020</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>1045</v>
+        <v>1027</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>1046</v>
+        <v>1028</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>1047</v>
+        <v>1029</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>1042</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="34" ht="42" customHeight="1" spans="1:5">
       <c r="A34" s="11" t="s">
-        <v>1038</v>
+        <v>1020</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>1048</v>
+        <v>1030</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>1049</v>
+        <v>1031</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>1050</v>
+        <v>1032</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>1042</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="35" ht="42" customHeight="1" spans="1:5">
       <c r="A35" s="11" t="s">
-        <v>1038</v>
+        <v>1020</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>1051</v>
+        <v>1033</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>1052</v>
+        <v>1034</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>1053</v>
+        <v>1035</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>1042</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="36" ht="42" customHeight="1" spans="1:5">
       <c r="A36" s="11" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D36" s="12" t="s">
         <v>1038</v>
       </c>
-      <c r="B36" s="11" t="s">
-        <v>1054</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>1055</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>1056</v>
-      </c>
       <c r="E36" s="13" t="s">
-        <v>1042</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="37" ht="42" customHeight="1" spans="1:5">
       <c r="A37" s="11" t="s">
-        <v>1038</v>
+        <v>1020</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>1057</v>
+        <v>1039</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>1058</v>
+        <v>1040</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>1059</v>
+        <v>1041</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>1042</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="38" ht="42" customHeight="1" spans="1:5">
       <c r="A38" s="11" t="s">
-        <v>1038</v>
+        <v>1020</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>1060</v>
+        <v>1042</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>1061</v>
+        <v>1043</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>1062</v>
+        <v>1044</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>1042</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="39" ht="42" customHeight="1" spans="1:5">
       <c r="A39" s="11" t="s">
-        <v>1038</v>
+        <v>1020</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>1063</v>
+        <v>1045</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>1064</v>
+        <v>1046</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>1065</v>
+        <v>1047</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>1042</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="40" ht="42" customHeight="1" spans="1:5">
       <c r="A40" s="11" t="s">
-        <v>1066</v>
+        <v>1048</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>1067</v>
+        <v>1049</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>1068</v>
+        <v>1050</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>1069</v>
+        <v>1051</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>986</v>
+        <v>968</v>
       </c>
     </row>
     <row r="41" ht="42" customHeight="1" spans="1:5">
       <c r="A41" s="11" t="s">
-        <v>1066</v>
+        <v>1048</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>1070</v>
+        <v>1052</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>1071</v>
+        <v>1053</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>1072</v>
+        <v>1054</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>1073</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="42" ht="42" customHeight="1" spans="1:5">
       <c r="A42" s="11" t="s">
-        <v>1066</v>
+        <v>1048</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>1074</v>
+        <v>1056</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>1075</v>
+        <v>1057</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>1076</v>
+        <v>1058</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>1077</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="43" ht="42" customHeight="1" spans="1:5">
       <c r="A43" s="11" t="s">
-        <v>1066</v>
+        <v>1048</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>1078</v>
+        <v>1060</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>1079</v>
+        <v>1061</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>1080</v>
+        <v>1062</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>1081</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="44" ht="42" customHeight="1" spans="1:5">
       <c r="A44" s="11" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D44" s="12" t="s">
         <v>1066</v>
       </c>
-      <c r="B44" s="11" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>1083</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>1084</v>
-      </c>
       <c r="E44" s="13" t="s">
-        <v>1085</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="45" ht="42" customHeight="1" spans="1:5">
       <c r="A45" s="11" t="s">
-        <v>1066</v>
+        <v>1048</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>1086</v>
+        <v>1068</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>1087</v>
+        <v>1069</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>1088</v>
+        <v>1070</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>1089</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="46" ht="42" customHeight="1" spans="1:5">
       <c r="A46" s="11" t="s">
-        <v>1066</v>
+        <v>1048</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>1090</v>
+        <v>1072</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>1091</v>
+        <v>1073</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>1092</v>
+        <v>1074</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>1093</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="47" ht="42" customHeight="1" spans="1:5">
       <c r="A47" s="11" t="s">
-        <v>1066</v>
+        <v>1048</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>1094</v>
+        <v>1076</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>1095</v>
+        <v>1077</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>1096</v>
+        <v>1078</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>1097</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="48" ht="42" customHeight="1" spans="1:5">
       <c r="A48" s="11" t="s">
-        <v>1066</v>
+        <v>1048</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>1098</v>
+        <v>1080</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>1099</v>
+        <v>1081</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>1100</v>
+        <v>1082</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>1101</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="49" ht="42" customHeight="1" spans="1:5">
       <c r="A49" s="11" t="s">
-        <v>1066</v>
+        <v>1048</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>1102</v>
+        <v>1084</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>1103</v>
+        <v>1085</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>1104</v>
+        <v>1086</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>1105</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="50" ht="42" customHeight="1" spans="1:5">
       <c r="A50" s="11" t="s">
-        <v>1066</v>
+        <v>1048</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>1106</v>
+        <v>1088</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>1107</v>
+        <v>1089</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>1108</v>
+        <v>1090</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>1109</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="51" ht="42" customHeight="1" spans="1:5">
       <c r="A51" s="11" t="s">
-        <v>1066</v>
+        <v>1048</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>1110</v>
+        <v>1092</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>1111</v>
+        <v>1093</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>1112</v>
+        <v>1094</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>1113</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="52" ht="42" customHeight="1" spans="1:5">
       <c r="A52" s="11" t="s">
-        <v>1114</v>
+        <v>1096</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>1115</v>
+        <v>1097</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>1116</v>
+        <v>1098</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>1117</v>
+        <v>1099</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>1118</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="53" ht="42" customHeight="1" spans="1:5">
       <c r="A53" s="11" t="s">
-        <v>1114</v>
+        <v>1096</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>1119</v>
+        <v>1101</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>1120</v>
+        <v>1102</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>1121</v>
+        <v>1103</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>1122</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="54" ht="42" customHeight="1" spans="1:5">
       <c r="A54" s="11" t="s">
-        <v>1114</v>
+        <v>1096</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>1123</v>
+        <v>1105</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>1124</v>
+        <v>1106</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>1125</v>
+        <v>1107</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>1126</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="55" ht="42" customHeight="1" spans="1:5">
       <c r="A55" s="11" t="s">
-        <v>1114</v>
+        <v>1096</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>1127</v>
+        <v>1109</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>1128</v>
+        <v>1110</v>
       </c>
       <c r="D55" s="18">
         <v>8</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>1129</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="56" ht="42" customHeight="1" spans="1:5">
       <c r="A56" s="11" t="s">
-        <v>1130</v>
+        <v>1112</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>1131</v>
+        <v>1113</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>1132</v>
+        <v>1114</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>1133</v>
+        <v>1115</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>986</v>
+        <v>968</v>
       </c>
     </row>
     <row r="57" ht="42" customHeight="1" spans="1:5">
       <c r="A57" s="11" t="s">
-        <v>1130</v>
+        <v>1112</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>1134</v>
+        <v>1116</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>1135</v>
+        <v>1117</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>1130</v>
+        <v>1112</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>1136</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="58" ht="42" customHeight="1" spans="1:5">
       <c r="A58" s="11" t="s">
-        <v>1130</v>
+        <v>1112</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>1137</v>
+        <v>1119</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>1138</v>
+        <v>1120</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>1139</v>
+        <v>1121</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>1140</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="59" ht="42" customHeight="1" spans="1:5">
       <c r="A59" s="11" t="s">
-        <v>1130</v>
+        <v>1112</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>1141</v>
+        <v>1123</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>1142</v>
+        <v>1124</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>1143</v>
+        <v>1125</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>1144</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="60" ht="42" customHeight="1" spans="1:5">
       <c r="A60" s="11" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E60" s="13" t="s">
         <v>1130</v>
-      </c>
-      <c r="B60" s="11" t="s">
-        <v>1145</v>
-      </c>
-      <c r="C60" s="11" t="s">
-        <v>1146</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>1147</v>
-      </c>
-      <c r="E60" s="13" t="s">
-        <v>1148</v>
       </c>
     </row>
     <row r="61" ht="42" customHeight="1" spans="1:5">
       <c r="A61" s="11" t="s">
-        <v>1130</v>
+        <v>1112</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>1149</v>
+        <v>1131</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>1150</v>
+        <v>1132</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>1151</v>
+        <v>1133</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>1144</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="62" ht="42" customHeight="1" spans="1:5">
       <c r="A62" s="11" t="s">
-        <v>1130</v>
+        <v>1112</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>1152</v>
+        <v>1134</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>1153</v>
+        <v>1135</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>1154</v>
+        <v>1136</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>1155</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="63" ht="42" customHeight="1" spans="1:5">
       <c r="A63" s="11" t="s">
-        <v>1130</v>
+        <v>1112</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>1156</v>
+        <v>1138</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>1157</v>
+        <v>1139</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>1158</v>
+        <v>1140</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>1144</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="64" ht="42" customHeight="1" spans="1:5">
       <c r="A64" s="11" t="s">
-        <v>1130</v>
+        <v>1112</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>1159</v>
+        <v>1141</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>1160</v>
+        <v>1142</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>1161</v>
+        <v>1143</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>1162</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="65" ht="42" customHeight="1" spans="1:5">
       <c r="A65" s="11" t="s">
-        <v>1130</v>
+        <v>1112</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>1163</v>
+        <v>1145</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>1164</v>
+        <v>1146</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>1165</v>
+        <v>1147</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>1144</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="66" ht="42" customHeight="1" spans="1:5">
       <c r="A66" s="11" t="s">
-        <v>1130</v>
+        <v>1112</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>1166</v>
+        <v>1148</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>1167</v>
+        <v>1149</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>1168</v>
+        <v>1150</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>1169</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="67" ht="42" customHeight="1" spans="1:5">
       <c r="A67" s="11" t="s">
-        <v>1130</v>
+        <v>1112</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>1170</v>
+        <v>1152</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>1171</v>
+        <v>1153</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>1172</v>
+        <v>1154</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>1144</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="68" ht="42" customHeight="1" spans="1:5">
       <c r="A68" s="11" t="s">
-        <v>1130</v>
+        <v>1112</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>1173</v>
+        <v>1155</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>1174</v>
+        <v>1156</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>1175</v>
+        <v>1157</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>1176</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="69" ht="42" customHeight="1" spans="1:5">
       <c r="A69" s="11" t="s">
-        <v>1130</v>
+        <v>1112</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>1177</v>
+        <v>1159</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>1178</v>
+        <v>1160</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>1179</v>
+        <v>1161</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>1144</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="70" ht="42" customHeight="1" spans="1:5">
       <c r="A70" s="11" t="s">
-        <v>1130</v>
+        <v>1112</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>1180</v>
+        <v>1162</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>1181</v>
+        <v>1163</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>1182</v>
+        <v>1164</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>1183</v>
+        <v>1165</v>
       </c>
     </row>
   </sheetData>
@@ -16893,7 +16839,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:40">
       <c r="A1" s="14" t="s">
-        <v>1184</v>
+        <v>1166</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
@@ -16937,7 +16883,7 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:40">
       <c r="A2" s="15" t="s">
-        <v>1185</v>
+        <v>1167</v>
       </c>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -17019,13 +16965,13 @@
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:40">
       <c r="A4" s="3" t="s">
-        <v>1186</v>
+        <v>1168</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1187</v>
+        <v>1169</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1188</v>
+        <v>1170</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>7</v>
@@ -17034,22 +16980,22 @@
         <v>8</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>984</v>
+        <v>966</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1189</v>
+        <v>1171</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>996</v>
+        <v>978</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>1190</v>
+        <v>1172</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>1191</v>
+        <v>1173</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>1192</v>
+        <v>1174</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>12</v>
@@ -17058,73 +17004,73 @@
         <v>13</v>
       </c>
       <c r="N4" s="3" t="s">
+        <v>1175</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>1176</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>1177</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>1178</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>1179</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>1180</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>1181</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>1182</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>1183</v>
+      </c>
+      <c r="W4" s="3" t="s">
+        <v>1184</v>
+      </c>
+      <c r="X4" s="3" t="s">
+        <v>1185</v>
+      </c>
+      <c r="Y4" s="3" t="s">
+        <v>1186</v>
+      </c>
+      <c r="Z4" s="3" t="s">
+        <v>1187</v>
+      </c>
+      <c r="AA4" s="3" t="s">
+        <v>1188</v>
+      </c>
+      <c r="AB4" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="AC4" s="3" t="s">
+        <v>1124</v>
+      </c>
+      <c r="AD4" s="3" t="s">
+        <v>1190</v>
+      </c>
+      <c r="AE4" s="3" t="s">
+        <v>1132</v>
+      </c>
+      <c r="AF4" s="3" t="s">
+        <v>1191</v>
+      </c>
+      <c r="AG4" s="3" t="s">
+        <v>1139</v>
+      </c>
+      <c r="AH4" s="3" t="s">
+        <v>1192</v>
+      </c>
+      <c r="AI4" s="3" t="s">
         <v>1193</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="AJ4" s="3" t="s">
         <v>1194</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>1195</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>1196</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>1197</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>1198</v>
-      </c>
-      <c r="T4" s="3" t="s">
-        <v>1199</v>
-      </c>
-      <c r="U4" s="3" t="s">
-        <v>1200</v>
-      </c>
-      <c r="V4" s="3" t="s">
-        <v>1201</v>
-      </c>
-      <c r="W4" s="3" t="s">
-        <v>1202</v>
-      </c>
-      <c r="X4" s="3" t="s">
-        <v>1203</v>
-      </c>
-      <c r="Y4" s="3" t="s">
-        <v>1204</v>
-      </c>
-      <c r="Z4" s="3" t="s">
-        <v>1205</v>
-      </c>
-      <c r="AA4" s="3" t="s">
-        <v>1206</v>
-      </c>
-      <c r="AB4" s="3" t="s">
-        <v>1207</v>
-      </c>
-      <c r="AC4" s="3" t="s">
-        <v>1142</v>
-      </c>
-      <c r="AD4" s="3" t="s">
-        <v>1208</v>
-      </c>
-      <c r="AE4" s="3" t="s">
-        <v>1150</v>
-      </c>
-      <c r="AF4" s="3" t="s">
-        <v>1209</v>
-      </c>
-      <c r="AG4" s="3" t="s">
-        <v>1157</v>
-      </c>
-      <c r="AH4" s="3" t="s">
-        <v>1210</v>
-      </c>
-      <c r="AI4" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="AJ4" s="3" t="s">
-        <v>1212</v>
       </c>
       <c r="AK4" s="3" t="s">
         <v>22</v>
@@ -17147,106 +17093,106 @@
         <v>41</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>1198</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>1199</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>1200</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>1201</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>1202</v>
+      </c>
+      <c r="K5" s="16" t="s">
+        <v>1203</v>
+      </c>
+      <c r="L5" s="16" t="s">
+        <v>1204</v>
+      </c>
+      <c r="M5" s="16" t="s">
+        <v>1205</v>
+      </c>
+      <c r="N5" s="16" t="s">
+        <v>1206</v>
+      </c>
+      <c r="O5" s="16" t="s">
+        <v>1207</v>
+      </c>
+      <c r="P5" s="16" t="s">
+        <v>1208</v>
+      </c>
+      <c r="Q5" s="16" t="s">
+        <v>1209</v>
+      </c>
+      <c r="R5" s="16" t="s">
+        <v>1210</v>
+      </c>
+      <c r="S5" s="16" t="s">
+        <v>1211</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>1212</v>
+      </c>
+      <c r="U5" s="4" t="s">
         <v>1213</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="V5" s="4" t="s">
         <v>1214</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="W5" s="4" t="s">
         <v>1215</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="X5" s="16" t="s">
         <v>1216</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="Y5" s="4" t="s">
         <v>1217</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="Z5" s="4" t="s">
+        <v>1115</v>
+      </c>
+      <c r="AA5" s="4" t="s">
         <v>1218</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="AB5" s="16" t="s">
         <v>1219</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="AC5" s="16" t="s">
         <v>1220</v>
       </c>
-      <c r="K5" s="16" t="s">
+      <c r="AD5" s="16" t="s">
         <v>1221</v>
       </c>
-      <c r="L5" s="16" t="s">
+      <c r="AE5" s="16" t="s">
         <v>1222</v>
       </c>
-      <c r="M5" s="16" t="s">
+      <c r="AF5" s="16" t="s">
         <v>1223</v>
       </c>
-      <c r="N5" s="16" t="s">
+      <c r="AG5" s="16" t="s">
         <v>1224</v>
       </c>
-      <c r="O5" s="16" t="s">
+      <c r="AH5" s="16" t="s">
         <v>1225</v>
       </c>
-      <c r="P5" s="16" t="s">
+      <c r="AI5" s="4" t="s">
         <v>1226</v>
       </c>
-      <c r="Q5" s="16" t="s">
+      <c r="AJ5" s="4" t="s">
         <v>1227</v>
-      </c>
-      <c r="R5" s="16" t="s">
-        <v>1228</v>
-      </c>
-      <c r="S5" s="16" t="s">
-        <v>1229</v>
-      </c>
-      <c r="T5" s="4" t="s">
-        <v>1230</v>
-      </c>
-      <c r="U5" s="4" t="s">
-        <v>1231</v>
-      </c>
-      <c r="V5" s="4" t="s">
-        <v>1232</v>
-      </c>
-      <c r="W5" s="4" t="s">
-        <v>1233</v>
-      </c>
-      <c r="X5" s="4" t="s">
-        <v>1234</v>
-      </c>
-      <c r="Y5" s="4" t="s">
-        <v>1235</v>
-      </c>
-      <c r="Z5" s="4" t="s">
-        <v>1133</v>
-      </c>
-      <c r="AA5" s="4" t="s">
-        <v>1236</v>
-      </c>
-      <c r="AB5" s="4" t="s">
-        <v>1237</v>
-      </c>
-      <c r="AC5" s="16" t="s">
-        <v>1238</v>
-      </c>
-      <c r="AD5" s="16" t="s">
-        <v>1239</v>
-      </c>
-      <c r="AE5" s="16" t="s">
-        <v>1240</v>
-      </c>
-      <c r="AF5" s="16" t="s">
-        <v>1241</v>
-      </c>
-      <c r="AG5" s="16" t="s">
-        <v>1242</v>
-      </c>
-      <c r="AH5" s="16" t="s">
-        <v>1243</v>
-      </c>
-      <c r="AI5" s="4" t="s">
-        <v>1244</v>
-      </c>
-      <c r="AJ5" s="4" t="s">
-        <v>1245</v>
       </c>
       <c r="AK5" s="4" t="s">
         <v>60</v>
@@ -17269,106 +17215,106 @@
         <v>235</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1246</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>1247</v>
+        <v>1228</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>1229</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>1248</v>
+        <v>1230</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>1216</v>
+        <v>1198</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>1249</v>
+        <v>1231</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>1250</v>
+        <v>1232</v>
       </c>
       <c r="I6" s="4" t="s">
+        <v>1201</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>1202</v>
+      </c>
+      <c r="K6" s="16" t="s">
+        <v>1233</v>
+      </c>
+      <c r="L6" s="16" t="s">
+        <v>1234</v>
+      </c>
+      <c r="M6" s="16" t="s">
+        <v>1235</v>
+      </c>
+      <c r="N6" s="16" t="s">
+        <v>1206</v>
+      </c>
+      <c r="O6" s="16" t="s">
+        <v>1207</v>
+      </c>
+      <c r="P6" s="16" t="s">
+        <v>1208</v>
+      </c>
+      <c r="Q6" s="16" t="s">
+        <v>1236</v>
+      </c>
+      <c r="R6" s="16" t="s">
+        <v>1210</v>
+      </c>
+      <c r="S6" s="16" t="s">
+        <v>1237</v>
+      </c>
+      <c r="T6" s="4" t="s">
+        <v>1212</v>
+      </c>
+      <c r="U6" s="4" t="s">
+        <v>1238</v>
+      </c>
+      <c r="V6" s="4" t="s">
+        <v>1214</v>
+      </c>
+      <c r="W6" s="4" t="s">
+        <v>1215</v>
+      </c>
+      <c r="X6" s="16" t="s">
+        <v>1239</v>
+      </c>
+      <c r="Y6" s="4" t="s">
+        <v>1217</v>
+      </c>
+      <c r="Z6" s="4" t="s">
+        <v>1115</v>
+      </c>
+      <c r="AA6" s="4" t="s">
+        <v>1240</v>
+      </c>
+      <c r="AB6" s="16" t="s">
         <v>1219</v>
       </c>
-      <c r="J6" s="4" t="s">
-        <v>1220</v>
-      </c>
-      <c r="K6" s="16" t="s">
-        <v>1251</v>
-      </c>
-      <c r="L6" s="16" t="s">
-        <v>1252</v>
-      </c>
-      <c r="M6" s="16" t="s">
-        <v>1253</v>
-      </c>
-      <c r="N6" s="16" t="s">
+      <c r="AC6" s="16" t="s">
+        <v>1241</v>
+      </c>
+      <c r="AD6" s="16" t="s">
+        <v>1221</v>
+      </c>
+      <c r="AE6" s="16" t="s">
+        <v>1222</v>
+      </c>
+      <c r="AF6" s="16" t="s">
+        <v>1223</v>
+      </c>
+      <c r="AG6" s="16" t="s">
         <v>1224</v>
       </c>
-      <c r="O6" s="16" t="s">
+      <c r="AH6" s="4" t="s">
         <v>1225</v>
       </c>
-      <c r="P6" s="16" t="s">
+      <c r="AI6" s="4" t="s">
         <v>1226</v>
       </c>
-      <c r="Q6" s="16" t="s">
-        <v>1254</v>
-      </c>
-      <c r="R6" s="16" t="s">
-        <v>1228</v>
-      </c>
-      <c r="S6" s="16" t="s">
-        <v>1255</v>
-      </c>
-      <c r="T6" s="4" t="s">
-        <v>1230</v>
-      </c>
-      <c r="U6" s="4" t="s">
-        <v>1256</v>
-      </c>
-      <c r="V6" s="4" t="s">
-        <v>1232</v>
-      </c>
-      <c r="W6" s="4" t="s">
-        <v>1233</v>
-      </c>
-      <c r="X6" s="4" t="s">
-        <v>1257</v>
-      </c>
-      <c r="Y6" s="4" t="s">
-        <v>1235</v>
-      </c>
-      <c r="Z6" s="4" t="s">
-        <v>1133</v>
-      </c>
-      <c r="AA6" s="4" t="s">
-        <v>1258</v>
-      </c>
-      <c r="AB6" s="4" t="s">
-        <v>1237</v>
-      </c>
-      <c r="AC6" s="16" t="s">
-        <v>1259</v>
-      </c>
-      <c r="AD6" s="16" t="s">
-        <v>1239</v>
-      </c>
-      <c r="AE6" s="16" t="s">
-        <v>1240</v>
-      </c>
-      <c r="AF6" s="16" t="s">
-        <v>1241</v>
-      </c>
-      <c r="AG6" s="16" t="s">
-        <v>1242</v>
-      </c>
-      <c r="AH6" s="4" t="s">
-        <v>1243</v>
-      </c>
-      <c r="AI6" s="4" t="s">
-        <v>1244</v>
-      </c>
       <c r="AJ6" s="4" t="s">
-        <v>1245</v>
+        <v>1227</v>
       </c>
       <c r="AK6" s="4" t="s">
         <v>60</v>
@@ -17391,106 +17337,106 @@
         <v>409</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1260</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>1261</v>
+        <v>1242</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>1243</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>1262</v>
+        <v>1244</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>1216</v>
+        <v>1198</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>1263</v>
+        <v>1245</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>1264</v>
+        <v>1246</v>
       </c>
       <c r="I7" s="4" t="s">
+        <v>1201</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>1202</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>1247</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>1248</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>1249</v>
+      </c>
+      <c r="N7" s="16" t="s">
+        <v>1206</v>
+      </c>
+      <c r="O7" s="16" t="s">
+        <v>1207</v>
+      </c>
+      <c r="P7" s="16" t="s">
+        <v>1208</v>
+      </c>
+      <c r="Q7" s="16" t="s">
+        <v>1250</v>
+      </c>
+      <c r="R7" s="16" t="s">
+        <v>1251</v>
+      </c>
+      <c r="S7" s="16" t="s">
+        <v>1252</v>
+      </c>
+      <c r="T7" s="4" t="s">
+        <v>1212</v>
+      </c>
+      <c r="U7" s="4" t="s">
+        <v>1253</v>
+      </c>
+      <c r="V7" s="4" t="s">
+        <v>1214</v>
+      </c>
+      <c r="W7" s="4" t="s">
+        <v>1215</v>
+      </c>
+      <c r="X7" s="16" t="s">
+        <v>1254</v>
+      </c>
+      <c r="Y7" s="4" t="s">
+        <v>1217</v>
+      </c>
+      <c r="Z7" s="4" t="s">
+        <v>1115</v>
+      </c>
+      <c r="AA7" s="4" t="s">
+        <v>1255</v>
+      </c>
+      <c r="AB7" s="16" t="s">
         <v>1219</v>
       </c>
-      <c r="J7" s="4" t="s">
-        <v>1220</v>
-      </c>
-      <c r="K7" s="16" t="s">
-        <v>1265</v>
-      </c>
-      <c r="L7" s="16" t="s">
-        <v>1266</v>
-      </c>
-      <c r="M7" s="16" t="s">
-        <v>1267</v>
-      </c>
-      <c r="N7" s="16" t="s">
+      <c r="AC7" s="16" t="s">
+        <v>1256</v>
+      </c>
+      <c r="AD7" s="16" t="s">
+        <v>1221</v>
+      </c>
+      <c r="AE7" s="16" t="s">
+        <v>1222</v>
+      </c>
+      <c r="AF7" s="16" t="s">
+        <v>1223</v>
+      </c>
+      <c r="AG7" s="16" t="s">
         <v>1224</v>
       </c>
-      <c r="O7" s="16" t="s">
+      <c r="AH7" s="4" t="s">
         <v>1225</v>
       </c>
-      <c r="P7" s="16" t="s">
+      <c r="AI7" s="4" t="s">
         <v>1226</v>
       </c>
-      <c r="Q7" s="16" t="s">
-        <v>1268</v>
-      </c>
-      <c r="R7" s="16" t="s">
-        <v>1269</v>
-      </c>
-      <c r="S7" s="16" t="s">
-        <v>1270</v>
-      </c>
-      <c r="T7" s="4" t="s">
-        <v>1230</v>
-      </c>
-      <c r="U7" s="4" t="s">
-        <v>1271</v>
-      </c>
-      <c r="V7" s="4" t="s">
-        <v>1232</v>
-      </c>
-      <c r="W7" s="4" t="s">
-        <v>1233</v>
-      </c>
-      <c r="X7" s="4" t="s">
-        <v>1272</v>
-      </c>
-      <c r="Y7" s="4" t="s">
-        <v>1235</v>
-      </c>
-      <c r="Z7" s="4" t="s">
-        <v>1133</v>
-      </c>
-      <c r="AA7" s="4" t="s">
-        <v>1273</v>
-      </c>
-      <c r="AB7" s="4" t="s">
-        <v>1237</v>
-      </c>
-      <c r="AC7" s="16" t="s">
-        <v>1274</v>
-      </c>
-      <c r="AD7" s="16" t="s">
-        <v>1239</v>
-      </c>
-      <c r="AE7" s="16" t="s">
-        <v>1240</v>
-      </c>
-      <c r="AF7" s="16" t="s">
-        <v>1241</v>
-      </c>
-      <c r="AG7" s="16" t="s">
-        <v>1242</v>
-      </c>
-      <c r="AH7" s="4" t="s">
-        <v>1243</v>
-      </c>
-      <c r="AI7" s="4" t="s">
-        <v>1244</v>
-      </c>
       <c r="AJ7" s="4" t="s">
-        <v>1245</v>
+        <v>1227</v>
       </c>
       <c r="AK7" s="4" t="s">
         <v>60</v>
@@ -17513,106 +17459,106 @@
         <v>582</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1275</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>1276</v>
+        <v>1257</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>1258</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>1277</v>
+        <v>1259</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>1216</v>
+        <v>1198</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>1278</v>
+        <v>1260</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>1279</v>
+        <v>1261</v>
       </c>
       <c r="I8" s="4" t="s">
+        <v>1201</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>1202</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>1262</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>1263</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>1264</v>
+      </c>
+      <c r="N8" s="16" t="s">
+        <v>1206</v>
+      </c>
+      <c r="O8" s="16" t="s">
+        <v>1207</v>
+      </c>
+      <c r="P8" s="16" t="s">
+        <v>1208</v>
+      </c>
+      <c r="Q8" s="16" t="s">
+        <v>1265</v>
+      </c>
+      <c r="R8" s="16" t="s">
+        <v>1210</v>
+      </c>
+      <c r="S8" s="16" t="s">
+        <v>1252</v>
+      </c>
+      <c r="T8" s="4" t="s">
+        <v>1212</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>1266</v>
+      </c>
+      <c r="V8" s="4" t="s">
+        <v>1214</v>
+      </c>
+      <c r="W8" s="4" t="s">
+        <v>1215</v>
+      </c>
+      <c r="X8" s="16" t="s">
+        <v>1267</v>
+      </c>
+      <c r="Y8" s="4" t="s">
+        <v>1217</v>
+      </c>
+      <c r="Z8" s="4" t="s">
+        <v>1115</v>
+      </c>
+      <c r="AA8" s="4" t="s">
+        <v>1268</v>
+      </c>
+      <c r="AB8" s="16" t="s">
         <v>1219</v>
       </c>
-      <c r="J8" s="4" t="s">
-        <v>1220</v>
-      </c>
-      <c r="K8" s="16" t="s">
-        <v>1280</v>
-      </c>
-      <c r="L8" s="16" t="s">
-        <v>1281</v>
-      </c>
-      <c r="M8" s="16" t="s">
-        <v>1282</v>
-      </c>
-      <c r="N8" s="16" t="s">
+      <c r="AC8" s="16" t="s">
+        <v>1269</v>
+      </c>
+      <c r="AD8" s="16" t="s">
+        <v>1221</v>
+      </c>
+      <c r="AE8" s="16" t="s">
+        <v>1222</v>
+      </c>
+      <c r="AF8" s="16" t="s">
+        <v>1223</v>
+      </c>
+      <c r="AG8" s="16" t="s">
         <v>1224</v>
       </c>
-      <c r="O8" s="16" t="s">
+      <c r="AH8" s="4" t="s">
         <v>1225</v>
       </c>
-      <c r="P8" s="16" t="s">
+      <c r="AI8" s="4" t="s">
         <v>1226</v>
       </c>
-      <c r="Q8" s="16" t="s">
-        <v>1283</v>
-      </c>
-      <c r="R8" s="16" t="s">
-        <v>1228</v>
-      </c>
-      <c r="S8" s="16" t="s">
-        <v>1270</v>
-      </c>
-      <c r="T8" s="4" t="s">
-        <v>1230</v>
-      </c>
-      <c r="U8" s="4" t="s">
-        <v>1284</v>
-      </c>
-      <c r="V8" s="4" t="s">
-        <v>1232</v>
-      </c>
-      <c r="W8" s="4" t="s">
-        <v>1233</v>
-      </c>
-      <c r="X8" s="4" t="s">
-        <v>1285</v>
-      </c>
-      <c r="Y8" s="4" t="s">
-        <v>1235</v>
-      </c>
-      <c r="Z8" s="4" t="s">
-        <v>1133</v>
-      </c>
-      <c r="AA8" s="4" t="s">
-        <v>1286</v>
-      </c>
-      <c r="AB8" s="4" t="s">
-        <v>1237</v>
-      </c>
-      <c r="AC8" s="16" t="s">
-        <v>1287</v>
-      </c>
-      <c r="AD8" s="16" t="s">
-        <v>1239</v>
-      </c>
-      <c r="AE8" s="16" t="s">
-        <v>1240</v>
-      </c>
-      <c r="AF8" s="16" t="s">
-        <v>1241</v>
-      </c>
-      <c r="AG8" s="16" t="s">
-        <v>1242</v>
-      </c>
-      <c r="AH8" s="4" t="s">
-        <v>1243</v>
-      </c>
-      <c r="AI8" s="4" t="s">
-        <v>1244</v>
-      </c>
       <c r="AJ8" s="4" t="s">
-        <v>1245</v>
+        <v>1227</v>
       </c>
       <c r="AK8" s="4" t="s">
         <v>60</v>
@@ -17629,112 +17575,112 @@
     </row>
     <row r="9" ht="52" customHeight="1" spans="1:40">
       <c r="A9" s="4" t="s">
-        <v>755</v>
+        <v>737</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>756</v>
+        <v>738</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1288</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>1289</v>
+        <v>1270</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>1271</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>1290</v>
+        <v>1272</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>1216</v>
+        <v>1198</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>1291</v>
+        <v>1273</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>1292</v>
+        <v>1274</v>
       </c>
       <c r="I9" s="4" t="s">
+        <v>1201</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>1202</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>1275</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>1276</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>1277</v>
+      </c>
+      <c r="N9" s="16" t="s">
+        <v>1206</v>
+      </c>
+      <c r="O9" s="16" t="s">
+        <v>1207</v>
+      </c>
+      <c r="P9" s="16" t="s">
+        <v>1208</v>
+      </c>
+      <c r="Q9" s="16" t="s">
+        <v>1278</v>
+      </c>
+      <c r="R9" s="16" t="s">
+        <v>1210</v>
+      </c>
+      <c r="S9" s="16" t="s">
+        <v>1237</v>
+      </c>
+      <c r="T9" s="4" t="s">
+        <v>1212</v>
+      </c>
+      <c r="U9" s="4" t="s">
+        <v>1279</v>
+      </c>
+      <c r="V9" s="4" t="s">
+        <v>1214</v>
+      </c>
+      <c r="W9" s="4" t="s">
+        <v>1215</v>
+      </c>
+      <c r="X9" s="16" t="s">
+        <v>1280</v>
+      </c>
+      <c r="Y9" s="4" t="s">
+        <v>1217</v>
+      </c>
+      <c r="Z9" s="4" t="s">
+        <v>1115</v>
+      </c>
+      <c r="AA9" s="4" t="s">
+        <v>1281</v>
+      </c>
+      <c r="AB9" s="16" t="s">
         <v>1219</v>
       </c>
-      <c r="J9" s="4" t="s">
-        <v>1220</v>
-      </c>
-      <c r="K9" s="16" t="s">
-        <v>1293</v>
-      </c>
-      <c r="L9" s="16" t="s">
-        <v>1294</v>
-      </c>
-      <c r="M9" s="16" t="s">
-        <v>1295</v>
-      </c>
-      <c r="N9" s="16" t="s">
+      <c r="AC9" s="16" t="s">
+        <v>1282</v>
+      </c>
+      <c r="AD9" s="16" t="s">
+        <v>1221</v>
+      </c>
+      <c r="AE9" s="16" t="s">
+        <v>1222</v>
+      </c>
+      <c r="AF9" s="16" t="s">
+        <v>1223</v>
+      </c>
+      <c r="AG9" s="16" t="s">
         <v>1224</v>
       </c>
-      <c r="O9" s="16" t="s">
+      <c r="AH9" s="4" t="s">
         <v>1225</v>
       </c>
-      <c r="P9" s="16" t="s">
+      <c r="AI9" s="4" t="s">
         <v>1226</v>
       </c>
-      <c r="Q9" s="16" t="s">
-        <v>1296</v>
-      </c>
-      <c r="R9" s="16" t="s">
-        <v>1228</v>
-      </c>
-      <c r="S9" s="16" t="s">
-        <v>1255</v>
-      </c>
-      <c r="T9" s="4" t="s">
-        <v>1230</v>
-      </c>
-      <c r="U9" s="4" t="s">
-        <v>1297</v>
-      </c>
-      <c r="V9" s="4" t="s">
-        <v>1232</v>
-      </c>
-      <c r="W9" s="4" t="s">
-        <v>1233</v>
-      </c>
-      <c r="X9" s="4" t="s">
-        <v>1298</v>
-      </c>
-      <c r="Y9" s="4" t="s">
-        <v>1235</v>
-      </c>
-      <c r="Z9" s="4" t="s">
-        <v>1133</v>
-      </c>
-      <c r="AA9" s="4" t="s">
-        <v>1299</v>
-      </c>
-      <c r="AB9" s="4" t="s">
-        <v>1237</v>
-      </c>
-      <c r="AC9" s="16" t="s">
-        <v>1300</v>
-      </c>
-      <c r="AD9" s="16" t="s">
-        <v>1239</v>
-      </c>
-      <c r="AE9" s="16" t="s">
-        <v>1240</v>
-      </c>
-      <c r="AF9" s="16" t="s">
-        <v>1241</v>
-      </c>
-      <c r="AG9" s="16" t="s">
-        <v>1242</v>
-      </c>
-      <c r="AH9" s="4" t="s">
-        <v>1243</v>
-      </c>
-      <c r="AI9" s="4" t="s">
-        <v>1244</v>
-      </c>
       <c r="AJ9" s="4" t="s">
-        <v>1245</v>
+        <v>1227</v>
       </c>
       <c r="AK9" s="4" t="s">
         <v>60</v>
@@ -18631,7 +18577,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>1301</v>
+        <v>1283</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -18641,7 +18587,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6">
       <c r="A2" s="8" t="s">
-        <v>1302</v>
+        <v>1284</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -18659,2282 +18605,2282 @@
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:6">
       <c r="A4" s="10" t="s">
-        <v>1303</v>
+        <v>1285</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1304</v>
+        <v>1286</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>931</v>
+        <v>913</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>932</v>
+        <v>914</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>933</v>
+        <v>915</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>934</v>
+        <v>916</v>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:6">
       <c r="A5" s="11" t="s">
-        <v>962</v>
+        <v>944</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>1305</v>
+        <v>1287</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>1306</v>
+        <v>1288</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>962</v>
+        <v>944</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>1307</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:6">
       <c r="A6" s="11" t="s">
-        <v>962</v>
+        <v>944</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>1305</v>
+        <v>1287</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>967</v>
+        <v>949</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>1308</v>
+        <v>1290</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:6">
       <c r="A7" s="11" t="s">
-        <v>962</v>
+        <v>944</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>1305</v>
+        <v>1287</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>970</v>
+        <v>952</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>1310</v>
+        <v>1292</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:6">
       <c r="A8" s="11" t="s">
-        <v>962</v>
+        <v>944</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>1305</v>
+        <v>1287</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>983</v>
+        <v>965</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>984</v>
+        <v>966</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>1311</v>
+        <v>1293</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:6">
       <c r="A9" s="11" t="s">
-        <v>962</v>
+        <v>944</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>1305</v>
+        <v>1287</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>1312</v>
+        <v>1294</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>1189</v>
+        <v>1171</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>1313</v>
+        <v>1295</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:6">
       <c r="A10" s="11" t="s">
-        <v>962</v>
+        <v>944</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>1305</v>
+        <v>1287</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>995</v>
+        <v>977</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>1314</v>
+        <v>1296</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>1315</v>
+        <v>1297</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:6">
       <c r="A11" s="11" t="s">
-        <v>962</v>
+        <v>944</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>1305</v>
+        <v>1287</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>1316</v>
+        <v>1298</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>1317</v>
+        <v>1299</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>1318</v>
+        <v>1300</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:6">
       <c r="A12" s="11" t="s">
-        <v>962</v>
+        <v>944</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>1305</v>
+        <v>1287</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>1319</v>
+        <v>1301</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>1320</v>
+        <v>1302</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>1321</v>
+        <v>1303</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:6">
       <c r="A13" s="11" t="s">
-        <v>962</v>
+        <v>944</v>
       </c>
       <c r="B13" s="11" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>1305</v>
       </c>
-      <c r="C13" s="11" t="s">
-        <v>1322</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>1323</v>
-      </c>
       <c r="E13" s="12" t="s">
-        <v>1015</v>
+        <v>997</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:6">
       <c r="A14" s="11" t="s">
-        <v>962</v>
+        <v>944</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>1305</v>
+        <v>1287</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>1324</v>
+        <v>1306</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>1325</v>
+        <v>1307</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>1326</v>
+        <v>1308</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:6">
       <c r="A15" s="11" t="s">
-        <v>962</v>
+        <v>944</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>1305</v>
+        <v>1287</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>1327</v>
+        <v>1309</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>1328</v>
+        <v>1310</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>1329</v>
+        <v>1311</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:6">
       <c r="A16" s="11" t="s">
-        <v>962</v>
+        <v>944</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>1305</v>
+        <v>1287</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>1330</v>
+        <v>1312</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>1331</v>
+        <v>1313</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>1332</v>
+        <v>1314</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:6">
       <c r="A17" s="11" t="s">
-        <v>962</v>
+        <v>944</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>1305</v>
+        <v>1287</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>1333</v>
+        <v>1315</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>1334</v>
+        <v>1316</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>1335</v>
+        <v>1317</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:6">
       <c r="A18" s="11" t="s">
-        <v>962</v>
+        <v>944</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>1305</v>
+        <v>1287</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>1336</v>
+        <v>1318</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>1337</v>
+        <v>1319</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>1338</v>
+        <v>1320</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:6">
       <c r="A19" s="11" t="s">
-        <v>962</v>
+        <v>944</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>1305</v>
+        <v>1287</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>1339</v>
+        <v>1321</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>1340</v>
+        <v>1322</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>1341</v>
+        <v>1323</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:6">
       <c r="A20" s="11" t="s">
-        <v>962</v>
+        <v>944</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>1305</v>
+        <v>1287</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>1342</v>
+        <v>1324</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>1343</v>
+        <v>1325</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>1344</v>
+        <v>1326</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:6">
       <c r="A21" s="11" t="s">
-        <v>962</v>
+        <v>944</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>1305</v>
+        <v>1287</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>1345</v>
+        <v>1327</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>1346</v>
+        <v>1328</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>1347</v>
+        <v>1329</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:6">
       <c r="A22" s="11" t="s">
-        <v>962</v>
+        <v>944</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>1305</v>
+        <v>1287</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>1348</v>
+        <v>1330</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>1349</v>
+        <v>1331</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>1350</v>
+        <v>1332</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:6">
       <c r="A23" s="11" t="s">
-        <v>962</v>
+        <v>944</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>1305</v>
+        <v>1287</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>1351</v>
+        <v>1333</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>1352</v>
+        <v>1334</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>993</v>
+        <v>975</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:6">
       <c r="A24" s="11" t="s">
-        <v>962</v>
+        <v>944</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>1305</v>
+        <v>1287</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>1353</v>
+        <v>1335</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>1354</v>
+        <v>1336</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>1355</v>
+        <v>1337</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:6">
       <c r="A25" s="11" t="s">
-        <v>962</v>
+        <v>944</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>1305</v>
+        <v>1287</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>1356</v>
+        <v>1338</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>1357</v>
+        <v>1339</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>1358</v>
+        <v>1340</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:6">
       <c r="A26" s="11" t="s">
-        <v>962</v>
+        <v>944</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>1305</v>
+        <v>1287</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>1359</v>
+        <v>1341</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>1360</v>
+        <v>1342</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>1361</v>
+        <v>1343</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="27" ht="48" customHeight="1" spans="1:6">
       <c r="A27" s="11" t="s">
-        <v>962</v>
+        <v>944</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>1305</v>
+        <v>1287</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>1362</v>
+        <v>1344</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>1363</v>
+        <v>1345</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>1364</v>
+        <v>1346</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="28" ht="48" customHeight="1" spans="1:6">
       <c r="A28" s="11" t="s">
-        <v>962</v>
+        <v>944</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>1305</v>
+        <v>1287</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>1365</v>
+        <v>1347</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>1366</v>
+        <v>1348</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>1367</v>
+        <v>1349</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="29" ht="48" customHeight="1" spans="1:6">
       <c r="A29" s="11" t="s">
-        <v>962</v>
+        <v>944</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>1305</v>
+        <v>1287</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>1368</v>
+        <v>1350</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>1369</v>
+        <v>1351</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>1370</v>
+        <v>1352</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="30" ht="48" customHeight="1" spans="1:6">
       <c r="A30" s="11" t="s">
-        <v>965</v>
+        <v>947</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>1371</v>
+        <v>1353</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>1306</v>
+        <v>1288</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>965</v>
+        <v>947</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>1307</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="31" ht="48" customHeight="1" spans="1:6">
       <c r="A31" s="11" t="s">
-        <v>965</v>
+        <v>947</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>1371</v>
+        <v>1353</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>967</v>
+        <v>949</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>7</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>1372</v>
+        <v>1354</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="32" ht="48" customHeight="1" spans="1:6">
       <c r="A32" s="11" t="s">
-        <v>965</v>
+        <v>947</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>1371</v>
+        <v>1353</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>970</v>
+        <v>952</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>8</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>1373</v>
+        <v>1355</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="33" ht="48" customHeight="1" spans="1:6">
       <c r="A33" s="11" t="s">
+        <v>947</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C33" s="11" t="s">
         <v>965</v>
       </c>
-      <c r="B33" s="11" t="s">
-        <v>1371</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>983</v>
-      </c>
       <c r="D33" s="11" t="s">
-        <v>984</v>
+        <v>966</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>1374</v>
+        <v>1356</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="34" ht="48" customHeight="1" spans="1:6">
       <c r="A34" s="11" t="s">
-        <v>965</v>
+        <v>947</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>1371</v>
+        <v>1353</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>1312</v>
+        <v>1294</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>1189</v>
+        <v>1171</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>1375</v>
+        <v>1357</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="35" ht="48" customHeight="1" spans="1:6">
       <c r="A35" s="11" t="s">
-        <v>965</v>
+        <v>947</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>1371</v>
+        <v>1353</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>995</v>
+        <v>977</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>1314</v>
+        <v>1296</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>1373</v>
+        <v>1355</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="36" ht="48" customHeight="1" spans="1:6">
       <c r="A36" s="11" t="s">
-        <v>965</v>
+        <v>947</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>1371</v>
+        <v>1353</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>1376</v>
+        <v>1358</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>1377</v>
+        <v>1359</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>1378</v>
+        <v>1360</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="37" ht="48" customHeight="1" spans="1:6">
       <c r="A37" s="11" t="s">
-        <v>965</v>
+        <v>947</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>1371</v>
+        <v>1353</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>1379</v>
+        <v>1361</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>1380</v>
+        <v>1362</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>1381</v>
+        <v>1363</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="38" ht="48" customHeight="1" spans="1:6">
       <c r="A38" s="11" t="s">
-        <v>965</v>
+        <v>947</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>1371</v>
+        <v>1353</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>1382</v>
+        <v>1364</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>1383</v>
+        <v>1365</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>1384</v>
+        <v>1366</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="39" ht="48" customHeight="1" spans="1:6">
       <c r="A39" s="11" t="s">
-        <v>965</v>
+        <v>947</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>1371</v>
+        <v>1353</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>1385</v>
+        <v>1367</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>1386</v>
+        <v>1368</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>1387</v>
+        <v>1369</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="40" ht="48" customHeight="1" spans="1:6">
       <c r="A40" s="11" t="s">
-        <v>965</v>
+        <v>947</v>
       </c>
       <c r="B40" s="11" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D40" s="11" t="s">
         <v>1371</v>
       </c>
-      <c r="C40" s="11" t="s">
-        <v>1388</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>1389</v>
-      </c>
       <c r="E40" s="12" t="s">
-        <v>1390</v>
+        <v>1372</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="41" ht="48" customHeight="1" spans="1:6">
       <c r="A41" s="11" t="s">
-        <v>965</v>
+        <v>947</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>1371</v>
+        <v>1353</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>1391</v>
+        <v>1373</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>1392</v>
+        <v>1374</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>1393</v>
+        <v>1375</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="42" ht="48" customHeight="1" spans="1:6">
       <c r="A42" s="11" t="s">
-        <v>965</v>
+        <v>947</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>1371</v>
+        <v>1353</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>1394</v>
+        <v>1376</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>1395</v>
+        <v>1377</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>1396</v>
+        <v>1378</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="43" ht="48" customHeight="1" spans="1:6">
       <c r="A43" s="11" t="s">
-        <v>965</v>
+        <v>947</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>1371</v>
+        <v>1353</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>1397</v>
+        <v>1379</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>1398</v>
+        <v>1380</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>1399</v>
+        <v>1381</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="44" ht="48" customHeight="1" spans="1:6">
       <c r="A44" s="11" t="s">
-        <v>965</v>
+        <v>947</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>1371</v>
+        <v>1353</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>1400</v>
+        <v>1382</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="45" ht="48" customHeight="1" spans="1:6">
       <c r="A45" s="11" t="s">
-        <v>965</v>
+        <v>947</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>1371</v>
+        <v>1353</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>1405</v>
+        <v>1387</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="46" ht="48" customHeight="1" spans="1:6">
       <c r="A46" s="11" t="s">
-        <v>965</v>
+        <v>947</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>1371</v>
+        <v>1353</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>1406</v>
+        <v>1388</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>1407</v>
+        <v>1389</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>1378</v>
+        <v>1360</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="47" ht="48" customHeight="1" spans="1:6">
       <c r="A47" s="11" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>1306</v>
+        <v>1288</v>
       </c>
       <c r="D47" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>1307</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="48" ht="48" customHeight="1" spans="1:6">
       <c r="A48" s="11" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>967</v>
+        <v>949</v>
       </c>
       <c r="D48" s="11" t="s">
         <v>7</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>1410</v>
+        <v>1392</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="49" ht="48" customHeight="1" spans="1:6">
       <c r="A49" s="11" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>970</v>
+        <v>952</v>
       </c>
       <c r="D49" s="11" t="s">
         <v>8</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>1411</v>
+        <v>1393</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="50" ht="48" customHeight="1" spans="1:6">
       <c r="A50" s="11" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>983</v>
+        <v>965</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>984</v>
+        <v>966</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>1412</v>
+        <v>1394</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="51" ht="48" customHeight="1" spans="1:6">
       <c r="A51" s="11" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>1312</v>
+        <v>1294</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>1189</v>
+        <v>1171</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="52" ht="48" customHeight="1" spans="1:6">
       <c r="A52" s="11" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>995</v>
+        <v>977</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>1314</v>
+        <v>1296</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>1411</v>
+        <v>1393</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="53" ht="48" customHeight="1" spans="1:6">
       <c r="A53" s="11" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>1413</v>
+        <v>1395</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>1414</v>
+        <v>1396</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>1415</v>
+        <v>1397</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="54" ht="48" customHeight="1" spans="1:6">
       <c r="A54" s="11" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>1316</v>
+        <v>1298</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>1317</v>
+        <v>1299</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>1416</v>
+        <v>1398</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="55" ht="48" customHeight="1" spans="1:6">
       <c r="A55" s="11" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>1319</v>
+        <v>1301</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>1320</v>
+        <v>1302</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>1417</v>
+        <v>1399</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="56" ht="48" customHeight="1" spans="1:6">
       <c r="A56" s="11" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>1322</v>
+        <v>1304</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>1323</v>
+        <v>1305</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>1418</v>
+        <v>1400</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="57" ht="48" customHeight="1" spans="1:6">
       <c r="A57" s="11" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>1324</v>
+        <v>1306</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>1325</v>
+        <v>1307</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>1419</v>
+        <v>1401</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="58" ht="48" customHeight="1" spans="1:6">
       <c r="A58" s="11" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>1420</v>
+        <v>1402</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>1421</v>
+        <v>1403</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>1422</v>
+        <v>1404</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="59" ht="48" customHeight="1" spans="1:6">
       <c r="A59" s="11" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>1423</v>
+        <v>1405</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>1424</v>
+        <v>1406</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>1425</v>
+        <v>1407</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="60" ht="48" customHeight="1" spans="1:6">
       <c r="A60" s="11" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C60" s="11" t="s">
         <v>1408</v>
       </c>
-      <c r="B60" s="11" t="s">
+      <c r="D60" s="11" t="s">
         <v>1409</v>
       </c>
-      <c r="C60" s="11" t="s">
-        <v>1426</v>
-      </c>
-      <c r="D60" s="11" t="s">
-        <v>1427</v>
-      </c>
       <c r="E60" s="12" t="s">
-        <v>1428</v>
+        <v>1410</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="61" ht="48" customHeight="1" spans="1:6">
       <c r="A61" s="11" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>1330</v>
+        <v>1312</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>1331</v>
+        <v>1313</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>1429</v>
+        <v>1411</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="62" ht="48" customHeight="1" spans="1:6">
       <c r="A62" s="11" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>1333</v>
+        <v>1315</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>1334</v>
+        <v>1316</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>1430</v>
+        <v>1412</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="63" ht="48" customHeight="1" spans="1:6">
       <c r="A63" s="11" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>1336</v>
+        <v>1318</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>1337</v>
+        <v>1319</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>1431</v>
+        <v>1413</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="64" ht="48" customHeight="1" spans="1:6">
       <c r="A64" s="11" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>1342</v>
+        <v>1324</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>1343</v>
+        <v>1325</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>1432</v>
+        <v>1414</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="65" ht="48" customHeight="1" spans="1:6">
       <c r="A65" s="11" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>1433</v>
+        <v>1415</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>1434</v>
+        <v>1416</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>1435</v>
+        <v>1417</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="66" ht="48" customHeight="1" spans="1:6">
       <c r="A66" s="11" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>1436</v>
+        <v>1418</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>1437</v>
+        <v>1419</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>1023</v>
+        <v>1005</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="67" ht="48" customHeight="1" spans="1:6">
       <c r="A67" s="11" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>1348</v>
+        <v>1330</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>1349</v>
+        <v>1331</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>1438</v>
+        <v>1420</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="68" ht="48" customHeight="1" spans="1:6">
       <c r="A68" s="11" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>1439</v>
+        <v>1421</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>1440</v>
+        <v>1422</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>1441</v>
+        <v>1423</v>
       </c>
       <c r="F68" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="69" ht="48" customHeight="1" spans="1:6">
       <c r="A69" s="11" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>1442</v>
+        <v>1424</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>1443</v>
+        <v>1425</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>1023</v>
+        <v>1005</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="70" ht="48" customHeight="1" spans="1:6">
       <c r="A70" s="11" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>1444</v>
+        <v>1426</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>1445</v>
+        <v>1427</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>1446</v>
+        <v>1428</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="71" ht="48" customHeight="1" spans="1:6">
       <c r="A71" s="11" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>1447</v>
+        <v>1429</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>1448</v>
+        <v>1430</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>1449</v>
+        <v>1431</v>
       </c>
       <c r="F71" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="72" ht="48" customHeight="1" spans="1:6">
       <c r="A72" s="11" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>1450</v>
+        <v>1432</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>1451</v>
+        <v>1433</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>1023</v>
+        <v>1005</v>
       </c>
       <c r="F72" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="73" ht="48" customHeight="1" spans="1:6">
       <c r="A73" s="11" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>1452</v>
+        <v>1434</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>1453</v>
+        <v>1435</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>1454</v>
+        <v>1436</v>
       </c>
       <c r="F73" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="74" ht="48" customHeight="1" spans="1:6">
       <c r="A74" s="11" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>1455</v>
+        <v>1437</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>1456</v>
+        <v>1438</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>1457</v>
+        <v>1439</v>
       </c>
       <c r="F74" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="75" ht="48" customHeight="1" spans="1:6">
       <c r="A75" s="11" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>1458</v>
+        <v>1440</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>1459</v>
+        <v>1441</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>1023</v>
+        <v>1005</v>
       </c>
       <c r="F75" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="76" ht="48" customHeight="1" spans="1:6">
       <c r="A76" s="11" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>1460</v>
+        <v>1442</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>1461</v>
+        <v>1443</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>1462</v>
+        <v>1444</v>
       </c>
       <c r="F76" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="77" ht="48" customHeight="1" spans="1:6">
       <c r="A77" s="11" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>1463</v>
+        <v>1445</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>1464</v>
+        <v>1446</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>1465</v>
+        <v>1447</v>
       </c>
       <c r="F77" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="78" ht="48" customHeight="1" spans="1:6">
       <c r="A78" s="11" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>1466</v>
+        <v>1448</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>1467</v>
+        <v>1449</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>1468</v>
+        <v>1450</v>
       </c>
       <c r="F78" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="79" ht="48" customHeight="1" spans="1:6">
       <c r="A79" s="11" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>1470</v>
+        <v>1452</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>1306</v>
+        <v>1288</v>
       </c>
       <c r="D79" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="F79" s="13" t="s">
-        <v>1307</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="80" ht="48" customHeight="1" spans="1:6">
       <c r="A80" s="11" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>1470</v>
+        <v>1452</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>967</v>
+        <v>949</v>
       </c>
       <c r="D80" s="11" t="s">
         <v>7</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>1471</v>
+        <v>1453</v>
       </c>
       <c r="F80" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="81" ht="48" customHeight="1" spans="1:6">
       <c r="A81" s="11" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>1470</v>
+        <v>1452</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>970</v>
+        <v>952</v>
       </c>
       <c r="D81" s="11" t="s">
         <v>8</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>1472</v>
+        <v>1454</v>
       </c>
       <c r="F81" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="82" ht="48" customHeight="1" spans="1:6">
       <c r="A82" s="11" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>1470</v>
+        <v>1452</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>983</v>
+        <v>965</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>984</v>
+        <v>966</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>1473</v>
+        <v>1455</v>
       </c>
       <c r="F82" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="83" ht="48" customHeight="1" spans="1:6">
       <c r="A83" s="11" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>1470</v>
+        <v>1452</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>1312</v>
+        <v>1294</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>1189</v>
+        <v>1171</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="F83" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="84" ht="48" customHeight="1" spans="1:6">
       <c r="A84" s="11" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>1470</v>
+        <v>1452</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>995</v>
+        <v>977</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>1314</v>
+        <v>1296</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>1472</v>
+        <v>1454</v>
       </c>
       <c r="F84" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="85" ht="48" customHeight="1" spans="1:6">
       <c r="A85" s="11" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>1470</v>
+        <v>1452</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>1413</v>
+        <v>1395</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>1414</v>
+        <v>1396</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>1415</v>
+        <v>1397</v>
       </c>
       <c r="F85" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="86" ht="48" customHeight="1" spans="1:6">
       <c r="A86" s="11" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>1470</v>
+        <v>1452</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>1316</v>
+        <v>1298</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>1317</v>
+        <v>1299</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>1474</v>
+        <v>1456</v>
       </c>
       <c r="F86" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="87" ht="48" customHeight="1" spans="1:6">
       <c r="A87" s="11" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>1470</v>
+        <v>1452</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>1319</v>
+        <v>1301</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>1320</v>
+        <v>1302</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>1475</v>
+        <v>1457</v>
       </c>
       <c r="F87" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="88" ht="48" customHeight="1" spans="1:6">
       <c r="A88" s="11" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>1470</v>
+        <v>1452</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>1322</v>
+        <v>1304</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>1323</v>
+        <v>1305</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>1476</v>
+        <v>1458</v>
       </c>
       <c r="F88" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="89" ht="48" customHeight="1" spans="1:6">
       <c r="A89" s="11" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>1470</v>
+        <v>1452</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>1324</v>
+        <v>1306</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>1325</v>
+        <v>1307</v>
       </c>
       <c r="E89" s="12" t="s">
-        <v>1477</v>
+        <v>1459</v>
       </c>
       <c r="F89" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="90" ht="48" customHeight="1" spans="1:6">
       <c r="A90" s="11" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>1470</v>
+        <v>1452</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>1420</v>
+        <v>1402</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>1421</v>
+        <v>1403</v>
       </c>
       <c r="E90" s="12" t="s">
-        <v>1422</v>
+        <v>1404</v>
       </c>
       <c r="F90" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="91" ht="48" customHeight="1" spans="1:6">
       <c r="A91" s="11" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>1470</v>
+        <v>1452</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>1423</v>
+        <v>1405</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>1424</v>
+        <v>1406</v>
       </c>
       <c r="E91" s="12" t="s">
-        <v>1478</v>
+        <v>1460</v>
       </c>
       <c r="F91" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="92" ht="48" customHeight="1" spans="1:6">
       <c r="A92" s="11" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>1470</v>
+        <v>1452</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>1426</v>
+        <v>1408</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>1427</v>
+        <v>1409</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>1479</v>
+        <v>1461</v>
       </c>
       <c r="F92" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="93" ht="48" customHeight="1" spans="1:6">
       <c r="A93" s="11" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>1470</v>
+        <v>1452</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>1330</v>
+        <v>1312</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>1331</v>
+        <v>1313</v>
       </c>
       <c r="E93" s="12" t="s">
-        <v>1480</v>
+        <v>1462</v>
       </c>
       <c r="F93" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="94" ht="48" customHeight="1" spans="1:6">
       <c r="A94" s="11" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>1470</v>
+        <v>1452</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>1333</v>
+        <v>1315</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>1334</v>
+        <v>1316</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>1481</v>
+        <v>1463</v>
       </c>
       <c r="F94" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="95" ht="48" customHeight="1" spans="1:6">
       <c r="A95" s="11" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>1470</v>
+        <v>1452</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>1336</v>
+        <v>1318</v>
       </c>
       <c r="D95" s="11" t="s">
-        <v>1337</v>
+        <v>1319</v>
       </c>
       <c r="E95" s="12" t="s">
-        <v>1023</v>
+        <v>1005</v>
       </c>
       <c r="F95" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="96" ht="48" customHeight="1" spans="1:6">
       <c r="A96" s="11" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>1470</v>
+        <v>1452</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>1342</v>
+        <v>1324</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>1343</v>
+        <v>1325</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>1482</v>
+        <v>1464</v>
       </c>
       <c r="F96" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="97" ht="48" customHeight="1" spans="1:6">
       <c r="A97" s="11" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>1470</v>
+        <v>1452</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>1433</v>
+        <v>1415</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>1434</v>
+        <v>1416</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>1483</v>
+        <v>1465</v>
       </c>
       <c r="F97" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="98" ht="48" customHeight="1" spans="1:6">
       <c r="A98" s="11" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>1470</v>
+        <v>1452</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>1436</v>
+        <v>1418</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>1437</v>
+        <v>1419</v>
       </c>
       <c r="E98" s="12" t="s">
-        <v>1023</v>
+        <v>1005</v>
       </c>
       <c r="F98" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="99" ht="48" customHeight="1" spans="1:6">
       <c r="A99" s="11" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>1470</v>
+        <v>1452</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>1348</v>
+        <v>1330</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>1349</v>
+        <v>1331</v>
       </c>
       <c r="E99" s="12" t="s">
-        <v>1484</v>
+        <v>1466</v>
       </c>
       <c r="F99" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="100" ht="48" customHeight="1" spans="1:6">
       <c r="A100" s="11" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>1470</v>
+        <v>1452</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>1439</v>
+        <v>1421</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>1440</v>
+        <v>1422</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>1485</v>
+        <v>1467</v>
       </c>
       <c r="F100" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="101" ht="48" customHeight="1" spans="1:6">
       <c r="A101" s="11" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>1470</v>
+        <v>1452</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>1442</v>
+        <v>1424</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>1443</v>
+        <v>1425</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>1023</v>
+        <v>1005</v>
       </c>
       <c r="F101" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="102" ht="48" customHeight="1" spans="1:6">
       <c r="A102" s="11" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>1470</v>
+        <v>1452</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>1444</v>
+        <v>1426</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>1445</v>
+        <v>1427</v>
       </c>
       <c r="E102" s="12" t="s">
-        <v>1486</v>
+        <v>1468</v>
       </c>
       <c r="F102" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="103" ht="48" customHeight="1" spans="1:6">
       <c r="A103" s="11" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B103" s="11" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C103" s="11" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D103" s="11" t="s">
+        <v>1430</v>
+      </c>
+      <c r="E103" s="12" t="s">
         <v>1469</v>
       </c>
-      <c r="B103" s="11" t="s">
-        <v>1470</v>
-      </c>
-      <c r="C103" s="11" t="s">
-        <v>1447</v>
-      </c>
-      <c r="D103" s="11" t="s">
-        <v>1448</v>
-      </c>
-      <c r="E103" s="12" t="s">
-        <v>1487</v>
-      </c>
       <c r="F103" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="104" ht="48" customHeight="1" spans="1:6">
       <c r="A104" s="11" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>1470</v>
+        <v>1452</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>1450</v>
+        <v>1432</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>1451</v>
+        <v>1433</v>
       </c>
       <c r="E104" s="12" t="s">
-        <v>1023</v>
+        <v>1005</v>
       </c>
       <c r="F104" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="105" ht="48" customHeight="1" spans="1:6">
       <c r="A105" s="11" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="B105" s="11" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C105" s="11" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D105" s="11" t="s">
+        <v>1435</v>
+      </c>
+      <c r="E105" s="12" t="s">
         <v>1470</v>
       </c>
-      <c r="C105" s="11" t="s">
-        <v>1452</v>
-      </c>
-      <c r="D105" s="11" t="s">
-        <v>1453</v>
-      </c>
-      <c r="E105" s="12" t="s">
-        <v>1488</v>
-      </c>
       <c r="F105" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="106" ht="48" customHeight="1" spans="1:6">
       <c r="A106" s="11" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>1470</v>
+        <v>1452</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>1455</v>
+        <v>1437</v>
       </c>
       <c r="D106" s="11" t="s">
-        <v>1456</v>
+        <v>1438</v>
       </c>
       <c r="E106" s="12" t="s">
-        <v>1489</v>
+        <v>1471</v>
       </c>
       <c r="F106" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="107" ht="48" customHeight="1" spans="1:6">
       <c r="A107" s="11" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>1470</v>
+        <v>1452</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>1458</v>
+        <v>1440</v>
       </c>
       <c r="D107" s="11" t="s">
-        <v>1459</v>
+        <v>1441</v>
       </c>
       <c r="E107" s="12" t="s">
-        <v>1023</v>
+        <v>1005</v>
       </c>
       <c r="F107" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="108" ht="48" customHeight="1" spans="1:6">
       <c r="A108" s="11" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>1470</v>
+        <v>1452</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>1460</v>
+        <v>1442</v>
       </c>
       <c r="D108" s="11" t="s">
-        <v>1461</v>
+        <v>1443</v>
       </c>
       <c r="E108" s="12" t="s">
-        <v>1490</v>
+        <v>1472</v>
       </c>
       <c r="F108" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="109" ht="48" customHeight="1" spans="1:6">
       <c r="A109" s="11" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>1470</v>
+        <v>1452</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>1463</v>
+        <v>1445</v>
       </c>
       <c r="D109" s="11" t="s">
-        <v>1464</v>
+        <v>1446</v>
       </c>
       <c r="E109" s="12" t="s">
-        <v>1491</v>
+        <v>1473</v>
       </c>
       <c r="F109" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="110" ht="48" customHeight="1" spans="1:6">
       <c r="A110" s="11" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>1470</v>
+        <v>1452</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>1466</v>
+        <v>1448</v>
       </c>
       <c r="D110" s="11" t="s">
-        <v>1467</v>
+        <v>1449</v>
       </c>
       <c r="E110" s="12" t="s">
-        <v>1023</v>
+        <v>1005</v>
       </c>
       <c r="F110" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="111" ht="48" customHeight="1" spans="1:6">
       <c r="A111" s="11" t="s">
-        <v>1492</v>
+        <v>1474</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>1493</v>
+        <v>1475</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>1306</v>
+        <v>1288</v>
       </c>
       <c r="D111" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E111" s="12" t="s">
-        <v>1492</v>
+        <v>1474</v>
       </c>
       <c r="F111" s="13" t="s">
-        <v>1307</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="112" ht="48" customHeight="1" spans="1:6">
       <c r="A112" s="11" t="s">
-        <v>1492</v>
+        <v>1474</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>1493</v>
+        <v>1475</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>967</v>
+        <v>949</v>
       </c>
       <c r="D112" s="11" t="s">
         <v>7</v>
       </c>
       <c r="E112" s="12" t="s">
-        <v>1494</v>
+        <v>1476</v>
       </c>
       <c r="F112" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="113" ht="48" customHeight="1" spans="1:6">
       <c r="A113" s="11" t="s">
-        <v>1492</v>
+        <v>1474</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>1493</v>
+        <v>1475</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>970</v>
+        <v>952</v>
       </c>
       <c r="D113" s="11" t="s">
         <v>8</v>
       </c>
       <c r="E113" s="12" t="s">
-        <v>1495</v>
+        <v>1477</v>
       </c>
       <c r="F113" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="114" ht="48" customHeight="1" spans="1:6">
       <c r="A114" s="11" t="s">
-        <v>1492</v>
+        <v>1474</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>1493</v>
+        <v>1475</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>983</v>
+        <v>965</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>984</v>
+        <v>966</v>
       </c>
       <c r="E114" s="12" t="s">
-        <v>1496</v>
+        <v>1478</v>
       </c>
       <c r="F114" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="115" ht="48" customHeight="1" spans="1:6">
       <c r="A115" s="11" t="s">
-        <v>1492</v>
+        <v>1474</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>1493</v>
+        <v>1475</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>1312</v>
+        <v>1294</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>1189</v>
+        <v>1171</v>
       </c>
       <c r="E115" s="12" t="s">
-        <v>1497</v>
+        <v>1479</v>
       </c>
       <c r="F115" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="116" ht="48" customHeight="1" spans="1:6">
       <c r="A116" s="11" t="s">
-        <v>1492</v>
+        <v>1474</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>1493</v>
+        <v>1475</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>995</v>
+        <v>977</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>1314</v>
+        <v>1296</v>
       </c>
       <c r="E116" s="12" t="s">
-        <v>1498</v>
+        <v>1480</v>
       </c>
       <c r="F116" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="117" ht="48" customHeight="1" spans="1:6">
       <c r="A117" s="11" t="s">
-        <v>1492</v>
+        <v>1474</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>1493</v>
+        <v>1475</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>1499</v>
+        <v>1481</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>1500</v>
+        <v>1482</v>
       </c>
       <c r="E117" s="12" t="s">
-        <v>1501</v>
+        <v>1483</v>
       </c>
       <c r="F117" s="13" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
   </sheetData>
@@ -20963,7 +20909,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>1502</v>
+        <v>1484</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -20972,7 +20918,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:5">
       <c r="A2" s="8" t="s">
-        <v>1503</v>
+        <v>1485</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -20988,274 +20934,274 @@
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:5">
       <c r="A4" s="10" t="s">
-        <v>930</v>
+        <v>912</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>931</v>
+        <v>913</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>932</v>
+        <v>914</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>933</v>
+        <v>915</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>934</v>
+        <v>916</v>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1" spans="1:5">
       <c r="A5" s="11" t="s">
-        <v>1504</v>
+        <v>1486</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>1505</v>
+        <v>1487</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>1506</v>
+        <v>1488</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1507</v>
+        <v>1489</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>1508</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1" spans="1:5">
       <c r="A6" s="11" t="s">
-        <v>1509</v>
+        <v>1491</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>1385</v>
+        <v>1367</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>1386</v>
+        <v>1368</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>1510</v>
+        <v>1492</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>1023</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1" spans="1:5">
       <c r="A7" s="11" t="s">
-        <v>1509</v>
+        <v>1491</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>1511</v>
+        <v>1493</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>1510</v>
+        <v>1492</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>1512</v>
+        <v>1494</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>1513</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1" spans="1:5">
       <c r="A8" s="11" t="s">
-        <v>1509</v>
+        <v>1491</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>1388</v>
+        <v>1370</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>1389</v>
+        <v>1371</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>1514</v>
+        <v>1496</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>1023</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1" spans="1:5">
       <c r="A9" s="11" t="s">
-        <v>1509</v>
+        <v>1491</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>1515</v>
+        <v>1497</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>1516</v>
+        <v>1498</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>1517</v>
+        <v>1499</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>1513</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1" spans="1:5">
       <c r="A10" s="11" t="s">
-        <v>1518</v>
+        <v>1500</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>1519</v>
+        <v>1501</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>1520</v>
+        <v>1502</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>1521</v>
+        <v>1503</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>1023</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1" spans="1:5">
       <c r="A11" s="11" t="s">
-        <v>1518</v>
+        <v>1500</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>1522</v>
+        <v>1504</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>1523</v>
+        <v>1505</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1524</v>
+        <v>1506</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>1023</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:5">
       <c r="A12" s="11" t="s">
-        <v>1525</v>
+        <v>1507</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>1526</v>
+        <v>1508</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>1527</v>
+        <v>1509</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>962</v>
+        <v>944</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>1023</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1" spans="1:5">
       <c r="A13" s="11" t="s">
-        <v>1525</v>
+        <v>1507</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>1528</v>
+        <v>1510</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>1529</v>
+        <v>1511</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>965</v>
+        <v>947</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>1023</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1" spans="1:5">
       <c r="A14" s="11" t="s">
-        <v>1525</v>
+        <v>1507</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>1530</v>
+        <v>1512</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>1531</v>
+        <v>1513</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>1023</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1" spans="1:5">
       <c r="A15" s="11" t="s">
-        <v>1525</v>
+        <v>1507</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>1532</v>
+        <v>1514</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>1533</v>
+        <v>1515</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>1023</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1" spans="1:5">
       <c r="A16" s="11" t="s">
-        <v>1534</v>
+        <v>1516</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>1535</v>
+        <v>1517</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>1536</v>
+        <v>1518</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>1537</v>
+        <v>1519</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>1023</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1" spans="1:5">
       <c r="A17" s="11" t="s">
-        <v>1399</v>
+        <v>1381</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>1538</v>
+        <v>1520</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>1539</v>
+        <v>1521</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>1540</v>
+        <v>1522</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>1023</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1" spans="1:5">
       <c r="A18" s="11" t="s">
-        <v>1399</v>
+        <v>1381</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>1541</v>
+        <v>1523</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>1542</v>
+        <v>1524</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>1543</v>
+        <v>1525</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>1023</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1" spans="1:5">
       <c r="A19" s="11" t="s">
-        <v>1399</v>
+        <v>1381</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>1544</v>
+        <v>1526</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>1545</v>
+        <v>1527</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>1378</v>
+        <v>1360</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>1023</v>
+        <v>1005</v>
       </c>
     </row>
   </sheetData>
@@ -21282,7 +21228,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>1546</v>
+        <v>1528</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -21294,7 +21240,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>1547</v>
+        <v>1529</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -21306,50 +21252,50 @@
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:8">
       <c r="A4" s="3" t="s">
-        <v>1548</v>
+        <v>1530</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1549</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:8">
       <c r="A5" s="4" t="s">
-        <v>1550</v>
+        <v>1532</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1551</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:8">
       <c r="A6" s="4" t="s">
-        <v>1552</v>
+        <v>1534</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1553</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:8">
       <c r="A7" s="4" t="s">
-        <v>1554</v>
+        <v>1536</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1555</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:8">
       <c r="A8" s="4" t="s">
-        <v>1556</v>
+        <v>1538</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1557</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:8">
       <c r="A9" s="4" t="s">
-        <v>1558</v>
+        <v>1540</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1559</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:8">
@@ -21357,10 +21303,10 @@
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:8">
       <c r="A11" s="3" t="s">
-        <v>1560</v>
+        <v>1542</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1561</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:8">
@@ -21368,7 +21314,7 @@
         <v>22</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1562</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:8">
@@ -21376,47 +21322,47 @@
         <v>23</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1563</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:8">
       <c r="A14" s="4" t="s">
-        <v>1564</v>
+        <v>1546</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1565</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:8">
       <c r="A15" s="4" t="s">
-        <v>1566</v>
+        <v>1548</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1567</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:8">
       <c r="A16" s="4" t="s">
-        <v>1568</v>
+        <v>1550</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1569</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>1570</v>
+        <v>1552</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1571</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:2">
       <c r="A18" s="4" t="s">
-        <v>1572</v>
+        <v>1554</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1573</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:2">
@@ -21424,10 +21370,10 @@
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:2">
       <c r="A20" s="3" t="s">
-        <v>1574</v>
+        <v>1556</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>1575</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:2">
@@ -21435,7 +21381,7 @@
         <v>1</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1576</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:2">
@@ -21443,7 +21389,7 @@
         <v>2</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1577</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:2">
@@ -21451,7 +21397,7 @@
         <v>3</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1578</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1" spans="1:2">
@@ -21459,7 +21405,7 @@
         <v>4</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1579</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:2">
@@ -21467,7 +21413,7 @@
         <v>5</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1580</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1" spans="1:2">
@@ -21475,7 +21421,7 @@
         <v>6</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>1581</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1" spans="1:2">
@@ -21483,7 +21429,7 @@
         <v>7</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>1582</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1" spans="1:2">
@@ -21491,7 +21437,7 @@
         <v>8</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>1583</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1" spans="1:2">
@@ -21499,7 +21445,7 @@
         <v>9</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>1584</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1" spans="1:2">
@@ -21507,7 +21453,7 @@
         <v>10</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1585</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1" spans="1:2">
@@ -21515,26 +21461,26 @@
     </row>
     <row r="32" ht="28" customHeight="1" spans="1:2">
       <c r="A32" s="3" t="s">
-        <v>1586</v>
+        <v>1568</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>1587</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1" spans="1:2">
       <c r="A33" s="4" t="s">
-        <v>1588</v>
+        <v>1570</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>1589</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1" spans="1:2">
       <c r="A34" s="7" t="s">
-        <v>1590</v>
+        <v>1572</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>1591</v>
+        <v>1573</v>
       </c>
     </row>
   </sheetData>

--- a/顶奢_整站资料批量编辑.xlsx
+++ b/顶奢_整站资料批量编辑.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2924" uniqueCount="1569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2944" uniqueCount="1572">
   <si>
     <t>顶奢 · 整站资料批量编辑</t>
   </si>
@@ -1783,13 +1783,13 @@
     <t>beijing</t>
   </si>
   <si>
-    <t>北京外围模特</t>
+    <t>北京外围小萝莉</t>
   </si>
   <si>
     <t>北京外围｜北京商务模特｜北京外围模特</t>
   </si>
   <si>
-    <t>浏览北京外围模特小萝莉白虎的独立资料、图片说明、内容介绍与相关推荐。</t>
+    <t>浏览北京外围模特小萝莉的独立资料、图片说明、内容介绍与相关推荐。</t>
   </si>
   <si>
     <t xml:space="preserve">🦋年龄: 18
@@ -1799,7 +1799,7 @@
 </t>
   </si>
   <si>
-    <t>萝莉白虎</t>
+    <t>萝莉｜白虎</t>
   </si>
   <si>
     <t xml:space="preserve">🦋无纹身 不🚬不🍷极品萝莉 白虎
@@ -1853,7 +1853,16 @@
     <t>北京外围模特萝莉白虎资料展示</t>
   </si>
   <si>
-    <t>北京外围 ｜北京外围女｜北京外围女联系方式</t>
+    <t>北京外围模特小萝莉资料视频</t>
+  </si>
+  <si>
+    <t>北京外围模特小萝莉相关资料视频</t>
+  </si>
+  <si>
+    <t>北京外围模特</t>
+  </si>
+  <si>
+    <t>北京外围｜北京外围女｜北京外围女联系方式</t>
   </si>
   <si>
     <t>浏览北京外围模特的独立资料、图片说明、内容介绍与相关推荐。</t>
@@ -9615,8 +9624,12 @@
       <c r="AF35" s="16" t="s">
         <v>603</v>
       </c>
-      <c r="AG35" s="4"/>
-      <c r="AH35" s="4"/>
+      <c r="AG35" s="16" t="s">
+        <v>604</v>
+      </c>
+      <c r="AH35" s="16" t="s">
+        <v>605</v>
+      </c>
       <c r="AI35" s="4"/>
       <c r="AJ35" s="17"/>
       <c r="AK35" s="4"/>
@@ -9638,16 +9651,16 @@
         <v>69</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>583</v>
+        <v>606</v>
       </c>
       <c r="F36" s="21" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="I36" s="4" t="s">
         <v>74</v>
@@ -9665,25 +9678,25 @@
         <v>591</v>
       </c>
       <c r="N36" s="20" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="O36" s="20" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="P36" s="20" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="Q36" s="20" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="R36" s="20" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="S36" s="22" t="s">
         <v>58</v>
       </c>
       <c r="T36" s="20" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="U36" s="4" t="s">
         <v>60</v>
@@ -9700,25 +9713,29 @@
       <c r="Y36" s="17"/>
       <c r="Z36" s="17"/>
       <c r="AA36" s="4" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="AB36" s="4" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="AC36" s="4" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="AD36" s="4" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="AE36" s="4" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="AF36" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="AG36" s="4"/>
-      <c r="AH36" s="4"/>
+        <v>621</v>
+      </c>
+      <c r="AG36" s="16" t="s">
+        <v>604</v>
+      </c>
+      <c r="AH36" s="16" t="s">
+        <v>605</v>
+      </c>
       <c r="AI36" s="4"/>
       <c r="AJ36" s="17"/>
       <c r="AK36" s="4"/>
@@ -9740,16 +9757,16 @@
         <v>88</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>583</v>
+        <v>606</v>
       </c>
       <c r="F37" s="21" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="I37" s="4" t="s">
         <v>93</v>
@@ -9767,25 +9784,25 @@
         <v>591</v>
       </c>
       <c r="N37" s="20" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="O37" s="20" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="P37" s="20" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="Q37" s="20" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="R37" s="20" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="S37" s="22" t="s">
         <v>58</v>
       </c>
       <c r="T37" s="20" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="U37" s="4" t="s">
         <v>60</v>
@@ -9802,25 +9819,29 @@
       <c r="Y37" s="17"/>
       <c r="Z37" s="17"/>
       <c r="AA37" s="4" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="AB37" s="4" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="AC37" s="4" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="AD37" s="4" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="AE37" s="4" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="AF37" s="4" t="s">
-        <v>632</v>
-      </c>
-      <c r="AG37" s="4"/>
-      <c r="AH37" s="4"/>
+        <v>635</v>
+      </c>
+      <c r="AG37" s="16" t="s">
+        <v>604</v>
+      </c>
+      <c r="AH37" s="16" t="s">
+        <v>605</v>
+      </c>
       <c r="AI37" s="4"/>
       <c r="AJ37" s="17"/>
       <c r="AK37" s="4"/>
@@ -9842,16 +9863,16 @@
         <v>107</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>583</v>
+        <v>606</v>
       </c>
       <c r="F38" s="21" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="I38" s="4" t="s">
         <v>112</v>
@@ -9869,25 +9890,25 @@
         <v>591</v>
       </c>
       <c r="N38" s="20" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="O38" s="20" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="P38" s="20" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="Q38" s="20" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="R38" s="20" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="S38" s="22" t="s">
         <v>58</v>
       </c>
       <c r="T38" s="20" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="U38" s="4" t="s">
         <v>60</v>
@@ -9904,25 +9925,29 @@
       <c r="Y38" s="17"/>
       <c r="Z38" s="17"/>
       <c r="AA38" s="4" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="AB38" s="4" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="AC38" s="4" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="AD38" s="4" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="AE38" s="4" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="AF38" s="4" t="s">
-        <v>646</v>
-      </c>
-      <c r="AG38" s="4"/>
-      <c r="AH38" s="4"/>
+        <v>649</v>
+      </c>
+      <c r="AG38" s="16" t="s">
+        <v>604</v>
+      </c>
+      <c r="AH38" s="16" t="s">
+        <v>605</v>
+      </c>
       <c r="AI38" s="4"/>
       <c r="AJ38" s="17"/>
       <c r="AK38" s="4"/>
@@ -9944,16 +9969,16 @@
         <v>126</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>583</v>
+        <v>606</v>
       </c>
       <c r="F39" s="21" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="I39" s="4" t="s">
         <v>131</v>
@@ -9971,25 +9996,25 @@
         <v>591</v>
       </c>
       <c r="N39" s="20" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="O39" s="20" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="P39" s="20" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="Q39" s="20" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="R39" s="20" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="S39" s="22" t="s">
         <v>58</v>
       </c>
       <c r="T39" s="20" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="U39" s="4" t="s">
         <v>60</v>
@@ -10006,25 +10031,29 @@
       <c r="Y39" s="17"/>
       <c r="Z39" s="17"/>
       <c r="AA39" s="4" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="AB39" s="4" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="AC39" s="4" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="AD39" s="4" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="AE39" s="4" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="AF39" s="4" t="s">
-        <v>660</v>
-      </c>
-      <c r="AG39" s="4"/>
-      <c r="AH39" s="4"/>
+        <v>663</v>
+      </c>
+      <c r="AG39" s="16" t="s">
+        <v>604</v>
+      </c>
+      <c r="AH39" s="16" t="s">
+        <v>605</v>
+      </c>
       <c r="AI39" s="4"/>
       <c r="AJ39" s="17"/>
       <c r="AK39" s="4"/>
@@ -10046,16 +10075,16 @@
         <v>145</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>583</v>
+        <v>606</v>
       </c>
       <c r="F40" s="21" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="I40" s="4" t="s">
         <v>48</v>
@@ -10073,25 +10102,25 @@
         <v>591</v>
       </c>
       <c r="N40" s="20" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="O40" s="20" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="P40" s="20" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="Q40" s="20" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="R40" s="20" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="S40" s="22" t="s">
         <v>58</v>
       </c>
       <c r="T40" s="20" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="U40" s="4" t="s">
         <v>60</v>
@@ -10108,25 +10137,29 @@
       <c r="Y40" s="17"/>
       <c r="Z40" s="17"/>
       <c r="AA40" s="4" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="AB40" s="4" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="AC40" s="4" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="AD40" s="4" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="AE40" s="4" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="AF40" s="4" t="s">
-        <v>674</v>
-      </c>
-      <c r="AG40" s="4"/>
-      <c r="AH40" s="4"/>
+        <v>677</v>
+      </c>
+      <c r="AG40" s="16" t="s">
+        <v>604</v>
+      </c>
+      <c r="AH40" s="16" t="s">
+        <v>605</v>
+      </c>
       <c r="AI40" s="4"/>
       <c r="AJ40" s="17"/>
       <c r="AK40" s="4"/>
@@ -10148,16 +10181,16 @@
         <v>163</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>583</v>
+        <v>606</v>
       </c>
       <c r="F41" s="21" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>74</v>
@@ -10175,25 +10208,25 @@
         <v>591</v>
       </c>
       <c r="N41" s="20" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="O41" s="20" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="P41" s="20" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="Q41" s="20" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="R41" s="20" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="S41" s="22" t="s">
         <v>58</v>
       </c>
       <c r="T41" s="20" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="U41" s="4" t="s">
         <v>60</v>
@@ -10210,25 +10243,29 @@
       <c r="Y41" s="17"/>
       <c r="Z41" s="17"/>
       <c r="AA41" s="4" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="AB41" s="4" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="AC41" s="4" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="AD41" s="4" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="AE41" s="4" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="AF41" s="4" t="s">
-        <v>688</v>
-      </c>
-      <c r="AG41" s="4"/>
-      <c r="AH41" s="4"/>
+        <v>691</v>
+      </c>
+      <c r="AG41" s="16" t="s">
+        <v>604</v>
+      </c>
+      <c r="AH41" s="16" t="s">
+        <v>605</v>
+      </c>
       <c r="AI41" s="4"/>
       <c r="AJ41" s="17"/>
       <c r="AK41" s="4"/>
@@ -10250,16 +10287,16 @@
         <v>181</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>583</v>
+        <v>606</v>
       </c>
       <c r="F42" s="21" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="I42" s="4" t="s">
         <v>93</v>
@@ -10277,25 +10314,25 @@
         <v>591</v>
       </c>
       <c r="N42" s="20" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="O42" s="20" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="P42" s="20" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="Q42" s="20" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="R42" s="20" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="S42" s="22" t="s">
         <v>58</v>
       </c>
       <c r="T42" s="20" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="U42" s="4" t="s">
         <v>60</v>
@@ -10312,25 +10349,29 @@
       <c r="Y42" s="17"/>
       <c r="Z42" s="17"/>
       <c r="AA42" s="4" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="AB42" s="4" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="AC42" s="4" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="AD42" s="4" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="AE42" s="4" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="AF42" s="4" t="s">
-        <v>702</v>
-      </c>
-      <c r="AG42" s="4"/>
-      <c r="AH42" s="4"/>
+        <v>705</v>
+      </c>
+      <c r="AG42" s="16" t="s">
+        <v>604</v>
+      </c>
+      <c r="AH42" s="16" t="s">
+        <v>605</v>
+      </c>
       <c r="AI42" s="4"/>
       <c r="AJ42" s="17"/>
       <c r="AK42" s="4"/>
@@ -10352,16 +10393,16 @@
         <v>199</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>583</v>
+        <v>606</v>
       </c>
       <c r="F43" s="21" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="I43" s="4" t="s">
         <v>112</v>
@@ -10379,25 +10420,25 @@
         <v>591</v>
       </c>
       <c r="N43" s="20" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="O43" s="20" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="P43" s="20" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="Q43" s="20" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="R43" s="20" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="S43" s="22" t="s">
         <v>58</v>
       </c>
       <c r="T43" s="20" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="U43" s="4" t="s">
         <v>60</v>
@@ -10414,25 +10455,29 @@
       <c r="Y43" s="17"/>
       <c r="Z43" s="17"/>
       <c r="AA43" s="4" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="AB43" s="4" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="AC43" s="4" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="AD43" s="4" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="AE43" s="4" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="AF43" s="4" t="s">
-        <v>716</v>
-      </c>
-      <c r="AG43" s="4"/>
-      <c r="AH43" s="4"/>
+        <v>719</v>
+      </c>
+      <c r="AG43" s="16" t="s">
+        <v>604</v>
+      </c>
+      <c r="AH43" s="16" t="s">
+        <v>605</v>
+      </c>
       <c r="AI43" s="4"/>
       <c r="AJ43" s="17"/>
       <c r="AK43" s="4"/>
@@ -10454,16 +10499,16 @@
         <v>217</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>583</v>
+        <v>606</v>
       </c>
       <c r="F44" s="21" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="I44" s="4" t="s">
         <v>131</v>
@@ -10481,25 +10526,25 @@
         <v>591</v>
       </c>
       <c r="N44" s="20" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="O44" s="20" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="P44" s="20" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="Q44" s="20" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="R44" s="20" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="S44" s="22" t="s">
         <v>58</v>
       </c>
       <c r="T44" s="20" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="U44" s="4" t="s">
         <v>60</v>
@@ -10516,25 +10561,29 @@
       <c r="Y44" s="17"/>
       <c r="Z44" s="17"/>
       <c r="AA44" s="4" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="AB44" s="4" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="AC44" s="4" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="AD44" s="4" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="AE44" s="4" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="AF44" s="4" t="s">
-        <v>730</v>
-      </c>
-      <c r="AG44" s="4"/>
-      <c r="AH44" s="4"/>
+        <v>733</v>
+      </c>
+      <c r="AG44" s="16" t="s">
+        <v>604</v>
+      </c>
+      <c r="AH44" s="16" t="s">
+        <v>605</v>
+      </c>
       <c r="AI44" s="4"/>
       <c r="AJ44" s="17"/>
       <c r="AK44" s="4"/>
@@ -10544,10 +10593,10 @@
     </row>
     <row r="45" ht="42" customHeight="1" spans="1:38">
       <c r="A45" s="19" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C45" s="20" t="s">
         <v>42</v>
@@ -10556,16 +10605,16 @@
         <v>43</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="F45" s="21" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="I45" s="4" t="s">
         <v>48</v>
@@ -10574,34 +10623,34 @@
         <v>49</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="L45" s="4" t="s">
         <v>241</v>
       </c>
       <c r="M45" s="4" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="N45" s="20" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="O45" s="20" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="P45" s="20" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="Q45" s="20" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="R45" s="20" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="S45" s="19" t="s">
         <v>58</v>
       </c>
       <c r="T45" s="20" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="U45" s="4" t="s">
         <v>60</v>
@@ -10618,22 +10667,22 @@
       <c r="Y45" s="17"/>
       <c r="Z45" s="17"/>
       <c r="AA45" s="4" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="AB45" s="4" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="AC45" s="4" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="AD45" s="4" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="AE45" s="4" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="AF45" s="4" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="AG45" s="4"/>
       <c r="AH45" s="4"/>
@@ -10646,10 +10695,10 @@
     </row>
     <row r="46" ht="42" customHeight="1" spans="1:38">
       <c r="A46" s="19" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C46" s="20" t="s">
         <v>68</v>
@@ -10658,16 +10707,16 @@
         <v>69</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="F46" s="21" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="I46" s="4" t="s">
         <v>74</v>
@@ -10676,34 +10725,34 @@
         <v>49</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="L46" s="4" t="s">
         <v>241</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="N46" s="20" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="O46" s="20" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="P46" s="20" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="Q46" s="20" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="R46" s="20" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="S46" s="19" t="s">
         <v>58</v>
       </c>
       <c r="T46" s="20" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="U46" s="4" t="s">
         <v>60</v>
@@ -10720,22 +10769,22 @@
       <c r="Y46" s="17"/>
       <c r="Z46" s="17"/>
       <c r="AA46" s="4" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="AB46" s="4" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="AC46" s="4" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="AD46" s="4" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="AE46" s="4" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="AF46" s="4" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="AG46" s="4"/>
       <c r="AH46" s="4"/>
@@ -10748,10 +10797,10 @@
     </row>
     <row r="47" ht="42" customHeight="1" spans="1:38">
       <c r="A47" s="19" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C47" s="20" t="s">
         <v>87</v>
@@ -10760,16 +10809,16 @@
         <v>88</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="F47" s="21" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I47" s="4" t="s">
         <v>93</v>
@@ -10778,34 +10827,34 @@
         <v>49</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="L47" s="4" t="s">
         <v>241</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="N47" s="20" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="O47" s="20" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="P47" s="20" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="Q47" s="20" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="R47" s="20" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="S47" s="19" t="s">
         <v>58</v>
       </c>
       <c r="T47" s="20" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="U47" s="4" t="s">
         <v>60</v>
@@ -10822,22 +10871,22 @@
       <c r="Y47" s="17"/>
       <c r="Z47" s="17"/>
       <c r="AA47" s="4" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="AB47" s="4" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="AC47" s="4" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="AD47" s="4" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="AE47" s="4" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="AF47" s="4" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="AG47" s="4"/>
       <c r="AH47" s="4"/>
@@ -10850,10 +10899,10 @@
     </row>
     <row r="48" ht="42" customHeight="1" spans="1:38">
       <c r="A48" s="19" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C48" s="20" t="s">
         <v>106</v>
@@ -10862,16 +10911,16 @@
         <v>107</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="F48" s="21" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>112</v>
@@ -10880,34 +10929,34 @@
         <v>49</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="L48" s="4" t="s">
         <v>241</v>
       </c>
       <c r="M48" s="4" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="N48" s="20" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="O48" s="20" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="P48" s="20" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="Q48" s="20" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="R48" s="20" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="S48" s="19" t="s">
         <v>58</v>
       </c>
       <c r="T48" s="20" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="U48" s="4" t="s">
         <v>60</v>
@@ -10924,22 +10973,22 @@
       <c r="Y48" s="17"/>
       <c r="Z48" s="17"/>
       <c r="AA48" s="4" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="AB48" s="4" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="AC48" s="4" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="AD48" s="4" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="AE48" s="4" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="AF48" s="4" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="AG48" s="4"/>
       <c r="AH48" s="4"/>
@@ -10952,10 +11001,10 @@
     </row>
     <row r="49" ht="42" customHeight="1" spans="1:38">
       <c r="A49" s="19" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C49" s="20" t="s">
         <v>125</v>
@@ -10964,16 +11013,16 @@
         <v>126</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="F49" s="21" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="I49" s="4" t="s">
         <v>131</v>
@@ -10982,34 +11031,34 @@
         <v>49</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="L49" s="4" t="s">
         <v>241</v>
       </c>
       <c r="M49" s="4" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="N49" s="20" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="O49" s="20" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="P49" s="20" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="Q49" s="20" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="R49" s="20" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="S49" s="19" t="s">
         <v>58</v>
       </c>
       <c r="T49" s="20" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="U49" s="4" t="s">
         <v>60</v>
@@ -11026,22 +11075,22 @@
       <c r="Y49" s="17"/>
       <c r="Z49" s="17"/>
       <c r="AA49" s="4" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="AB49" s="4" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="AC49" s="4" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="AD49" s="4" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="AE49" s="4" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="AF49" s="4" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="AG49" s="4"/>
       <c r="AH49" s="4"/>
@@ -11054,10 +11103,10 @@
     </row>
     <row r="50" ht="42" customHeight="1" spans="1:38">
       <c r="A50" s="19" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C50" s="20" t="s">
         <v>144</v>
@@ -11066,16 +11115,16 @@
         <v>145</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="F50" s="21" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="I50" s="4" t="s">
         <v>48</v>
@@ -11084,34 +11133,34 @@
         <v>49</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="L50" s="4" t="s">
         <v>241</v>
       </c>
       <c r="M50" s="4" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="N50" s="20" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="O50" s="20" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="P50" s="20" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="Q50" s="20" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="R50" s="20" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="S50" s="19" t="s">
         <v>58</v>
       </c>
       <c r="T50" s="20" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="U50" s="4" t="s">
         <v>60</v>
@@ -11128,22 +11177,22 @@
       <c r="Y50" s="17"/>
       <c r="Z50" s="17"/>
       <c r="AA50" s="4" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="AB50" s="4" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="AC50" s="4" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="AD50" s="4" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="AE50" s="4" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="AF50" s="4" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="AG50" s="4"/>
       <c r="AH50" s="4"/>
@@ -11156,10 +11205,10 @@
     </row>
     <row r="51" ht="42" customHeight="1" spans="1:38">
       <c r="A51" s="19" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C51" s="20" t="s">
         <v>162</v>
@@ -11168,16 +11217,16 @@
         <v>163</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="F51" s="21" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="I51" s="4" t="s">
         <v>74</v>
@@ -11186,34 +11235,34 @@
         <v>49</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="L51" s="4" t="s">
         <v>241</v>
       </c>
       <c r="M51" s="4" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="N51" s="20" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="O51" s="20" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="P51" s="20" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="Q51" s="20" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="R51" s="20" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="S51" s="19" t="s">
         <v>58</v>
       </c>
       <c r="T51" s="20" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="U51" s="4" t="s">
         <v>60</v>
@@ -11230,22 +11279,22 @@
       <c r="Y51" s="17"/>
       <c r="Z51" s="17"/>
       <c r="AA51" s="4" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="AB51" s="4" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="AC51" s="4" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="AD51" s="4" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="AE51" s="4" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="AF51" s="4" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="AG51" s="4"/>
       <c r="AH51" s="4"/>
@@ -11258,10 +11307,10 @@
     </row>
     <row r="52" ht="42" customHeight="1" spans="1:38">
       <c r="A52" s="19" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C52" s="20" t="s">
         <v>180</v>
@@ -11270,16 +11319,16 @@
         <v>181</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="F52" s="21" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="I52" s="4" t="s">
         <v>93</v>
@@ -11288,34 +11337,34 @@
         <v>49</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="L52" s="4" t="s">
         <v>241</v>
       </c>
       <c r="M52" s="4" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="N52" s="20" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="O52" s="20" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="P52" s="20" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="Q52" s="20" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="R52" s="20" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="S52" s="19" t="s">
         <v>58</v>
       </c>
       <c r="T52" s="20" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="U52" s="4" t="s">
         <v>60</v>
@@ -11332,22 +11381,22 @@
       <c r="Y52" s="17"/>
       <c r="Z52" s="17"/>
       <c r="AA52" s="4" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="AB52" s="4" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="AC52" s="4" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="AD52" s="4" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="AE52" s="4" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="AF52" s="4" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="AG52" s="4"/>
       <c r="AH52" s="4"/>
@@ -11360,10 +11409,10 @@
     </row>
     <row r="53" ht="42" customHeight="1" spans="1:38">
       <c r="A53" s="19" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="B53" s="20" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C53" s="20" t="s">
         <v>198</v>
@@ -11372,16 +11421,16 @@
         <v>199</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="F53" s="21" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="I53" s="4" t="s">
         <v>112</v>
@@ -11390,34 +11439,34 @@
         <v>49</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="L53" s="4" t="s">
         <v>241</v>
       </c>
       <c r="M53" s="4" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="N53" s="20" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="O53" s="20" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="P53" s="20" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="Q53" s="20" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="R53" s="20" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="S53" s="19" t="s">
         <v>58</v>
       </c>
       <c r="T53" s="20" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="U53" s="4" t="s">
         <v>60</v>
@@ -11434,22 +11483,22 @@
       <c r="Y53" s="17"/>
       <c r="Z53" s="17"/>
       <c r="AA53" s="4" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="AB53" s="4" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="AC53" s="4" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="AD53" s="4" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="AE53" s="4" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="AF53" s="4" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="AG53" s="4"/>
       <c r="AH53" s="4"/>
@@ -11462,10 +11511,10 @@
     </row>
     <row r="54" ht="42" customHeight="1" spans="1:38">
       <c r="A54" s="19" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C54" s="20" t="s">
         <v>216</v>
@@ -11474,16 +11523,16 @@
         <v>217</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="F54" s="21" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="I54" s="4" t="s">
         <v>131</v>
@@ -11492,34 +11541,34 @@
         <v>49</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="L54" s="4" t="s">
         <v>241</v>
       </c>
       <c r="M54" s="4" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="N54" s="20" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="O54" s="20" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="P54" s="20" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="Q54" s="20" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="R54" s="20" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="S54" s="19" t="s">
         <v>58</v>
       </c>
       <c r="T54" s="20" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="U54" s="4" t="s">
         <v>60</v>
@@ -11536,22 +11585,22 @@
       <c r="Y54" s="17"/>
       <c r="Z54" s="17"/>
       <c r="AA54" s="4" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="AB54" s="4" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="AC54" s="4" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="AD54" s="4" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="AE54" s="4" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="AF54" s="4" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="AG54" s="4"/>
       <c r="AH54" s="4"/>
@@ -15571,7 +15620,7 @@
     <dataValidation type="list" sqref="I5:I200">
       <formula1>"都会,雅致,轻奢,清新,典雅,精选,高定,现代"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="S5:S34 S35:S44 S45:S200">
+    <dataValidation type="list" sqref="S5:S200">
       <formula1>"否,是"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="U5:U154">
@@ -15613,7 +15662,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -15622,7 +15671,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:5">
       <c r="A2" s="8" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -15638,1141 +15687,1141 @@
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:5">
       <c r="A4" s="10" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1" spans="1:5">
       <c r="A5" s="11" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1" spans="1:5">
       <c r="A6" s="11" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1" spans="1:5">
       <c r="A7" s="11" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1" spans="1:5">
       <c r="A8" s="11" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1" spans="1:5">
       <c r="A9" s="11" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1" spans="1:5">
       <c r="A10" s="11" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1" spans="1:5">
       <c r="A11" s="11" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:5">
       <c r="A12" s="11" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1" spans="1:5">
       <c r="A13" s="11" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>7</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1" spans="1:5">
       <c r="A14" s="11" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1" spans="1:5">
       <c r="A15" s="11" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1" spans="1:5">
       <c r="A16" s="11" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1" spans="1:5">
       <c r="A17" s="11" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1" spans="1:5">
       <c r="A18" s="11" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1" spans="1:5">
       <c r="A19" s="11" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1" spans="1:5">
       <c r="A20" s="11" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1" spans="1:5">
       <c r="A21" s="11" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
     </row>
     <row r="22" ht="42" customHeight="1" spans="1:5">
       <c r="A22" s="11" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="D22" s="12" t="s">
+        <v>985</v>
+      </c>
+      <c r="E22" s="13" t="s">
         <v>982</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>979</v>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1" spans="1:5">
       <c r="A23" s="11" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
     </row>
     <row r="24" ht="42" customHeight="1" spans="1:5">
       <c r="A24" s="11" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
     </row>
     <row r="25" ht="42" customHeight="1" spans="1:5">
       <c r="A25" s="11" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
     </row>
     <row r="26" ht="42" customHeight="1" spans="1:5">
       <c r="A26" s="11" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="27" ht="42" customHeight="1" spans="1:5">
       <c r="A27" s="11" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="D27" s="12" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E27" s="13" t="s">
         <v>1002</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>999</v>
       </c>
     </row>
     <row r="28" ht="42" customHeight="1" spans="1:5">
       <c r="A28" s="11" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="29" ht="42" customHeight="1" spans="1:5">
       <c r="A29" s="11" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="30" ht="42" customHeight="1" spans="1:5">
       <c r="A30" s="11" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="31" ht="42" customHeight="1" spans="1:5">
       <c r="A31" s="11" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="32" ht="42" customHeight="1" spans="1:5">
       <c r="A32" s="11" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="33" ht="42" customHeight="1" spans="1:5">
       <c r="A33" s="11" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="B33" s="11" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E33" s="13" t="s">
         <v>1021</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>1022</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>1023</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>1018</v>
       </c>
     </row>
     <row r="34" ht="42" customHeight="1" spans="1:5">
       <c r="A34" s="11" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="35" ht="42" customHeight="1" spans="1:5">
       <c r="A35" s="11" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="36" ht="42" customHeight="1" spans="1:5">
       <c r="A36" s="11" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="37" ht="42" customHeight="1" spans="1:5">
       <c r="A37" s="11" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="38" ht="42" customHeight="1" spans="1:5">
       <c r="A38" s="11" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="39" ht="42" customHeight="1" spans="1:5">
       <c r="A39" s="11" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="40" ht="42" customHeight="1" spans="1:5">
       <c r="A40" s="11" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
     </row>
     <row r="41" ht="42" customHeight="1" spans="1:5">
       <c r="A41" s="11" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="42" ht="42" customHeight="1" spans="1:5">
       <c r="A42" s="11" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="43" ht="42" customHeight="1" spans="1:5">
       <c r="A43" s="11" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="44" ht="42" customHeight="1" spans="1:5">
       <c r="A44" s="11" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="45" ht="42" customHeight="1" spans="1:5">
       <c r="A45" s="11" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="46" ht="42" customHeight="1" spans="1:5">
       <c r="A46" s="11" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="47" ht="42" customHeight="1" spans="1:5">
       <c r="A47" s="11" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="48" ht="42" customHeight="1" spans="1:5">
       <c r="A48" s="11" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="49" ht="42" customHeight="1" spans="1:5">
       <c r="A49" s="11" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="50" ht="42" customHeight="1" spans="1:5">
       <c r="A50" s="11" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="51" ht="42" customHeight="1" spans="1:5">
       <c r="A51" s="11" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="52" ht="42" customHeight="1" spans="1:5">
       <c r="A52" s="11" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="53" ht="42" customHeight="1" spans="1:5">
       <c r="A53" s="11" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="54" ht="42" customHeight="1" spans="1:5">
       <c r="A54" s="11" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="55" ht="42" customHeight="1" spans="1:5">
       <c r="A55" s="11" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="D55" s="18">
         <v>8</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="56" ht="42" customHeight="1" spans="1:5">
       <c r="A56" s="11" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
     </row>
     <row r="57" ht="42" customHeight="1" spans="1:5">
       <c r="A57" s="11" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="58" ht="42" customHeight="1" spans="1:5">
       <c r="A58" s="11" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="59" ht="42" customHeight="1" spans="1:5">
       <c r="A59" s="11" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="60" ht="42" customHeight="1" spans="1:5">
       <c r="A60" s="11" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="61" ht="42" customHeight="1" spans="1:5">
       <c r="A61" s="11" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="62" ht="42" customHeight="1" spans="1:5">
       <c r="A62" s="11" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="63" ht="42" customHeight="1" spans="1:5">
       <c r="A63" s="11" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>1132</v>
+        <v>1135</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>1133</v>
+        <v>1136</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="64" ht="42" customHeight="1" spans="1:5">
       <c r="A64" s="11" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="65" ht="42" customHeight="1" spans="1:5">
       <c r="A65" s="11" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="66" ht="42" customHeight="1" spans="1:5">
       <c r="A66" s="11" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>1144</v>
+        <v>1147</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>1145</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="67" ht="42" customHeight="1" spans="1:5">
       <c r="A67" s="11" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>1146</v>
+        <v>1149</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="68" ht="42" customHeight="1" spans="1:5">
       <c r="A68" s="11" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="69" ht="42" customHeight="1" spans="1:5">
       <c r="A69" s="11" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="70" ht="42" customHeight="1" spans="1:5">
       <c r="A70" s="11" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
     </row>
   </sheetData>
@@ -16831,7 +16880,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:40">
       <c r="A1" s="14" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
@@ -16875,7 +16924,7 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:40">
       <c r="A2" s="15" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -16957,13 +17006,13 @@
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:40">
       <c r="A4" s="3" t="s">
-        <v>1162</v>
+        <v>1165</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1164</v>
+        <v>1167</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>7</v>
@@ -16972,22 +17021,22 @@
         <v>8</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1165</v>
+        <v>1168</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>12</v>
@@ -16996,73 +17045,73 @@
         <v>13</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>1171</v>
+        <v>1174</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>1174</v>
+        <v>1177</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>1175</v>
+        <v>1178</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>1176</v>
+        <v>1179</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>1178</v>
+        <v>1181</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>1179</v>
+        <v>1182</v>
       </c>
       <c r="Y4" s="3" t="s">
-        <v>1180</v>
+        <v>1183</v>
       </c>
       <c r="Z4" s="3" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="AA4" s="3" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
       <c r="AB4" s="3" t="s">
-        <v>1183</v>
+        <v>1186</v>
       </c>
       <c r="AC4" s="3" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="AD4" s="3" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
       <c r="AE4" s="3" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="AF4" s="3" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="AG4" s="3" t="s">
-        <v>1133</v>
+        <v>1136</v>
       </c>
       <c r="AH4" s="3" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="AI4" s="3" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="AJ4" s="3" t="s">
-        <v>1188</v>
+        <v>1191</v>
       </c>
       <c r="AK4" s="3" t="s">
         <v>22</v>
@@ -17085,112 +17134,112 @@
         <v>41</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>1190</v>
+        <v>1193</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>1191</v>
+        <v>1194</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>1192</v>
+        <v>1195</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>1193</v>
+        <v>1196</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>1194</v>
+        <v>1197</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>1196</v>
+        <v>1199</v>
       </c>
       <c r="K5" s="16" t="s">
-        <v>1197</v>
+        <v>1200</v>
       </c>
       <c r="L5" s="16" t="s">
-        <v>1198</v>
+        <v>1201</v>
       </c>
       <c r="M5" s="16" t="s">
-        <v>1199</v>
+        <v>1202</v>
       </c>
       <c r="N5" s="16" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="O5" s="16" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="P5" s="16" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="Q5" s="16" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
       <c r="R5" s="16" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
       <c r="S5" s="16" t="s">
-        <v>1205</v>
+        <v>1208</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>1207</v>
+        <v>1210</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="X5" s="16" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="Y5" s="4" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="Z5" s="4" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="AA5" s="4" t="s">
-        <v>1212</v>
+        <v>1215</v>
       </c>
       <c r="AB5" s="16" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
       <c r="AC5" s="16" t="s">
-        <v>1214</v>
+        <v>1217</v>
       </c>
       <c r="AD5" s="16" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="AE5" s="16" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="AF5" s="16" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
       <c r="AG5" s="16" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="AH5" s="16" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
       <c r="AI5" s="4" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="AJ5" s="4" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="AK5" s="4" t="s">
         <v>60</v>
       </c>
       <c r="AL5" s="4" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="AM5" s="4">
         <v>1</v>
@@ -17207,112 +17256,112 @@
         <v>235</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>1227</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>1228</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>1195</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>1229</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>1230</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>1199</v>
+      </c>
+      <c r="K6" s="16" t="s">
+        <v>1231</v>
+      </c>
+      <c r="L6" s="16" t="s">
+        <v>1232</v>
+      </c>
+      <c r="M6" s="16" t="s">
+        <v>1233</v>
+      </c>
+      <c r="N6" s="16" t="s">
+        <v>1203</v>
+      </c>
+      <c r="O6" s="16" t="s">
+        <v>1204</v>
+      </c>
+      <c r="P6" s="16" t="s">
+        <v>1205</v>
+      </c>
+      <c r="Q6" s="16" t="s">
+        <v>1234</v>
+      </c>
+      <c r="R6" s="16" t="s">
+        <v>1207</v>
+      </c>
+      <c r="S6" s="16" t="s">
+        <v>1235</v>
+      </c>
+      <c r="T6" s="4" t="s">
+        <v>1209</v>
+      </c>
+      <c r="U6" s="4" t="s">
+        <v>1236</v>
+      </c>
+      <c r="V6" s="4" t="s">
+        <v>1211</v>
+      </c>
+      <c r="W6" s="4" t="s">
+        <v>1212</v>
+      </c>
+      <c r="X6" s="16" t="s">
+        <v>1237</v>
+      </c>
+      <c r="Y6" s="4" t="s">
+        <v>1214</v>
+      </c>
+      <c r="Z6" s="4" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AA6" s="4" t="s">
+        <v>1238</v>
+      </c>
+      <c r="AB6" s="16" t="s">
+        <v>1216</v>
+      </c>
+      <c r="AC6" s="16" t="s">
+        <v>1239</v>
+      </c>
+      <c r="AD6" s="16" t="s">
+        <v>1218</v>
+      </c>
+      <c r="AE6" s="16" t="s">
+        <v>1219</v>
+      </c>
+      <c r="AF6" s="16" t="s">
+        <v>1220</v>
+      </c>
+      <c r="AG6" s="16" t="s">
+        <v>1221</v>
+      </c>
+      <c r="AH6" s="4" t="s">
+        <v>1222</v>
+      </c>
+      <c r="AI6" s="4" t="s">
         <v>1223</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="AJ6" s="4" t="s">
         <v>1224</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>1225</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>1192</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>1226</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>1227</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>1195</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>1196</v>
-      </c>
-      <c r="K6" s="16" t="s">
-        <v>1228</v>
-      </c>
-      <c r="L6" s="16" t="s">
-        <v>1229</v>
-      </c>
-      <c r="M6" s="16" t="s">
-        <v>1230</v>
-      </c>
-      <c r="N6" s="16" t="s">
-        <v>1200</v>
-      </c>
-      <c r="O6" s="16" t="s">
-        <v>1201</v>
-      </c>
-      <c r="P6" s="16" t="s">
-        <v>1202</v>
-      </c>
-      <c r="Q6" s="16" t="s">
-        <v>1231</v>
-      </c>
-      <c r="R6" s="16" t="s">
-        <v>1204</v>
-      </c>
-      <c r="S6" s="16" t="s">
-        <v>1232</v>
-      </c>
-      <c r="T6" s="4" t="s">
-        <v>1206</v>
-      </c>
-      <c r="U6" s="4" t="s">
-        <v>1233</v>
-      </c>
-      <c r="V6" s="4" t="s">
-        <v>1208</v>
-      </c>
-      <c r="W6" s="4" t="s">
-        <v>1209</v>
-      </c>
-      <c r="X6" s="16" t="s">
-        <v>1234</v>
-      </c>
-      <c r="Y6" s="4" t="s">
-        <v>1211</v>
-      </c>
-      <c r="Z6" s="4" t="s">
-        <v>1109</v>
-      </c>
-      <c r="AA6" s="4" t="s">
-        <v>1235</v>
-      </c>
-      <c r="AB6" s="16" t="s">
-        <v>1213</v>
-      </c>
-      <c r="AC6" s="16" t="s">
-        <v>1236</v>
-      </c>
-      <c r="AD6" s="16" t="s">
-        <v>1215</v>
-      </c>
-      <c r="AE6" s="16" t="s">
-        <v>1216</v>
-      </c>
-      <c r="AF6" s="16" t="s">
-        <v>1217</v>
-      </c>
-      <c r="AG6" s="16" t="s">
-        <v>1218</v>
-      </c>
-      <c r="AH6" s="4" t="s">
-        <v>1219</v>
-      </c>
-      <c r="AI6" s="4" t="s">
-        <v>1220</v>
-      </c>
-      <c r="AJ6" s="4" t="s">
-        <v>1221</v>
       </c>
       <c r="AK6" s="4" t="s">
         <v>60</v>
       </c>
       <c r="AL6" s="4" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="AM6" s="4">
         <v>2</v>
@@ -17329,112 +17378,112 @@
         <v>409</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1237</v>
+        <v>1240</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>1238</v>
+        <v>1241</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>1239</v>
+        <v>1242</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>1192</v>
+        <v>1195</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>1240</v>
+        <v>1243</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>1241</v>
+        <v>1244</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>1196</v>
+        <v>1199</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
       <c r="L7" s="16" t="s">
-        <v>1243</v>
+        <v>1246</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="N7" s="16" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="O7" s="16" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="P7" s="16" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="Q7" s="16" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="R7" s="16" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
       <c r="S7" s="16" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="V7" s="4" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
       <c r="W7" s="4" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="X7" s="16" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="Y7" s="4" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="Z7" s="4" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="AA7" s="4" t="s">
-        <v>1250</v>
+        <v>1253</v>
       </c>
       <c r="AB7" s="16" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
       <c r="AC7" s="16" t="s">
-        <v>1251</v>
+        <v>1254</v>
       </c>
       <c r="AD7" s="16" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="AE7" s="16" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="AF7" s="16" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
       <c r="AG7" s="16" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="AH7" s="4" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
       <c r="AI7" s="4" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="AJ7" s="4" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="AK7" s="4" t="s">
         <v>60</v>
       </c>
       <c r="AL7" s="4" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="AM7" s="4">
         <v>3</v>
@@ -17451,112 +17500,112 @@
         <v>582</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1252</v>
+        <v>1255</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>1253</v>
+        <v>1256</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>1254</v>
+        <v>1257</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>1192</v>
+        <v>1195</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>1196</v>
+        <v>1199</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>1258</v>
+        <v>1261</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>1259</v>
+        <v>1262</v>
       </c>
       <c r="N8" s="16" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="O8" s="16" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="P8" s="16" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="Q8" s="16" t="s">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="R8" s="16" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
       <c r="S8" s="16" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="V8" s="4" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="X8" s="16" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="Y8" s="4" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="Z8" s="4" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="AA8" s="4" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="AB8" s="16" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
       <c r="AC8" s="16" t="s">
-        <v>1264</v>
+        <v>1267</v>
       </c>
       <c r="AD8" s="16" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="AE8" s="16" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="AF8" s="16" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
       <c r="AG8" s="16" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="AH8" s="4" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
       <c r="AI8" s="4" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="AJ8" s="4" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="AK8" s="4" t="s">
         <v>60</v>
       </c>
       <c r="AL8" s="4" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="AM8" s="4">
         <v>4</v>
@@ -17567,118 +17616,118 @@
     </row>
     <row r="9" ht="52" customHeight="1" spans="1:40">
       <c r="A9" s="4" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>1192</v>
+        <v>1195</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>1196</v>
+        <v>1199</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>1272</v>
+        <v>1275</v>
       </c>
       <c r="N9" s="16" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="O9" s="16" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="P9" s="16" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="Q9" s="16" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="R9" s="16" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
       <c r="S9" s="16" t="s">
-        <v>1232</v>
+        <v>1235</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>1274</v>
+        <v>1277</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
       <c r="W9" s="4" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="X9" s="16" t="s">
-        <v>1275</v>
+        <v>1278</v>
       </c>
       <c r="Y9" s="4" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="Z9" s="4" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="AA9" s="4" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
       <c r="AB9" s="16" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
       <c r="AC9" s="16" t="s">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="AD9" s="16" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="AE9" s="16" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="AF9" s="16" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
       <c r="AG9" s="16" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="AH9" s="4" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
       <c r="AI9" s="4" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="AJ9" s="4" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="AK9" s="4" t="s">
         <v>60</v>
       </c>
       <c r="AL9" s="4" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="AM9" s="4">
         <v>5</v>
@@ -18569,7 +18618,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>1278</v>
+        <v>1281</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -18579,7 +18628,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6">
       <c r="A2" s="8" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -18597,2282 +18646,2282 @@
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:6">
       <c r="A4" s="10" t="s">
-        <v>1280</v>
+        <v>1283</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1281</v>
+        <v>1284</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:6">
       <c r="A5" s="11" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:6">
       <c r="A6" s="11" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>1285</v>
+        <v>1288</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:6">
       <c r="A7" s="11" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>1287</v>
+        <v>1290</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:6">
       <c r="A8" s="11" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>1288</v>
+        <v>1291</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:6">
       <c r="A9" s="11" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="C9" s="11" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="F9" s="13" t="s">
         <v>1289</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>1165</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>1290</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>1286</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:6">
       <c r="A10" s="11" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:6">
       <c r="A11" s="11" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>1293</v>
+        <v>1296</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>1294</v>
+        <v>1297</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>1295</v>
+        <v>1298</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:6">
       <c r="A12" s="11" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>1297</v>
+        <v>1300</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>1298</v>
+        <v>1301</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:6">
       <c r="A13" s="11" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>1299</v>
+        <v>1302</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:6">
       <c r="A14" s="11" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>1301</v>
+        <v>1304</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>1303</v>
+        <v>1306</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:6">
       <c r="A15" s="11" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>1304</v>
+        <v>1307</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>1305</v>
+        <v>1308</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:6">
       <c r="A16" s="11" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>1307</v>
+        <v>1310</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>1308</v>
+        <v>1311</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>1309</v>
+        <v>1312</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:6">
       <c r="A17" s="11" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>1310</v>
+        <v>1313</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>1311</v>
+        <v>1314</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>1312</v>
+        <v>1315</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:6">
       <c r="A18" s="11" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>1313</v>
+        <v>1316</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>1314</v>
+        <v>1317</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>1315</v>
+        <v>1318</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:6">
       <c r="A19" s="11" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>1317</v>
+        <v>1320</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>1318</v>
+        <v>1321</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:6">
       <c r="A20" s="11" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>1319</v>
+        <v>1322</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:6">
       <c r="A21" s="11" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>1322</v>
+        <v>1325</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>1323</v>
+        <v>1326</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>1324</v>
+        <v>1327</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:6">
       <c r="A22" s="11" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>1325</v>
+        <v>1328</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>1326</v>
+        <v>1329</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>1327</v>
+        <v>1330</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:6">
       <c r="A23" s="11" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>1328</v>
+        <v>1331</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>1329</v>
+        <v>1332</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:6">
       <c r="A24" s="11" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>1330</v>
+        <v>1333</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>1331</v>
+        <v>1334</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>1332</v>
+        <v>1335</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:6">
       <c r="A25" s="11" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>1333</v>
+        <v>1336</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>1334</v>
+        <v>1337</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>1335</v>
+        <v>1338</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:6">
       <c r="A26" s="11" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>1337</v>
+        <v>1340</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>1338</v>
+        <v>1341</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="27" ht="48" customHeight="1" spans="1:6">
       <c r="A27" s="11" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>1339</v>
+        <v>1342</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>1340</v>
+        <v>1343</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>1341</v>
+        <v>1344</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="28" ht="48" customHeight="1" spans="1:6">
       <c r="A28" s="11" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>1342</v>
+        <v>1345</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>1343</v>
+        <v>1346</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>1344</v>
+        <v>1347</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="29" ht="48" customHeight="1" spans="1:6">
       <c r="A29" s="11" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>1345</v>
+        <v>1348</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>1346</v>
+        <v>1349</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>1347</v>
+        <v>1350</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="30" ht="48" customHeight="1" spans="1:6">
       <c r="A30" s="11" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="31" ht="48" customHeight="1" spans="1:6">
       <c r="A31" s="11" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>7</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="32" ht="48" customHeight="1" spans="1:6">
       <c r="A32" s="11" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>8</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="33" ht="48" customHeight="1" spans="1:6">
       <c r="A33" s="11" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>1351</v>
+        <v>1354</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="34" ht="48" customHeight="1" spans="1:6">
       <c r="A34" s="11" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="C34" s="11" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>1355</v>
+      </c>
+      <c r="F34" s="13" t="s">
         <v>1289</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>1165</v>
-      </c>
-      <c r="E34" s="12" t="s">
-        <v>1352</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>1286</v>
       </c>
     </row>
     <row r="35" ht="48" customHeight="1" spans="1:6">
       <c r="A35" s="11" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="36" ht="48" customHeight="1" spans="1:6">
       <c r="A36" s="11" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>1353</v>
+        <v>1356</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>1354</v>
+        <v>1357</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>1355</v>
+        <v>1358</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="37" ht="48" customHeight="1" spans="1:6">
       <c r="A37" s="11" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>1356</v>
+        <v>1359</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>1357</v>
+        <v>1360</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>1358</v>
+        <v>1361</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="38" ht="48" customHeight="1" spans="1:6">
       <c r="A38" s="11" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>1360</v>
+        <v>1363</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="39" ht="48" customHeight="1" spans="1:6">
       <c r="A39" s="11" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>1362</v>
+        <v>1365</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>1363</v>
+        <v>1366</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>1364</v>
+        <v>1367</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="40" ht="48" customHeight="1" spans="1:6">
       <c r="A40" s="11" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>1366</v>
+        <v>1369</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>1367</v>
+        <v>1370</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="41" ht="48" customHeight="1" spans="1:6">
       <c r="A41" s="11" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>1368</v>
+        <v>1371</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>1369</v>
+        <v>1372</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>1370</v>
+        <v>1373</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="42" ht="48" customHeight="1" spans="1:6">
       <c r="A42" s="11" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>1371</v>
+        <v>1374</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>1372</v>
+        <v>1375</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>1373</v>
+        <v>1376</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="43" ht="48" customHeight="1" spans="1:6">
       <c r="A43" s="11" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>1374</v>
+        <v>1377</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>1375</v>
+        <v>1378</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>1376</v>
+        <v>1379</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="44" ht="48" customHeight="1" spans="1:6">
       <c r="A44" s="11" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>1378</v>
+        <v>1381</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>1379</v>
+        <v>1382</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="45" ht="48" customHeight="1" spans="1:6">
       <c r="A45" s="11" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>1380</v>
+        <v>1383</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>1381</v>
+        <v>1384</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>1382</v>
+        <v>1385</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="46" ht="48" customHeight="1" spans="1:6">
       <c r="A46" s="11" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>1383</v>
+        <v>1386</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>1384</v>
+        <v>1387</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>1355</v>
+        <v>1358</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="47" ht="48" customHeight="1" spans="1:6">
       <c r="A47" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="D47" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="48" ht="48" customHeight="1" spans="1:6">
       <c r="A48" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="D48" s="11" t="s">
         <v>7</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>1387</v>
+        <v>1390</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="49" ht="48" customHeight="1" spans="1:6">
       <c r="A49" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="D49" s="11" t="s">
         <v>8</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>1388</v>
+        <v>1391</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="50" ht="48" customHeight="1" spans="1:6">
       <c r="A50" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>1389</v>
+        <v>1392</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="51" ht="48" customHeight="1" spans="1:6">
       <c r="A51" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C51" s="11" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>1388</v>
+      </c>
+      <c r="F51" s="13" t="s">
         <v>1289</v>
-      </c>
-      <c r="D51" s="11" t="s">
-        <v>1165</v>
-      </c>
-      <c r="E51" s="12" t="s">
-        <v>1385</v>
-      </c>
-      <c r="F51" s="13" t="s">
-        <v>1286</v>
       </c>
     </row>
     <row r="52" ht="48" customHeight="1" spans="1:6">
       <c r="A52" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>1388</v>
+        <v>1391</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="53" ht="48" customHeight="1" spans="1:6">
       <c r="A53" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>1390</v>
+        <v>1393</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="54" ht="48" customHeight="1" spans="1:6">
       <c r="A54" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>1293</v>
+        <v>1296</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>1294</v>
+        <v>1297</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>1393</v>
+        <v>1396</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="55" ht="48" customHeight="1" spans="1:6">
       <c r="A55" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>1297</v>
+        <v>1300</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>1394</v>
+        <v>1397</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="56" ht="48" customHeight="1" spans="1:6">
       <c r="A56" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>1299</v>
+        <v>1302</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>1395</v>
+        <v>1398</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="57" ht="48" customHeight="1" spans="1:6">
       <c r="A57" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>1301</v>
+        <v>1304</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>1396</v>
+        <v>1399</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="58" ht="48" customHeight="1" spans="1:6">
       <c r="A58" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>1397</v>
+        <v>1400</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>1398</v>
+        <v>1401</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>1399</v>
+        <v>1402</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="59" ht="48" customHeight="1" spans="1:6">
       <c r="A59" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>1400</v>
+        <v>1403</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>1401</v>
+        <v>1404</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>1402</v>
+        <v>1405</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="60" ht="48" customHeight="1" spans="1:6">
       <c r="A60" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>1403</v>
+        <v>1406</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>1404</v>
+        <v>1407</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>1405</v>
+        <v>1408</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="61" ht="48" customHeight="1" spans="1:6">
       <c r="A61" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>1307</v>
+        <v>1310</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>1308</v>
+        <v>1311</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>1406</v>
+        <v>1409</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="62" ht="48" customHeight="1" spans="1:6">
       <c r="A62" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>1310</v>
+        <v>1313</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>1311</v>
+        <v>1314</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>1407</v>
+        <v>1410</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="63" ht="48" customHeight="1" spans="1:6">
       <c r="A63" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>1313</v>
+        <v>1316</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>1314</v>
+        <v>1317</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>1408</v>
+        <v>1411</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="64" ht="48" customHeight="1" spans="1:6">
       <c r="A64" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>1319</v>
+        <v>1322</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>1409</v>
+        <v>1412</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="65" ht="48" customHeight="1" spans="1:6">
       <c r="A65" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>1411</v>
+        <v>1414</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>1412</v>
+        <v>1415</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="66" ht="48" customHeight="1" spans="1:6">
       <c r="A66" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>1413</v>
+        <v>1416</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>1414</v>
+        <v>1417</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="67" ht="48" customHeight="1" spans="1:6">
       <c r="A67" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>1325</v>
+        <v>1328</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>1326</v>
+        <v>1329</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>1415</v>
+        <v>1418</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="68" ht="48" customHeight="1" spans="1:6">
       <c r="A68" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>1416</v>
+        <v>1419</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>1417</v>
+        <v>1420</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>1418</v>
+        <v>1421</v>
       </c>
       <c r="F68" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="69" ht="48" customHeight="1" spans="1:6">
       <c r="A69" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>1419</v>
+        <v>1422</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>1420</v>
+        <v>1423</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="70" ht="48" customHeight="1" spans="1:6">
       <c r="A70" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>1421</v>
+        <v>1424</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>1422</v>
+        <v>1425</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>1423</v>
+        <v>1426</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="71" ht="48" customHeight="1" spans="1:6">
       <c r="A71" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>1424</v>
+        <v>1427</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>1425</v>
+        <v>1428</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>1426</v>
+        <v>1429</v>
       </c>
       <c r="F71" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="72" ht="48" customHeight="1" spans="1:6">
       <c r="A72" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>1427</v>
+        <v>1430</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>1428</v>
+        <v>1431</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="F72" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="73" ht="48" customHeight="1" spans="1:6">
       <c r="A73" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>1429</v>
+        <v>1432</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>1430</v>
+        <v>1433</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>1431</v>
+        <v>1434</v>
       </c>
       <c r="F73" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="74" ht="48" customHeight="1" spans="1:6">
       <c r="A74" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>1432</v>
+        <v>1435</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>1433</v>
+        <v>1436</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>1434</v>
+        <v>1437</v>
       </c>
       <c r="F74" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="75" ht="48" customHeight="1" spans="1:6">
       <c r="A75" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>1435</v>
+        <v>1438</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>1436</v>
+        <v>1439</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="F75" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="76" ht="48" customHeight="1" spans="1:6">
       <c r="A76" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>1437</v>
+        <v>1440</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>1438</v>
+        <v>1441</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>1439</v>
+        <v>1442</v>
       </c>
       <c r="F76" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="77" ht="48" customHeight="1" spans="1:6">
       <c r="A77" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>1440</v>
+        <v>1443</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>1441</v>
+        <v>1444</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>1442</v>
+        <v>1445</v>
       </c>
       <c r="F77" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="78" ht="48" customHeight="1" spans="1:6">
       <c r="A78" s="11" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>1443</v>
+        <v>1446</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>1444</v>
+        <v>1447</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>1445</v>
+        <v>1448</v>
       </c>
       <c r="F78" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="79" ht="48" customHeight="1" spans="1:6">
       <c r="A79" s="11" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="D79" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="F79" s="13" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="80" ht="48" customHeight="1" spans="1:6">
       <c r="A80" s="11" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="D80" s="11" t="s">
         <v>7</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>1448</v>
+        <v>1451</v>
       </c>
       <c r="F80" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="81" ht="48" customHeight="1" spans="1:6">
       <c r="A81" s="11" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="D81" s="11" t="s">
         <v>8</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>1449</v>
+        <v>1452</v>
       </c>
       <c r="F81" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="82" ht="48" customHeight="1" spans="1:6">
       <c r="A82" s="11" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>1450</v>
+        <v>1453</v>
       </c>
       <c r="F82" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="83" ht="48" customHeight="1" spans="1:6">
       <c r="A83" s="11" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C83" s="11" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D83" s="11" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E83" s="12" t="s">
+        <v>1449</v>
+      </c>
+      <c r="F83" s="13" t="s">
         <v>1289</v>
-      </c>
-      <c r="D83" s="11" t="s">
-        <v>1165</v>
-      </c>
-      <c r="E83" s="12" t="s">
-        <v>1446</v>
-      </c>
-      <c r="F83" s="13" t="s">
-        <v>1286</v>
       </c>
     </row>
     <row r="84" ht="48" customHeight="1" spans="1:6">
       <c r="A84" s="11" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>1449</v>
+        <v>1452</v>
       </c>
       <c r="F84" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="85" ht="48" customHeight="1" spans="1:6">
       <c r="A85" s="11" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>1390</v>
+        <v>1393</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="F85" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="86" ht="48" customHeight="1" spans="1:6">
       <c r="A86" s="11" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>1293</v>
+        <v>1296</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>1294</v>
+        <v>1297</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>1451</v>
+        <v>1454</v>
       </c>
       <c r="F86" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="87" ht="48" customHeight="1" spans="1:6">
       <c r="A87" s="11" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>1297</v>
+        <v>1300</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>1452</v>
+        <v>1455</v>
       </c>
       <c r="F87" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="88" ht="48" customHeight="1" spans="1:6">
       <c r="A88" s="11" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>1299</v>
+        <v>1302</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>1453</v>
+        <v>1456</v>
       </c>
       <c r="F88" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="89" ht="48" customHeight="1" spans="1:6">
       <c r="A89" s="11" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>1301</v>
+        <v>1304</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="E89" s="12" t="s">
-        <v>1454</v>
+        <v>1457</v>
       </c>
       <c r="F89" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="90" ht="48" customHeight="1" spans="1:6">
       <c r="A90" s="11" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>1397</v>
+        <v>1400</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>1398</v>
+        <v>1401</v>
       </c>
       <c r="E90" s="12" t="s">
-        <v>1399</v>
+        <v>1402</v>
       </c>
       <c r="F90" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="91" ht="48" customHeight="1" spans="1:6">
       <c r="A91" s="11" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>1400</v>
+        <v>1403</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>1401</v>
+        <v>1404</v>
       </c>
       <c r="E91" s="12" t="s">
-        <v>1455</v>
+        <v>1458</v>
       </c>
       <c r="F91" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="92" ht="48" customHeight="1" spans="1:6">
       <c r="A92" s="11" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>1403</v>
+        <v>1406</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>1404</v>
+        <v>1407</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>1456</v>
+        <v>1459</v>
       </c>
       <c r="F92" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="93" ht="48" customHeight="1" spans="1:6">
       <c r="A93" s="11" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>1307</v>
+        <v>1310</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>1308</v>
+        <v>1311</v>
       </c>
       <c r="E93" s="12" t="s">
-        <v>1457</v>
+        <v>1460</v>
       </c>
       <c r="F93" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="94" ht="48" customHeight="1" spans="1:6">
       <c r="A94" s="11" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>1310</v>
+        <v>1313</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>1311</v>
+        <v>1314</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>1458</v>
+        <v>1461</v>
       </c>
       <c r="F94" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="95" ht="48" customHeight="1" spans="1:6">
       <c r="A95" s="11" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>1313</v>
+        <v>1316</v>
       </c>
       <c r="D95" s="11" t="s">
-        <v>1314</v>
+        <v>1317</v>
       </c>
       <c r="E95" s="12" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="F95" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="96" ht="48" customHeight="1" spans="1:6">
       <c r="A96" s="11" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>1319</v>
+        <v>1322</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>1459</v>
+        <v>1462</v>
       </c>
       <c r="F96" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="97" ht="48" customHeight="1" spans="1:6">
       <c r="A97" s="11" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>1411</v>
+        <v>1414</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>1460</v>
+        <v>1463</v>
       </c>
       <c r="F97" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="98" ht="48" customHeight="1" spans="1:6">
       <c r="A98" s="11" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>1413</v>
+        <v>1416</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>1414</v>
+        <v>1417</v>
       </c>
       <c r="E98" s="12" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="F98" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="99" ht="48" customHeight="1" spans="1:6">
       <c r="A99" s="11" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>1325</v>
+        <v>1328</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>1326</v>
+        <v>1329</v>
       </c>
       <c r="E99" s="12" t="s">
-        <v>1461</v>
+        <v>1464</v>
       </c>
       <c r="F99" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="100" ht="48" customHeight="1" spans="1:6">
       <c r="A100" s="11" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>1416</v>
+        <v>1419</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>1417</v>
+        <v>1420</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>1462</v>
+        <v>1465</v>
       </c>
       <c r="F100" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="101" ht="48" customHeight="1" spans="1:6">
       <c r="A101" s="11" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>1419</v>
+        <v>1422</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>1420</v>
+        <v>1423</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="F101" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="102" ht="48" customHeight="1" spans="1:6">
       <c r="A102" s="11" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>1421</v>
+        <v>1424</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>1422</v>
+        <v>1425</v>
       </c>
       <c r="E102" s="12" t="s">
-        <v>1463</v>
+        <v>1466</v>
       </c>
       <c r="F102" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="103" ht="48" customHeight="1" spans="1:6">
       <c r="A103" s="11" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>1424</v>
+        <v>1427</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>1425</v>
+        <v>1428</v>
       </c>
       <c r="E103" s="12" t="s">
-        <v>1464</v>
+        <v>1467</v>
       </c>
       <c r="F103" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="104" ht="48" customHeight="1" spans="1:6">
       <c r="A104" s="11" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>1427</v>
+        <v>1430</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>1428</v>
+        <v>1431</v>
       </c>
       <c r="E104" s="12" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="F104" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="105" ht="48" customHeight="1" spans="1:6">
       <c r="A105" s="11" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>1429</v>
+        <v>1432</v>
       </c>
       <c r="D105" s="11" t="s">
-        <v>1430</v>
+        <v>1433</v>
       </c>
       <c r="E105" s="12" t="s">
-        <v>1465</v>
+        <v>1468</v>
       </c>
       <c r="F105" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="106" ht="48" customHeight="1" spans="1:6">
       <c r="A106" s="11" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>1432</v>
+        <v>1435</v>
       </c>
       <c r="D106" s="11" t="s">
-        <v>1433</v>
+        <v>1436</v>
       </c>
       <c r="E106" s="12" t="s">
-        <v>1466</v>
+        <v>1469</v>
       </c>
       <c r="F106" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="107" ht="48" customHeight="1" spans="1:6">
       <c r="A107" s="11" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>1435</v>
+        <v>1438</v>
       </c>
       <c r="D107" s="11" t="s">
-        <v>1436</v>
+        <v>1439</v>
       </c>
       <c r="E107" s="12" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="F107" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="108" ht="48" customHeight="1" spans="1:6">
       <c r="A108" s="11" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>1437</v>
+        <v>1440</v>
       </c>
       <c r="D108" s="11" t="s">
-        <v>1438</v>
+        <v>1441</v>
       </c>
       <c r="E108" s="12" t="s">
-        <v>1467</v>
+        <v>1470</v>
       </c>
       <c r="F108" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="109" ht="48" customHeight="1" spans="1:6">
       <c r="A109" s="11" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>1440</v>
+        <v>1443</v>
       </c>
       <c r="D109" s="11" t="s">
-        <v>1441</v>
+        <v>1444</v>
       </c>
       <c r="E109" s="12" t="s">
-        <v>1468</v>
+        <v>1471</v>
       </c>
       <c r="F109" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="110" ht="48" customHeight="1" spans="1:6">
       <c r="A110" s="11" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B110" s="11" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C110" s="11" t="s">
         <v>1446</v>
       </c>
-      <c r="B110" s="11" t="s">
+      <c r="D110" s="11" t="s">
         <v>1447</v>
       </c>
-      <c r="C110" s="11" t="s">
-        <v>1443</v>
-      </c>
-      <c r="D110" s="11" t="s">
-        <v>1444</v>
-      </c>
       <c r="E110" s="12" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="F110" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="111" ht="48" customHeight="1" spans="1:6">
       <c r="A111" s="11" t="s">
-        <v>1469</v>
+        <v>1472</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>1470</v>
+        <v>1473</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="D111" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E111" s="12" t="s">
-        <v>1469</v>
+        <v>1472</v>
       </c>
       <c r="F111" s="13" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="112" ht="48" customHeight="1" spans="1:6">
       <c r="A112" s="11" t="s">
-        <v>1469</v>
+        <v>1472</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>1470</v>
+        <v>1473</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="D112" s="11" t="s">
         <v>7</v>
       </c>
       <c r="E112" s="12" t="s">
-        <v>1471</v>
+        <v>1474</v>
       </c>
       <c r="F112" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="113" ht="48" customHeight="1" spans="1:6">
       <c r="A113" s="11" t="s">
-        <v>1469</v>
+        <v>1472</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>1470</v>
+        <v>1473</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="D113" s="11" t="s">
         <v>8</v>
       </c>
       <c r="E113" s="12" t="s">
-        <v>1472</v>
+        <v>1475</v>
       </c>
       <c r="F113" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="114" ht="48" customHeight="1" spans="1:6">
       <c r="A114" s="11" t="s">
-        <v>1469</v>
+        <v>1472</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>1470</v>
+        <v>1473</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="E114" s="12" t="s">
-        <v>1473</v>
+        <v>1476</v>
       </c>
       <c r="F114" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="115" ht="48" customHeight="1" spans="1:6">
       <c r="A115" s="11" t="s">
-        <v>1469</v>
+        <v>1472</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>1470</v>
+        <v>1473</v>
       </c>
       <c r="C115" s="11" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D115" s="11" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E115" s="12" t="s">
+        <v>1477</v>
+      </c>
+      <c r="F115" s="13" t="s">
         <v>1289</v>
-      </c>
-      <c r="D115" s="11" t="s">
-        <v>1165</v>
-      </c>
-      <c r="E115" s="12" t="s">
-        <v>1474</v>
-      </c>
-      <c r="F115" s="13" t="s">
-        <v>1286</v>
       </c>
     </row>
     <row r="116" ht="48" customHeight="1" spans="1:6">
       <c r="A116" s="11" t="s">
-        <v>1469</v>
+        <v>1472</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>1470</v>
+        <v>1473</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="E116" s="12" t="s">
-        <v>1475</v>
+        <v>1478</v>
       </c>
       <c r="F116" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="117" ht="48" customHeight="1" spans="1:6">
       <c r="A117" s="11" t="s">
-        <v>1469</v>
+        <v>1472</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>1470</v>
+        <v>1473</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>1476</v>
+        <v>1479</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>1477</v>
+        <v>1480</v>
       </c>
       <c r="E117" s="12" t="s">
-        <v>1478</v>
+        <v>1481</v>
       </c>
       <c r="F117" s="13" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
     </row>
   </sheetData>
@@ -20901,7 +20950,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>1479</v>
+        <v>1482</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -20910,7 +20959,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:5">
       <c r="A2" s="8" t="s">
-        <v>1480</v>
+        <v>1483</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -20926,274 +20975,274 @@
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:5">
       <c r="A4" s="10" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1" spans="1:5">
       <c r="A5" s="11" t="s">
-        <v>1481</v>
+        <v>1484</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>1482</v>
+        <v>1485</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>1483</v>
+        <v>1486</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1484</v>
+        <v>1487</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>1485</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1" spans="1:5">
       <c r="A6" s="11" t="s">
-        <v>1486</v>
+        <v>1489</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>1362</v>
+        <v>1365</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>1363</v>
+        <v>1366</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>1487</v>
+        <v>1490</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1" spans="1:5">
       <c r="A7" s="11" t="s">
-        <v>1486</v>
+        <v>1489</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>1488</v>
+        <v>1491</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>1487</v>
+        <v>1490</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>1489</v>
+        <v>1492</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>1490</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1" spans="1:5">
       <c r="A8" s="11" t="s">
-        <v>1486</v>
+        <v>1489</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>1366</v>
+        <v>1369</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>1491</v>
+        <v>1494</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1" spans="1:5">
       <c r="A9" s="11" t="s">
-        <v>1486</v>
+        <v>1489</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>1492</v>
+        <v>1495</v>
       </c>
       <c r="C9" s="11" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>1497</v>
+      </c>
+      <c r="E9" s="13" t="s">
         <v>1493</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>1494</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>1490</v>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1" spans="1:5">
       <c r="A10" s="11" t="s">
-        <v>1495</v>
+        <v>1498</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>1496</v>
+        <v>1499</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>1498</v>
+        <v>1501</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1" spans="1:5">
       <c r="A11" s="11" t="s">
-        <v>1495</v>
+        <v>1498</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>1499</v>
+        <v>1502</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>1500</v>
+        <v>1503</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:5">
       <c r="A12" s="11" t="s">
-        <v>1502</v>
+        <v>1505</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>1503</v>
+        <v>1506</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>1504</v>
+        <v>1507</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1" spans="1:5">
       <c r="A13" s="11" t="s">
-        <v>1502</v>
+        <v>1505</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>1505</v>
+        <v>1508</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1" spans="1:5">
       <c r="A14" s="11" t="s">
-        <v>1502</v>
+        <v>1505</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>1507</v>
+        <v>1510</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>1508</v>
+        <v>1511</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1" spans="1:5">
       <c r="A15" s="11" t="s">
-        <v>1502</v>
+        <v>1505</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>1509</v>
+        <v>1512</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>1510</v>
+        <v>1513</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1" spans="1:5">
       <c r="A16" s="11" t="s">
-        <v>1511</v>
+        <v>1514</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>1513</v>
+        <v>1516</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>1514</v>
+        <v>1517</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1" spans="1:5">
       <c r="A17" s="11" t="s">
-        <v>1376</v>
+        <v>1379</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>1515</v>
+        <v>1518</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>1516</v>
+        <v>1519</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>1517</v>
+        <v>1520</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1" spans="1:5">
       <c r="A18" s="11" t="s">
-        <v>1376</v>
+        <v>1379</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>1518</v>
+        <v>1521</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>1519</v>
+        <v>1522</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>1520</v>
+        <v>1523</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1" spans="1:5">
       <c r="A19" s="11" t="s">
-        <v>1376</v>
+        <v>1379</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>1521</v>
+        <v>1524</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>1522</v>
+        <v>1525</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>1355</v>
+        <v>1358</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
     </row>
   </sheetData>
@@ -21220,7 +21269,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>1523</v>
+        <v>1526</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -21232,7 +21281,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>1524</v>
+        <v>1527</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -21244,50 +21293,50 @@
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:8">
       <c r="A4" s="3" t="s">
-        <v>1525</v>
+        <v>1528</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1526</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:8">
       <c r="A5" s="4" t="s">
-        <v>1527</v>
+        <v>1530</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1528</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:8">
       <c r="A6" s="4" t="s">
-        <v>1529</v>
+        <v>1532</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1530</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:8">
       <c r="A7" s="4" t="s">
-        <v>1531</v>
+        <v>1534</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1532</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:8">
       <c r="A8" s="4" t="s">
-        <v>1533</v>
+        <v>1536</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1534</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:8">
       <c r="A9" s="4" t="s">
-        <v>1535</v>
+        <v>1538</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1536</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:8">
@@ -21295,10 +21344,10 @@
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:8">
       <c r="A11" s="3" t="s">
-        <v>1537</v>
+        <v>1540</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1538</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:8">
@@ -21306,7 +21355,7 @@
         <v>22</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1539</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:8">
@@ -21314,47 +21363,47 @@
         <v>23</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:8">
       <c r="A14" s="4" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:8">
       <c r="A15" s="4" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1544</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:8">
       <c r="A16" s="4" t="s">
-        <v>1545</v>
+        <v>1548</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1546</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>1547</v>
+        <v>1550</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1548</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:2">
       <c r="A18" s="4" t="s">
-        <v>1549</v>
+        <v>1552</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1550</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:2">
@@ -21362,10 +21411,10 @@
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:2">
       <c r="A20" s="3" t="s">
-        <v>1551</v>
+        <v>1554</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>1552</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:2">
@@ -21373,7 +21422,7 @@
         <v>1</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1553</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:2">
@@ -21381,7 +21430,7 @@
         <v>2</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1554</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:2">
@@ -21389,7 +21438,7 @@
         <v>3</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1555</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1" spans="1:2">
@@ -21397,7 +21446,7 @@
         <v>4</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:2">
@@ -21405,7 +21454,7 @@
         <v>5</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1557</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1" spans="1:2">
@@ -21413,7 +21462,7 @@
         <v>6</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>1558</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1" spans="1:2">
@@ -21421,7 +21470,7 @@
         <v>7</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>1559</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1" spans="1:2">
@@ -21429,7 +21478,7 @@
         <v>8</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>1560</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1" spans="1:2">
@@ -21437,7 +21486,7 @@
         <v>9</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1" spans="1:2">
@@ -21445,7 +21494,7 @@
         <v>10</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1" spans="1:2">
@@ -21453,26 +21502,26 @@
     </row>
     <row r="32" ht="28" customHeight="1" spans="1:2">
       <c r="A32" s="3" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1" spans="1:2">
       <c r="A33" s="4" t="s">
-        <v>1565</v>
+        <v>1568</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>1566</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1" spans="1:2">
       <c r="A34" s="7" t="s">
-        <v>1567</v>
+        <v>1570</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>1568</v>
+        <v>1571</v>
       </c>
     </row>
   </sheetData>

--- a/顶奢_整站资料批量编辑.xlsx
+++ b/顶奢_整站资料批量编辑.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2944" uniqueCount="1572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2944" uniqueCount="1578">
   <si>
     <t>顶奢 · 整站资料批量编辑</t>
   </si>
@@ -1835,22 +1835,22 @@
     <t>https://hqq2.com/beijing/model-001/</t>
   </si>
   <si>
-    <t>北京外围模特萝莉白虎主图</t>
-  </si>
-  <si>
-    <t>北京外围模特萝莉白虎资料主图</t>
-  </si>
-  <si>
-    <t>北京外围模特萝莉白虎集细节图</t>
-  </si>
-  <si>
-    <t>北京外围模特萝莉白虎资料细节</t>
-  </si>
-  <si>
-    <t>北京外围模特萝莉白虎集展示图</t>
-  </si>
-  <si>
-    <t>北京外围模特萝莉白虎资料展示</t>
+    <t>北京外围模特小萝莉主图</t>
+  </si>
+  <si>
+    <t>北京外围模特小萝莉资料主图</t>
+  </si>
+  <si>
+    <t>北京外围模特小萝莉细节图</t>
+  </si>
+  <si>
+    <t>北京外围模特小萝莉资料细节</t>
+  </si>
+  <si>
+    <t>北京外围模特小萝莉展示图</t>
+  </si>
+  <si>
+    <t>北京外围模特小萝莉资料展示</t>
   </si>
   <si>
     <t>北京外围模特小萝莉资料视频</t>
@@ -1859,55 +1859,79 @@
     <t>北京外围模特小萝莉相关资料视频</t>
   </si>
   <si>
+    <t>北京外围兼职学妹</t>
+  </si>
+  <si>
+    <t>北京外围｜北京外围女｜北京外围女联系方式</t>
+  </si>
+  <si>
+    <t>浏览北京外围模特兼职学妹的独立资料、图片说明、内容介绍与相关推荐。</t>
+  </si>
+  <si>
+    <t>·Age年龄: 06年 
+·Weight体重:42kg
+·Height身高: 173cm
+·Bust胸围: C-cup</t>
+  </si>
+  <si>
+    <t>清纯｜学妹</t>
+  </si>
+  <si>
+    <t>温柔气质纯天然无整容
+干净而纯粹的白·简单又纯净
+无纹身 不抽烟 A4腰·纤长细腿·黄金比例温柔·清纯·高级·气质温婉
+一个心中有梦 眼里有光的女孩</t>
+  </si>
+  <si>
+    <t>以上是北京外围女模特兼职学妹的照片、资料、无需注册登录即可浏览。</t>
+  </si>
+  <si>
+    <t>photos/beijing-model-002</t>
+  </si>
+  <si>
+    <t>photos/beijing-model-002/01.jpg</t>
+  </si>
+  <si>
+    <t>photos/beijing-model-002/02.jpg</t>
+  </si>
+  <si>
+    <t>photos/beijing-model-002/03.jpg</t>
+  </si>
+  <si>
+    <t>photos/beijing-model-002/profile.mp4</t>
+  </si>
+  <si>
+    <t>https://hqq2.com/beijing/model-002/</t>
+  </si>
+  <si>
+    <t>北京外围模特兼职学妹主图</t>
+  </si>
+  <si>
+    <t>北京外围模特兼职学妹细节图</t>
+  </si>
+  <si>
+    <t>北京外围模特兼职学妹资料细节</t>
+  </si>
+  <si>
+    <t>北京外围模特兼职学妹展示图</t>
+  </si>
+  <si>
+    <t>北京外围模特兼职学妹资料展示</t>
+  </si>
+  <si>
+    <t>北京外围模特兼职学妹资料视频</t>
+  </si>
+  <si>
+    <t>北京外围模特兼职学妹相关资料视频</t>
+  </si>
+  <si>
     <t>北京外围模特</t>
   </si>
   <si>
-    <t>北京外围｜北京外围女｜北京外围女联系方式</t>
+    <t>北京外围｜北京朝阳区外围｜北京外围上门</t>
   </si>
   <si>
     <t>浏览北京外围模特的独立资料、图片说明、内容介绍与相关推荐。</t>
-  </si>
-  <si>
-    <t>北京鎏金映像主题资料展示页，内容、图片和视频可按实际资料独立更新。</t>
-  </si>
-  <si>
-    <t>photos/beijing-model-002</t>
-  </si>
-  <si>
-    <t>photos/beijing-model-002/01.jpg</t>
-  </si>
-  <si>
-    <t>photos/beijing-model-002/02.jpg</t>
-  </si>
-  <si>
-    <t>photos/beijing-model-002/03.jpg</t>
-  </si>
-  <si>
-    <t>photos/beijing-model-002/profile.mp4</t>
-  </si>
-  <si>
-    <t>https://hqq2.com/beijing/model-002/</t>
-  </si>
-  <si>
-    <t>北京鎏金映像主图</t>
-  </si>
-  <si>
-    <t>北京鎏金映像资料主图</t>
-  </si>
-  <si>
-    <t>北京鎏金映像细节图</t>
-  </si>
-  <si>
-    <t>北京鎏金映像资料细节</t>
-  </si>
-  <si>
-    <t>北京鎏金映像展示图</t>
-  </si>
-  <si>
-    <t>北京鎏金映像资料展示</t>
-  </si>
-  <si>
-    <t>北京外围｜北京朝阳区外围｜北京外围上门</t>
   </si>
   <si>
     <t>北京云端风尚主题资料展示页，内容、图片和视频可按实际资料独立更新。</t>
@@ -9659,17 +9683,17 @@
       <c r="G36" s="16" t="s">
         <v>608</v>
       </c>
-      <c r="H36" s="4" t="s">
+      <c r="H36" s="16" t="s">
         <v>609</v>
       </c>
-      <c r="I36" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="J36" s="4" t="s">
-        <v>49</v>
+      <c r="I36" s="16" t="s">
+        <v>610</v>
+      </c>
+      <c r="J36" s="16" t="s">
+        <v>611</v>
       </c>
       <c r="K36" s="16" t="s">
-        <v>589</v>
+        <v>612</v>
       </c>
       <c r="L36" s="16" t="s">
         <v>590</v>
@@ -9678,25 +9702,25 @@
         <v>591</v>
       </c>
       <c r="N36" s="20" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="O36" s="20" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="P36" s="20" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="Q36" s="20" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="R36" s="20" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="S36" s="22" t="s">
         <v>58</v>
       </c>
       <c r="T36" s="20" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="U36" s="4" t="s">
         <v>60</v>
@@ -9712,29 +9736,29 @@
       </c>
       <c r="Y36" s="17"/>
       <c r="Z36" s="17"/>
-      <c r="AA36" s="4" t="s">
-        <v>616</v>
-      </c>
-      <c r="AB36" s="4" t="s">
-        <v>617</v>
-      </c>
-      <c r="AC36" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="AD36" s="4" t="s">
+      <c r="AA36" s="16" t="s">
         <v>619</v>
       </c>
-      <c r="AE36" s="4" t="s">
+      <c r="AB36" s="16" t="s">
+        <v>619</v>
+      </c>
+      <c r="AC36" s="16" t="s">
         <v>620</v>
       </c>
-      <c r="AF36" s="4" t="s">
+      <c r="AD36" s="16" t="s">
         <v>621</v>
       </c>
+      <c r="AE36" s="16" t="s">
+        <v>622</v>
+      </c>
+      <c r="AF36" s="16" t="s">
+        <v>623</v>
+      </c>
       <c r="AG36" s="16" t="s">
-        <v>604</v>
+        <v>624</v>
       </c>
       <c r="AH36" s="16" t="s">
-        <v>605</v>
+        <v>625</v>
       </c>
       <c r="AI36" s="4"/>
       <c r="AJ36" s="17"/>
@@ -9757,16 +9781,16 @@
         <v>88</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>606</v>
+        <v>626</v>
       </c>
       <c r="F37" s="21" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="I37" s="4" t="s">
         <v>93</v>
@@ -9784,25 +9808,25 @@
         <v>591</v>
       </c>
       <c r="N37" s="20" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="O37" s="20" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="P37" s="20" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="Q37" s="20" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="R37" s="20" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="S37" s="22" t="s">
         <v>58</v>
       </c>
       <c r="T37" s="20" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="U37" s="4" t="s">
         <v>60</v>
@@ -9819,22 +9843,22 @@
       <c r="Y37" s="17"/>
       <c r="Z37" s="17"/>
       <c r="AA37" s="4" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="AB37" s="4" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="AC37" s="4" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="AD37" s="4" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="AE37" s="4" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="AF37" s="4" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="AG37" s="16" t="s">
         <v>604</v>
@@ -9863,16 +9887,16 @@
         <v>107</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>606</v>
+        <v>626</v>
       </c>
       <c r="F38" s="21" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="I38" s="4" t="s">
         <v>112</v>
@@ -9890,25 +9914,25 @@
         <v>591</v>
       </c>
       <c r="N38" s="20" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="O38" s="20" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="P38" s="20" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="Q38" s="20" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="R38" s="20" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="S38" s="22" t="s">
         <v>58</v>
       </c>
       <c r="T38" s="20" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="U38" s="4" t="s">
         <v>60</v>
@@ -9925,22 +9949,22 @@
       <c r="Y38" s="17"/>
       <c r="Z38" s="17"/>
       <c r="AA38" s="4" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="AB38" s="4" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="AC38" s="4" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="AD38" s="4" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="AE38" s="4" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="AF38" s="4" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="AG38" s="16" t="s">
         <v>604</v>
@@ -9969,16 +9993,16 @@
         <v>126</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>606</v>
+        <v>626</v>
       </c>
       <c r="F39" s="21" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="I39" s="4" t="s">
         <v>131</v>
@@ -9996,25 +10020,25 @@
         <v>591</v>
       </c>
       <c r="N39" s="20" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="O39" s="20" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="P39" s="20" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="Q39" s="20" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="R39" s="20" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="S39" s="22" t="s">
         <v>58</v>
       </c>
       <c r="T39" s="20" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="U39" s="4" t="s">
         <v>60</v>
@@ -10031,22 +10055,22 @@
       <c r="Y39" s="17"/>
       <c r="Z39" s="17"/>
       <c r="AA39" s="4" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="AB39" s="4" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="AC39" s="4" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="AD39" s="4" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="AE39" s="4" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="AF39" s="4" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="AG39" s="16" t="s">
         <v>604</v>
@@ -10075,16 +10099,16 @@
         <v>145</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>606</v>
+        <v>626</v>
       </c>
       <c r="F40" s="21" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="I40" s="4" t="s">
         <v>48</v>
@@ -10102,25 +10126,25 @@
         <v>591</v>
       </c>
       <c r="N40" s="20" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="O40" s="20" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="P40" s="20" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="Q40" s="20" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="R40" s="20" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="S40" s="22" t="s">
         <v>58</v>
       </c>
       <c r="T40" s="20" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="U40" s="4" t="s">
         <v>60</v>
@@ -10137,22 +10161,22 @@
       <c r="Y40" s="17"/>
       <c r="Z40" s="17"/>
       <c r="AA40" s="4" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="AB40" s="4" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="AC40" s="4" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="AD40" s="4" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="AE40" s="4" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="AF40" s="4" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="AG40" s="16" t="s">
         <v>604</v>
@@ -10181,16 +10205,16 @@
         <v>163</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>606</v>
+        <v>626</v>
       </c>
       <c r="F41" s="21" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>74</v>
@@ -10208,25 +10232,25 @@
         <v>591</v>
       </c>
       <c r="N41" s="20" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="O41" s="20" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="P41" s="20" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="Q41" s="20" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="R41" s="20" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="S41" s="22" t="s">
         <v>58</v>
       </c>
       <c r="T41" s="20" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="U41" s="4" t="s">
         <v>60</v>
@@ -10243,22 +10267,22 @@
       <c r="Y41" s="17"/>
       <c r="Z41" s="17"/>
       <c r="AA41" s="4" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="AB41" s="4" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="AC41" s="4" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="AD41" s="4" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="AE41" s="4" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="AF41" s="4" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="AG41" s="16" t="s">
         <v>604</v>
@@ -10287,16 +10311,16 @@
         <v>181</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>606</v>
+        <v>626</v>
       </c>
       <c r="F42" s="21" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="I42" s="4" t="s">
         <v>93</v>
@@ -10314,25 +10338,25 @@
         <v>591</v>
       </c>
       <c r="N42" s="20" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="O42" s="20" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="P42" s="20" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="Q42" s="20" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="R42" s="20" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="S42" s="22" t="s">
         <v>58</v>
       </c>
       <c r="T42" s="20" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="U42" s="4" t="s">
         <v>60</v>
@@ -10349,22 +10373,22 @@
       <c r="Y42" s="17"/>
       <c r="Z42" s="17"/>
       <c r="AA42" s="4" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="AB42" s="4" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="AC42" s="4" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="AD42" s="4" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="AE42" s="4" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="AF42" s="4" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="AG42" s="16" t="s">
         <v>604</v>
@@ -10393,16 +10417,16 @@
         <v>199</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>606</v>
+        <v>626</v>
       </c>
       <c r="F43" s="21" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="I43" s="4" t="s">
         <v>112</v>
@@ -10420,25 +10444,25 @@
         <v>591</v>
       </c>
       <c r="N43" s="20" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="O43" s="20" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="P43" s="20" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="Q43" s="20" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="R43" s="20" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="S43" s="22" t="s">
         <v>58</v>
       </c>
       <c r="T43" s="20" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="U43" s="4" t="s">
         <v>60</v>
@@ -10455,22 +10479,22 @@
       <c r="Y43" s="17"/>
       <c r="Z43" s="17"/>
       <c r="AA43" s="4" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="AB43" s="4" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="AC43" s="4" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="AD43" s="4" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="AE43" s="4" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="AF43" s="4" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="AG43" s="16" t="s">
         <v>604</v>
@@ -10499,16 +10523,16 @@
         <v>217</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>606</v>
+        <v>626</v>
       </c>
       <c r="F44" s="21" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="I44" s="4" t="s">
         <v>131</v>
@@ -10526,25 +10550,25 @@
         <v>591</v>
       </c>
       <c r="N44" s="20" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="O44" s="20" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="P44" s="20" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="Q44" s="20" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="R44" s="20" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="S44" s="22" t="s">
         <v>58</v>
       </c>
       <c r="T44" s="20" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="U44" s="4" t="s">
         <v>60</v>
@@ -10561,22 +10585,22 @@
       <c r="Y44" s="17"/>
       <c r="Z44" s="17"/>
       <c r="AA44" s="4" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="AB44" s="4" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="AC44" s="4" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="AD44" s="4" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="AE44" s="4" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="AF44" s="4" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="AG44" s="16" t="s">
         <v>604</v>
@@ -10593,10 +10617,10 @@
     </row>
     <row r="45" ht="42" customHeight="1" spans="1:38">
       <c r="A45" s="19" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="C45" s="20" t="s">
         <v>42</v>
@@ -10605,16 +10629,16 @@
         <v>43</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="F45" s="21" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="I45" s="4" t="s">
         <v>48</v>
@@ -10623,34 +10647,34 @@
         <v>49</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="L45" s="4" t="s">
         <v>241</v>
       </c>
       <c r="M45" s="4" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="N45" s="20" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="O45" s="20" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="P45" s="20" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="Q45" s="20" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="R45" s="20" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="S45" s="19" t="s">
         <v>58</v>
       </c>
       <c r="T45" s="20" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="U45" s="4" t="s">
         <v>60</v>
@@ -10667,22 +10691,22 @@
       <c r="Y45" s="17"/>
       <c r="Z45" s="17"/>
       <c r="AA45" s="4" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="AB45" s="4" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="AC45" s="4" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
       <c r="AD45" s="4" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="AE45" s="4" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
       <c r="AF45" s="4" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="AG45" s="4"/>
       <c r="AH45" s="4"/>
@@ -10695,10 +10719,10 @@
     </row>
     <row r="46" ht="42" customHeight="1" spans="1:38">
       <c r="A46" s="19" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="C46" s="20" t="s">
         <v>68</v>
@@ -10707,16 +10731,16 @@
         <v>69</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="F46" s="21" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
       <c r="I46" s="4" t="s">
         <v>74</v>
@@ -10725,34 +10749,34 @@
         <v>49</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>758</v>
+        <v>764</v>
       </c>
       <c r="L46" s="4" t="s">
         <v>241</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="N46" s="20" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="O46" s="20" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="P46" s="20" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="Q46" s="20" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="R46" s="20" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
       <c r="S46" s="19" t="s">
         <v>58</v>
       </c>
       <c r="T46" s="20" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="U46" s="4" t="s">
         <v>60</v>
@@ -10769,22 +10793,22 @@
       <c r="Y46" s="17"/>
       <c r="Z46" s="17"/>
       <c r="AA46" s="4" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="AB46" s="4" t="s">
-        <v>766</v>
+        <v>772</v>
       </c>
       <c r="AC46" s="4" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="AD46" s="4" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
       <c r="AE46" s="4" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
       <c r="AF46" s="4" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
       <c r="AG46" s="4"/>
       <c r="AH46" s="4"/>
@@ -10797,10 +10821,10 @@
     </row>
     <row r="47" ht="42" customHeight="1" spans="1:38">
       <c r="A47" s="19" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="C47" s="20" t="s">
         <v>87</v>
@@ -10809,16 +10833,16 @@
         <v>88</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="F47" s="21" t="s">
-        <v>772</v>
+        <v>778</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="I47" s="4" t="s">
         <v>93</v>
@@ -10827,34 +10851,34 @@
         <v>49</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="L47" s="4" t="s">
         <v>241</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="N47" s="20" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="O47" s="20" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="P47" s="20" t="s">
-        <v>778</v>
+        <v>784</v>
       </c>
       <c r="Q47" s="20" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="R47" s="20" t="s">
-        <v>780</v>
+        <v>786</v>
       </c>
       <c r="S47" s="19" t="s">
         <v>58</v>
       </c>
       <c r="T47" s="20" t="s">
-        <v>781</v>
+        <v>787</v>
       </c>
       <c r="U47" s="4" t="s">
         <v>60</v>
@@ -10871,22 +10895,22 @@
       <c r="Y47" s="17"/>
       <c r="Z47" s="17"/>
       <c r="AA47" s="4" t="s">
-        <v>782</v>
+        <v>788</v>
       </c>
       <c r="AB47" s="4" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="AC47" s="4" t="s">
-        <v>784</v>
+        <v>790</v>
       </c>
       <c r="AD47" s="4" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="AE47" s="4" t="s">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="AF47" s="4" t="s">
-        <v>787</v>
+        <v>793</v>
       </c>
       <c r="AG47" s="4"/>
       <c r="AH47" s="4"/>
@@ -10899,10 +10923,10 @@
     </row>
     <row r="48" ht="42" customHeight="1" spans="1:38">
       <c r="A48" s="19" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="C48" s="20" t="s">
         <v>106</v>
@@ -10911,16 +10935,16 @@
         <v>107</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="F48" s="21" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>112</v>
@@ -10929,34 +10953,34 @@
         <v>49</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>792</v>
+        <v>798</v>
       </c>
       <c r="L48" s="4" t="s">
         <v>241</v>
       </c>
       <c r="M48" s="4" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="N48" s="20" t="s">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="O48" s="20" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="P48" s="20" t="s">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="Q48" s="20" t="s">
-        <v>796</v>
+        <v>802</v>
       </c>
       <c r="R48" s="20" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="S48" s="19" t="s">
         <v>58</v>
       </c>
       <c r="T48" s="20" t="s">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="U48" s="4" t="s">
         <v>60</v>
@@ -10973,22 +10997,22 @@
       <c r="Y48" s="17"/>
       <c r="Z48" s="17"/>
       <c r="AA48" s="4" t="s">
-        <v>799</v>
+        <v>805</v>
       </c>
       <c r="AB48" s="4" t="s">
-        <v>800</v>
+        <v>806</v>
       </c>
       <c r="AC48" s="4" t="s">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="AD48" s="4" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="AE48" s="4" t="s">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="AF48" s="4" t="s">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="AG48" s="4"/>
       <c r="AH48" s="4"/>
@@ -11001,10 +11025,10 @@
     </row>
     <row r="49" ht="42" customHeight="1" spans="1:38">
       <c r="A49" s="19" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="C49" s="20" t="s">
         <v>125</v>
@@ -11013,16 +11037,16 @@
         <v>126</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>805</v>
+        <v>811</v>
       </c>
       <c r="F49" s="21" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="I49" s="4" t="s">
         <v>131</v>
@@ -11031,34 +11055,34 @@
         <v>49</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>809</v>
+        <v>815</v>
       </c>
       <c r="L49" s="4" t="s">
         <v>241</v>
       </c>
       <c r="M49" s="4" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="N49" s="20" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="O49" s="20" t="s">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="P49" s="20" t="s">
-        <v>812</v>
+        <v>818</v>
       </c>
       <c r="Q49" s="20" t="s">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="R49" s="20" t="s">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="S49" s="19" t="s">
         <v>58</v>
       </c>
       <c r="T49" s="20" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="U49" s="4" t="s">
         <v>60</v>
@@ -11075,22 +11099,22 @@
       <c r="Y49" s="17"/>
       <c r="Z49" s="17"/>
       <c r="AA49" s="4" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="AB49" s="4" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="AC49" s="4" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="AD49" s="4" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="AE49" s="4" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="AF49" s="4" t="s">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="AG49" s="4"/>
       <c r="AH49" s="4"/>
@@ -11103,10 +11127,10 @@
     </row>
     <row r="50" ht="42" customHeight="1" spans="1:38">
       <c r="A50" s="19" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="C50" s="20" t="s">
         <v>144</v>
@@ -11115,16 +11139,16 @@
         <v>145</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="F50" s="21" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="I50" s="4" t="s">
         <v>48</v>
@@ -11133,34 +11157,34 @@
         <v>49</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="L50" s="4" t="s">
         <v>241</v>
       </c>
       <c r="M50" s="4" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="N50" s="20" t="s">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="O50" s="20" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="P50" s="20" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="Q50" s="20" t="s">
-        <v>830</v>
+        <v>836</v>
       </c>
       <c r="R50" s="20" t="s">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="S50" s="19" t="s">
         <v>58</v>
       </c>
       <c r="T50" s="20" t="s">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="U50" s="4" t="s">
         <v>60</v>
@@ -11177,22 +11201,22 @@
       <c r="Y50" s="17"/>
       <c r="Z50" s="17"/>
       <c r="AA50" s="4" t="s">
-        <v>833</v>
+        <v>839</v>
       </c>
       <c r="AB50" s="4" t="s">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="AC50" s="4" t="s">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="AD50" s="4" t="s">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="AE50" s="4" t="s">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="AF50" s="4" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="AG50" s="4"/>
       <c r="AH50" s="4"/>
@@ -11205,10 +11229,10 @@
     </row>
     <row r="51" ht="42" customHeight="1" spans="1:38">
       <c r="A51" s="19" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="C51" s="20" t="s">
         <v>162</v>
@@ -11217,16 +11241,16 @@
         <v>163</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="F51" s="21" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="I51" s="4" t="s">
         <v>74</v>
@@ -11235,34 +11259,34 @@
         <v>49</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="L51" s="4" t="s">
         <v>241</v>
       </c>
       <c r="M51" s="4" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="N51" s="20" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="O51" s="20" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="P51" s="20" t="s">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="Q51" s="20" t="s">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="R51" s="20" t="s">
-        <v>848</v>
+        <v>854</v>
       </c>
       <c r="S51" s="19" t="s">
         <v>58</v>
       </c>
       <c r="T51" s="20" t="s">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="U51" s="4" t="s">
         <v>60</v>
@@ -11279,22 +11303,22 @@
       <c r="Y51" s="17"/>
       <c r="Z51" s="17"/>
       <c r="AA51" s="4" t="s">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="AB51" s="4" t="s">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="AC51" s="4" t="s">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="AD51" s="4" t="s">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="AE51" s="4" t="s">
-        <v>854</v>
+        <v>860</v>
       </c>
       <c r="AF51" s="4" t="s">
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="AG51" s="4"/>
       <c r="AH51" s="4"/>
@@ -11307,10 +11331,10 @@
     </row>
     <row r="52" ht="42" customHeight="1" spans="1:38">
       <c r="A52" s="19" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="C52" s="20" t="s">
         <v>180</v>
@@ -11319,16 +11343,16 @@
         <v>181</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="F52" s="21" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="I52" s="4" t="s">
         <v>93</v>
@@ -11337,34 +11361,34 @@
         <v>49</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="L52" s="4" t="s">
         <v>241</v>
       </c>
       <c r="M52" s="4" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="N52" s="20" t="s">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="O52" s="20" t="s">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="P52" s="20" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="Q52" s="20" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="R52" s="20" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="S52" s="19" t="s">
         <v>58</v>
       </c>
       <c r="T52" s="20" t="s">
-        <v>866</v>
+        <v>872</v>
       </c>
       <c r="U52" s="4" t="s">
         <v>60</v>
@@ -11381,22 +11405,22 @@
       <c r="Y52" s="17"/>
       <c r="Z52" s="17"/>
       <c r="AA52" s="4" t="s">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="AB52" s="4" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="AC52" s="4" t="s">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="AD52" s="4" t="s">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="AE52" s="4" t="s">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="AF52" s="4" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="AG52" s="4"/>
       <c r="AH52" s="4"/>
@@ -11409,10 +11433,10 @@
     </row>
     <row r="53" ht="42" customHeight="1" spans="1:38">
       <c r="A53" s="19" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="B53" s="20" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="C53" s="20" t="s">
         <v>198</v>
@@ -11421,16 +11445,16 @@
         <v>199</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>873</v>
+        <v>879</v>
       </c>
       <c r="F53" s="21" t="s">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="I53" s="4" t="s">
         <v>112</v>
@@ -11439,34 +11463,34 @@
         <v>49</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="L53" s="4" t="s">
         <v>241</v>
       </c>
       <c r="M53" s="4" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="N53" s="20" t="s">
-        <v>878</v>
+        <v>884</v>
       </c>
       <c r="O53" s="20" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="P53" s="20" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="Q53" s="20" t="s">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="R53" s="20" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="S53" s="19" t="s">
         <v>58</v>
       </c>
       <c r="T53" s="20" t="s">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="U53" s="4" t="s">
         <v>60</v>
@@ -11483,22 +11507,22 @@
       <c r="Y53" s="17"/>
       <c r="Z53" s="17"/>
       <c r="AA53" s="4" t="s">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="AB53" s="4" t="s">
-        <v>885</v>
+        <v>891</v>
       </c>
       <c r="AC53" s="4" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
       <c r="AD53" s="4" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="AE53" s="4" t="s">
-        <v>888</v>
+        <v>894</v>
       </c>
       <c r="AF53" s="4" t="s">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="AG53" s="4"/>
       <c r="AH53" s="4"/>
@@ -11511,10 +11535,10 @@
     </row>
     <row r="54" ht="42" customHeight="1" spans="1:38">
       <c r="A54" s="19" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="C54" s="20" t="s">
         <v>216</v>
@@ -11523,16 +11547,16 @@
         <v>217</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="F54" s="21" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="I54" s="4" t="s">
         <v>131</v>
@@ -11541,34 +11565,34 @@
         <v>49</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>894</v>
+        <v>900</v>
       </c>
       <c r="L54" s="4" t="s">
         <v>241</v>
       </c>
       <c r="M54" s="4" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="N54" s="20" t="s">
-        <v>895</v>
+        <v>901</v>
       </c>
       <c r="O54" s="20" t="s">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="P54" s="20" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="Q54" s="20" t="s">
-        <v>898</v>
+        <v>904</v>
       </c>
       <c r="R54" s="20" t="s">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="S54" s="19" t="s">
         <v>58</v>
       </c>
       <c r="T54" s="20" t="s">
-        <v>900</v>
+        <v>906</v>
       </c>
       <c r="U54" s="4" t="s">
         <v>60</v>
@@ -11585,22 +11609,22 @@
       <c r="Y54" s="17"/>
       <c r="Z54" s="17"/>
       <c r="AA54" s="4" t="s">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="AB54" s="4" t="s">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="AC54" s="4" t="s">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="AD54" s="4" t="s">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="AE54" s="4" t="s">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="AF54" s="4" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="AG54" s="4"/>
       <c r="AH54" s="4"/>
@@ -15662,7 +15686,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>907</v>
+        <v>913</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -15671,7 +15695,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:5">
       <c r="A2" s="8" t="s">
-        <v>908</v>
+        <v>914</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -15687,1141 +15711,1141 @@
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:5">
       <c r="A4" s="10" t="s">
-        <v>909</v>
+        <v>915</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>913</v>
+        <v>919</v>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1" spans="1:5">
       <c r="A5" s="11" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>915</v>
+        <v>921</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>917</v>
+        <v>923</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1" spans="1:5">
       <c r="A6" s="11" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>921</v>
+        <v>927</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>922</v>
+        <v>928</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1" spans="1:5">
       <c r="A7" s="11" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>923</v>
+        <v>929</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>924</v>
+        <v>930</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>925</v>
+        <v>931</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1" spans="1:5">
       <c r="A8" s="11" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>927</v>
+        <v>933</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>928</v>
+        <v>934</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>929</v>
+        <v>935</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>930</v>
+        <v>936</v>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1" spans="1:5">
       <c r="A9" s="11" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>933</v>
+        <v>939</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>934</v>
+        <v>940</v>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1" spans="1:5">
       <c r="A10" s="11" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>938</v>
+        <v>944</v>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1" spans="1:5">
       <c r="A11" s="11" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:5">
       <c r="A12" s="11" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1" spans="1:5">
       <c r="A13" s="11" t="s">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>946</v>
+        <v>952</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>7</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>948</v>
+        <v>954</v>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1" spans="1:5">
       <c r="A14" s="11" t="s">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>951</v>
+        <v>957</v>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1" spans="1:5">
       <c r="A15" s="11" t="s">
-        <v>952</v>
+        <v>958</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>954</v>
+        <v>960</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>955</v>
+        <v>961</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>956</v>
+        <v>962</v>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1" spans="1:5">
       <c r="A16" s="11" t="s">
-        <v>952</v>
+        <v>958</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>958</v>
+        <v>964</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>960</v>
+        <v>966</v>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1" spans="1:5">
       <c r="A17" s="11" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>964</v>
+        <v>970</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>965</v>
+        <v>971</v>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1" spans="1:5">
       <c r="A18" s="11" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>966</v>
+        <v>972</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>967</v>
+        <v>973</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>969</v>
+        <v>975</v>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1" spans="1:5">
       <c r="A19" s="11" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>970</v>
+        <v>976</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>971</v>
+        <v>977</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>973</v>
+        <v>979</v>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1" spans="1:5">
       <c r="A20" s="11" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>974</v>
+        <v>980</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1" spans="1:5">
       <c r="A21" s="11" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>980</v>
+        <v>986</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>982</v>
+        <v>988</v>
       </c>
     </row>
     <row r="22" ht="42" customHeight="1" spans="1:5">
       <c r="A22" s="11" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>984</v>
+        <v>990</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>985</v>
+        <v>991</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>982</v>
+        <v>988</v>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1" spans="1:5">
       <c r="A23" s="11" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>986</v>
+        <v>992</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>988</v>
+        <v>994</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>989</v>
+        <v>995</v>
       </c>
     </row>
     <row r="24" ht="42" customHeight="1" spans="1:5">
       <c r="A24" s="11" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>990</v>
+        <v>996</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>991</v>
+        <v>997</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>992</v>
+        <v>998</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
     </row>
     <row r="25" ht="42" customHeight="1" spans="1:5">
       <c r="A25" s="11" t="s">
-        <v>994</v>
+        <v>1000</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>995</v>
+        <v>1001</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>996</v>
+        <v>1002</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>997</v>
+        <v>1003</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>998</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="26" ht="42" customHeight="1" spans="1:5">
       <c r="A26" s="11" t="s">
-        <v>994</v>
+        <v>1000</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>1000</v>
+        <v>1006</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="27" ht="42" customHeight="1" spans="1:5">
       <c r="A27" s="11" t="s">
-        <v>994</v>
+        <v>1000</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>1003</v>
+        <v>1009</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>1004</v>
+        <v>1010</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="28" ht="42" customHeight="1" spans="1:5">
       <c r="A28" s="11" t="s">
-        <v>994</v>
+        <v>1000</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>1006</v>
+        <v>1012</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>1008</v>
+        <v>1014</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>1009</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="29" ht="42" customHeight="1" spans="1:5">
       <c r="A29" s="11" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>1011</v>
+        <v>1017</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>1012</v>
+        <v>1018</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>1013</v>
+        <v>1019</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="30" ht="42" customHeight="1" spans="1:5">
       <c r="A30" s="11" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>1016</v>
+        <v>1022</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="31" ht="42" customHeight="1" spans="1:5">
       <c r="A31" s="11" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>1018</v>
+        <v>1024</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>1019</v>
+        <v>1025</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>1020</v>
+        <v>1026</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="32" ht="42" customHeight="1" spans="1:5">
       <c r="A32" s="11" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>1022</v>
+        <v>1028</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>1023</v>
+        <v>1029</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="33" ht="42" customHeight="1" spans="1:5">
       <c r="A33" s="11" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>1024</v>
+        <v>1030</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>1026</v>
+        <v>1032</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="34" ht="42" customHeight="1" spans="1:5">
       <c r="A34" s="11" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="B34" s="11" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E34" s="13" t="s">
         <v>1027</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>1028</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>1029</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>1021</v>
       </c>
     </row>
     <row r="35" ht="42" customHeight="1" spans="1:5">
       <c r="A35" s="11" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>1030</v>
+        <v>1036</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>1031</v>
+        <v>1037</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>1032</v>
+        <v>1038</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="36" ht="42" customHeight="1" spans="1:5">
       <c r="A36" s="11" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>1033</v>
+        <v>1039</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>1034</v>
+        <v>1040</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>1035</v>
+        <v>1041</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="37" ht="42" customHeight="1" spans="1:5">
       <c r="A37" s="11" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>1036</v>
+        <v>1042</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>1037</v>
+        <v>1043</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>1038</v>
+        <v>1044</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="38" ht="42" customHeight="1" spans="1:5">
       <c r="A38" s="11" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>1039</v>
+        <v>1045</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>1040</v>
+        <v>1046</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>1041</v>
+        <v>1047</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="39" ht="42" customHeight="1" spans="1:5">
       <c r="A39" s="11" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>1042</v>
+        <v>1048</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>1043</v>
+        <v>1049</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>1044</v>
+        <v>1050</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="40" ht="42" customHeight="1" spans="1:5">
       <c r="A40" s="11" t="s">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>1046</v>
+        <v>1052</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>1048</v>
+        <v>1054</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>965</v>
+        <v>971</v>
       </c>
     </row>
     <row r="41" ht="42" customHeight="1" spans="1:5">
       <c r="A41" s="11" t="s">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>1049</v>
+        <v>1055</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>1050</v>
+        <v>1056</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>1051</v>
+        <v>1057</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>1052</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="42" ht="42" customHeight="1" spans="1:5">
       <c r="A42" s="11" t="s">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>1054</v>
+        <v>1060</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>1055</v>
+        <v>1061</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>1056</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="43" ht="42" customHeight="1" spans="1:5">
       <c r="A43" s="11" t="s">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>1058</v>
+        <v>1064</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>1059</v>
+        <v>1065</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>1060</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="44" ht="42" customHeight="1" spans="1:5">
       <c r="A44" s="11" t="s">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="45" ht="42" customHeight="1" spans="1:5">
       <c r="A45" s="11" t="s">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>1065</v>
+        <v>1071</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>1066</v>
+        <v>1072</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>1067</v>
+        <v>1073</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>1068</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="46" ht="42" customHeight="1" spans="1:5">
       <c r="A46" s="11" t="s">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>1069</v>
+        <v>1075</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>1070</v>
+        <v>1076</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>1071</v>
+        <v>1077</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>1072</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="47" ht="42" customHeight="1" spans="1:5">
       <c r="A47" s="11" t="s">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>1073</v>
+        <v>1079</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>1074</v>
+        <v>1080</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>1075</v>
+        <v>1081</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>1076</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="48" ht="42" customHeight="1" spans="1:5">
       <c r="A48" s="11" t="s">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>1077</v>
+        <v>1083</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>1078</v>
+        <v>1084</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>1079</v>
+        <v>1085</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>1080</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="49" ht="42" customHeight="1" spans="1:5">
       <c r="A49" s="11" t="s">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>1081</v>
+        <v>1087</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>1084</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="50" ht="42" customHeight="1" spans="1:5">
       <c r="A50" s="11" t="s">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>1085</v>
+        <v>1091</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>1086</v>
+        <v>1092</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>1088</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="51" ht="42" customHeight="1" spans="1:5">
       <c r="A51" s="11" t="s">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>1089</v>
+        <v>1095</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>1090</v>
+        <v>1096</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>1091</v>
+        <v>1097</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>1092</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="52" ht="42" customHeight="1" spans="1:5">
       <c r="A52" s="11" t="s">
-        <v>1093</v>
+        <v>1099</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>1094</v>
+        <v>1100</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="53" ht="42" customHeight="1" spans="1:5">
       <c r="A53" s="11" t="s">
-        <v>1093</v>
+        <v>1099</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>1098</v>
+        <v>1104</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>1099</v>
+        <v>1105</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>1100</v>
+        <v>1106</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>1101</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="54" ht="42" customHeight="1" spans="1:5">
       <c r="A54" s="11" t="s">
-        <v>1093</v>
+        <v>1099</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>1102</v>
+        <v>1108</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>1103</v>
+        <v>1109</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>1104</v>
+        <v>1110</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>1105</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="55" ht="42" customHeight="1" spans="1:5">
       <c r="A55" s="11" t="s">
-        <v>1093</v>
+        <v>1099</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>1107</v>
+        <v>1113</v>
       </c>
       <c r="D55" s="18">
         <v>8</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>1108</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="56" ht="42" customHeight="1" spans="1:5">
       <c r="A56" s="11" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>1110</v>
+        <v>1116</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>1111</v>
+        <v>1117</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>1112</v>
+        <v>1118</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>965</v>
+        <v>971</v>
       </c>
     </row>
     <row r="57" ht="42" customHeight="1" spans="1:5">
       <c r="A57" s="11" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>1113</v>
+        <v>1119</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>1115</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="58" ht="42" customHeight="1" spans="1:5">
       <c r="A58" s="11" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>1116</v>
+        <v>1122</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>1117</v>
+        <v>1123</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>1119</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="59" ht="42" customHeight="1" spans="1:5">
       <c r="A59" s="11" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>1121</v>
+        <v>1127</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>1122</v>
+        <v>1128</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>1123</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="60" ht="42" customHeight="1" spans="1:5">
       <c r="A60" s="11" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>1124</v>
+        <v>1130</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>1125</v>
+        <v>1131</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>1126</v>
+        <v>1132</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>1127</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="61" ht="42" customHeight="1" spans="1:5">
       <c r="A61" s="11" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>1128</v>
+        <v>1134</v>
       </c>
       <c r="C61" s="11" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E61" s="13" t="s">
         <v>1129</v>
-      </c>
-      <c r="D61" s="12" t="s">
-        <v>1130</v>
-      </c>
-      <c r="E61" s="13" t="s">
-        <v>1123</v>
       </c>
     </row>
     <row r="62" ht="42" customHeight="1" spans="1:5">
       <c r="A62" s="11" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>1131</v>
+        <v>1137</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>1132</v>
+        <v>1138</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>1133</v>
+        <v>1139</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>1134</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="63" ht="42" customHeight="1" spans="1:5">
       <c r="A63" s="11" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>1135</v>
+        <v>1141</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>1136</v>
+        <v>1142</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>1137</v>
+        <v>1143</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>1123</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="64" ht="42" customHeight="1" spans="1:5">
       <c r="A64" s="11" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>1138</v>
+        <v>1144</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>1139</v>
+        <v>1145</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>1140</v>
+        <v>1146</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>1141</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="65" ht="42" customHeight="1" spans="1:5">
       <c r="A65" s="11" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>1142</v>
+        <v>1148</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>1143</v>
+        <v>1149</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>1144</v>
+        <v>1150</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>1123</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="66" ht="42" customHeight="1" spans="1:5">
       <c r="A66" s="11" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>1145</v>
+        <v>1151</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>1146</v>
+        <v>1152</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>1147</v>
+        <v>1153</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>1148</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="67" ht="42" customHeight="1" spans="1:5">
       <c r="A67" s="11" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>1149</v>
+        <v>1155</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>1150</v>
+        <v>1156</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>1151</v>
+        <v>1157</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>1123</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="68" ht="42" customHeight="1" spans="1:5">
       <c r="A68" s="11" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>1152</v>
+        <v>1158</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>1153</v>
+        <v>1159</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>1154</v>
+        <v>1160</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>1155</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="69" ht="42" customHeight="1" spans="1:5">
       <c r="A69" s="11" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>1156</v>
+        <v>1162</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>1157</v>
+        <v>1163</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>1158</v>
+        <v>1164</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>1123</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="70" ht="42" customHeight="1" spans="1:5">
       <c r="A70" s="11" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>1159</v>
+        <v>1165</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>1160</v>
+        <v>1166</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>1161</v>
+        <v>1167</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>1162</v>
+        <v>1168</v>
       </c>
     </row>
   </sheetData>
@@ -16880,7 +16904,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:40">
       <c r="A1" s="14" t="s">
-        <v>1163</v>
+        <v>1169</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
@@ -16924,7 +16948,7 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:40">
       <c r="A2" s="15" t="s">
-        <v>1164</v>
+        <v>1170</v>
       </c>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -17006,13 +17030,13 @@
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:40">
       <c r="A4" s="3" t="s">
-        <v>1165</v>
+        <v>1171</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1166</v>
+        <v>1172</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1167</v>
+        <v>1173</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>7</v>
@@ -17021,22 +17045,22 @@
         <v>8</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1168</v>
+        <v>1174</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>1169</v>
+        <v>1175</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>1170</v>
+        <v>1176</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>1171</v>
+        <v>1177</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>12</v>
@@ -17045,73 +17069,73 @@
         <v>13</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>1172</v>
+        <v>1178</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>1173</v>
+        <v>1179</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>1175</v>
+        <v>1181</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>1176</v>
+        <v>1182</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>1177</v>
+        <v>1183</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>1178</v>
+        <v>1184</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>1179</v>
+        <v>1185</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>1180</v>
+        <v>1186</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>1181</v>
+        <v>1187</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>1182</v>
+        <v>1188</v>
       </c>
       <c r="Y4" s="3" t="s">
-        <v>1183</v>
+        <v>1189</v>
       </c>
       <c r="Z4" s="3" t="s">
-        <v>1184</v>
+        <v>1190</v>
       </c>
       <c r="AA4" s="3" t="s">
-        <v>1185</v>
+        <v>1191</v>
       </c>
       <c r="AB4" s="3" t="s">
-        <v>1186</v>
+        <v>1192</v>
       </c>
       <c r="AC4" s="3" t="s">
-        <v>1121</v>
+        <v>1127</v>
       </c>
       <c r="AD4" s="3" t="s">
-        <v>1187</v>
+        <v>1193</v>
       </c>
       <c r="AE4" s="3" t="s">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="AF4" s="3" t="s">
-        <v>1188</v>
+        <v>1194</v>
       </c>
       <c r="AG4" s="3" t="s">
-        <v>1136</v>
+        <v>1142</v>
       </c>
       <c r="AH4" s="3" t="s">
-        <v>1189</v>
+        <v>1195</v>
       </c>
       <c r="AI4" s="3" t="s">
-        <v>1190</v>
+        <v>1196</v>
       </c>
       <c r="AJ4" s="3" t="s">
-        <v>1191</v>
+        <v>1197</v>
       </c>
       <c r="AK4" s="3" t="s">
         <v>22</v>
@@ -17134,112 +17158,112 @@
         <v>41</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1192</v>
+        <v>1198</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>1193</v>
+        <v>1199</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>1194</v>
+        <v>1200</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>1195</v>
+        <v>1201</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>1196</v>
+        <v>1202</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>1198</v>
+        <v>1204</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>1199</v>
+        <v>1205</v>
       </c>
       <c r="K5" s="16" t="s">
-        <v>1200</v>
+        <v>1206</v>
       </c>
       <c r="L5" s="16" t="s">
-        <v>1201</v>
+        <v>1207</v>
       </c>
       <c r="M5" s="16" t="s">
-        <v>1202</v>
+        <v>1208</v>
       </c>
       <c r="N5" s="16" t="s">
-        <v>1203</v>
+        <v>1209</v>
       </c>
       <c r="O5" s="16" t="s">
-        <v>1204</v>
+        <v>1210</v>
       </c>
       <c r="P5" s="16" t="s">
-        <v>1205</v>
+        <v>1211</v>
       </c>
       <c r="Q5" s="16" t="s">
-        <v>1206</v>
+        <v>1212</v>
       </c>
       <c r="R5" s="16" t="s">
-        <v>1207</v>
+        <v>1213</v>
       </c>
       <c r="S5" s="16" t="s">
-        <v>1208</v>
+        <v>1214</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>1209</v>
+        <v>1215</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>1210</v>
+        <v>1216</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>1211</v>
+        <v>1217</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>1212</v>
+        <v>1218</v>
       </c>
       <c r="X5" s="16" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="Y5" s="4" t="s">
-        <v>1214</v>
+        <v>1220</v>
       </c>
       <c r="Z5" s="4" t="s">
-        <v>1112</v>
+        <v>1118</v>
       </c>
       <c r="AA5" s="4" t="s">
-        <v>1215</v>
+        <v>1221</v>
       </c>
       <c r="AB5" s="16" t="s">
-        <v>1216</v>
+        <v>1222</v>
       </c>
       <c r="AC5" s="16" t="s">
-        <v>1217</v>
+        <v>1223</v>
       </c>
       <c r="AD5" s="16" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="AE5" s="16" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="AF5" s="16" t="s">
-        <v>1220</v>
+        <v>1226</v>
       </c>
       <c r="AG5" s="16" t="s">
-        <v>1221</v>
+        <v>1227</v>
       </c>
       <c r="AH5" s="16" t="s">
-        <v>1222</v>
+        <v>1228</v>
       </c>
       <c r="AI5" s="4" t="s">
-        <v>1223</v>
+        <v>1229</v>
       </c>
       <c r="AJ5" s="4" t="s">
-        <v>1224</v>
+        <v>1230</v>
       </c>
       <c r="AK5" s="4" t="s">
         <v>60</v>
       </c>
       <c r="AL5" s="4" t="s">
-        <v>1225</v>
+        <v>1231</v>
       </c>
       <c r="AM5" s="4">
         <v>1</v>
@@ -17256,112 +17280,112 @@
         <v>235</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>1201</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>1235</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>1236</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>1205</v>
+      </c>
+      <c r="K6" s="16" t="s">
+        <v>1237</v>
+      </c>
+      <c r="L6" s="16" t="s">
+        <v>1238</v>
+      </c>
+      <c r="M6" s="16" t="s">
+        <v>1239</v>
+      </c>
+      <c r="N6" s="16" t="s">
+        <v>1209</v>
+      </c>
+      <c r="O6" s="16" t="s">
+        <v>1210</v>
+      </c>
+      <c r="P6" s="16" t="s">
+        <v>1211</v>
+      </c>
+      <c r="Q6" s="16" t="s">
+        <v>1240</v>
+      </c>
+      <c r="R6" s="16" t="s">
+        <v>1213</v>
+      </c>
+      <c r="S6" s="16" t="s">
+        <v>1241</v>
+      </c>
+      <c r="T6" s="4" t="s">
+        <v>1215</v>
+      </c>
+      <c r="U6" s="4" t="s">
+        <v>1242</v>
+      </c>
+      <c r="V6" s="4" t="s">
+        <v>1217</v>
+      </c>
+      <c r="W6" s="4" t="s">
+        <v>1218</v>
+      </c>
+      <c r="X6" s="16" t="s">
+        <v>1243</v>
+      </c>
+      <c r="Y6" s="4" t="s">
+        <v>1220</v>
+      </c>
+      <c r="Z6" s="4" t="s">
+        <v>1118</v>
+      </c>
+      <c r="AA6" s="4" t="s">
+        <v>1244</v>
+      </c>
+      <c r="AB6" s="16" t="s">
+        <v>1222</v>
+      </c>
+      <c r="AC6" s="16" t="s">
+        <v>1245</v>
+      </c>
+      <c r="AD6" s="16" t="s">
+        <v>1224</v>
+      </c>
+      <c r="AE6" s="16" t="s">
+        <v>1225</v>
+      </c>
+      <c r="AF6" s="16" t="s">
         <v>1226</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="AG6" s="16" t="s">
         <v>1227</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="AH6" s="4" t="s">
         <v>1228</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>1195</v>
-      </c>
-      <c r="G6" s="4" t="s">
+      <c r="AI6" s="4" t="s">
         <v>1229</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="AJ6" s="4" t="s">
         <v>1230</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>1198</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>1199</v>
-      </c>
-      <c r="K6" s="16" t="s">
-        <v>1231</v>
-      </c>
-      <c r="L6" s="16" t="s">
-        <v>1232</v>
-      </c>
-      <c r="M6" s="16" t="s">
-        <v>1233</v>
-      </c>
-      <c r="N6" s="16" t="s">
-        <v>1203</v>
-      </c>
-      <c r="O6" s="16" t="s">
-        <v>1204</v>
-      </c>
-      <c r="P6" s="16" t="s">
-        <v>1205</v>
-      </c>
-      <c r="Q6" s="16" t="s">
-        <v>1234</v>
-      </c>
-      <c r="R6" s="16" t="s">
-        <v>1207</v>
-      </c>
-      <c r="S6" s="16" t="s">
-        <v>1235</v>
-      </c>
-      <c r="T6" s="4" t="s">
-        <v>1209</v>
-      </c>
-      <c r="U6" s="4" t="s">
-        <v>1236</v>
-      </c>
-      <c r="V6" s="4" t="s">
-        <v>1211</v>
-      </c>
-      <c r="W6" s="4" t="s">
-        <v>1212</v>
-      </c>
-      <c r="X6" s="16" t="s">
-        <v>1237</v>
-      </c>
-      <c r="Y6" s="4" t="s">
-        <v>1214</v>
-      </c>
-      <c r="Z6" s="4" t="s">
-        <v>1112</v>
-      </c>
-      <c r="AA6" s="4" t="s">
-        <v>1238</v>
-      </c>
-      <c r="AB6" s="16" t="s">
-        <v>1216</v>
-      </c>
-      <c r="AC6" s="16" t="s">
-        <v>1239</v>
-      </c>
-      <c r="AD6" s="16" t="s">
-        <v>1218</v>
-      </c>
-      <c r="AE6" s="16" t="s">
-        <v>1219</v>
-      </c>
-      <c r="AF6" s="16" t="s">
-        <v>1220</v>
-      </c>
-      <c r="AG6" s="16" t="s">
-        <v>1221</v>
-      </c>
-      <c r="AH6" s="4" t="s">
-        <v>1222</v>
-      </c>
-      <c r="AI6" s="4" t="s">
-        <v>1223</v>
-      </c>
-      <c r="AJ6" s="4" t="s">
-        <v>1224</v>
       </c>
       <c r="AK6" s="4" t="s">
         <v>60</v>
       </c>
       <c r="AL6" s="4" t="s">
-        <v>1225</v>
+        <v>1231</v>
       </c>
       <c r="AM6" s="4">
         <v>2</v>
@@ -17378,112 +17402,112 @@
         <v>409</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1240</v>
+        <v>1246</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>1241</v>
+        <v>1247</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>1195</v>
+        <v>1201</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>1243</v>
+        <v>1249</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>1244</v>
+        <v>1250</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>1198</v>
+        <v>1204</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>1199</v>
+        <v>1205</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="L7" s="16" t="s">
-        <v>1246</v>
+        <v>1252</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>1247</v>
+        <v>1253</v>
       </c>
       <c r="N7" s="16" t="s">
-        <v>1203</v>
+        <v>1209</v>
       </c>
       <c r="O7" s="16" t="s">
-        <v>1204</v>
+        <v>1210</v>
       </c>
       <c r="P7" s="16" t="s">
-        <v>1205</v>
+        <v>1211</v>
       </c>
       <c r="Q7" s="16" t="s">
-        <v>1248</v>
+        <v>1254</v>
       </c>
       <c r="R7" s="16" t="s">
-        <v>1249</v>
+        <v>1255</v>
       </c>
       <c r="S7" s="16" t="s">
-        <v>1250</v>
+        <v>1256</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>1209</v>
+        <v>1215</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>1251</v>
+        <v>1257</v>
       </c>
       <c r="V7" s="4" t="s">
-        <v>1211</v>
+        <v>1217</v>
       </c>
       <c r="W7" s="4" t="s">
-        <v>1212</v>
+        <v>1218</v>
       </c>
       <c r="X7" s="16" t="s">
-        <v>1252</v>
+        <v>1258</v>
       </c>
       <c r="Y7" s="4" t="s">
-        <v>1214</v>
+        <v>1220</v>
       </c>
       <c r="Z7" s="4" t="s">
-        <v>1112</v>
+        <v>1118</v>
       </c>
       <c r="AA7" s="4" t="s">
-        <v>1253</v>
+        <v>1259</v>
       </c>
       <c r="AB7" s="16" t="s">
-        <v>1216</v>
+        <v>1222</v>
       </c>
       <c r="AC7" s="16" t="s">
-        <v>1254</v>
+        <v>1260</v>
       </c>
       <c r="AD7" s="16" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="AE7" s="16" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="AF7" s="16" t="s">
-        <v>1220</v>
+        <v>1226</v>
       </c>
       <c r="AG7" s="16" t="s">
-        <v>1221</v>
+        <v>1227</v>
       </c>
       <c r="AH7" s="4" t="s">
-        <v>1222</v>
+        <v>1228</v>
       </c>
       <c r="AI7" s="4" t="s">
-        <v>1223</v>
+        <v>1229</v>
       </c>
       <c r="AJ7" s="4" t="s">
-        <v>1224</v>
+        <v>1230</v>
       </c>
       <c r="AK7" s="4" t="s">
         <v>60</v>
       </c>
       <c r="AL7" s="4" t="s">
-        <v>1225</v>
+        <v>1231</v>
       </c>
       <c r="AM7" s="4">
         <v>3</v>
@@ -17500,112 +17524,112 @@
         <v>582</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1255</v>
+        <v>1261</v>
       </c>
       <c r="D8" s="16" t="s">
+        <v>1262</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>1263</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>1201</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>1265</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>1205</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>1266</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>1267</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>1268</v>
+      </c>
+      <c r="N8" s="16" t="s">
+        <v>1209</v>
+      </c>
+      <c r="O8" s="16" t="s">
+        <v>1210</v>
+      </c>
+      <c r="P8" s="16" t="s">
+        <v>1211</v>
+      </c>
+      <c r="Q8" s="16" t="s">
+        <v>1269</v>
+      </c>
+      <c r="R8" s="16" t="s">
+        <v>1213</v>
+      </c>
+      <c r="S8" s="16" t="s">
         <v>1256</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>1257</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>1195</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>1258</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>1259</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>1198</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>1199</v>
-      </c>
-      <c r="K8" s="16" t="s">
-        <v>1260</v>
-      </c>
-      <c r="L8" s="16" t="s">
-        <v>1261</v>
-      </c>
-      <c r="M8" s="16" t="s">
-        <v>1262</v>
-      </c>
-      <c r="N8" s="16" t="s">
-        <v>1203</v>
-      </c>
-      <c r="O8" s="16" t="s">
-        <v>1204</v>
-      </c>
-      <c r="P8" s="16" t="s">
-        <v>1205</v>
-      </c>
-      <c r="Q8" s="16" t="s">
-        <v>1263</v>
-      </c>
-      <c r="R8" s="16" t="s">
-        <v>1207</v>
-      </c>
-      <c r="S8" s="16" t="s">
-        <v>1250</v>
-      </c>
       <c r="T8" s="4" t="s">
-        <v>1209</v>
+        <v>1215</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>1264</v>
+        <v>1270</v>
       </c>
       <c r="V8" s="4" t="s">
-        <v>1211</v>
+        <v>1217</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>1212</v>
+        <v>1218</v>
       </c>
       <c r="X8" s="16" t="s">
-        <v>1265</v>
+        <v>1271</v>
       </c>
       <c r="Y8" s="4" t="s">
-        <v>1214</v>
+        <v>1220</v>
       </c>
       <c r="Z8" s="4" t="s">
-        <v>1112</v>
+        <v>1118</v>
       </c>
       <c r="AA8" s="4" t="s">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="AB8" s="16" t="s">
-        <v>1216</v>
+        <v>1222</v>
       </c>
       <c r="AC8" s="16" t="s">
-        <v>1267</v>
+        <v>1273</v>
       </c>
       <c r="AD8" s="16" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="AE8" s="16" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="AF8" s="16" t="s">
-        <v>1220</v>
+        <v>1226</v>
       </c>
       <c r="AG8" s="16" t="s">
-        <v>1221</v>
+        <v>1227</v>
       </c>
       <c r="AH8" s="4" t="s">
-        <v>1222</v>
+        <v>1228</v>
       </c>
       <c r="AI8" s="4" t="s">
-        <v>1223</v>
+        <v>1229</v>
       </c>
       <c r="AJ8" s="4" t="s">
-        <v>1224</v>
+        <v>1230</v>
       </c>
       <c r="AK8" s="4" t="s">
         <v>60</v>
       </c>
       <c r="AL8" s="4" t="s">
-        <v>1225</v>
+        <v>1231</v>
       </c>
       <c r="AM8" s="4">
         <v>4</v>
@@ -17616,118 +17640,118 @@
     </row>
     <row r="9" ht="52" customHeight="1" spans="1:40">
       <c r="A9" s="4" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1268</v>
+        <v>1274</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>1269</v>
+        <v>1275</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>1195</v>
+        <v>1201</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>1271</v>
+        <v>1277</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>1272</v>
+        <v>1278</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>1198</v>
+        <v>1204</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>1199</v>
+        <v>1205</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>1273</v>
+        <v>1279</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>1275</v>
+        <v>1281</v>
       </c>
       <c r="N9" s="16" t="s">
-        <v>1203</v>
+        <v>1209</v>
       </c>
       <c r="O9" s="16" t="s">
-        <v>1204</v>
+        <v>1210</v>
       </c>
       <c r="P9" s="16" t="s">
-        <v>1205</v>
+        <v>1211</v>
       </c>
       <c r="Q9" s="16" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="R9" s="16" t="s">
-        <v>1207</v>
+        <v>1213</v>
       </c>
       <c r="S9" s="16" t="s">
-        <v>1235</v>
+        <v>1241</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>1209</v>
+        <v>1215</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>1277</v>
+        <v>1283</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>1211</v>
+        <v>1217</v>
       </c>
       <c r="W9" s="4" t="s">
-        <v>1212</v>
+        <v>1218</v>
       </c>
       <c r="X9" s="16" t="s">
-        <v>1278</v>
+        <v>1284</v>
       </c>
       <c r="Y9" s="4" t="s">
-        <v>1214</v>
+        <v>1220</v>
       </c>
       <c r="Z9" s="4" t="s">
-        <v>1112</v>
+        <v>1118</v>
       </c>
       <c r="AA9" s="4" t="s">
-        <v>1279</v>
+        <v>1285</v>
       </c>
       <c r="AB9" s="16" t="s">
-        <v>1216</v>
+        <v>1222</v>
       </c>
       <c r="AC9" s="16" t="s">
-        <v>1280</v>
+        <v>1286</v>
       </c>
       <c r="AD9" s="16" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="AE9" s="16" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="AF9" s="16" t="s">
-        <v>1220</v>
+        <v>1226</v>
       </c>
       <c r="AG9" s="16" t="s">
-        <v>1221</v>
+        <v>1227</v>
       </c>
       <c r="AH9" s="4" t="s">
-        <v>1222</v>
+        <v>1228</v>
       </c>
       <c r="AI9" s="4" t="s">
-        <v>1223</v>
+        <v>1229</v>
       </c>
       <c r="AJ9" s="4" t="s">
-        <v>1224</v>
+        <v>1230</v>
       </c>
       <c r="AK9" s="4" t="s">
         <v>60</v>
       </c>
       <c r="AL9" s="4" t="s">
-        <v>1225</v>
+        <v>1231</v>
       </c>
       <c r="AM9" s="4">
         <v>5</v>
@@ -18618,7 +18642,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>1281</v>
+        <v>1287</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -18628,7 +18652,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6">
       <c r="A2" s="8" t="s">
-        <v>1282</v>
+        <v>1288</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -18646,2282 +18670,2282 @@
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:6">
       <c r="A4" s="10" t="s">
-        <v>1283</v>
+        <v>1289</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1284</v>
+        <v>1290</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>913</v>
+        <v>919</v>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:6">
       <c r="A5" s="11" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>1286</v>
+        <v>1292</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>1287</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:6">
       <c r="A6" s="11" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>946</v>
+        <v>952</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>1288</v>
+        <v>1294</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:6">
       <c r="A7" s="11" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>1290</v>
+        <v>1296</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:6">
       <c r="A8" s="11" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>1291</v>
+        <v>1297</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:6">
       <c r="A9" s="11" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>1292</v>
+        <v>1298</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>1168</v>
+        <v>1174</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>1293</v>
+        <v>1299</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:6">
       <c r="A10" s="11" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>974</v>
+        <v>980</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>1294</v>
+        <v>1300</v>
       </c>
       <c r="E10" s="12" t="s">
+        <v>1301</v>
+      </c>
+      <c r="F10" s="13" t="s">
         <v>1295</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>1289</v>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:6">
       <c r="A11" s="11" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>1296</v>
+        <v>1302</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>1297</v>
+        <v>1303</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>1298</v>
+        <v>1304</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:6">
       <c r="A12" s="11" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>1299</v>
+        <v>1305</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>1300</v>
+        <v>1306</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>1301</v>
+        <v>1307</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:6">
       <c r="A13" s="11" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>1302</v>
+        <v>1308</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>1303</v>
+        <v>1309</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>994</v>
+        <v>1000</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:6">
       <c r="A14" s="11" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>1304</v>
+        <v>1310</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>1305</v>
+        <v>1311</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>1306</v>
+        <v>1312</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:6">
       <c r="A15" s="11" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>1307</v>
+        <v>1313</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>1308</v>
+        <v>1314</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>1309</v>
+        <v>1315</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:6">
       <c r="A16" s="11" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>1310</v>
+        <v>1316</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>1311</v>
+        <v>1317</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>1312</v>
+        <v>1318</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:6">
       <c r="A17" s="11" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>1313</v>
+        <v>1319</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>1314</v>
+        <v>1320</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>1315</v>
+        <v>1321</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:6">
       <c r="A18" s="11" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>1316</v>
+        <v>1322</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>1317</v>
+        <v>1323</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>1318</v>
+        <v>1324</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:6">
       <c r="A19" s="11" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>1319</v>
+        <v>1325</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>1320</v>
+        <v>1326</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>1321</v>
+        <v>1327</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:6">
       <c r="A20" s="11" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>1322</v>
+        <v>1328</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>1323</v>
+        <v>1329</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>1324</v>
+        <v>1330</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:6">
       <c r="A21" s="11" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>1325</v>
+        <v>1331</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>1326</v>
+        <v>1332</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>1327</v>
+        <v>1333</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:6">
       <c r="A22" s="11" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>1328</v>
+        <v>1334</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>1329</v>
+        <v>1335</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>1330</v>
+        <v>1336</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:6">
       <c r="A23" s="11" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>1331</v>
+        <v>1337</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>1332</v>
+        <v>1338</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:6">
       <c r="A24" s="11" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>1333</v>
+        <v>1339</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>1334</v>
+        <v>1340</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>1335</v>
+        <v>1341</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:6">
       <c r="A25" s="11" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>1336</v>
+        <v>1342</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>1337</v>
+        <v>1343</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>1338</v>
+        <v>1344</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:6">
       <c r="A26" s="11" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>1339</v>
+        <v>1345</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>1340</v>
+        <v>1346</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>1341</v>
+        <v>1347</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="27" ht="48" customHeight="1" spans="1:6">
       <c r="A27" s="11" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>1342</v>
+        <v>1348</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>1343</v>
+        <v>1349</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>1344</v>
+        <v>1350</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="28" ht="48" customHeight="1" spans="1:6">
       <c r="A28" s="11" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>1345</v>
+        <v>1351</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>1346</v>
+        <v>1352</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>1347</v>
+        <v>1353</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="29" ht="48" customHeight="1" spans="1:6">
       <c r="A29" s="11" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>1348</v>
+        <v>1354</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>1349</v>
+        <v>1355</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>1350</v>
+        <v>1356</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="30" ht="48" customHeight="1" spans="1:6">
       <c r="A30" s="11" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>1351</v>
+        <v>1357</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>1286</v>
+        <v>1292</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>1287</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="31" ht="48" customHeight="1" spans="1:6">
       <c r="A31" s="11" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>1351</v>
+        <v>1357</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>946</v>
+        <v>952</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>7</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>1352</v>
+        <v>1358</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="32" ht="48" customHeight="1" spans="1:6">
       <c r="A32" s="11" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>1351</v>
+        <v>1357</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>8</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>1353</v>
+        <v>1359</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="33" ht="48" customHeight="1" spans="1:6">
       <c r="A33" s="11" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>1351</v>
+        <v>1357</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>1354</v>
+        <v>1360</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="34" ht="48" customHeight="1" spans="1:6">
       <c r="A34" s="11" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>1351</v>
+        <v>1357</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>1292</v>
+        <v>1298</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>1168</v>
+        <v>1174</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>1355</v>
+        <v>1361</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="35" ht="48" customHeight="1" spans="1:6">
       <c r="A35" s="11" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>1351</v>
+        <v>1357</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>974</v>
+        <v>980</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>1294</v>
+        <v>1300</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>1353</v>
+        <v>1359</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="36" ht="48" customHeight="1" spans="1:6">
       <c r="A36" s="11" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>1351</v>
+        <v>1357</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>1356</v>
+        <v>1362</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>1357</v>
+        <v>1363</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>1358</v>
+        <v>1364</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="37" ht="48" customHeight="1" spans="1:6">
       <c r="A37" s="11" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>1351</v>
+        <v>1357</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>1359</v>
+        <v>1365</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>1360</v>
+        <v>1366</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>1361</v>
+        <v>1367</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="38" ht="48" customHeight="1" spans="1:6">
       <c r="A38" s="11" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>1351</v>
+        <v>1357</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>1362</v>
+        <v>1368</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>1363</v>
+        <v>1369</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>1364</v>
+        <v>1370</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="39" ht="48" customHeight="1" spans="1:6">
       <c r="A39" s="11" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>1351</v>
+        <v>1357</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>1365</v>
+        <v>1371</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>1366</v>
+        <v>1372</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>1367</v>
+        <v>1373</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="40" ht="48" customHeight="1" spans="1:6">
       <c r="A40" s="11" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>1351</v>
+        <v>1357</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>1368</v>
+        <v>1374</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>1369</v>
+        <v>1375</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>1370</v>
+        <v>1376</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="41" ht="48" customHeight="1" spans="1:6">
       <c r="A41" s="11" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>1351</v>
+        <v>1357</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>1371</v>
+        <v>1377</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>1372</v>
+        <v>1378</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>1373</v>
+        <v>1379</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="42" ht="48" customHeight="1" spans="1:6">
       <c r="A42" s="11" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>1351</v>
+        <v>1357</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>1374</v>
+        <v>1380</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>1375</v>
+        <v>1381</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>1376</v>
+        <v>1382</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="43" ht="48" customHeight="1" spans="1:6">
       <c r="A43" s="11" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>1351</v>
+        <v>1357</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>1377</v>
+        <v>1383</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>1379</v>
+        <v>1385</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="44" ht="48" customHeight="1" spans="1:6">
       <c r="A44" s="11" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>1351</v>
+        <v>1357</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>1381</v>
+        <v>1387</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>1382</v>
+        <v>1388</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="45" ht="48" customHeight="1" spans="1:6">
       <c r="A45" s="11" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>1351</v>
+        <v>1357</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>1383</v>
+        <v>1389</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>1384</v>
+        <v>1390</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>1385</v>
+        <v>1391</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="46" ht="48" customHeight="1" spans="1:6">
       <c r="A46" s="11" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>1351</v>
+        <v>1357</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>1386</v>
+        <v>1392</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>1387</v>
+        <v>1393</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>1358</v>
+        <v>1364</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="47" ht="48" customHeight="1" spans="1:6">
       <c r="A47" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>1286</v>
+        <v>1292</v>
       </c>
       <c r="D47" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>1287</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="48" ht="48" customHeight="1" spans="1:6">
       <c r="A48" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>946</v>
+        <v>952</v>
       </c>
       <c r="D48" s="11" t="s">
         <v>7</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>1390</v>
+        <v>1396</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="49" ht="48" customHeight="1" spans="1:6">
       <c r="A49" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="D49" s="11" t="s">
         <v>8</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>1391</v>
+        <v>1397</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="50" ht="48" customHeight="1" spans="1:6">
       <c r="A50" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>1392</v>
+        <v>1398</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="51" ht="48" customHeight="1" spans="1:6">
       <c r="A51" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>1292</v>
+        <v>1298</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>1168</v>
+        <v>1174</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="52" ht="48" customHeight="1" spans="1:6">
       <c r="A52" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>974</v>
+        <v>980</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>1294</v>
+        <v>1300</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>1391</v>
+        <v>1397</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="53" ht="48" customHeight="1" spans="1:6">
       <c r="A53" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>1393</v>
+        <v>1399</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>1395</v>
+        <v>1401</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="54" ht="48" customHeight="1" spans="1:6">
       <c r="A54" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>1296</v>
+        <v>1302</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>1297</v>
+        <v>1303</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>1396</v>
+        <v>1402</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="55" ht="48" customHeight="1" spans="1:6">
       <c r="A55" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>1299</v>
+        <v>1305</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>1300</v>
+        <v>1306</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>1397</v>
+        <v>1403</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="56" ht="48" customHeight="1" spans="1:6">
       <c r="A56" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>1302</v>
+        <v>1308</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>1303</v>
+        <v>1309</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>1398</v>
+        <v>1404</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="57" ht="48" customHeight="1" spans="1:6">
       <c r="A57" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>1304</v>
+        <v>1310</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>1305</v>
+        <v>1311</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>1399</v>
+        <v>1405</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="58" ht="48" customHeight="1" spans="1:6">
       <c r="A58" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>1400</v>
+        <v>1406</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>1401</v>
+        <v>1407</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>1402</v>
+        <v>1408</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="59" ht="48" customHeight="1" spans="1:6">
       <c r="A59" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>1403</v>
+        <v>1409</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>1404</v>
+        <v>1410</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>1405</v>
+        <v>1411</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="60" ht="48" customHeight="1" spans="1:6">
       <c r="A60" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>1406</v>
+        <v>1412</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>1407</v>
+        <v>1413</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>1408</v>
+        <v>1414</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="61" ht="48" customHeight="1" spans="1:6">
       <c r="A61" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>1310</v>
+        <v>1316</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>1311</v>
+        <v>1317</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>1409</v>
+        <v>1415</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="62" ht="48" customHeight="1" spans="1:6">
       <c r="A62" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>1313</v>
+        <v>1319</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>1314</v>
+        <v>1320</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>1410</v>
+        <v>1416</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="63" ht="48" customHeight="1" spans="1:6">
       <c r="A63" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>1316</v>
+        <v>1322</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>1317</v>
+        <v>1323</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>1411</v>
+        <v>1417</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="64" ht="48" customHeight="1" spans="1:6">
       <c r="A64" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>1322</v>
+        <v>1328</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>1323</v>
+        <v>1329</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>1412</v>
+        <v>1418</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="65" ht="48" customHeight="1" spans="1:6">
       <c r="A65" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>1413</v>
+        <v>1419</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>1414</v>
+        <v>1420</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>1415</v>
+        <v>1421</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="66" ht="48" customHeight="1" spans="1:6">
       <c r="A66" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>1416</v>
+        <v>1422</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>1417</v>
+        <v>1423</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="67" ht="48" customHeight="1" spans="1:6">
       <c r="A67" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>1328</v>
+        <v>1334</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>1329</v>
+        <v>1335</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>1418</v>
+        <v>1424</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="68" ht="48" customHeight="1" spans="1:6">
       <c r="A68" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>1419</v>
+        <v>1425</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>1420</v>
+        <v>1426</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>1421</v>
+        <v>1427</v>
       </c>
       <c r="F68" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="69" ht="48" customHeight="1" spans="1:6">
       <c r="A69" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>1422</v>
+        <v>1428</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>1423</v>
+        <v>1429</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="70" ht="48" customHeight="1" spans="1:6">
       <c r="A70" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>1424</v>
+        <v>1430</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>1425</v>
+        <v>1431</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>1426</v>
+        <v>1432</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="71" ht="48" customHeight="1" spans="1:6">
       <c r="A71" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>1427</v>
+        <v>1433</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>1428</v>
+        <v>1434</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>1429</v>
+        <v>1435</v>
       </c>
       <c r="F71" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="72" ht="48" customHeight="1" spans="1:6">
       <c r="A72" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>1430</v>
+        <v>1436</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>1431</v>
+        <v>1437</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="F72" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="73" ht="48" customHeight="1" spans="1:6">
       <c r="A73" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>1432</v>
+        <v>1438</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>1433</v>
+        <v>1439</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>1434</v>
+        <v>1440</v>
       </c>
       <c r="F73" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="74" ht="48" customHeight="1" spans="1:6">
       <c r="A74" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>1435</v>
+        <v>1441</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>1436</v>
+        <v>1442</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>1437</v>
+        <v>1443</v>
       </c>
       <c r="F74" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="75" ht="48" customHeight="1" spans="1:6">
       <c r="A75" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>1438</v>
+        <v>1444</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>1439</v>
+        <v>1445</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="F75" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="76" ht="48" customHeight="1" spans="1:6">
       <c r="A76" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>1440</v>
+        <v>1446</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>1441</v>
+        <v>1447</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>1442</v>
+        <v>1448</v>
       </c>
       <c r="F76" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="77" ht="48" customHeight="1" spans="1:6">
       <c r="A77" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>1443</v>
+        <v>1449</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>1444</v>
+        <v>1450</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>1445</v>
+        <v>1451</v>
       </c>
       <c r="F77" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="78" ht="48" customHeight="1" spans="1:6">
       <c r="A78" s="11" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>1446</v>
+        <v>1452</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>1447</v>
+        <v>1453</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>1448</v>
+        <v>1454</v>
       </c>
       <c r="F78" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="79" ht="48" customHeight="1" spans="1:6">
       <c r="A79" s="11" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>1286</v>
+        <v>1292</v>
       </c>
       <c r="D79" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="F79" s="13" t="s">
-        <v>1287</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="80" ht="48" customHeight="1" spans="1:6">
       <c r="A80" s="11" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>946</v>
+        <v>952</v>
       </c>
       <c r="D80" s="11" t="s">
         <v>7</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>1451</v>
+        <v>1457</v>
       </c>
       <c r="F80" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="81" ht="48" customHeight="1" spans="1:6">
       <c r="A81" s="11" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="D81" s="11" t="s">
         <v>8</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>1452</v>
+        <v>1458</v>
       </c>
       <c r="F81" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="82" ht="48" customHeight="1" spans="1:6">
       <c r="A82" s="11" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>1453</v>
+        <v>1459</v>
       </c>
       <c r="F82" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="83" ht="48" customHeight="1" spans="1:6">
       <c r="A83" s="11" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>1292</v>
+        <v>1298</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>1168</v>
+        <v>1174</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="F83" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="84" ht="48" customHeight="1" spans="1:6">
       <c r="A84" s="11" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>974</v>
+        <v>980</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>1294</v>
+        <v>1300</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>1452</v>
+        <v>1458</v>
       </c>
       <c r="F84" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="85" ht="48" customHeight="1" spans="1:6">
       <c r="A85" s="11" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>1393</v>
+        <v>1399</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>1395</v>
+        <v>1401</v>
       </c>
       <c r="F85" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="86" ht="48" customHeight="1" spans="1:6">
       <c r="A86" s="11" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>1296</v>
+        <v>1302</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>1297</v>
+        <v>1303</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="F86" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="87" ht="48" customHeight="1" spans="1:6">
       <c r="A87" s="11" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>1299</v>
+        <v>1305</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>1300</v>
+        <v>1306</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="F87" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="88" ht="48" customHeight="1" spans="1:6">
       <c r="A88" s="11" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>1302</v>
+        <v>1308</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>1303</v>
+        <v>1309</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="F88" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="89" ht="48" customHeight="1" spans="1:6">
       <c r="A89" s="11" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>1304</v>
+        <v>1310</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>1305</v>
+        <v>1311</v>
       </c>
       <c r="E89" s="12" t="s">
-        <v>1457</v>
+        <v>1463</v>
       </c>
       <c r="F89" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="90" ht="48" customHeight="1" spans="1:6">
       <c r="A90" s="11" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>1400</v>
+        <v>1406</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>1401</v>
+        <v>1407</v>
       </c>
       <c r="E90" s="12" t="s">
-        <v>1402</v>
+        <v>1408</v>
       </c>
       <c r="F90" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="91" ht="48" customHeight="1" spans="1:6">
       <c r="A91" s="11" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>1403</v>
+        <v>1409</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>1404</v>
+        <v>1410</v>
       </c>
       <c r="E91" s="12" t="s">
-        <v>1458</v>
+        <v>1464</v>
       </c>
       <c r="F91" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="92" ht="48" customHeight="1" spans="1:6">
       <c r="A92" s="11" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>1406</v>
+        <v>1412</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>1407</v>
+        <v>1413</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>1459</v>
+        <v>1465</v>
       </c>
       <c r="F92" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="93" ht="48" customHeight="1" spans="1:6">
       <c r="A93" s="11" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>1310</v>
+        <v>1316</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>1311</v>
+        <v>1317</v>
       </c>
       <c r="E93" s="12" t="s">
-        <v>1460</v>
+        <v>1466</v>
       </c>
       <c r="F93" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="94" ht="48" customHeight="1" spans="1:6">
       <c r="A94" s="11" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>1313</v>
+        <v>1319</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>1314</v>
+        <v>1320</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>1461</v>
+        <v>1467</v>
       </c>
       <c r="F94" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="95" ht="48" customHeight="1" spans="1:6">
       <c r="A95" s="11" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>1316</v>
+        <v>1322</v>
       </c>
       <c r="D95" s="11" t="s">
-        <v>1317</v>
+        <v>1323</v>
       </c>
       <c r="E95" s="12" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="F95" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="96" ht="48" customHeight="1" spans="1:6">
       <c r="A96" s="11" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>1322</v>
+        <v>1328</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>1323</v>
+        <v>1329</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>1462</v>
+        <v>1468</v>
       </c>
       <c r="F96" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="97" ht="48" customHeight="1" spans="1:6">
       <c r="A97" s="11" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>1413</v>
+        <v>1419</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>1414</v>
+        <v>1420</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>1463</v>
+        <v>1469</v>
       </c>
       <c r="F97" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="98" ht="48" customHeight="1" spans="1:6">
       <c r="A98" s="11" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>1416</v>
+        <v>1422</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>1417</v>
+        <v>1423</v>
       </c>
       <c r="E98" s="12" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="F98" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="99" ht="48" customHeight="1" spans="1:6">
       <c r="A99" s="11" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>1328</v>
+        <v>1334</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>1329</v>
+        <v>1335</v>
       </c>
       <c r="E99" s="12" t="s">
-        <v>1464</v>
+        <v>1470</v>
       </c>
       <c r="F99" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="100" ht="48" customHeight="1" spans="1:6">
       <c r="A100" s="11" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>1419</v>
+        <v>1425</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>1420</v>
+        <v>1426</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>1465</v>
+        <v>1471</v>
       </c>
       <c r="F100" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="101" ht="48" customHeight="1" spans="1:6">
       <c r="A101" s="11" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>1422</v>
+        <v>1428</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>1423</v>
+        <v>1429</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="F101" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="102" ht="48" customHeight="1" spans="1:6">
       <c r="A102" s="11" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>1424</v>
+        <v>1430</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>1425</v>
+        <v>1431</v>
       </c>
       <c r="E102" s="12" t="s">
-        <v>1466</v>
+        <v>1472</v>
       </c>
       <c r="F102" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="103" ht="48" customHeight="1" spans="1:6">
       <c r="A103" s="11" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>1427</v>
+        <v>1433</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>1428</v>
+        <v>1434</v>
       </c>
       <c r="E103" s="12" t="s">
-        <v>1467</v>
+        <v>1473</v>
       </c>
       <c r="F103" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="104" ht="48" customHeight="1" spans="1:6">
       <c r="A104" s="11" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>1430</v>
+        <v>1436</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>1431</v>
+        <v>1437</v>
       </c>
       <c r="E104" s="12" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="F104" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="105" ht="48" customHeight="1" spans="1:6">
       <c r="A105" s="11" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>1432</v>
+        <v>1438</v>
       </c>
       <c r="D105" s="11" t="s">
-        <v>1433</v>
+        <v>1439</v>
       </c>
       <c r="E105" s="12" t="s">
-        <v>1468</v>
+        <v>1474</v>
       </c>
       <c r="F105" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="106" ht="48" customHeight="1" spans="1:6">
       <c r="A106" s="11" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>1435</v>
+        <v>1441</v>
       </c>
       <c r="D106" s="11" t="s">
-        <v>1436</v>
+        <v>1442</v>
       </c>
       <c r="E106" s="12" t="s">
-        <v>1469</v>
+        <v>1475</v>
       </c>
       <c r="F106" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="107" ht="48" customHeight="1" spans="1:6">
       <c r="A107" s="11" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>1438</v>
+        <v>1444</v>
       </c>
       <c r="D107" s="11" t="s">
-        <v>1439</v>
+        <v>1445</v>
       </c>
       <c r="E107" s="12" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="F107" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="108" ht="48" customHeight="1" spans="1:6">
       <c r="A108" s="11" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>1440</v>
+        <v>1446</v>
       </c>
       <c r="D108" s="11" t="s">
-        <v>1441</v>
+        <v>1447</v>
       </c>
       <c r="E108" s="12" t="s">
-        <v>1470</v>
+        <v>1476</v>
       </c>
       <c r="F108" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="109" ht="48" customHeight="1" spans="1:6">
       <c r="A109" s="11" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B109" s="11" t="s">
+        <v>1456</v>
+      </c>
+      <c r="C109" s="11" t="s">
         <v>1449</v>
       </c>
-      <c r="B109" s="11" t="s">
+      <c r="D109" s="11" t="s">
         <v>1450</v>
       </c>
-      <c r="C109" s="11" t="s">
-        <v>1443</v>
-      </c>
-      <c r="D109" s="11" t="s">
-        <v>1444</v>
-      </c>
       <c r="E109" s="12" t="s">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="F109" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="110" ht="48" customHeight="1" spans="1:6">
       <c r="A110" s="11" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>1446</v>
+        <v>1452</v>
       </c>
       <c r="D110" s="11" t="s">
-        <v>1447</v>
+        <v>1453</v>
       </c>
       <c r="E110" s="12" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="F110" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="111" ht="48" customHeight="1" spans="1:6">
       <c r="A111" s="11" t="s">
-        <v>1472</v>
+        <v>1478</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>1473</v>
+        <v>1479</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>1286</v>
+        <v>1292</v>
       </c>
       <c r="D111" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E111" s="12" t="s">
-        <v>1472</v>
+        <v>1478</v>
       </c>
       <c r="F111" s="13" t="s">
-        <v>1287</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="112" ht="48" customHeight="1" spans="1:6">
       <c r="A112" s="11" t="s">
-        <v>1472</v>
+        <v>1478</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>1473</v>
+        <v>1479</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>946</v>
+        <v>952</v>
       </c>
       <c r="D112" s="11" t="s">
         <v>7</v>
       </c>
       <c r="E112" s="12" t="s">
-        <v>1474</v>
+        <v>1480</v>
       </c>
       <c r="F112" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="113" ht="48" customHeight="1" spans="1:6">
       <c r="A113" s="11" t="s">
-        <v>1472</v>
+        <v>1478</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>1473</v>
+        <v>1479</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="D113" s="11" t="s">
         <v>8</v>
       </c>
       <c r="E113" s="12" t="s">
-        <v>1475</v>
+        <v>1481</v>
       </c>
       <c r="F113" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="114" ht="48" customHeight="1" spans="1:6">
       <c r="A114" s="11" t="s">
-        <v>1472</v>
+        <v>1478</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>1473</v>
+        <v>1479</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="E114" s="12" t="s">
-        <v>1476</v>
+        <v>1482</v>
       </c>
       <c r="F114" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="115" ht="48" customHeight="1" spans="1:6">
       <c r="A115" s="11" t="s">
-        <v>1472</v>
+        <v>1478</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>1473</v>
+        <v>1479</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>1292</v>
+        <v>1298</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>1168</v>
+        <v>1174</v>
       </c>
       <c r="E115" s="12" t="s">
-        <v>1477</v>
+        <v>1483</v>
       </c>
       <c r="F115" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="116" ht="48" customHeight="1" spans="1:6">
       <c r="A116" s="11" t="s">
-        <v>1472</v>
+        <v>1478</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>1473</v>
+        <v>1479</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>974</v>
+        <v>980</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>1294</v>
+        <v>1300</v>
       </c>
       <c r="E116" s="12" t="s">
-        <v>1478</v>
+        <v>1484</v>
       </c>
       <c r="F116" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="117" ht="48" customHeight="1" spans="1:6">
       <c r="A117" s="11" t="s">
-        <v>1472</v>
+        <v>1478</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>1473</v>
+        <v>1479</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>1479</v>
+        <v>1485</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>1480</v>
+        <v>1486</v>
       </c>
       <c r="E117" s="12" t="s">
-        <v>1481</v>
+        <v>1487</v>
       </c>
       <c r="F117" s="13" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
   </sheetData>
@@ -20950,7 +20974,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>1482</v>
+        <v>1488</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -20959,7 +20983,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:5">
       <c r="A2" s="8" t="s">
-        <v>1483</v>
+        <v>1489</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -20975,274 +20999,274 @@
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:5">
       <c r="A4" s="10" t="s">
-        <v>909</v>
+        <v>915</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>913</v>
+        <v>919</v>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1" spans="1:5">
       <c r="A5" s="11" t="s">
-        <v>1484</v>
+        <v>1490</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>1485</v>
+        <v>1491</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1487</v>
+        <v>1493</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>1488</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1" spans="1:5">
       <c r="A6" s="11" t="s">
-        <v>1489</v>
+        <v>1495</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>1365</v>
+        <v>1371</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>1366</v>
+        <v>1372</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>1490</v>
+        <v>1496</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1" spans="1:5">
       <c r="A7" s="11" t="s">
-        <v>1489</v>
+        <v>1495</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>1491</v>
+        <v>1497</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>1490</v>
+        <v>1496</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>1492</v>
+        <v>1498</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>1493</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1" spans="1:5">
       <c r="A8" s="11" t="s">
-        <v>1489</v>
+        <v>1495</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>1368</v>
+        <v>1374</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>1369</v>
+        <v>1375</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>1494</v>
+        <v>1500</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1" spans="1:5">
       <c r="A9" s="11" t="s">
-        <v>1489</v>
+        <v>1495</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>1495</v>
+        <v>1501</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>1496</v>
+        <v>1502</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>1497</v>
+        <v>1503</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>1493</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1" spans="1:5">
       <c r="A10" s="11" t="s">
-        <v>1498</v>
+        <v>1504</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>1499</v>
+        <v>1505</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>1500</v>
+        <v>1506</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>1501</v>
+        <v>1507</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1" spans="1:5">
       <c r="A11" s="11" t="s">
-        <v>1498</v>
+        <v>1504</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>1502</v>
+        <v>1508</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>1503</v>
+        <v>1509</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1504</v>
+        <v>1510</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:5">
       <c r="A12" s="11" t="s">
-        <v>1505</v>
+        <v>1511</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>1506</v>
+        <v>1512</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>1507</v>
+        <v>1513</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1" spans="1:5">
       <c r="A13" s="11" t="s">
-        <v>1505</v>
+        <v>1511</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>1508</v>
+        <v>1514</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>1509</v>
+        <v>1515</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1" spans="1:5">
       <c r="A14" s="11" t="s">
-        <v>1505</v>
+        <v>1511</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>1510</v>
+        <v>1516</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>1511</v>
+        <v>1517</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1" spans="1:5">
       <c r="A15" s="11" t="s">
-        <v>1505</v>
+        <v>1511</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>1512</v>
+        <v>1518</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>1513</v>
+        <v>1519</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1" spans="1:5">
       <c r="A16" s="11" t="s">
-        <v>1514</v>
+        <v>1520</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>1515</v>
+        <v>1521</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>1516</v>
+        <v>1522</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>1517</v>
+        <v>1523</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1" spans="1:5">
       <c r="A17" s="11" t="s">
-        <v>1379</v>
+        <v>1385</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>1518</v>
+        <v>1524</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>1519</v>
+        <v>1525</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>1520</v>
+        <v>1526</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1" spans="1:5">
       <c r="A18" s="11" t="s">
-        <v>1379</v>
+        <v>1385</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>1521</v>
+        <v>1527</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>1522</v>
+        <v>1528</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>1523</v>
+        <v>1529</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1" spans="1:5">
       <c r="A19" s="11" t="s">
-        <v>1379</v>
+        <v>1385</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>1524</v>
+        <v>1530</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>1525</v>
+        <v>1531</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>1358</v>
+        <v>1364</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
     </row>
   </sheetData>
@@ -21269,7 +21293,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>1526</v>
+        <v>1532</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -21281,7 +21305,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>1527</v>
+        <v>1533</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -21293,50 +21317,50 @@
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:8">
       <c r="A4" s="3" t="s">
-        <v>1528</v>
+        <v>1534</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1529</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:8">
       <c r="A5" s="4" t="s">
-        <v>1530</v>
+        <v>1536</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1531</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:8">
       <c r="A6" s="4" t="s">
-        <v>1532</v>
+        <v>1538</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1533</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:8">
       <c r="A7" s="4" t="s">
-        <v>1534</v>
+        <v>1540</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1535</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:8">
       <c r="A8" s="4" t="s">
-        <v>1536</v>
+        <v>1542</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1537</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:8">
       <c r="A9" s="4" t="s">
-        <v>1538</v>
+        <v>1544</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1539</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:8">
@@ -21344,10 +21368,10 @@
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:8">
       <c r="A11" s="3" t="s">
-        <v>1540</v>
+        <v>1546</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1541</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:8">
@@ -21355,7 +21379,7 @@
         <v>22</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1542</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:8">
@@ -21363,47 +21387,47 @@
         <v>23</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1543</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:8">
       <c r="A14" s="4" t="s">
-        <v>1544</v>
+        <v>1550</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1545</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:8">
       <c r="A15" s="4" t="s">
-        <v>1546</v>
+        <v>1552</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1547</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:8">
       <c r="A16" s="4" t="s">
-        <v>1548</v>
+        <v>1554</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1549</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>1550</v>
+        <v>1556</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1551</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:2">
       <c r="A18" s="4" t="s">
-        <v>1552</v>
+        <v>1558</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1553</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:2">
@@ -21411,10 +21435,10 @@
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:2">
       <c r="A20" s="3" t="s">
-        <v>1554</v>
+        <v>1560</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>1555</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:2">
@@ -21422,7 +21446,7 @@
         <v>1</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1556</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:2">
@@ -21430,7 +21454,7 @@
         <v>2</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1557</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:2">
@@ -21438,7 +21462,7 @@
         <v>3</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1558</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1" spans="1:2">
@@ -21446,7 +21470,7 @@
         <v>4</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1559</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:2">
@@ -21454,7 +21478,7 @@
         <v>5</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1560</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1" spans="1:2">
@@ -21462,7 +21486,7 @@
         <v>6</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1" spans="1:2">
@@ -21470,7 +21494,7 @@
         <v>7</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>1562</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1" spans="1:2">
@@ -21478,7 +21502,7 @@
         <v>8</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>1563</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1" spans="1:2">
@@ -21486,7 +21510,7 @@
         <v>9</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>1564</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1" spans="1:2">
@@ -21494,7 +21518,7 @@
         <v>10</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1565</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1" spans="1:2">
@@ -21502,26 +21526,26 @@
     </row>
     <row r="32" ht="28" customHeight="1" spans="1:2">
       <c r="A32" s="3" t="s">
-        <v>1566</v>
+        <v>1572</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>1567</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1" spans="1:2">
       <c r="A33" s="4" t="s">
-        <v>1568</v>
+        <v>1574</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>1569</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1" spans="1:2">
       <c r="A34" s="7" t="s">
-        <v>1570</v>
+        <v>1576</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>1571</v>
+        <v>1577</v>
       </c>
     </row>
   </sheetData>

--- a/顶奢_整站资料批量编辑.xlsx
+++ b/顶奢_整站资料批量编辑.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16455"/>
+    <workbookView windowHeight="16455" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="资料批量编辑" sheetId="1" r:id="rId1"/>
@@ -923,9 +923,6 @@
     <t>photos/guangzhou-model-001/profile.mp4</t>
   </si>
   <si>
-    <t>是</t>
-  </si>
-  <si>
     <t>https://hqq2.com/guangzhou/model-001/</t>
   </si>
   <si>
@@ -936,6 +933,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF2B2424"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>05年</t>
     </r>
     <r>
@@ -971,6 +974,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF2B2424"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>极品白小纯 刚下氵
 🌸温柔乖巧•你的初恋女友
 🌸可甜可盐•A4腰  肌肤雪白嫩滑</t>
@@ -1155,6 +1164,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF2B2424"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>净身高 180 D 体重</t>
     </r>
     <r>
@@ -1208,6 +1223,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF2B2424"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>身高172 </t>
     </r>
     <r>
@@ -1240,6 +1261,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF2B2424"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>学生兼职</t>
     </r>
     <r>
@@ -1387,6 +1414,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF2B2424"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>05年</t>
     </r>
     <r>
@@ -2546,6 +2579,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF2B2424"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>极品天菜
 只见绅士  提前预约🎫
 自行车运动员</t>
@@ -2652,6 +2691,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF2B2424"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>杭州外围模特</t>
     </r>
     <r>
@@ -2672,6 +2717,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF2B2424"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>❄️在读MBA  一口流利英文 
 ❄️冷白皮  妈生脸  高级明星气质
 ❄️无风尘味</t>
@@ -2721,6 +2772,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF2B2424"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>身高/175  年龄</t>
     </r>
     <r>
@@ -2771,6 +2828,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF2B2424"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>天然无整/五官精致/鹅蛋脸/全身雪白/无纹身</t>
     </r>
     <r>
@@ -2988,6 +3051,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF2B2424"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>身高 173  48kg </t>
     </r>
     <r>
@@ -3024,7 +3093,7 @@
     <t>https://hqq2.com/hangzhou/model-009/</t>
   </si>
   <si>
-    <t>杭州外围模特周</t>
+    <t>杭州外围模特周周</t>
   </si>
   <si>
     <t>杭州外围｜杭州女大学生外围｜杭州高端外围</t>
@@ -3034,6 +3103,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF2B2424"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>絕頂长腿美杀 腿模 
 身材窈窕气质高级</t>
     </r>
@@ -3314,1105 +3389,1111 @@
     <t>首屏主标题</t>
   </si>
   <si>
+    <t>顶奢甄选</t>
+  </si>
+  <si>
+    <t>第一行标题</t>
+  </si>
+  <si>
+    <t>hero_title_emphasis</t>
+  </si>
+  <si>
+    <t>首屏强调标题</t>
+  </si>
+  <si>
+    <t>尊享非凡</t>
+  </si>
+  <si>
+    <t>第二行金色标题</t>
+  </si>
+  <si>
+    <t>hero_description</t>
+  </si>
+  <si>
+    <t>首屏简介</t>
+  </si>
+  <si>
+    <t>欢迎来到顶奢商务模特外围工作室！我们的服务覆盖全国一二线城市，为您提供需要的商务模特选择。</t>
+  </si>
+  <si>
+    <t>主标题下方文字</t>
+  </si>
+  <si>
+    <t>首页统计</t>
+  </si>
+  <si>
+    <t>stat_city_label</t>
+  </si>
+  <si>
+    <t>城市数量标签</t>
+  </si>
+  <si>
+    <t>座城市</t>
+  </si>
+  <si>
+    <t>数字自动统计</t>
+  </si>
+  <si>
+    <t>stat_profile_label</t>
+  </si>
+  <si>
+    <t>资料数量标签</t>
+  </si>
+  <si>
+    <t>套资料</t>
+  </si>
+  <si>
+    <t>stat_media_value</t>
+  </si>
+  <si>
+    <t>媒体数量文字</t>
+  </si>
+  <si>
+    <t>自动统计</t>
+  </si>
+  <si>
+    <t>例如 3+1</t>
+  </si>
+  <si>
+    <t>stat_media_label</t>
+  </si>
+  <si>
+    <t>媒体数量标签</t>
+  </si>
+  <si>
+    <t>媒体文件</t>
+  </si>
+  <si>
+    <t>例如 媒体位</t>
+  </si>
+  <si>
+    <t>城市入口</t>
+  </si>
+  <si>
+    <t>city_section_kicker</t>
+  </si>
+  <si>
+    <t>城市区英文</t>
+  </si>
+  <si>
+    <t>EXPLORE BY CITY</t>
+  </si>
+  <si>
+    <t>城市入口标题上方英文</t>
+  </si>
+  <si>
+    <t>city_section_title</t>
+  </si>
+  <si>
+    <t>城市区标题</t>
+  </si>
+  <si>
+    <t>按城市浏览</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>city_section_description</t>
+  </si>
+  <si>
+    <t>城市区说明</t>
+  </si>
+  <si>
+    <t>已发布城市会自动显示在这里，后续可通过工作表继续增加城市和资料。</t>
+  </si>
+  <si>
+    <t>city_card_link_label</t>
+  </si>
+  <si>
+    <t>城市卡按钮</t>
+  </si>
+  <si>
+    <t>进入资源库</t>
+  </si>
+  <si>
+    <t>按钮后自动添加箭头</t>
+  </si>
+  <si>
+    <t>精选资料</t>
+  </si>
+  <si>
+    <t>featured_kicker</t>
+  </si>
+  <si>
+    <t>精选区英文</t>
+  </si>
+  <si>
+    <t>SELECTED PROFILES</t>
+  </si>
+  <si>
+    <t>featured_title</t>
+  </si>
+  <si>
+    <t>精选区标题</t>
+  </si>
+  <si>
+    <t>首批精选</t>
+  </si>
+  <si>
+    <t>底部卖点</t>
+  </si>
+  <si>
+    <t>promise_1_label</t>
+  </si>
+  <si>
+    <t>卖点1标签</t>
+  </si>
+  <si>
+    <t>专属页面</t>
+  </si>
+  <si>
+    <t>已从首页移除，不再显示；保留字段仅用于兼容旧工作表</t>
+  </si>
+  <si>
+    <t>promise_1_title</t>
+  </si>
+  <si>
+    <t>卖点1标题</t>
+  </si>
+  <si>
+    <t>独立呈现</t>
+  </si>
+  <si>
+    <t>promise_1_text</t>
+  </si>
+  <si>
+    <t>卖点1说明</t>
+  </si>
+  <si>
+    <t>每套资料拥有稳定网址和独立 SEO 信息。</t>
+  </si>
+  <si>
+    <t>promise_2_label</t>
+  </si>
+  <si>
+    <t>卖点2标签</t>
+  </si>
+  <si>
+    <t>图文视频</t>
+  </si>
+  <si>
+    <t>promise_2_title</t>
+  </si>
+  <si>
+    <t>卖点2标题</t>
+  </si>
+  <si>
+    <t>多媒体结构</t>
+  </si>
+  <si>
+    <t>promise_2_text</t>
+  </si>
+  <si>
+    <t>卖点2说明</t>
+  </si>
+  <si>
+    <t>图片和视频按实际资料配置，并提供独立说明与元数据。</t>
+  </si>
+  <si>
+    <t>promise_3_label</t>
+  </si>
+  <si>
+    <t>卖点3标签</t>
+  </si>
+  <si>
+    <t>持续更新</t>
+  </si>
+  <si>
+    <t>promise_3_title</t>
+  </si>
+  <si>
+    <t>卖点3标题</t>
+  </si>
+  <si>
+    <t>灵活扩展</t>
+  </si>
+  <si>
+    <t>promise_3_text</t>
+  </si>
+  <si>
+    <t>卖点3说明</t>
+  </si>
+  <si>
+    <t>城市、资料数量和内容均可继续追加。</t>
+  </si>
+  <si>
+    <t>预约流程</t>
+  </si>
+  <si>
+    <t>process_kicker</t>
+  </si>
+  <si>
+    <t>流程区英文</t>
+  </si>
+  <si>
+    <t>CONSULTATION PROCESS</t>
+  </si>
+  <si>
+    <t>process_title</t>
+  </si>
+  <si>
+    <t>流程区标题</t>
+  </si>
+  <si>
+    <t>预约咨询流程</t>
+  </si>
+  <si>
+    <t>首页五步流程标题</t>
+  </si>
+  <si>
+    <t>process_1_label</t>
+  </si>
+  <si>
+    <t>步骤1标题</t>
+  </si>
+  <si>
+    <t>加入会员</t>
+  </si>
+  <si>
+    <t>第一个流程按钮</t>
+  </si>
+  <si>
+    <t>process_1_text</t>
+  </si>
+  <si>
+    <t>步骤1说明</t>
+  </si>
+  <si>
+    <t>打开顶奢专属客服咨询并加入会员，享受会员相关权益，解锁更多同城资源。</t>
+  </si>
+  <si>
+    <t>点击步骤1后显示</t>
+  </si>
+  <si>
+    <t>process_2_label</t>
+  </si>
+  <si>
+    <t>步骤2标题</t>
+  </si>
+  <si>
+    <t>告知需求</t>
+  </si>
+  <si>
+    <t>第二个流程按钮</t>
+  </si>
+  <si>
+    <t>process_2_text</t>
+  </si>
+  <si>
+    <t>步骤2说明</t>
+  </si>
+  <si>
+    <t>提供城市、时间和偏好，方便客服快速筛选合适资料。</t>
+  </si>
+  <si>
+    <t>点击步骤2后显示</t>
+  </si>
+  <si>
+    <t>process_3_label</t>
+  </si>
+  <si>
+    <t>步骤3标题</t>
+  </si>
+  <si>
+    <t>查看资料</t>
+  </si>
+  <si>
+    <t>第三个流程按钮</t>
+  </si>
+  <si>
+    <t>process_3_text</t>
+  </si>
+  <si>
+    <t>步骤3说明</t>
+  </si>
+  <si>
+    <t>确定需求后，推送符合条件人员资料，挑选合适人选。</t>
+  </si>
+  <si>
+    <t>点击步骤3后显示</t>
+  </si>
+  <si>
+    <t>process_4_label</t>
+  </si>
+  <si>
+    <t>步骤4标题</t>
+  </si>
+  <si>
+    <t>确认安排</t>
+  </si>
+  <si>
+    <t>第四个流程按钮</t>
+  </si>
+  <si>
+    <t>process_4_text</t>
+  </si>
+  <si>
+    <t>步骤4说明</t>
+  </si>
+  <si>
+    <t>确认选择、时间和必要事项；如有变化请及时沟通。</t>
+  </si>
+  <si>
+    <t>点击步骤4后显示</t>
+  </si>
+  <si>
+    <t>process_5_label</t>
+  </si>
+  <si>
+    <t>步骤5标题</t>
+  </si>
+  <si>
+    <t>保持联系</t>
+  </si>
+  <si>
+    <t>第五个流程按钮</t>
+  </si>
+  <si>
+    <t>process_5_text</t>
+  </si>
+  <si>
+    <t>步骤5说明</t>
+  </si>
+  <si>
+    <t>按确认好的计划前往，并根据实际安排保持联系。见到mm确认无误，先付款后体验。</t>
+  </si>
+  <si>
+    <t>点击步骤5后显示</t>
+  </si>
+  <si>
+    <t>随机推荐</t>
+  </si>
+  <si>
+    <t>random_kicker</t>
+  </si>
+  <si>
+    <t>推荐区英文</t>
+  </si>
+  <si>
+    <t>DISCOVER MORE</t>
+  </si>
+  <si>
+    <t>随机资料标题上方英文</t>
+  </si>
+  <si>
+    <t>random_title</t>
+  </si>
+  <si>
+    <t>推荐区标题</t>
+  </si>
+  <si>
+    <t>相关资料推荐</t>
+  </si>
+  <si>
+    <t>首页随机资料标题</t>
+  </si>
+  <si>
+    <t>random_description</t>
+  </si>
+  <si>
+    <t>推荐区说明</t>
+  </si>
+  <si>
+    <t>每次打开页面都会随机展示不同城市的资料入口。</t>
+  </si>
+  <si>
+    <t>随机卡片上方说明</t>
+  </si>
+  <si>
+    <t>random_count</t>
+  </si>
+  <si>
+    <t>首页显示数量</t>
+  </si>
+  <si>
+    <t>请输入 4 至 12 的整数</t>
+  </si>
+  <si>
+    <t>常见问题</t>
+  </si>
+  <si>
+    <t>home_faq_kicker</t>
+  </si>
+  <si>
+    <t>问答区英文</t>
+  </si>
+  <si>
+    <t>COMMON QUESTIONS</t>
+  </si>
+  <si>
+    <t>home_faq_title</t>
+  </si>
+  <si>
+    <t>问答区标题</t>
+  </si>
+  <si>
+    <t>首页问答标题</t>
+  </si>
+  <si>
+    <t>home_faq_description</t>
+  </si>
+  <si>
+    <t>问答区说明</t>
+  </si>
+  <si>
+    <t>关于资料浏览、媒体更新和客服入口的说明。</t>
+  </si>
+  <si>
+    <t>首页问答简介</t>
+  </si>
+  <si>
+    <t>home_faq_1_question</t>
+  </si>
+  <si>
+    <t>问题1</t>
+  </si>
+  <si>
+    <t>外围模特怎么选？</t>
+  </si>
+  <si>
+    <t>点击后展开答案</t>
+  </si>
+  <si>
+    <t>home_faq_1_answer</t>
+  </si>
+  <si>
+    <t>答案1</t>
+  </si>
+  <si>
+    <t>我们会按照您的要求将同城可以预约的女孩照片视频发送给您挑选。</t>
+  </si>
+  <si>
+    <t>问题1答案</t>
+  </si>
+  <si>
+    <t>home_faq_2_question</t>
+  </si>
+  <si>
+    <t>问题2</t>
+  </si>
+  <si>
+    <t>见面不满意怎么办？</t>
+  </si>
+  <si>
+    <t>home_faq_2_answer</t>
+  </si>
+  <si>
+    <t>答案2</t>
+  </si>
+  <si>
+    <t>如果不满意您可以支付路费（路费实报实销）给女孩我们给您换人，直到您满意为止。</t>
+  </si>
+  <si>
+    <t>问题2答案</t>
+  </si>
+  <si>
+    <t>home_faq_3_question</t>
+  </si>
+  <si>
+    <t>问题3</t>
+  </si>
+  <si>
+    <t>价格如何？怎么消费？</t>
+  </si>
+  <si>
+    <t>home_faq_3_answer</t>
+  </si>
+  <si>
+    <t>答案3</t>
+  </si>
+  <si>
+    <t>中圈2.4K-3.5K两次 夜6K+ 普通大圈3K一次夜8K 高级大圈5K一次夜1.5W 特殊定制服务请与我们联系告知需求获得报价。</t>
+  </si>
+  <si>
+    <t>问题3答案</t>
+  </si>
+  <si>
+    <t>home_faq_4_question</t>
+  </si>
+  <si>
+    <t>问题4</t>
+  </si>
+  <si>
+    <t>可以上门服务吗？</t>
+  </si>
+  <si>
+    <t>home_faq_4_answer</t>
+  </si>
+  <si>
+    <t>答案4</t>
+  </si>
+  <si>
+    <t>可以上门服务或是您去mm那，具体情况看您如何安排方便。</t>
+  </si>
+  <si>
+    <t>问题4答案</t>
+  </si>
+  <si>
+    <t>home_faq_5_question</t>
+  </si>
+  <si>
+    <t>问题5</t>
+  </si>
+  <si>
+    <t>如何联系顶奢客服？</t>
+  </si>
+  <si>
+    <t>home_faq_5_answer</t>
+  </si>
+  <si>
+    <t>答案5</t>
+  </si>
+  <si>
+    <t>点击页面右下角的顶奢专属咨询按钮，即可在当前页面打开客服窗口。</t>
+  </si>
+  <si>
+    <t>问题5答案</t>
+  </si>
+  <si>
+    <t>home_faq_6_question</t>
+  </si>
+  <si>
+    <t>问题6</t>
+  </si>
+  <si>
+    <t>后续会增加更多城市吗？</t>
+  </si>
+  <si>
+    <t>home_faq_6_answer</t>
+  </si>
+  <si>
+    <t>答案6</t>
+  </si>
+  <si>
+    <t>会的。后续会增加更多城市和资料！</t>
+  </si>
+  <si>
+    <t>问题6答案</t>
+  </si>
+  <si>
+    <t>顶奢 · 城市首页批量编辑</t>
+  </si>
+  <si>
+    <t>现有城市代码不要修改；新增城市可在下一空白行填写全部内容，并设置发布、收录和显示顺序。</t>
+  </si>
+  <si>
+    <t>城市名称</t>
+  </si>
+  <si>
+    <t>城市代码</t>
+  </si>
+  <si>
+    <t>导航短句</t>
+  </si>
+  <si>
+    <t>首屏标题</t>
+  </si>
+  <si>
+    <t>数量标签</t>
+  </si>
+  <si>
+    <t>专题英文</t>
+  </si>
+  <si>
+    <t>专题标题</t>
+  </si>
+  <si>
+    <t>亮点1标题</t>
+  </si>
+  <si>
+    <t>亮点1说明</t>
+  </si>
+  <si>
+    <t>亮点2标题</t>
+  </si>
+  <si>
+    <t>亮点2说明</t>
+  </si>
+  <si>
+    <t>亮点3标题</t>
+  </si>
+  <si>
+    <t>亮点3说明</t>
+  </si>
+  <si>
+    <t>精选英文</t>
+  </si>
+  <si>
+    <t>精选标题</t>
+  </si>
+  <si>
+    <t>精选说明</t>
+  </si>
+  <si>
+    <t>全部英文</t>
+  </si>
+  <si>
+    <t>全部标题</t>
+  </si>
+  <si>
+    <t>全部说明</t>
+  </si>
+  <si>
+    <t>FAQ英文</t>
+  </si>
+  <si>
+    <t>FAQ标题</t>
+  </si>
+  <si>
+    <t>FAQ说明</t>
+  </si>
+  <si>
+    <t>回答1</t>
+  </si>
+  <si>
+    <t>回答2</t>
+  </si>
+  <si>
+    <t>回答3</t>
+  </si>
+  <si>
+    <t>更多城市英文</t>
+  </si>
+  <si>
+    <t>更多城市标题</t>
+  </si>
+  <si>
+    <t>海派格调与都会精选</t>
+  </si>
+  <si>
+    <t>上海外围｜上海模特预约｜顶奢</t>
+  </si>
+  <si>
+    <t>顶奢上海资源库，集中展示上海城市精选资料、独立图片、视频、风格介绍与相关推荐。</t>
+  </si>
+  <si>
+    <t>CITY COLLECTION</t>
+  </si>
+  <si>
+    <t>上海精选资料</t>
+  </si>
+  <si>
+    <t>欢迎您来到顶奢上海精选，网页只展示部分女孩资料，进入独立详情页查看照片、视频与完整介绍，更多资源请联系客服加入会员后解锁！</t>
+  </si>
+  <si>
+    <t>套独立资料</t>
+  </si>
+  <si>
+    <t>CITY GUIDE</t>
+  </si>
+  <si>
+    <t>上海资料浏览指南</t>
+  </si>
+  <si>
+    <t>上海兼具都会节奏与精致审美，资料库收录不同风格的城市精选内容。你可以从个人气质、形象特点和展示风格入手，进入独立详情页查看照片、视频与完整介绍。</t>
+  </si>
+  <si>
+    <t>如果你对静安、徐汇、闵行、宝山、浦东等区域有明确偏好，可以在咨询时告诉客服，可以更高效地找到符合需求的资料</t>
+  </si>
+  <si>
+    <t>资源丰富</t>
+  </si>
+  <si>
+    <t>涵盖清新、御姐、模特等不同资料风格。</t>
+  </si>
+  <si>
+    <t>区域选择</t>
+  </si>
+  <si>
+    <t>可根据静安、徐汇、闵行、宝山、浦东等区域说明需求。</t>
+  </si>
+  <si>
+    <t>专属客服</t>
+  </si>
+  <si>
+    <t>提供偏好和时间，客服可协助快速查找合适资料。</t>
+  </si>
+  <si>
+    <t>EDITOR'S SELECTION</t>
+  </si>
+  <si>
+    <t>上海精选入口</t>
+  </si>
+  <si>
+    <t>先从代表性资料开始，再浏览本页完整列表。</t>
+  </si>
+  <si>
+    <t>ALL PROFILES</t>
+  </si>
+  <si>
+    <t>上海部分资料展示</t>
+  </si>
+  <si>
+    <t>当前共 {count} 个可直接访问的独立详情页。</t>
+  </si>
+  <si>
+    <t>上海资源常见问题</t>
+  </si>
+  <si>
+    <t>关于流程与价格的简要说明。</t>
+  </si>
+  <si>
+    <t>怎样查看上海全部资料？</t>
+  </si>
+  <si>
+    <t>联系客服加入会员后可解锁当天全部资料！</t>
+  </si>
+  <si>
+    <t>关于价格，怎么消费？</t>
+  </si>
+  <si>
+    <t>普通快3夜8，高级快5夜1.5，无其他隐形消费！且见人满意再付。特殊定制服务请与我们联系告知需求获得报价。</t>
+  </si>
+  <si>
+    <t>不如会可以安排吗？</t>
+  </si>
+  <si>
+    <t>非会员一律不安排，毕竟网络时代，我们没有办法一一甄别。希望您能理解，我们以诚信为基础，对各方负责。非会员放鸽子几率太高，浪费我们资源和时间，如果您诚心有需求，入会既可给予我们一些信任，另外也让我们把时间花在了真正需要的人身上。</t>
+  </si>
+  <si>
+    <t>MORE CITIES</t>
+  </si>
+  <si>
+    <t>继续浏览其他城市</t>
+  </si>
+  <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>岭南风尚与城市精选</t>
+  </si>
+  <si>
+    <t>广州外围｜广州模特预约｜顶奢</t>
+  </si>
+  <si>
+    <t>顶奢广州资源库，浏览广州城市精选资料、专属图片、视频介绍及相关城市内容。</t>
+  </si>
+  <si>
+    <t>广州精选资料</t>
+  </si>
+  <si>
+    <t>欢迎您来到顶奢广州精选，网页只展示部分女孩资料，更多资源请联系客服加入会员后解锁！</t>
+  </si>
+  <si>
+    <t>广州资料浏览指南</t>
+  </si>
+  <si>
+    <t>广州城市资料注重自然气质与多样风格，每套资料均有独立页面，可查看图片、视频和详细介绍。</t>
+  </si>
+  <si>
+    <t>可以结合天河、越秀、海珠或珠江新城等常见区域进行选择。说明时间安排与活动区域，可以更高效地找到符合需求的资料</t>
+  </si>
+  <si>
+    <t>可说明天河、越秀、海珠等区域偏好，方便进一步查找。</t>
+  </si>
+  <si>
+    <t>详情请和客服咨询逐步完成预约。</t>
+  </si>
+  <si>
+    <t>广州精选入口</t>
+  </si>
+  <si>
+    <t>广州部分资料展示</t>
+  </si>
+  <si>
+    <t>广州资源常见问题</t>
+  </si>
+  <si>
+    <t>怎样查看广州全部资料？</t>
+  </si>
+  <si>
+    <t>湾区新锐与现代精选</t>
+  </si>
+  <si>
+    <t>深圳外围｜深圳模特预约｜顶奢</t>
+  </si>
+  <si>
+    <t>顶奢深圳资源库，查看深圳现代城市精选资料、图片展示、视频位置与相关推荐。</t>
+  </si>
+  <si>
+    <t>深圳精选资料</t>
+  </si>
+  <si>
+    <t>欢迎您来到顶奢深圳精选，网页只展示部分女孩资料，更多资源请联系客服加入会员后解锁！</t>
+  </si>
+  <si>
+    <t>深圳资料浏览指南</t>
+  </si>
+  <si>
+    <t>深圳资料库以现代、时尚和年轻化风格为主，收录不同气质的城市精选资料。你可以通过资料卡快速了解基本特点，再进入详情页查看完整图片、视频与介绍。</t>
+  </si>
+  <si>
+    <t>如果你关注福田、南山、罗湖、宝安、龙华等区域，可以在咨询时提前说明。结合风格偏好、时间安排与活动区域，可以更高效地找到符合需求的资料。</t>
+  </si>
+  <si>
+    <t>可根据福田、南山、罗湖、龙华、宝安等区域进一步筛选。</t>
+  </si>
+  <si>
+    <t>快速匹配</t>
+  </si>
+  <si>
+    <t>说明个人偏好后，可由客服协助整理和比较资料。</t>
+  </si>
+  <si>
+    <t>深圳精选入口</t>
+  </si>
+  <si>
+    <t>深圳部分资料展示</t>
+  </si>
+  <si>
+    <t>深圳资源常见问题</t>
+  </si>
+  <si>
+    <t>怎样查看深圳全部资料？</t>
+  </si>
+  <si>
+    <t>京华气韵与城市精选</t>
+  </si>
+  <si>
+    <t>北京外围｜北京模特预约｜顶奢</t>
+  </si>
+  <si>
+    <t>顶奢北京资源库，汇总北京城市精选资料、独立图片、视频、专题说明和相关推荐。</t>
+  </si>
+  <si>
+    <t>北京精选资料</t>
+  </si>
+  <si>
+    <t>欢迎您来到顶奢北京精选，网页只展示部分女孩资料，更多资源请联系客服加入会员后解锁！</t>
+  </si>
+  <si>
+    <t>北京资料浏览指南</t>
+  </si>
+  <si>
+    <t>朝阳、海淀、东城等区域都有工作室，也可以上门，具体要求请在咨询时说明。</t>
+  </si>
+  <si>
+    <t>可以找客服解锁更多感兴趣的资料，再结合时间、区域和风格进行进一步确认预约。</t>
+  </si>
+  <si>
+    <t>可说明朝阳、海淀、东城等区域偏好，方便快速查找。</t>
+  </si>
+  <si>
+    <t>北京精选入口</t>
+  </si>
+  <si>
+    <t>北京部分资料展示</t>
+  </si>
+  <si>
+    <t>北京资源常见问题</t>
+  </si>
+  <si>
+    <t>怎样查看北京全部资料？</t>
+  </si>
+  <si>
+    <t>江南雅意与城市精选</t>
+  </si>
+  <si>
+    <t>杭州外围｜杭州模特预约｜顶奢</t>
+  </si>
+  <si>
+    <t>顶奢杭州资源库，浏览杭州城市精选资料、独立图片说明、视频信息、独立说明与站内推荐。</t>
+  </si>
+  <si>
+    <t>杭州精选资料</t>
+  </si>
+  <si>
+    <t>欢迎您来到顶奢杭州精选，网页只展示部分女孩资料，更多资源请联系客服加入会员后解锁！</t>
+  </si>
+  <si>
+    <t>杭州资料浏览指南</t>
+  </si>
+  <si>
+    <t>杭州城市资料以雅致和精致风格为主，适合按照个人气质、形象特点喜好和展示内容进行浏览。每套资料都有独立页面，便于查看照片、视频和详细说明。</t>
+  </si>
+  <si>
+    <t>如果你关注西湖、上城、滨江，拱墅等区域，可以在咨询时提前说明。通过风格、区域和时间三个方向进行筛选，可以更快找到感兴趣的资料。</t>
+  </si>
+  <si>
+    <t>可根据西湖、上城、滨江、拱墅等区域说明个人偏好。</t>
+  </si>
+  <si>
+    <t>杭州精选入口</t>
+  </si>
+  <si>
+    <t>杭州部分资料展示</t>
+  </si>
+  <si>
+    <t>杭州资源常见问题</t>
+  </si>
+  <si>
+    <t>怎样查看杭州全部资料？</t>
+  </si>
+  <si>
+    <t>顶奢 · 固定页面内容</t>
+  </si>
+  <si>
+    <t>包括关于我们、联系我们、隐私政策、服务条款和 404 页面；只修改黄色内容列。</t>
+  </si>
+  <si>
+    <t>页面</t>
+  </si>
+  <si>
+    <t>page_code</t>
+  </si>
+  <si>
+    <t>about</t>
+  </si>
+  <si>
+    <t>page_name</t>
+  </si>
+  <si>
+    <t>页面分组名称</t>
+  </si>
+  <si>
+    <t>关于我们｜顶奢</t>
+  </si>
+  <si>
+    <t>修改后会重新生成该页面</t>
+  </si>
+  <si>
+    <t>了解顶奢城市资料库的内容结构、更新方式与浏览路径。</t>
+  </si>
+  <si>
+    <t>ABOUT · DINGSHE</t>
+  </si>
+  <si>
+    <t>hero_title</t>
+  </si>
+  <si>
+    <t>关于顶奢</t>
+  </si>
+  <si>
+    <t>首屏说明</t>
+  </si>
+  <si>
+    <t>顶奢旗下拥有海量高端外围模特资源，满足各界顶尖商务人士娱乐活动和商务交际需求。</t>
+  </si>
+  <si>
+    <t>sidebar_title</t>
+  </si>
+  <si>
+    <t>侧栏英文标题</t>
+  </si>
+  <si>
+    <t>ABOUT US</t>
+  </si>
+  <si>
+    <t>sidebar_1</t>
+  </si>
+  <si>
+    <t>侧栏第1项</t>
+  </si>
+  <si>
+    <t>sidebar_2</t>
+  </si>
+  <si>
+    <t>侧栏第2项</t>
+  </si>
+  <si>
+    <t>sidebar_3</t>
+  </si>
+  <si>
+    <t>侧栏第3项</t>
+  </si>
+  <si>
+    <t>内容标准</t>
+  </si>
+  <si>
+    <t>section_1_kicker</t>
+  </si>
+  <si>
+    <t>第1段英文</t>
+  </si>
+  <si>
+    <t>OUR PURPOSE</t>
+  </si>
+  <si>
+    <t>section_1_title</t>
+  </si>
+  <si>
+    <t>第1段标题</t>
+  </si>
+  <si>
+    <t>让每套资料拥有清晰、可持续的页面</t>
+  </si>
+  <si>
+    <t>section_1_body_1</t>
+  </si>
+  <si>
+    <t>第1段正文1</t>
+  </si>
+  <si>
+    <t>我们靠谱专业提供100%真实北京外围、上海外围、深圳外围、广州外围、佛山外围、东莞外围、武汉外围、南京外围、成都外围、重庆外围、福州外围、厦门外围、杭州外围、长沙外围、济南外围、郑州外围、西安外围、青岛外围。</t>
+  </si>
+  <si>
+    <t>section_1_body_2</t>
+  </si>
+  <si>
+    <t>第1段正文2</t>
+  </si>
+  <si>
+    <t>、以及国内主流城市和国外主流城市的高端外围模特、平面模特、商务模特、网红模特、车模、泳装模特、内衣模特、兼职空姐、coser、洛丽塔等高端资源。平台专业为社会名流高端人士提供高端靠谱商务外围服务，找全球伴游、兼职外围女模特、高端商务陪同、极品外围女请与我们联系。覆盖国内各大城市，规范化服务流程，注重客户隐私保护。</t>
+  </si>
+  <si>
+    <t>section_2_kicker</t>
+  </si>
+  <si>
+    <t>第2段英文</t>
+  </si>
+  <si>
+    <t>CITY DIRECTORY</t>
+  </si>
+  <si>
+    <t>section_2_title</t>
+  </si>
+  <si>
+    <t>第2段标题</t>
+  </si>
+  <si>
+    <t>从已发布城市开始浏览</t>
+  </si>
+  <si>
+    <t>section_3_kicker</t>
+  </si>
+  <si>
+    <t>第3段英文</t>
+  </si>
+  <si>
+    <t>CONTENT PRINCIPLES</t>
+  </si>
+  <si>
+    <t>section_3_title</t>
+  </si>
+  <si>
+    <t>第3段标题</t>
+  </si>
+  <si>
+    <t>顶奢资料特色</t>
+  </si>
+  <si>
+    <t>point_1_title</t>
+  </si>
+  <si>
+    <t>要点1标题</t>
+  </si>
+  <si>
     <t>城市精选</t>
   </si>
   <si>
-    <t>第一行标题</t>
-  </si>
-  <si>
-    <t>hero_title_emphasis</t>
-  </si>
-  <si>
-    <t>首屏强调标题</t>
-  </si>
-  <si>
-    <t>独立呈现</t>
-  </si>
-  <si>
-    <t>第二行金色标题</t>
-  </si>
-  <si>
-    <t>hero_description</t>
-  </si>
-  <si>
-    <t>首屏简介</t>
-  </si>
-  <si>
-    <t>按城市浏览独立资料。每个页面拥有稳定网址，并可持续更新文字、图片和视频内容。</t>
-  </si>
-  <si>
-    <t>主标题下方文字</t>
-  </si>
-  <si>
-    <t>首页统计</t>
-  </si>
-  <si>
-    <t>stat_city_label</t>
-  </si>
-  <si>
-    <t>城市数量标签</t>
-  </si>
-  <si>
-    <t>座城市</t>
-  </si>
-  <si>
-    <t>数字自动统计</t>
-  </si>
-  <si>
-    <t>stat_profile_label</t>
-  </si>
-  <si>
-    <t>资料数量标签</t>
-  </si>
-  <si>
-    <t>套资料</t>
-  </si>
-  <si>
-    <t>stat_media_value</t>
-  </si>
-  <si>
-    <t>媒体数量文字</t>
-  </si>
-  <si>
-    <t>自动统计</t>
-  </si>
-  <si>
-    <t>例如 3+1</t>
-  </si>
-  <si>
-    <t>stat_media_label</t>
-  </si>
-  <si>
-    <t>媒体数量标签</t>
-  </si>
-  <si>
-    <t>媒体文件</t>
-  </si>
-  <si>
-    <t>例如 媒体位</t>
-  </si>
-  <si>
-    <t>城市入口</t>
-  </si>
-  <si>
-    <t>city_section_kicker</t>
-  </si>
-  <si>
-    <t>城市区英文</t>
-  </si>
-  <si>
-    <t>EXPLORE BY CITY</t>
-  </si>
-  <si>
-    <t>城市入口标题上方英文</t>
-  </si>
-  <si>
-    <t>city_section_title</t>
-  </si>
-  <si>
-    <t>城市区标题</t>
-  </si>
-  <si>
-    <t>按城市浏览</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>city_section_description</t>
-  </si>
-  <si>
-    <t>城市区说明</t>
-  </si>
-  <si>
-    <t>已发布城市会自动显示在这里，后续可通过工作表继续增加城市和资料。</t>
-  </si>
-  <si>
-    <t>city_card_link_label</t>
-  </si>
-  <si>
-    <t>城市卡按钮</t>
-  </si>
-  <si>
-    <t>进入资源库</t>
-  </si>
-  <si>
-    <t>按钮后自动添加箭头</t>
-  </si>
-  <si>
-    <t>精选资料</t>
-  </si>
-  <si>
-    <t>featured_kicker</t>
-  </si>
-  <si>
-    <t>精选区英文</t>
-  </si>
-  <si>
-    <t>SELECTED PROFILES</t>
-  </si>
-  <si>
-    <t>featured_title</t>
-  </si>
-  <si>
-    <t>精选区标题</t>
-  </si>
-  <si>
-    <t>首批精选</t>
-  </si>
-  <si>
-    <t>底部卖点</t>
-  </si>
-  <si>
-    <t>promise_1_label</t>
-  </si>
-  <si>
-    <t>卖点1标签</t>
-  </si>
-  <si>
-    <t>专属页面</t>
-  </si>
-  <si>
-    <t>已从首页移除，不再显示；保留字段仅用于兼容旧工作表</t>
-  </si>
-  <si>
-    <t>promise_1_title</t>
-  </si>
-  <si>
-    <t>卖点1标题</t>
-  </si>
-  <si>
-    <t>promise_1_text</t>
-  </si>
-  <si>
-    <t>卖点1说明</t>
-  </si>
-  <si>
-    <t>每套资料拥有稳定网址和独立 SEO 信息。</t>
-  </si>
-  <si>
-    <t>promise_2_label</t>
-  </si>
-  <si>
-    <t>卖点2标签</t>
-  </si>
-  <si>
-    <t>图文视频</t>
-  </si>
-  <si>
-    <t>promise_2_title</t>
-  </si>
-  <si>
-    <t>卖点2标题</t>
-  </si>
-  <si>
-    <t>多媒体结构</t>
-  </si>
-  <si>
-    <t>promise_2_text</t>
-  </si>
-  <si>
-    <t>卖点2说明</t>
-  </si>
-  <si>
-    <t>图片和视频按实际资料配置，并提供独立说明与元数据。</t>
-  </si>
-  <si>
-    <t>promise_3_label</t>
-  </si>
-  <si>
-    <t>卖点3标签</t>
-  </si>
-  <si>
-    <t>持续更新</t>
-  </si>
-  <si>
-    <t>promise_3_title</t>
-  </si>
-  <si>
-    <t>卖点3标题</t>
-  </si>
-  <si>
-    <t>灵活扩展</t>
-  </si>
-  <si>
-    <t>promise_3_text</t>
-  </si>
-  <si>
-    <t>卖点3说明</t>
-  </si>
-  <si>
-    <t>城市、资料数量和内容均可继续追加。</t>
-  </si>
-  <si>
-    <t>预约流程</t>
-  </si>
-  <si>
-    <t>process_kicker</t>
-  </si>
-  <si>
-    <t>流程区英文</t>
-  </si>
-  <si>
-    <t>CONSULTATION PROCESS</t>
-  </si>
-  <si>
-    <t>process_title</t>
-  </si>
-  <si>
-    <t>流程区标题</t>
-  </si>
-  <si>
-    <t>预约咨询流程</t>
-  </si>
-  <si>
-    <t>首页五步流程标题</t>
-  </si>
-  <si>
-    <t>process_1_label</t>
-  </si>
-  <si>
-    <t>步骤1标题</t>
-  </si>
-  <si>
-    <t>联系客服</t>
-  </si>
-  <si>
-    <t>第一个流程按钮</t>
-  </si>
-  <si>
-    <t>process_1_text</t>
-  </si>
-  <si>
-    <t>步骤1说明</t>
-  </si>
-  <si>
-    <t>打开顶奢专属客服，说明想浏览或咨询的城市资料。</t>
-  </si>
-  <si>
-    <t>点击步骤1后显示</t>
-  </si>
-  <si>
-    <t>process_2_label</t>
-  </si>
-  <si>
-    <t>步骤2标题</t>
-  </si>
-  <si>
-    <t>告知需求</t>
-  </si>
-  <si>
-    <t>第二个流程按钮</t>
-  </si>
-  <si>
-    <t>process_2_text</t>
-  </si>
-  <si>
-    <t>步骤2说明</t>
-  </si>
-  <si>
-    <t>提供城市、时间和偏好，方便客服快速筛选合适资料。</t>
-  </si>
-  <si>
-    <t>点击步骤2后显示</t>
-  </si>
-  <si>
-    <t>process_3_label</t>
-  </si>
-  <si>
-    <t>步骤3标题</t>
-  </si>
-  <si>
-    <t>查看资料</t>
-  </si>
-  <si>
-    <t>第三个流程按钮</t>
-  </si>
-  <si>
-    <t>process_3_text</t>
-  </si>
-  <si>
-    <t>步骤3说明</t>
-  </si>
-  <si>
-    <t>客服发送可查看的页面与媒体内容，您可以继续比较和筛选。</t>
-  </si>
-  <si>
-    <t>点击步骤3后显示</t>
-  </si>
-  <si>
-    <t>process_4_label</t>
-  </si>
-  <si>
-    <t>步骤4标题</t>
-  </si>
-  <si>
-    <t>确认安排</t>
-  </si>
-  <si>
-    <t>第四个流程按钮</t>
-  </si>
-  <si>
-    <t>process_4_text</t>
-  </si>
-  <si>
-    <t>步骤4说明</t>
-  </si>
-  <si>
-    <t>确认选择、时间和必要事项；如有变化请及时沟通。</t>
-  </si>
-  <si>
-    <t>点击步骤4后显示</t>
-  </si>
-  <si>
-    <t>process_5_label</t>
-  </si>
-  <si>
-    <t>步骤5标题</t>
-  </si>
-  <si>
-    <t>保持联系</t>
-  </si>
-  <si>
-    <t>第五个流程按钮</t>
-  </si>
-  <si>
-    <t>process_5_text</t>
-  </si>
-  <si>
-    <t>步骤5说明</t>
-  </si>
-  <si>
-    <t>按确认信息进行后续沟通，并通过官方客服核对最新情况。</t>
-  </si>
-  <si>
-    <t>点击步骤5后显示</t>
-  </si>
-  <si>
-    <t>随机推荐</t>
-  </si>
-  <si>
-    <t>random_kicker</t>
-  </si>
-  <si>
-    <t>推荐区英文</t>
-  </si>
-  <si>
-    <t>DISCOVER MORE</t>
-  </si>
-  <si>
-    <t>随机资料标题上方英文</t>
-  </si>
-  <si>
-    <t>random_title</t>
-  </si>
-  <si>
-    <t>推荐区标题</t>
-  </si>
-  <si>
-    <t>相关资料推荐</t>
-  </si>
-  <si>
-    <t>首页随机资料标题</t>
-  </si>
-  <si>
-    <t>random_description</t>
-  </si>
-  <si>
-    <t>推荐区说明</t>
-  </si>
-  <si>
-    <t>每次打开页面都会随机展示不同城市的资料入口。</t>
-  </si>
-  <si>
-    <t>随机卡片上方说明</t>
-  </si>
-  <si>
-    <t>random_count</t>
-  </si>
-  <si>
-    <t>首页显示数量</t>
-  </si>
-  <si>
-    <t>请输入 4 至 12 的整数</t>
-  </si>
-  <si>
-    <t>常见问题</t>
-  </si>
-  <si>
-    <t>home_faq_kicker</t>
-  </si>
-  <si>
-    <t>问答区英文</t>
-  </si>
-  <si>
-    <t>COMMON QUESTIONS</t>
-  </si>
-  <si>
-    <t>home_faq_title</t>
-  </si>
-  <si>
-    <t>问答区标题</t>
-  </si>
-  <si>
-    <t>首页问答标题</t>
-  </si>
-  <si>
-    <t>home_faq_description</t>
-  </si>
-  <si>
-    <t>问答区说明</t>
-  </si>
-  <si>
-    <t>关于资料浏览、媒体更新和客服入口的说明。</t>
-  </si>
-  <si>
-    <t>首页问答简介</t>
-  </si>
-  <si>
-    <t>home_faq_1_question</t>
-  </si>
-  <si>
-    <t>问题1</t>
-  </si>
-  <si>
-    <t>如何选择城市资料？</t>
-  </si>
-  <si>
-    <t>点击后展开答案</t>
-  </si>
-  <si>
-    <t>home_faq_1_answer</t>
-  </si>
-  <si>
-    <t>答案1</t>
-  </si>
-  <si>
-    <t>可先从首页选择城市，再通过资料卡进入独立详情页；也可以联系在线客服说明偏好。</t>
-  </si>
-  <si>
-    <t>问题1答案</t>
-  </si>
-  <si>
-    <t>home_faq_2_question</t>
-  </si>
-  <si>
-    <t>问题2</t>
-  </si>
-  <si>
-    <t>每套资料是否有独立页面？</t>
-  </si>
-  <si>
-    <t>home_faq_2_answer</t>
-  </si>
-  <si>
-    <t>答案2</t>
-  </si>
-  <si>
-    <t>是。每套资料使用固定详情页，文字、图片和视频可独立更新。</t>
-  </si>
-  <si>
-    <t>问题2答案</t>
-  </si>
-  <si>
-    <t>home_faq_3_question</t>
-  </si>
-  <si>
-    <t>问题3</t>
-  </si>
-  <si>
-    <t>图片和视频如何查看？</t>
-  </si>
-  <si>
-    <t>home_faq_3_answer</t>
-  </si>
-  <si>
-    <t>答案3</t>
-  </si>
-  <si>
-    <t>已上传的真实媒体会显示在详情页；未上传内容会保留品牌占位图，不会伪造资料。</t>
-  </si>
-  <si>
-    <t>问题3答案</t>
-  </si>
-  <si>
-    <t>home_faq_4_question</t>
-  </si>
-  <si>
-    <t>问题4</t>
-  </si>
-  <si>
-    <t>页面内容多久更新？</t>
-  </si>
-  <si>
-    <t>home_faq_4_answer</t>
-  </si>
-  <si>
-    <t>答案4</t>
-  </si>
-  <si>
-    <t>城市和资料可持续增加；页面会显示真实更新时间，Sitemap 仅提交允许收录的页面。</t>
-  </si>
-  <si>
-    <t>问题4答案</t>
-  </si>
-  <si>
-    <t>home_faq_5_question</t>
-  </si>
-  <si>
-    <t>问题5</t>
-  </si>
-  <si>
-    <t>如何联系顶奢客服？</t>
-  </si>
-  <si>
-    <t>home_faq_5_answer</t>
-  </si>
-  <si>
-    <t>答案5</t>
-  </si>
-  <si>
-    <t>点击页面右下角的顶奢专属咨询按钮，即可在当前页面打开客服窗口。</t>
-  </si>
-  <si>
-    <t>问题5答案</t>
-  </si>
-  <si>
-    <t>home_faq_6_question</t>
-  </si>
-  <si>
-    <t>问题6</t>
-  </si>
-  <si>
-    <t>后续会增加更多城市吗？</t>
-  </si>
-  <si>
-    <t>home_faq_6_answer</t>
-  </si>
-  <si>
-    <t>答案6</t>
-  </si>
-  <si>
-    <t>可以。新增城市和资料会沿用现有结构，并通过首页、城市页和相关推荐连接。</t>
-  </si>
-  <si>
-    <t>问题6答案</t>
-  </si>
-  <si>
-    <t>顶奢 · 城市首页批量编辑</t>
-  </si>
-  <si>
-    <t>现有城市代码不要修改；新增城市可在下一空白行填写全部内容，并设置发布、收录和显示顺序。</t>
-  </si>
-  <si>
-    <t>城市名称</t>
-  </si>
-  <si>
-    <t>城市代码</t>
-  </si>
-  <si>
-    <t>导航短句</t>
-  </si>
-  <si>
-    <t>首屏标题</t>
-  </si>
-  <si>
-    <t>数量标签</t>
-  </si>
-  <si>
-    <t>专题英文</t>
-  </si>
-  <si>
-    <t>专题标题</t>
-  </si>
-  <si>
-    <t>亮点1标题</t>
-  </si>
-  <si>
-    <t>亮点1说明</t>
-  </si>
-  <si>
-    <t>亮点2标题</t>
-  </si>
-  <si>
-    <t>亮点2说明</t>
-  </si>
-  <si>
-    <t>亮点3标题</t>
-  </si>
-  <si>
-    <t>亮点3说明</t>
-  </si>
-  <si>
-    <t>精选英文</t>
-  </si>
-  <si>
-    <t>精选标题</t>
-  </si>
-  <si>
-    <t>精选说明</t>
-  </si>
-  <si>
-    <t>全部英文</t>
-  </si>
-  <si>
-    <t>全部标题</t>
-  </si>
-  <si>
-    <t>全部说明</t>
-  </si>
-  <si>
-    <t>FAQ英文</t>
-  </si>
-  <si>
-    <t>FAQ标题</t>
-  </si>
-  <si>
-    <t>FAQ说明</t>
-  </si>
-  <si>
-    <t>回答1</t>
-  </si>
-  <si>
-    <t>回答2</t>
-  </si>
-  <si>
-    <t>回答3</t>
-  </si>
-  <si>
-    <t>更多城市英文</t>
-  </si>
-  <si>
-    <t>更多城市标题</t>
-  </si>
-  <si>
-    <t>海派格调与都会精选</t>
-  </si>
-  <si>
-    <t>上海外围｜上海模特预约｜顶奢</t>
-  </si>
-  <si>
-    <t>顶奢上海资源库，集中展示上海城市精选资料、独立图片、视频、风格介绍与相关推荐。</t>
-  </si>
-  <si>
-    <t>CITY COLLECTION</t>
-  </si>
-  <si>
-    <t>上海精选资料</t>
-  </si>
-  <si>
-    <t>欢迎您来到顶奢上海精选，网页只展示部分女孩资料，进入独立详情页查看照片、视频与完整介绍，更多资源请联系客服加入会员后解锁！</t>
-  </si>
-  <si>
-    <t>套独立资料</t>
-  </si>
-  <si>
-    <t>CITY GUIDE</t>
-  </si>
-  <si>
-    <t>上海资料浏览指南</t>
-  </si>
-  <si>
-    <t>上海兼具都会节奏与精致审美，资料库收录不同风格的城市精选内容。你可以从个人气质、形象特点和展示风格入手，进入独立详情页查看照片、视频与完整介绍。</t>
-  </si>
-  <si>
-    <t>如果你对静安、徐汇、闵行、宝山、浦东等区域有明确偏好，可以在咨询时告诉客服，可以更高效地找到符合需求的资料</t>
-  </si>
-  <si>
-    <t>资源丰富</t>
-  </si>
-  <si>
-    <t>涵盖清新、御姐、模特等不同资料风格。</t>
-  </si>
-  <si>
-    <t>区域选择</t>
-  </si>
-  <si>
-    <t>可根据静安、徐汇、闵行、宝山、浦东等区域说明需求。</t>
-  </si>
-  <si>
-    <t>专属客服</t>
-  </si>
-  <si>
-    <t>提供偏好和时间，客服可协助快速查找合适资料。</t>
-  </si>
-  <si>
-    <t>EDITOR'S SELECTION</t>
-  </si>
-  <si>
-    <t>上海精选入口</t>
-  </si>
-  <si>
-    <t>先从代表性资料开始，再浏览本页完整列表。</t>
-  </si>
-  <si>
-    <t>ALL PROFILES</t>
-  </si>
-  <si>
-    <t>上海部分资料展示</t>
-  </si>
-  <si>
-    <t>当前共 {count} 个可直接访问的独立详情页。</t>
-  </si>
-  <si>
-    <t>上海资源常见问题</t>
-  </si>
-  <si>
-    <t>关于流程与价格的简要说明。</t>
-  </si>
-  <si>
-    <t>怎样查看上海全部资料？</t>
-  </si>
-  <si>
-    <t>联系客服加入会员后可解锁当天全部资料！</t>
-  </si>
-  <si>
-    <t>关于价格，怎么消费？</t>
-  </si>
-  <si>
-    <t>普通快3夜8，高级快5夜1.5，无其他隐形消费！且见人满意再付。特殊定制服务请与我们联系告知需求获得报价。</t>
-  </si>
-  <si>
-    <t>不如会可以安排吗？</t>
-  </si>
-  <si>
-    <t>非会员一律不安排，毕竟网络时代，我们没有办法一一甄别。希望您能理解，我们以诚信为基础，对各方负责。非会员放鸽子几率太高，浪费我们资源和时间，如果您诚心有需求，入会既可给予我们一些信任，另外也让我们把时间花在了真正需要的人身上。</t>
-  </si>
-  <si>
-    <t>MORE CITIES</t>
-  </si>
-  <si>
-    <t>继续浏览其他城市</t>
-  </si>
-  <si>
-    <t>岭南风尚与城市精选</t>
-  </si>
-  <si>
-    <t>广州外围｜广州模特预约｜顶奢</t>
-  </si>
-  <si>
-    <t>顶奢广州资源库，浏览广州城市精选资料、专属图片、视频介绍及相关城市内容。</t>
-  </si>
-  <si>
-    <t>广州精选资料</t>
-  </si>
-  <si>
-    <t>欢迎您来到顶奢广州精选，网页只展示部分女孩资料，更多资源请联系客服加入会员后解锁！</t>
-  </si>
-  <si>
-    <t>广州资料浏览指南</t>
-  </si>
-  <si>
-    <t>广州城市资料注重自然气质与多样风格，每套资料均有独立页面，可查看图片、视频和详细介绍。</t>
-  </si>
-  <si>
-    <t>可以结合天河、越秀、海珠或珠江新城等常见区域进行选择。说明时间安排与活动区域，可以更高效地找到符合需求的资料</t>
-  </si>
-  <si>
-    <t>可说明天河、越秀、海珠等区域偏好，方便进一步查找。</t>
-  </si>
-  <si>
-    <t>详情请和客服咨询逐步完成预约。</t>
-  </si>
-  <si>
-    <t>广州精选入口</t>
-  </si>
-  <si>
-    <t>广州部分资料展示</t>
-  </si>
-  <si>
-    <t>广州资源常见问题</t>
-  </si>
-  <si>
-    <t>怎样查看广州全部资料？</t>
-  </si>
-  <si>
-    <t>湾区新锐与现代精选</t>
-  </si>
-  <si>
-    <t>深圳外围｜深圳模特预约｜顶奢</t>
-  </si>
-  <si>
-    <t>顶奢深圳资源库，查看深圳现代城市精选资料、图片展示、视频位置与相关推荐。</t>
-  </si>
-  <si>
-    <t>深圳精选资料</t>
-  </si>
-  <si>
-    <t>欢迎您来到顶奢深圳精选，网页只展示部分女孩资料，更多资源请联系客服加入会员后解锁！</t>
-  </si>
-  <si>
-    <t>深圳资料浏览指南</t>
-  </si>
-  <si>
-    <t>深圳资料库以现代、时尚和年轻化风格为主，收录不同气质的城市精选资料。你可以通过资料卡快速了解基本特点，再进入详情页查看完整图片、视频与介绍。</t>
-  </si>
-  <si>
-    <t>如果你关注福田、南山、罗湖、宝安、龙华等区域，可以在咨询时提前说明。结合风格偏好、时间安排与活动区域，可以更高效地找到符合需求的资料。</t>
-  </si>
-  <si>
-    <t>可根据福田、南山、罗湖、龙华、宝安等区域进一步筛选。</t>
-  </si>
-  <si>
-    <t>快速匹配</t>
-  </si>
-  <si>
-    <t>说明个人偏好后，可由客服协助整理和比较资料。</t>
-  </si>
-  <si>
-    <t>深圳精选入口</t>
-  </si>
-  <si>
-    <t>深圳部分资料展示</t>
-  </si>
-  <si>
-    <t>深圳资源常见问题</t>
-  </si>
-  <si>
-    <t>怎样查看深圳全部资料？</t>
-  </si>
-  <si>
-    <t>京华气韵与城市精选</t>
-  </si>
-  <si>
-    <t>北京外围｜北京模特预约｜顶奢</t>
-  </si>
-  <si>
-    <t>顶奢北京资源库，汇总北京城市精选资料、独立图片、视频、专题说明和相关推荐。</t>
-  </si>
-  <si>
-    <t>北京精选资料</t>
-  </si>
-  <si>
-    <t>欢迎您来到顶奢北京精选，网页只展示部分女孩资料，更多资源请联系客服加入会员后解锁！</t>
-  </si>
-  <si>
-    <t>北京资料浏览指南</t>
-  </si>
-  <si>
-    <t>朝阳、海淀、东城等区域都有工作室，也可以上门，具体要求请在咨询时说明。</t>
-  </si>
-  <si>
-    <t>可以找客服解锁更多感兴趣的资料，再结合时间、区域和风格进行进一步确认预约。</t>
-  </si>
-  <si>
-    <t>可说明朝阳、海淀、东城等区域偏好，方便快速查找。</t>
-  </si>
-  <si>
-    <t>北京精选入口</t>
-  </si>
-  <si>
-    <t>北京部分资料展示</t>
-  </si>
-  <si>
-    <t>北京资源常见问题</t>
-  </si>
-  <si>
-    <t>怎样查看北京全部资料？</t>
-  </si>
-  <si>
-    <t>江南雅意与城市精选</t>
-  </si>
-  <si>
-    <t>杭州外围｜杭州模特预约｜顶奢</t>
-  </si>
-  <si>
-    <t>顶奢杭州资源库，浏览杭州城市精选资料、独立图片说明、视频信息、独立说明与站内推荐。</t>
-  </si>
-  <si>
-    <t>杭州精选资料</t>
-  </si>
-  <si>
-    <t>欢迎您来到顶奢杭州精选，网页只展示部分女孩资料，更多资源请联系客服加入会员后解锁！</t>
-  </si>
-  <si>
-    <t>杭州资料浏览指南</t>
-  </si>
-  <si>
-    <t>杭州城市资料以雅致和精致风格为主，适合按照个人气质、形象特点喜好和展示内容进行浏览。每套资料都有独立页面，便于查看照片、视频和详细说明。</t>
-  </si>
-  <si>
-    <t>如果你关注西湖、上城、滨江，拱墅等区域，可以在咨询时提前说明。通过风格、区域和时间三个方向进行筛选，可以更快找到感兴趣的资料。</t>
-  </si>
-  <si>
-    <t>可根据西湖、上城、滨江、拱墅等区域说明个人偏好。</t>
-  </si>
-  <si>
-    <t>杭州精选入口</t>
-  </si>
-  <si>
-    <t>杭州部分资料展示</t>
-  </si>
-  <si>
-    <t>杭州资源常见问题</t>
-  </si>
-  <si>
-    <t>怎样查看杭州全部资料？</t>
-  </si>
-  <si>
-    <t>顶奢 · 固定页面内容</t>
-  </si>
-  <si>
-    <t>包括关于我们、联系我们、隐私政策、服务条款和 404 页面；只修改黄色内容列。</t>
-  </si>
-  <si>
-    <t>页面</t>
-  </si>
-  <si>
-    <t>page_code</t>
-  </si>
-  <si>
-    <t>about</t>
-  </si>
-  <si>
-    <t>page_name</t>
-  </si>
-  <si>
-    <t>页面分组名称</t>
-  </si>
-  <si>
-    <t>关于我们｜顶奢</t>
-  </si>
-  <si>
-    <t>修改后会重新生成该页面</t>
-  </si>
-  <si>
-    <t>了解顶奢城市资料库的内容结构、更新方式与浏览路径。</t>
-  </si>
-  <si>
-    <t>ABOUT · DINGSHE</t>
-  </si>
-  <si>
-    <t>hero_title</t>
-  </si>
-  <si>
-    <t>关于顶奢</t>
-  </si>
-  <si>
-    <t>首屏说明</t>
-  </si>
-  <si>
-    <t>顶奢按已发布城市组织独立资料，并持续更新页面文字、图片、视频和站内链接。</t>
-  </si>
-  <si>
-    <t>sidebar_title</t>
-  </si>
-  <si>
-    <t>侧栏英文标题</t>
-  </si>
-  <si>
-    <t>ABOUT US</t>
-  </si>
-  <si>
-    <t>sidebar_1</t>
-  </si>
-  <si>
-    <t>侧栏第1项</t>
-  </si>
-  <si>
-    <t>网站定位</t>
-  </si>
-  <si>
-    <t>sidebar_2</t>
-  </si>
-  <si>
-    <t>侧栏第2项</t>
-  </si>
-  <si>
-    <t>sidebar_3</t>
-  </si>
-  <si>
-    <t>侧栏第3项</t>
-  </si>
-  <si>
-    <t>内容标准</t>
-  </si>
-  <si>
-    <t>section_1_kicker</t>
-  </si>
-  <si>
-    <t>第1段英文</t>
-  </si>
-  <si>
-    <t>OUR PURPOSE</t>
-  </si>
-  <si>
-    <t>section_1_title</t>
-  </si>
-  <si>
-    <t>第1段标题</t>
-  </si>
-  <si>
-    <t>让每套资料拥有清晰、可持续的页面</t>
-  </si>
-  <si>
-    <t>section_1_body_1</t>
-  </si>
-  <si>
-    <t>第1段正文1</t>
-  </si>
-  <si>
-    <t>顶奢是按城市组织的资料展示站。我们以“首页—城市资源库—独立详情页”的结构整理内容，让访问者快速定位城市，也让每套资料拥有稳定网址、独立媒体说明和持续更新空间。</t>
-  </si>
-  <si>
-    <t>section_1_body_2</t>
-  </si>
-  <si>
-    <t>第1段正文2</t>
-  </si>
-  <si>
-    <t>城市页负责介绍本地内容与提供完整入口；详情页根据实际资料承载图片、视频、文字说明和相关推荐。后续增加城市或资料时，现有页面路径不会被打乱。</t>
-  </si>
-  <si>
-    <t>section_2_kicker</t>
-  </si>
-  <si>
-    <t>第2段英文</t>
-  </si>
-  <si>
-    <t>CITY DIRECTORY</t>
-  </si>
-  <si>
-    <t>section_2_title</t>
-  </si>
-  <si>
-    <t>第2段标题</t>
-  </si>
-  <si>
-    <t>从已发布城市开始浏览</t>
-  </si>
-  <si>
-    <t>section_3_kicker</t>
-  </si>
-  <si>
-    <t>第3段英文</t>
-  </si>
-  <si>
-    <t>CONTENT PRINCIPLES</t>
-  </si>
-  <si>
-    <t>section_3_title</t>
-  </si>
-  <si>
-    <t>第3段标题</t>
-  </si>
-  <si>
-    <t>我们的内容标准</t>
-  </si>
-  <si>
-    <t>point_1_title</t>
-  </si>
-  <si>
-    <t>要点1标题</t>
-  </si>
-  <si>
     <t>point_1_text</t>
   </si>
   <si>
     <t>要点1说明</t>
   </si>
   <si>
-    <t>为每套资料提供独立标题、介绍、媒体说明与详情网址。</t>
+    <t>按城市整理精选资料，每套内容独立展示，查找更加清晰便捷。</t>
   </si>
   <si>
     <t>point_2_title</t>
@@ -4421,7 +4502,7 @@
     <t>要点2标题</t>
   </si>
   <si>
-    <t>图文一致</t>
+    <t>图文展示</t>
   </si>
   <si>
     <t>point_2_text</t>
@@ -4430,7 +4511,7 @@
     <t>要点2说明</t>
   </si>
   <si>
-    <t>图片替代文字、主图说明和附近正文围绕同一页面主题编写。</t>
+    <t>每套资料可展示详细介绍、高清图片和相关视频，内容一目了然。</t>
   </si>
   <si>
     <t>point_3_title</t>
@@ -4439,16 +4520,13 @@
     <t>要点3标题</t>
   </si>
   <si>
-    <t>清晰互联</t>
-  </si>
-  <si>
     <t>point_3_text</t>
   </si>
   <si>
     <t>要点3说明</t>
   </si>
   <si>
-    <t>通过城市回链、相关推荐和有意义的锚文本连接重要页面。</t>
+    <t>页面内容会随时补充与更新，并提供更多同城资料推荐。</t>
   </si>
   <si>
     <t>closing_text</t>
@@ -4499,7 +4577,7 @@
     <t>介绍正文</t>
   </si>
   <si>
-    <t>需要了解城市资料、页面内容或其他信息时，可直接打开在线客服。客服入口已接入顶奢专属客服，并会在当前页面打开沟通窗口。</t>
+    <t>需要了解其他城市资料，可直接打开在线客服咨询加入会员。</t>
   </si>
   <si>
     <t>email_label</t>
@@ -4526,7 +4604,7 @@
     <t>提示文字</t>
   </si>
   <si>
-    <t>开始咨询前，你也可以查看我们的隐私政策与服务条款。</t>
+    <t>开始咨询前，可以先浏览精选资源！</t>
   </si>
   <si>
     <t>card_kicker</t>
@@ -4709,7 +4787,7 @@
     <t>第5段标题</t>
   </si>
   <si>
-    <t>5. 保存与安全</t>
+    <t>5. 隐私与安全</t>
   </si>
   <si>
     <t>section_5_body_1</t>
@@ -4718,7 +4796,7 @@
     <t>第5段正文1</t>
   </si>
   <si>
-    <t>我们会在实现运营、回复咨询、安全审计或履行必要义务所需的期限内保存相关信息，并采取合理措施减少未经授权的访问、泄露或滥用风险。互联网传输无法保证绝对安全。</t>
+    <t>我们非常重视客户的隐私和安全，采取严格的措施保障信息和资料的最高级别保密。</t>
   </si>
   <si>
     <t>section_5_body_2</t>
@@ -4868,7 +4946,7 @@
     <t>页脚品牌说明</t>
   </si>
   <si>
-    <t>按城市浏览独立资料。每套内容拥有固定网址、独立媒体与可持续扩展的页面结构。</t>
+    <t>顶奢平台专业为社会名流高端人士提供高端靠谱商务外围服务，找全球伴游、兼职外围女模特、高端商务陪同、极品外围女请与我们联系。资源覆盖国内一二线城市以及海外各大主流城市，规范化服务流程，注重客户隐私保护。</t>
   </si>
   <si>
     <t>全站每个页面都会显示</t>
@@ -7988,10 +8066,10 @@
         <v>182</v>
       </c>
       <c r="S15" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="T15" s="21" t="s">
         <v>183</v>
-      </c>
-      <c r="T15" s="21" t="s">
-        <v>184</v>
       </c>
       <c r="U15" s="5" t="s">
         <v>58</v>
@@ -8060,23 +8138,23 @@
         <v>61</v>
       </c>
       <c r="E16" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="F16" s="22" t="s">
         <v>185</v>
-      </c>
-      <c r="F16" s="22" t="s">
-        <v>186</v>
       </c>
       <c r="G16" s="5" t="str">
         <f t="shared" si="0"/>
         <v>浏览广州外围模特小雨的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H16" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="I16" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="I16" s="17" t="s">
+      <c r="J16" s="17" t="s">
         <v>188</v>
-      </c>
-      <c r="J16" s="17" t="s">
-        <v>189</v>
       </c>
       <c r="K16" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8089,25 +8167,25 @@
         <v>177</v>
       </c>
       <c r="N16" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="O16" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="O16" s="21" t="s">
+      <c r="P16" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="P16" s="21" t="s">
+      <c r="Q16" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="Q16" s="21" t="s">
+      <c r="R16" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="R16" s="21" t="s">
+      <c r="S16" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="T16" s="21" t="s">
         <v>194</v>
-      </c>
-      <c r="S16" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="T16" s="21" t="s">
-        <v>195</v>
       </c>
       <c r="U16" s="5" t="s">
         <v>58</v>
@@ -8176,23 +8254,23 @@
         <v>73</v>
       </c>
       <c r="E17" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="F17" s="22" t="s">
         <v>196</v>
-      </c>
-      <c r="F17" s="22" t="s">
-        <v>197</v>
       </c>
       <c r="G17" s="5" t="str">
         <f t="shared" si="0"/>
         <v>浏览广州外围模特喵喵的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H17" s="17" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>136</v>
       </c>
       <c r="J17" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K17" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8205,25 +8283,25 @@
         <v>177</v>
       </c>
       <c r="N17" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="O17" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="O17" s="21" t="s">
+      <c r="P17" s="21" t="s">
         <v>201</v>
       </c>
-      <c r="P17" s="21" t="s">
+      <c r="Q17" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="Q17" s="21" t="s">
+      <c r="R17" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="R17" s="21" t="s">
+      <c r="S17" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="T17" s="21" t="s">
         <v>204</v>
-      </c>
-      <c r="S17" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="T17" s="21" t="s">
-        <v>205</v>
       </c>
       <c r="U17" s="5" t="s">
         <v>58</v>
@@ -8292,23 +8370,23 @@
         <v>85</v>
       </c>
       <c r="E18" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="F18" s="22" t="s">
         <v>206</v>
-      </c>
-      <c r="F18" s="22" t="s">
-        <v>207</v>
       </c>
       <c r="G18" s="5" t="str">
         <f t="shared" si="0"/>
         <v>浏览广州外围模特凯莉的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H18" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="I18" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="I18" s="5" t="s">
+      <c r="J18" s="17" t="s">
         <v>209</v>
-      </c>
-      <c r="J18" s="17" t="s">
-        <v>210</v>
       </c>
       <c r="K18" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8321,25 +8399,25 @@
         <v>177</v>
       </c>
       <c r="N18" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="O18" s="21" t="s">
         <v>211</v>
       </c>
-      <c r="O18" s="21" t="s">
+      <c r="P18" s="21" t="s">
         <v>212</v>
       </c>
-      <c r="P18" s="21" t="s">
+      <c r="Q18" s="21" t="s">
         <v>213</v>
       </c>
-      <c r="Q18" s="21" t="s">
+      <c r="R18" s="21" t="s">
         <v>214</v>
       </c>
-      <c r="R18" s="21" t="s">
+      <c r="S18" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="T18" s="21" t="s">
         <v>215</v>
-      </c>
-      <c r="S18" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="T18" s="21" t="s">
-        <v>216</v>
       </c>
       <c r="U18" s="5" t="s">
         <v>58</v>
@@ -8408,23 +8486,23 @@
         <v>97</v>
       </c>
       <c r="E19" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F19" s="22" t="s">
         <v>217</v>
-      </c>
-      <c r="F19" s="22" t="s">
-        <v>218</v>
       </c>
       <c r="G19" s="5" t="str">
         <f t="shared" si="0"/>
         <v>浏览广州外围模特秋秋的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I19" s="17" t="s">
         <v>47</v>
       </c>
       <c r="J19" s="17" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K19" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8437,25 +8515,25 @@
         <v>177</v>
       </c>
       <c r="N19" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="O19" s="21" t="s">
         <v>221</v>
       </c>
-      <c r="O19" s="21" t="s">
+      <c r="P19" s="21" t="s">
         <v>222</v>
       </c>
-      <c r="P19" s="21" t="s">
+      <c r="Q19" s="21" t="s">
         <v>223</v>
       </c>
-      <c r="Q19" s="21" t="s">
+      <c r="R19" s="21" t="s">
         <v>224</v>
       </c>
-      <c r="R19" s="21" t="s">
+      <c r="S19" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="T19" s="21" t="s">
         <v>225</v>
-      </c>
-      <c r="S19" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="T19" s="21" t="s">
-        <v>226</v>
       </c>
       <c r="U19" s="5" t="s">
         <v>58</v>
@@ -8524,23 +8602,23 @@
         <v>109</v>
       </c>
       <c r="E20" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="F20" s="22" t="s">
         <v>227</v>
-      </c>
-      <c r="F20" s="22" t="s">
-        <v>228</v>
       </c>
       <c r="G20" s="5" t="str">
         <f t="shared" si="0"/>
         <v>浏览广州外围模特林西西的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>174</v>
       </c>
       <c r="J20" s="17" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K20" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8553,25 +8631,25 @@
         <v>177</v>
       </c>
       <c r="N20" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="O20" s="21" t="s">
         <v>231</v>
       </c>
-      <c r="O20" s="21" t="s">
+      <c r="P20" s="21" t="s">
         <v>232</v>
       </c>
-      <c r="P20" s="21" t="s">
+      <c r="Q20" s="21" t="s">
         <v>233</v>
       </c>
-      <c r="Q20" s="21" t="s">
+      <c r="R20" s="21" t="s">
         <v>234</v>
       </c>
-      <c r="R20" s="21" t="s">
+      <c r="S20" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="T20" s="21" t="s">
         <v>235</v>
-      </c>
-      <c r="S20" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="T20" s="21" t="s">
-        <v>236</v>
       </c>
       <c r="U20" s="5" t="s">
         <v>58</v>
@@ -8640,23 +8718,23 @@
         <v>121</v>
       </c>
       <c r="E21" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="F21" s="22" t="s">
         <v>237</v>
-      </c>
-      <c r="F21" s="22" t="s">
-        <v>238</v>
       </c>
       <c r="G21" s="5" t="str">
         <f t="shared" si="0"/>
         <v>浏览广州外围模特舒舒的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H21" s="17" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>124</v>
       </c>
       <c r="J21" s="17" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K21" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8669,25 +8747,25 @@
         <v>177</v>
       </c>
       <c r="N21" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="O21" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O21" s="21" t="s">
+      <c r="P21" s="21" t="s">
         <v>242</v>
       </c>
-      <c r="P21" s="21" t="s">
+      <c r="Q21" s="21" t="s">
         <v>243</v>
       </c>
-      <c r="Q21" s="21" t="s">
+      <c r="R21" s="21" t="s">
         <v>244</v>
       </c>
-      <c r="R21" s="21" t="s">
+      <c r="S21" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="T21" s="21" t="s">
         <v>245</v>
-      </c>
-      <c r="S21" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="T21" s="21" t="s">
-        <v>246</v>
       </c>
       <c r="U21" s="5" t="s">
         <v>58</v>
@@ -8756,23 +8834,23 @@
         <v>133</v>
       </c>
       <c r="E22" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="F22" s="22" t="s">
         <v>247</v>
-      </c>
-      <c r="F22" s="22" t="s">
-        <v>248</v>
       </c>
       <c r="G22" s="5" t="str">
         <f t="shared" si="0"/>
         <v>浏览广州外围模特小雅的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I22" s="5" t="s">
         <v>136</v>
       </c>
       <c r="J22" s="17" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K22" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8785,25 +8863,25 @@
         <v>177</v>
       </c>
       <c r="N22" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="O22" s="21" t="s">
         <v>251</v>
       </c>
-      <c r="O22" s="21" t="s">
+      <c r="P22" s="21" t="s">
         <v>252</v>
       </c>
-      <c r="P22" s="21" t="s">
+      <c r="Q22" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="Q22" s="21" t="s">
+      <c r="R22" s="21" t="s">
         <v>254</v>
       </c>
-      <c r="R22" s="21" t="s">
+      <c r="S22" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="T22" s="21" t="s">
         <v>255</v>
-      </c>
-      <c r="S22" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="T22" s="21" t="s">
-        <v>256</v>
       </c>
       <c r="U22" s="5" t="s">
         <v>58</v>
@@ -8872,23 +8950,23 @@
         <v>145</v>
       </c>
       <c r="E23" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="F23" s="22" t="s">
         <v>257</v>
-      </c>
-      <c r="F23" s="22" t="s">
-        <v>258</v>
       </c>
       <c r="G23" s="5" t="str">
         <f t="shared" si="0"/>
         <v>浏览广州外围模特林晚的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H23" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="I23" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="J23" s="17" t="s">
         <v>259</v>
-      </c>
-      <c r="I23" s="17" t="s">
-        <v>209</v>
-      </c>
-      <c r="J23" s="17" t="s">
-        <v>260</v>
       </c>
       <c r="K23" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8901,25 +8979,25 @@
         <v>177</v>
       </c>
       <c r="N23" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="O23" s="21" t="s">
         <v>261</v>
       </c>
-      <c r="O23" s="21" t="s">
+      <c r="P23" s="21" t="s">
         <v>262</v>
       </c>
-      <c r="P23" s="21" t="s">
+      <c r="Q23" s="21" t="s">
         <v>263</v>
       </c>
-      <c r="Q23" s="21" t="s">
+      <c r="R23" s="21" t="s">
         <v>264</v>
       </c>
-      <c r="R23" s="21" t="s">
+      <c r="S23" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="T23" s="21" t="s">
         <v>265</v>
-      </c>
-      <c r="S23" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="T23" s="21" t="s">
-        <v>266</v>
       </c>
       <c r="U23" s="5" t="s">
         <v>58</v>
@@ -8988,23 +9066,23 @@
         <v>158</v>
       </c>
       <c r="E24" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="F24" s="22" t="s">
         <v>267</v>
-      </c>
-      <c r="F24" s="22" t="s">
-        <v>268</v>
       </c>
       <c r="G24" s="5" t="str">
         <f t="shared" si="0"/>
         <v>浏览广州外围模特羽莱的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H24" s="17" t="s">
+        <v>268</v>
+      </c>
+      <c r="I24" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="J24" s="17" t="s">
         <v>269</v>
-      </c>
-      <c r="I24" s="17" t="s">
-        <v>209</v>
-      </c>
-      <c r="J24" s="17" t="s">
-        <v>270</v>
       </c>
       <c r="K24" s="5" t="str">
         <f t="shared" si="1"/>
@@ -9017,25 +9095,25 @@
         <v>177</v>
       </c>
       <c r="N24" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="O24" s="21" t="s">
         <v>271</v>
       </c>
-      <c r="O24" s="21" t="s">
+      <c r="P24" s="21" t="s">
         <v>272</v>
       </c>
-      <c r="P24" s="21" t="s">
+      <c r="Q24" s="21" t="s">
         <v>273</v>
       </c>
-      <c r="Q24" s="21" t="s">
+      <c r="R24" s="21" t="s">
         <v>274</v>
       </c>
-      <c r="R24" s="21" t="s">
+      <c r="S24" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="T24" s="21" t="s">
         <v>275</v>
-      </c>
-      <c r="S24" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="T24" s="21" t="s">
-        <v>276</v>
       </c>
       <c r="U24" s="5" t="s">
         <v>58</v>
@@ -9092,10 +9170,10 @@
     </row>
     <row r="25" ht="42" customHeight="1" spans="1:38">
       <c r="A25" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="B25" s="21" t="s">
         <v>277</v>
-      </c>
-      <c r="B25" s="21" t="s">
-        <v>278</v>
       </c>
       <c r="C25" s="21" t="s">
         <v>42</v>
@@ -9104,23 +9182,23 @@
         <v>43</v>
       </c>
       <c r="E25" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="F25" s="22" t="s">
         <v>279</v>
-      </c>
-      <c r="F25" s="22" t="s">
-        <v>280</v>
       </c>
       <c r="G25" s="5" t="str">
         <f t="shared" si="0"/>
         <v>浏览深圳外围模特的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H25" s="17" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I25" s="17" t="s">
         <v>47</v>
       </c>
       <c r="J25" s="17" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K25" s="5" t="str">
         <f t="shared" si="1"/>
@@ -9130,28 +9208,28 @@
         <v>176</v>
       </c>
       <c r="M25" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="N25" s="21" t="s">
         <v>283</v>
       </c>
-      <c r="N25" s="21" t="s">
+      <c r="O25" s="21" t="s">
         <v>284</v>
       </c>
-      <c r="O25" s="21" t="s">
+      <c r="P25" s="21" t="s">
         <v>285</v>
       </c>
-      <c r="P25" s="21" t="s">
+      <c r="Q25" s="21" t="s">
         <v>286</v>
       </c>
-      <c r="Q25" s="21" t="s">
+      <c r="R25" s="21" t="s">
         <v>287</v>
-      </c>
-      <c r="R25" s="21" t="s">
-        <v>288</v>
       </c>
       <c r="S25" s="23" t="s">
         <v>56</v>
       </c>
       <c r="T25" s="21" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="U25" s="5" t="s">
         <v>58</v>
@@ -9208,10 +9286,10 @@
     </row>
     <row r="26" ht="42" customHeight="1" spans="1:38">
       <c r="A26" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="B26" s="21" t="s">
         <v>277</v>
-      </c>
-      <c r="B26" s="21" t="s">
-        <v>278</v>
       </c>
       <c r="C26" s="21" t="s">
         <v>60</v>
@@ -9220,23 +9298,23 @@
         <v>61</v>
       </c>
       <c r="E26" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="F26" s="22" t="s">
         <v>290</v>
-      </c>
-      <c r="F26" s="22" t="s">
-        <v>291</v>
       </c>
       <c r="G26" s="5" t="str">
         <f t="shared" si="0"/>
         <v>浏览深圳外围模特懒咩咩的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I26" s="5" t="s">
         <v>124</v>
       </c>
       <c r="J26" s="17" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="K26" s="5" t="str">
         <f t="shared" si="1"/>
@@ -9246,28 +9324,28 @@
         <v>176</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N26" s="21" t="s">
+        <v>293</v>
+      </c>
+      <c r="O26" s="21" t="s">
         <v>294</v>
       </c>
-      <c r="O26" s="21" t="s">
+      <c r="P26" s="21" t="s">
         <v>295</v>
       </c>
-      <c r="P26" s="21" t="s">
+      <c r="Q26" s="21" t="s">
         <v>296</v>
       </c>
-      <c r="Q26" s="21" t="s">
+      <c r="R26" s="21" t="s">
         <v>297</v>
-      </c>
-      <c r="R26" s="21" t="s">
-        <v>298</v>
       </c>
       <c r="S26" s="23" t="s">
         <v>56</v>
       </c>
       <c r="T26" s="21" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="U26" s="5" t="s">
         <v>58</v>
@@ -9324,10 +9402,10 @@
     </row>
     <row r="27" ht="42" customHeight="1" spans="1:38">
       <c r="A27" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="B27" s="21" t="s">
         <v>277</v>
-      </c>
-      <c r="B27" s="21" t="s">
-        <v>278</v>
       </c>
       <c r="C27" s="21" t="s">
         <v>72</v>
@@ -9336,23 +9414,23 @@
         <v>73</v>
       </c>
       <c r="E27" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="F27" s="22" t="s">
         <v>300</v>
-      </c>
-      <c r="F27" s="22" t="s">
-        <v>301</v>
       </c>
       <c r="G27" s="5" t="str">
         <f t="shared" si="0"/>
         <v>浏览深圳外围模特汤晨的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>136</v>
       </c>
       <c r="J27" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="K27" s="5" t="str">
         <f t="shared" si="1"/>
@@ -9362,28 +9440,28 @@
         <v>176</v>
       </c>
       <c r="M27" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N27" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="O27" s="21" t="s">
         <v>304</v>
       </c>
-      <c r="O27" s="21" t="s">
+      <c r="P27" s="21" t="s">
         <v>305</v>
       </c>
-      <c r="P27" s="21" t="s">
+      <c r="Q27" s="21" t="s">
         <v>306</v>
       </c>
-      <c r="Q27" s="21" t="s">
+      <c r="R27" s="21" t="s">
         <v>307</v>
-      </c>
-      <c r="R27" s="21" t="s">
-        <v>308</v>
       </c>
       <c r="S27" s="23" t="s">
         <v>56</v>
       </c>
       <c r="T27" s="21" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="U27" s="5" t="s">
         <v>58</v>
@@ -9440,10 +9518,10 @@
     </row>
     <row r="28" ht="42" customHeight="1" spans="1:38">
       <c r="A28" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="B28" s="21" t="s">
         <v>277</v>
-      </c>
-      <c r="B28" s="21" t="s">
-        <v>278</v>
       </c>
       <c r="C28" s="21" t="s">
         <v>84</v>
@@ -9452,23 +9530,23 @@
         <v>85</v>
       </c>
       <c r="E28" s="17" t="s">
+        <v>309</v>
+      </c>
+      <c r="F28" s="22" t="s">
         <v>310</v>
-      </c>
-      <c r="F28" s="22" t="s">
-        <v>311</v>
       </c>
       <c r="G28" s="5" t="str">
         <f t="shared" si="0"/>
         <v>浏览深圳外围模特鹿鹿的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I28" s="17" t="s">
         <v>47</v>
       </c>
       <c r="J28" s="17" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K28" s="5" t="str">
         <f t="shared" si="1"/>
@@ -9478,28 +9556,28 @@
         <v>176</v>
       </c>
       <c r="M28" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N28" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="O28" s="21" t="s">
         <v>314</v>
       </c>
-      <c r="O28" s="21" t="s">
+      <c r="P28" s="21" t="s">
         <v>315</v>
       </c>
-      <c r="P28" s="21" t="s">
+      <c r="Q28" s="21" t="s">
         <v>316</v>
       </c>
-      <c r="Q28" s="21" t="s">
+      <c r="R28" s="21" t="s">
         <v>317</v>
-      </c>
-      <c r="R28" s="21" t="s">
-        <v>318</v>
       </c>
       <c r="S28" s="23" t="s">
         <v>56</v>
       </c>
       <c r="T28" s="21" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="U28" s="5" t="s">
         <v>58</v>
@@ -9556,10 +9634,10 @@
     </row>
     <row r="29" ht="42" customHeight="1" spans="1:38">
       <c r="A29" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="B29" s="21" t="s">
         <v>277</v>
-      </c>
-      <c r="B29" s="21" t="s">
-        <v>278</v>
       </c>
       <c r="C29" s="21" t="s">
         <v>96</v>
@@ -9568,23 +9646,23 @@
         <v>97</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G29" s="5" t="str">
         <f t="shared" si="0"/>
         <v>浏览深圳外围模特的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I29" s="17" t="s">
         <v>47</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="K29" s="5" t="str">
         <f t="shared" si="1"/>
@@ -9594,28 +9672,28 @@
         <v>176</v>
       </c>
       <c r="M29" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N29" s="21" t="s">
+        <v>322</v>
+      </c>
+      <c r="O29" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="O29" s="21" t="s">
+      <c r="P29" s="21" t="s">
         <v>324</v>
       </c>
-      <c r="P29" s="21" t="s">
+      <c r="Q29" s="21" t="s">
         <v>325</v>
       </c>
-      <c r="Q29" s="21" t="s">
+      <c r="R29" s="21" t="s">
         <v>326</v>
-      </c>
-      <c r="R29" s="21" t="s">
-        <v>327</v>
       </c>
       <c r="S29" s="23" t="s">
         <v>56</v>
       </c>
       <c r="T29" s="21" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="U29" s="5" t="s">
         <v>58</v>
@@ -9672,10 +9750,10 @@
     </row>
     <row r="30" ht="42" customHeight="1" spans="1:38">
       <c r="A30" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="B30" s="21" t="s">
         <v>277</v>
-      </c>
-      <c r="B30" s="21" t="s">
-        <v>278</v>
       </c>
       <c r="C30" s="21" t="s">
         <v>108</v>
@@ -9684,23 +9762,23 @@
         <v>109</v>
       </c>
       <c r="E30" s="17" t="s">
+        <v>328</v>
+      </c>
+      <c r="F30" s="22" t="s">
         <v>329</v>
-      </c>
-      <c r="F30" s="22" t="s">
-        <v>330</v>
       </c>
       <c r="G30" s="5" t="str">
         <f t="shared" si="0"/>
         <v>浏览深圳外围模特兮兮的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H30" s="17" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I30" s="5" t="s">
         <v>174</v>
       </c>
       <c r="J30" s="17" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="K30" s="5" t="str">
         <f t="shared" si="1"/>
@@ -9710,28 +9788,28 @@
         <v>176</v>
       </c>
       <c r="M30" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N30" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="O30" s="21" t="s">
         <v>333</v>
       </c>
-      <c r="O30" s="21" t="s">
+      <c r="P30" s="21" t="s">
         <v>334</v>
       </c>
-      <c r="P30" s="21" t="s">
+      <c r="Q30" s="21" t="s">
         <v>335</v>
       </c>
-      <c r="Q30" s="21" t="s">
+      <c r="R30" s="21" t="s">
         <v>336</v>
-      </c>
-      <c r="R30" s="21" t="s">
-        <v>337</v>
       </c>
       <c r="S30" s="23" t="s">
         <v>56</v>
       </c>
       <c r="T30" s="21" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="U30" s="5" t="s">
         <v>58</v>
@@ -9788,10 +9866,10 @@
     </row>
     <row r="31" ht="42" customHeight="1" spans="1:38">
       <c r="A31" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="B31" s="21" t="s">
         <v>277</v>
-      </c>
-      <c r="B31" s="21" t="s">
-        <v>278</v>
       </c>
       <c r="C31" s="21" t="s">
         <v>120</v>
@@ -9800,23 +9878,23 @@
         <v>121</v>
       </c>
       <c r="E31" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="F31" s="22" t="s">
         <v>339</v>
-      </c>
-      <c r="F31" s="22" t="s">
-        <v>340</v>
       </c>
       <c r="G31" s="5" t="str">
         <f t="shared" si="0"/>
         <v>浏览深圳外围模特桐丫丫的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H31" s="17" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>124</v>
       </c>
       <c r="J31" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="K31" s="5" t="str">
         <f t="shared" si="1"/>
@@ -9826,28 +9904,28 @@
         <v>176</v>
       </c>
       <c r="M31" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N31" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="O31" s="21" t="s">
         <v>343</v>
       </c>
-      <c r="O31" s="21" t="s">
+      <c r="P31" s="21" t="s">
         <v>344</v>
       </c>
-      <c r="P31" s="21" t="s">
+      <c r="Q31" s="21" t="s">
         <v>345</v>
       </c>
-      <c r="Q31" s="21" t="s">
+      <c r="R31" s="21" t="s">
         <v>346</v>
-      </c>
-      <c r="R31" s="21" t="s">
-        <v>347</v>
       </c>
       <c r="S31" s="23" t="s">
         <v>56</v>
       </c>
       <c r="T31" s="21" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="U31" s="5" t="s">
         <v>58</v>
@@ -9904,10 +9982,10 @@
     </row>
     <row r="32" ht="42" customHeight="1" spans="1:38">
       <c r="A32" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="B32" s="21" t="s">
         <v>277</v>
-      </c>
-      <c r="B32" s="21" t="s">
-        <v>278</v>
       </c>
       <c r="C32" s="21" t="s">
         <v>132</v>
@@ -9916,23 +9994,23 @@
         <v>133</v>
       </c>
       <c r="E32" s="17" t="s">
+        <v>348</v>
+      </c>
+      <c r="F32" s="22" t="s">
         <v>349</v>
-      </c>
-      <c r="F32" s="22" t="s">
-        <v>350</v>
       </c>
       <c r="G32" s="5" t="str">
         <f t="shared" si="0"/>
         <v>浏览深圳外围模特拉拉的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H32" s="17" t="s">
+        <v>350</v>
+      </c>
+      <c r="I32" s="17" t="s">
         <v>351</v>
       </c>
-      <c r="I32" s="17" t="s">
+      <c r="J32" s="17" t="s">
         <v>352</v>
-      </c>
-      <c r="J32" s="17" t="s">
-        <v>353</v>
       </c>
       <c r="K32" s="5" t="str">
         <f t="shared" si="1"/>
@@ -9942,28 +10020,28 @@
         <v>176</v>
       </c>
       <c r="M32" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N32" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="O32" s="21" t="s">
         <v>354</v>
       </c>
-      <c r="O32" s="21" t="s">
+      <c r="P32" s="21" t="s">
         <v>355</v>
       </c>
-      <c r="P32" s="21" t="s">
+      <c r="Q32" s="21" t="s">
         <v>356</v>
       </c>
-      <c r="Q32" s="21" t="s">
+      <c r="R32" s="21" t="s">
         <v>357</v>
-      </c>
-      <c r="R32" s="21" t="s">
-        <v>358</v>
       </c>
       <c r="S32" s="23" t="s">
         <v>56</v>
       </c>
       <c r="T32" s="21" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="U32" s="5" t="s">
         <v>58</v>
@@ -10020,10 +10098,10 @@
     </row>
     <row r="33" ht="42" customHeight="1" spans="1:38">
       <c r="A33" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="B33" s="21" t="s">
         <v>277</v>
-      </c>
-      <c r="B33" s="21" t="s">
-        <v>278</v>
       </c>
       <c r="C33" s="21" t="s">
         <v>144</v>
@@ -10032,23 +10110,23 @@
         <v>145</v>
       </c>
       <c r="E33" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="F33" s="22" t="s">
         <v>360</v>
-      </c>
-      <c r="F33" s="22" t="s">
-        <v>361</v>
       </c>
       <c r="G33" s="5" t="str">
         <f t="shared" si="0"/>
         <v>浏览深圳外围模特醒醒的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I33" s="17" t="s">
         <v>47</v>
       </c>
       <c r="J33" s="17" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="K33" s="5" t="str">
         <f t="shared" si="1"/>
@@ -10058,28 +10136,28 @@
         <v>176</v>
       </c>
       <c r="M33" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N33" s="21" t="s">
+        <v>363</v>
+      </c>
+      <c r="O33" s="21" t="s">
         <v>364</v>
       </c>
-      <c r="O33" s="21" t="s">
+      <c r="P33" s="21" t="s">
         <v>365</v>
       </c>
-      <c r="P33" s="21" t="s">
+      <c r="Q33" s="21" t="s">
         <v>366</v>
       </c>
-      <c r="Q33" s="21" t="s">
+      <c r="R33" s="21" t="s">
         <v>367</v>
-      </c>
-      <c r="R33" s="21" t="s">
-        <v>368</v>
       </c>
       <c r="S33" s="23" t="s">
         <v>56</v>
       </c>
       <c r="T33" s="21" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="U33" s="5" t="s">
         <v>58</v>
@@ -10136,10 +10214,10 @@
     </row>
     <row r="34" ht="42" customHeight="1" spans="1:38">
       <c r="A34" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="B34" s="21" t="s">
         <v>277</v>
-      </c>
-      <c r="B34" s="21" t="s">
-        <v>278</v>
       </c>
       <c r="C34" s="21" t="s">
         <v>157</v>
@@ -10148,23 +10226,23 @@
         <v>158</v>
       </c>
       <c r="E34" s="17" t="s">
+        <v>369</v>
+      </c>
+      <c r="F34" s="22" t="s">
         <v>370</v>
-      </c>
-      <c r="F34" s="22" t="s">
-        <v>371</v>
       </c>
       <c r="G34" s="5" t="str">
         <f t="shared" si="0"/>
         <v>浏览深圳外围模特山山的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I34" s="5" t="s">
         <v>161</v>
       </c>
       <c r="J34" s="17" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="K34" s="5" t="str">
         <f t="shared" si="1"/>
@@ -10174,28 +10252,28 @@
         <v>176</v>
       </c>
       <c r="M34" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N34" s="21" t="s">
+        <v>373</v>
+      </c>
+      <c r="O34" s="21" t="s">
         <v>374</v>
       </c>
-      <c r="O34" s="21" t="s">
+      <c r="P34" s="21" t="s">
         <v>375</v>
       </c>
-      <c r="P34" s="21" t="s">
+      <c r="Q34" s="21" t="s">
         <v>376</v>
       </c>
-      <c r="Q34" s="21" t="s">
+      <c r="R34" s="21" t="s">
         <v>377</v>
-      </c>
-      <c r="R34" s="21" t="s">
-        <v>378</v>
       </c>
       <c r="S34" s="23" t="s">
         <v>56</v>
       </c>
       <c r="T34" s="21" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="U34" s="5" t="s">
         <v>58</v>
@@ -10252,10 +10330,10 @@
     </row>
     <row r="35" ht="42" customHeight="1" spans="1:38">
       <c r="A35" s="20" t="s">
+        <v>379</v>
+      </c>
+      <c r="B35" s="21" t="s">
         <v>380</v>
-      </c>
-      <c r="B35" s="21" t="s">
-        <v>381</v>
       </c>
       <c r="C35" s="21" t="s">
         <v>42</v>
@@ -10264,54 +10342,54 @@
         <v>43</v>
       </c>
       <c r="E35" s="17" t="s">
+        <v>381</v>
+      </c>
+      <c r="F35" s="22" t="s">
         <v>382</v>
-      </c>
-      <c r="F35" s="22" t="s">
-        <v>383</v>
       </c>
       <c r="G35" s="17" t="str">
         <f t="shared" si="0"/>
         <v>浏览北京外围小萝莉的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H35" s="17" t="s">
+        <v>383</v>
+      </c>
+      <c r="I35" s="17" t="s">
         <v>384</v>
       </c>
-      <c r="I35" s="17" t="s">
+      <c r="J35" s="17" t="s">
         <v>385</v>
-      </c>
-      <c r="J35" s="17" t="s">
-        <v>386</v>
       </c>
       <c r="K35" s="17" t="str">
         <f t="shared" si="1"/>
         <v>以上是北京外围小萝莉的照片、资料、无需注册登录即可浏览。</v>
       </c>
       <c r="L35" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="M35" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="M35" s="17" t="s">
+      <c r="N35" s="21" t="s">
         <v>388</v>
       </c>
-      <c r="N35" s="21" t="s">
+      <c r="O35" s="21" t="s">
         <v>389</v>
       </c>
-      <c r="O35" s="21" t="s">
+      <c r="P35" s="21" t="s">
         <v>390</v>
       </c>
-      <c r="P35" s="21" t="s">
+      <c r="Q35" s="21" t="s">
         <v>391</v>
       </c>
-      <c r="Q35" s="21" t="s">
+      <c r="R35" s="21" t="s">
         <v>392</v>
-      </c>
-      <c r="R35" s="21" t="s">
-        <v>393</v>
       </c>
       <c r="S35" s="23" t="s">
         <v>56</v>
       </c>
       <c r="T35" s="21" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="U35" s="5" t="s">
         <v>58</v>
@@ -10368,10 +10446,10 @@
     </row>
     <row r="36" ht="42" customHeight="1" spans="1:38">
       <c r="A36" s="20" t="s">
+        <v>379</v>
+      </c>
+      <c r="B36" s="21" t="s">
         <v>380</v>
-      </c>
-      <c r="B36" s="21" t="s">
-        <v>381</v>
       </c>
       <c r="C36" s="21" t="s">
         <v>60</v>
@@ -10380,54 +10458,54 @@
         <v>61</v>
       </c>
       <c r="E36" s="17" t="s">
+        <v>394</v>
+      </c>
+      <c r="F36" s="22" t="s">
         <v>395</v>
-      </c>
-      <c r="F36" s="22" t="s">
-        <v>396</v>
       </c>
       <c r="G36" s="17" t="str">
         <f t="shared" si="0"/>
         <v>浏览北京外围兼职学妹的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H36" s="17" t="s">
+        <v>396</v>
+      </c>
+      <c r="I36" s="17" t="s">
         <v>397</v>
       </c>
-      <c r="I36" s="17" t="s">
+      <c r="J36" s="17" t="s">
         <v>398</v>
-      </c>
-      <c r="J36" s="17" t="s">
-        <v>399</v>
       </c>
       <c r="K36" s="17" t="str">
         <f t="shared" si="1"/>
         <v>以上是北京外围兼职学妹的照片、资料、无需注册登录即可浏览。</v>
       </c>
       <c r="L36" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="M36" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="M36" s="17" t="s">
-        <v>388</v>
-      </c>
       <c r="N36" s="21" t="s">
+        <v>399</v>
+      </c>
+      <c r="O36" s="21" t="s">
         <v>400</v>
       </c>
-      <c r="O36" s="21" t="s">
+      <c r="P36" s="21" t="s">
         <v>401</v>
       </c>
-      <c r="P36" s="21" t="s">
+      <c r="Q36" s="21" t="s">
         <v>402</v>
       </c>
-      <c r="Q36" s="21" t="s">
+      <c r="R36" s="21" t="s">
         <v>403</v>
-      </c>
-      <c r="R36" s="21" t="s">
-        <v>404</v>
       </c>
       <c r="S36" s="23" t="s">
         <v>56</v>
       </c>
       <c r="T36" s="21" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="U36" s="5" t="s">
         <v>58</v>
@@ -10484,10 +10562,10 @@
     </row>
     <row r="37" ht="42" customHeight="1" spans="1:38">
       <c r="A37" s="20" t="s">
+        <v>379</v>
+      </c>
+      <c r="B37" s="21" t="s">
         <v>380</v>
-      </c>
-      <c r="B37" s="21" t="s">
-        <v>381</v>
       </c>
       <c r="C37" s="21" t="s">
         <v>72</v>
@@ -10496,54 +10574,54 @@
         <v>73</v>
       </c>
       <c r="E37" s="17" t="s">
+        <v>405</v>
+      </c>
+      <c r="F37" s="22" t="s">
         <v>406</v>
-      </c>
-      <c r="F37" s="22" t="s">
-        <v>407</v>
       </c>
       <c r="G37" s="17" t="str">
         <f t="shared" si="0"/>
         <v>浏览北京外围模特御姐的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H37" s="17" t="s">
+        <v>407</v>
+      </c>
+      <c r="I37" s="17" t="s">
+        <v>351</v>
+      </c>
+      <c r="J37" s="17" t="s">
         <v>408</v>
-      </c>
-      <c r="I37" s="17" t="s">
-        <v>352</v>
-      </c>
-      <c r="J37" s="17" t="s">
-        <v>409</v>
       </c>
       <c r="K37" s="17" t="str">
         <f t="shared" si="1"/>
         <v>以上是北京外围模特御姐的照片、资料、无需注册登录即可浏览。</v>
       </c>
       <c r="L37" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="M37" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="M37" s="17" t="s">
-        <v>388</v>
-      </c>
       <c r="N37" s="21" t="s">
+        <v>409</v>
+      </c>
+      <c r="O37" s="21" t="s">
         <v>410</v>
       </c>
-      <c r="O37" s="21" t="s">
+      <c r="P37" s="21" t="s">
         <v>411</v>
       </c>
-      <c r="P37" s="21" t="s">
+      <c r="Q37" s="21" t="s">
         <v>412</v>
       </c>
-      <c r="Q37" s="21" t="s">
+      <c r="R37" s="21" t="s">
         <v>413</v>
-      </c>
-      <c r="R37" s="21" t="s">
-        <v>414</v>
       </c>
       <c r="S37" s="23" t="s">
         <v>56</v>
       </c>
       <c r="T37" s="21" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="U37" s="5" t="s">
         <v>58</v>
@@ -10600,10 +10678,10 @@
     </row>
     <row r="38" ht="42" customHeight="1" spans="1:38">
       <c r="A38" s="20" t="s">
+        <v>379</v>
+      </c>
+      <c r="B38" s="21" t="s">
         <v>380</v>
-      </c>
-      <c r="B38" s="21" t="s">
-        <v>381</v>
       </c>
       <c r="C38" s="21" t="s">
         <v>84</v>
@@ -10612,54 +10690,54 @@
         <v>85</v>
       </c>
       <c r="E38" s="17" t="s">
+        <v>415</v>
+      </c>
+      <c r="F38" s="22" t="s">
         <v>416</v>
-      </c>
-      <c r="F38" s="22" t="s">
-        <v>417</v>
       </c>
       <c r="G38" s="17" t="str">
         <f t="shared" si="0"/>
         <v>浏览北京外围模特清新的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I38" s="17" t="s">
         <v>136</v>
       </c>
       <c r="J38" s="17" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="K38" s="17" t="str">
         <f t="shared" si="1"/>
         <v>以上是北京外围模特清新的照片、资料、无需注册登录即可浏览。</v>
       </c>
       <c r="L38" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="M38" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="M38" s="17" t="s">
-        <v>388</v>
-      </c>
       <c r="N38" s="21" t="s">
+        <v>419</v>
+      </c>
+      <c r="O38" s="21" t="s">
         <v>420</v>
       </c>
-      <c r="O38" s="21" t="s">
+      <c r="P38" s="21" t="s">
         <v>421</v>
       </c>
-      <c r="P38" s="21" t="s">
+      <c r="Q38" s="21" t="s">
         <v>422</v>
       </c>
-      <c r="Q38" s="21" t="s">
+      <c r="R38" s="21" t="s">
         <v>423</v>
-      </c>
-      <c r="R38" s="21" t="s">
-        <v>424</v>
       </c>
       <c r="S38" s="23" t="s">
         <v>56</v>
       </c>
       <c r="T38" s="21" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="U38" s="5" t="s">
         <v>58</v>
@@ -10716,10 +10794,10 @@
     </row>
     <row r="39" ht="42" customHeight="1" spans="1:38">
       <c r="A39" s="20" t="s">
+        <v>379</v>
+      </c>
+      <c r="B39" s="21" t="s">
         <v>380</v>
-      </c>
-      <c r="B39" s="21" t="s">
-        <v>381</v>
       </c>
       <c r="C39" s="21" t="s">
         <v>96</v>
@@ -10728,54 +10806,54 @@
         <v>97</v>
       </c>
       <c r="E39" s="17" t="s">
+        <v>425</v>
+      </c>
+      <c r="F39" s="22" t="s">
         <v>426</v>
-      </c>
-      <c r="F39" s="22" t="s">
-        <v>427</v>
       </c>
       <c r="G39" s="17" t="str">
         <f t="shared" si="0"/>
         <v>浏览北京外围模特菲菲的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I39" s="17" t="s">
         <v>149</v>
       </c>
       <c r="J39" s="17" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="K39" s="17" t="str">
         <f t="shared" si="1"/>
         <v>以上是北京外围模特菲菲的照片、资料、无需注册登录即可浏览。</v>
       </c>
       <c r="L39" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="M39" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="M39" s="17" t="s">
-        <v>388</v>
-      </c>
       <c r="N39" s="21" t="s">
+        <v>429</v>
+      </c>
+      <c r="O39" s="21" t="s">
         <v>430</v>
       </c>
-      <c r="O39" s="21" t="s">
+      <c r="P39" s="21" t="s">
         <v>431</v>
       </c>
-      <c r="P39" s="21" t="s">
+      <c r="Q39" s="21" t="s">
         <v>432</v>
       </c>
-      <c r="Q39" s="21" t="s">
+      <c r="R39" s="21" t="s">
         <v>433</v>
-      </c>
-      <c r="R39" s="21" t="s">
-        <v>434</v>
       </c>
       <c r="S39" s="23" t="s">
         <v>56</v>
       </c>
       <c r="T39" s="21" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="U39" s="5" t="s">
         <v>58</v>
@@ -10832,10 +10910,10 @@
     </row>
     <row r="40" ht="42" customHeight="1" spans="1:38">
       <c r="A40" s="20" t="s">
+        <v>379</v>
+      </c>
+      <c r="B40" s="21" t="s">
         <v>380</v>
-      </c>
-      <c r="B40" s="21" t="s">
-        <v>381</v>
       </c>
       <c r="C40" s="21" t="s">
         <v>108</v>
@@ -10844,54 +10922,54 @@
         <v>109</v>
       </c>
       <c r="E40" s="17" t="s">
+        <v>435</v>
+      </c>
+      <c r="F40" s="22" t="s">
         <v>436</v>
-      </c>
-      <c r="F40" s="22" t="s">
-        <v>437</v>
       </c>
       <c r="G40" s="17" t="str">
         <f t="shared" si="0"/>
         <v>浏览北京外围模特娜美的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H40" s="17" t="s">
+        <v>437</v>
+      </c>
+      <c r="I40" s="17" t="s">
         <v>438</v>
       </c>
-      <c r="I40" s="17" t="s">
+      <c r="J40" s="17" t="s">
         <v>439</v>
-      </c>
-      <c r="J40" s="17" t="s">
-        <v>440</v>
       </c>
       <c r="K40" s="17" t="str">
         <f t="shared" si="1"/>
         <v>以上是北京外围模特娜美的照片、资料、无需注册登录即可浏览。</v>
       </c>
       <c r="L40" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="M40" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="M40" s="17" t="s">
-        <v>388</v>
-      </c>
       <c r="N40" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="O40" s="21" t="s">
         <v>441</v>
       </c>
-      <c r="O40" s="21" t="s">
+      <c r="P40" s="21" t="s">
         <v>442</v>
       </c>
-      <c r="P40" s="21" t="s">
+      <c r="Q40" s="21" t="s">
         <v>443</v>
       </c>
-      <c r="Q40" s="21" t="s">
+      <c r="R40" s="21" t="s">
         <v>444</v>
-      </c>
-      <c r="R40" s="21" t="s">
-        <v>445</v>
       </c>
       <c r="S40" s="23" t="s">
         <v>56</v>
       </c>
       <c r="T40" s="21" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="U40" s="5" t="s">
         <v>58</v>
@@ -10948,10 +11026,10 @@
     </row>
     <row r="41" ht="42" customHeight="1" spans="1:38">
       <c r="A41" s="20" t="s">
+        <v>379</v>
+      </c>
+      <c r="B41" s="21" t="s">
         <v>380</v>
-      </c>
-      <c r="B41" s="21" t="s">
-        <v>381</v>
       </c>
       <c r="C41" s="21" t="s">
         <v>120</v>
@@ -10960,54 +11038,54 @@
         <v>121</v>
       </c>
       <c r="E41" s="17" t="s">
+        <v>446</v>
+      </c>
+      <c r="F41" s="22" t="s">
         <v>447</v>
-      </c>
-      <c r="F41" s="22" t="s">
-        <v>448</v>
       </c>
       <c r="G41" s="17" t="str">
         <f t="shared" si="0"/>
         <v>浏览北京外围模特纯欲白虎的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H41" s="17" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="I41" s="17" t="s">
         <v>47</v>
       </c>
       <c r="J41" s="17" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="K41" s="17" t="str">
         <f t="shared" si="1"/>
         <v>以上是北京外围模特纯欲白虎的照片、资料、无需注册登录即可浏览。</v>
       </c>
       <c r="L41" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="M41" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="M41" s="17" t="s">
-        <v>388</v>
-      </c>
       <c r="N41" s="21" t="s">
+        <v>450</v>
+      </c>
+      <c r="O41" s="21" t="s">
         <v>451</v>
       </c>
-      <c r="O41" s="21" t="s">
+      <c r="P41" s="21" t="s">
         <v>452</v>
       </c>
-      <c r="P41" s="21" t="s">
+      <c r="Q41" s="21" t="s">
         <v>453</v>
       </c>
-      <c r="Q41" s="21" t="s">
+      <c r="R41" s="21" t="s">
         <v>454</v>
-      </c>
-      <c r="R41" s="21" t="s">
-        <v>455</v>
       </c>
       <c r="S41" s="23" t="s">
         <v>56</v>
       </c>
       <c r="T41" s="21" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="U41" s="5" t="s">
         <v>58</v>
@@ -11064,10 +11142,10 @@
     </row>
     <row r="42" ht="42" customHeight="1" spans="1:38">
       <c r="A42" s="20" t="s">
+        <v>379</v>
+      </c>
+      <c r="B42" s="21" t="s">
         <v>380</v>
-      </c>
-      <c r="B42" s="21" t="s">
-        <v>381</v>
       </c>
       <c r="C42" s="21" t="s">
         <v>132</v>
@@ -11076,54 +11154,54 @@
         <v>133</v>
       </c>
       <c r="E42" s="17" t="s">
+        <v>456</v>
+      </c>
+      <c r="F42" s="22" t="s">
         <v>457</v>
-      </c>
-      <c r="F42" s="22" t="s">
-        <v>458</v>
       </c>
       <c r="G42" s="17" t="str">
         <f t="shared" si="0"/>
         <v>浏览北京外围模特纯兼职新人的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H42" s="17" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I42" s="5" t="s">
         <v>136</v>
       </c>
       <c r="J42" s="17" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="K42" s="17" t="str">
         <f t="shared" si="1"/>
         <v>以上是北京外围模特纯兼职新人的照片、资料、无需注册登录即可浏览。</v>
       </c>
       <c r="L42" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="M42" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="M42" s="17" t="s">
-        <v>388</v>
-      </c>
       <c r="N42" s="21" t="s">
+        <v>460</v>
+      </c>
+      <c r="O42" s="21" t="s">
         <v>461</v>
       </c>
-      <c r="O42" s="21" t="s">
+      <c r="P42" s="21" t="s">
         <v>462</v>
       </c>
-      <c r="P42" s="21" t="s">
+      <c r="Q42" s="21" t="s">
         <v>463</v>
       </c>
-      <c r="Q42" s="21" t="s">
+      <c r="R42" s="21" t="s">
         <v>464</v>
-      </c>
-      <c r="R42" s="21" t="s">
-        <v>465</v>
       </c>
       <c r="S42" s="23" t="s">
         <v>56</v>
       </c>
       <c r="T42" s="21" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="U42" s="5" t="s">
         <v>58</v>
@@ -11180,10 +11258,10 @@
     </row>
     <row r="43" ht="42" customHeight="1" spans="1:38">
       <c r="A43" s="20" t="s">
+        <v>379</v>
+      </c>
+      <c r="B43" s="21" t="s">
         <v>380</v>
-      </c>
-      <c r="B43" s="21" t="s">
-        <v>381</v>
       </c>
       <c r="C43" s="21" t="s">
         <v>144</v>
@@ -11192,54 +11270,54 @@
         <v>145</v>
       </c>
       <c r="E43" s="17" t="s">
+        <v>466</v>
+      </c>
+      <c r="F43" s="22" t="s">
         <v>467</v>
-      </c>
-      <c r="F43" s="22" t="s">
-        <v>468</v>
       </c>
       <c r="G43" s="17" t="str">
         <f t="shared" si="0"/>
         <v>浏览北京外围模特极品纯欲的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H43" s="17" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="I43" s="17" t="s">
         <v>47</v>
       </c>
       <c r="J43" s="17" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K43" s="17" t="str">
         <f t="shared" si="1"/>
         <v>以上是北京外围模特极品纯欲的照片、资料、无需注册登录即可浏览。</v>
       </c>
       <c r="L43" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="M43" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="M43" s="17" t="s">
-        <v>388</v>
-      </c>
       <c r="N43" s="21" t="s">
+        <v>470</v>
+      </c>
+      <c r="O43" s="21" t="s">
         <v>471</v>
       </c>
-      <c r="O43" s="21" t="s">
+      <c r="P43" s="21" t="s">
         <v>472</v>
       </c>
-      <c r="P43" s="21" t="s">
+      <c r="Q43" s="21" t="s">
         <v>473</v>
       </c>
-      <c r="Q43" s="21" t="s">
+      <c r="R43" s="21" t="s">
         <v>474</v>
-      </c>
-      <c r="R43" s="21" t="s">
-        <v>475</v>
       </c>
       <c r="S43" s="23" t="s">
         <v>56</v>
       </c>
       <c r="T43" s="21" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="U43" s="5" t="s">
         <v>58</v>
@@ -11296,10 +11374,10 @@
     </row>
     <row r="44" ht="42" customHeight="1" spans="1:38">
       <c r="A44" s="20" t="s">
+        <v>379</v>
+      </c>
+      <c r="B44" s="21" t="s">
         <v>380</v>
-      </c>
-      <c r="B44" s="21" t="s">
-        <v>381</v>
       </c>
       <c r="C44" s="21" t="s">
         <v>157</v>
@@ -11308,54 +11386,54 @@
         <v>158</v>
       </c>
       <c r="E44" s="17" t="s">
+        <v>476</v>
+      </c>
+      <c r="F44" s="22" t="s">
         <v>477</v>
-      </c>
-      <c r="F44" s="22" t="s">
-        <v>478</v>
       </c>
       <c r="G44" s="17" t="str">
         <f t="shared" si="0"/>
         <v>浏览北京外围模特新人的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H44" s="17" t="s">
+        <v>478</v>
+      </c>
+      <c r="I44" s="17" t="s">
         <v>479</v>
       </c>
-      <c r="I44" s="17" t="s">
+      <c r="J44" s="17" t="s">
         <v>480</v>
-      </c>
-      <c r="J44" s="17" t="s">
-        <v>481</v>
       </c>
       <c r="K44" s="17" t="str">
         <f t="shared" si="1"/>
         <v>以上是北京外围模特新人的照片、资料、无需注册登录即可浏览。</v>
       </c>
       <c r="L44" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="M44" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="M44" s="17" t="s">
-        <v>388</v>
-      </c>
       <c r="N44" s="21" t="s">
+        <v>481</v>
+      </c>
+      <c r="O44" s="21" t="s">
         <v>482</v>
       </c>
-      <c r="O44" s="21" t="s">
+      <c r="P44" s="21" t="s">
         <v>483</v>
       </c>
-      <c r="P44" s="21" t="s">
+      <c r="Q44" s="21" t="s">
         <v>484</v>
       </c>
-      <c r="Q44" s="21" t="s">
+      <c r="R44" s="21" t="s">
         <v>485</v>
-      </c>
-      <c r="R44" s="21" t="s">
-        <v>486</v>
       </c>
       <c r="S44" s="23" t="s">
         <v>56</v>
       </c>
       <c r="T44" s="21" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="U44" s="5" t="s">
         <v>58</v>
@@ -11412,10 +11490,10 @@
     </row>
     <row r="45" ht="42" customHeight="1" spans="1:38">
       <c r="A45" s="20" t="s">
+        <v>487</v>
+      </c>
+      <c r="B45" s="21" t="s">
         <v>488</v>
-      </c>
-      <c r="B45" s="21" t="s">
-        <v>489</v>
       </c>
       <c r="C45" s="21" t="s">
         <v>42</v>
@@ -11424,23 +11502,23 @@
         <v>43</v>
       </c>
       <c r="E45" s="17" t="s">
+        <v>489</v>
+      </c>
+      <c r="F45" s="22" t="s">
         <v>490</v>
-      </c>
-      <c r="F45" s="22" t="s">
-        <v>491</v>
       </c>
       <c r="G45" s="5" t="str">
         <f t="shared" si="0"/>
         <v>浏览杭州外围模特蜜桃的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H45" s="17" t="s">
+        <v>491</v>
+      </c>
+      <c r="I45" s="17" t="s">
         <v>492</v>
       </c>
-      <c r="I45" s="17" t="s">
+      <c r="J45" s="17" t="s">
         <v>493</v>
-      </c>
-      <c r="J45" s="17" t="s">
-        <v>494</v>
       </c>
       <c r="K45" s="5" t="str">
         <f t="shared" si="1"/>
@@ -11450,28 +11528,28 @@
         <v>176</v>
       </c>
       <c r="M45" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="N45" s="21" t="s">
         <v>495</v>
       </c>
-      <c r="N45" s="21" t="s">
+      <c r="O45" s="21" t="s">
         <v>496</v>
       </c>
-      <c r="O45" s="21" t="s">
+      <c r="P45" s="21" t="s">
         <v>497</v>
       </c>
-      <c r="P45" s="21" t="s">
+      <c r="Q45" s="21" t="s">
         <v>498</v>
       </c>
-      <c r="Q45" s="21" t="s">
+      <c r="R45" s="21" t="s">
         <v>499</v>
       </c>
-      <c r="R45" s="21" t="s">
+      <c r="S45" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="T45" s="21" t="s">
         <v>500</v>
-      </c>
-      <c r="S45" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="T45" s="21" t="s">
-        <v>501</v>
       </c>
       <c r="U45" s="5" t="s">
         <v>58</v>
@@ -11528,10 +11606,10 @@
     </row>
     <row r="46" ht="42" customHeight="1" spans="1:38">
       <c r="A46" s="20" t="s">
+        <v>487</v>
+      </c>
+      <c r="B46" s="21" t="s">
         <v>488</v>
-      </c>
-      <c r="B46" s="21" t="s">
-        <v>489</v>
       </c>
       <c r="C46" s="21" t="s">
         <v>60</v>
@@ -11540,23 +11618,23 @@
         <v>61</v>
       </c>
       <c r="E46" s="17" t="s">
+        <v>501</v>
+      </c>
+      <c r="F46" s="22" t="s">
         <v>502</v>
-      </c>
-      <c r="F46" s="22" t="s">
-        <v>503</v>
       </c>
       <c r="G46" s="5" t="str">
         <f t="shared" si="0"/>
         <v>浏览杭州外围模特欣儿的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H46" s="17" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="I46" s="5" t="s">
         <v>124</v>
       </c>
       <c r="J46" s="17" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="K46" s="5" t="str">
         <f t="shared" si="1"/>
@@ -11566,28 +11644,28 @@
         <v>176</v>
       </c>
       <c r="M46" s="5" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="N46" s="21" t="s">
+        <v>505</v>
+      </c>
+      <c r="O46" s="21" t="s">
         <v>506</v>
       </c>
-      <c r="O46" s="21" t="s">
+      <c r="P46" s="21" t="s">
         <v>507</v>
       </c>
-      <c r="P46" s="21" t="s">
+      <c r="Q46" s="21" t="s">
         <v>508</v>
       </c>
-      <c r="Q46" s="21" t="s">
+      <c r="R46" s="21" t="s">
         <v>509</v>
       </c>
-      <c r="R46" s="21" t="s">
+      <c r="S46" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="T46" s="21" t="s">
         <v>510</v>
-      </c>
-      <c r="S46" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="T46" s="21" t="s">
-        <v>511</v>
       </c>
       <c r="U46" s="5" t="s">
         <v>58</v>
@@ -11644,10 +11722,10 @@
     </row>
     <row r="47" ht="42" customHeight="1" spans="1:38">
       <c r="A47" s="20" t="s">
+        <v>487</v>
+      </c>
+      <c r="B47" s="21" t="s">
         <v>488</v>
-      </c>
-      <c r="B47" s="21" t="s">
-        <v>489</v>
       </c>
       <c r="C47" s="21" t="s">
         <v>72</v>
@@ -11656,23 +11734,23 @@
         <v>73</v>
       </c>
       <c r="E47" s="17" t="s">
+        <v>511</v>
+      </c>
+      <c r="F47" s="22" t="s">
         <v>512</v>
-      </c>
-      <c r="F47" s="22" t="s">
-        <v>513</v>
       </c>
       <c r="G47" s="5" t="str">
         <f t="shared" si="0"/>
         <v>浏览杭州外围模特楚楚的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H47" s="17" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="I47" s="5" t="s">
         <v>136</v>
       </c>
       <c r="J47" s="17" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="K47" s="5" t="str">
         <f t="shared" si="1"/>
@@ -11682,28 +11760,28 @@
         <v>176</v>
       </c>
       <c r="M47" s="5" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="N47" s="21" t="s">
+        <v>515</v>
+      </c>
+      <c r="O47" s="21" t="s">
         <v>516</v>
       </c>
-      <c r="O47" s="21" t="s">
+      <c r="P47" s="21" t="s">
         <v>517</v>
       </c>
-      <c r="P47" s="21" t="s">
+      <c r="Q47" s="21" t="s">
         <v>518</v>
       </c>
-      <c r="Q47" s="21" t="s">
+      <c r="R47" s="21" t="s">
         <v>519</v>
       </c>
-      <c r="R47" s="21" t="s">
+      <c r="S47" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="T47" s="21" t="s">
         <v>520</v>
-      </c>
-      <c r="S47" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="T47" s="21" t="s">
-        <v>521</v>
       </c>
       <c r="U47" s="5" t="s">
         <v>58</v>
@@ -11760,10 +11838,10 @@
     </row>
     <row r="48" ht="42" customHeight="1" spans="1:38">
       <c r="A48" s="20" t="s">
+        <v>487</v>
+      </c>
+      <c r="B48" s="21" t="s">
         <v>488</v>
-      </c>
-      <c r="B48" s="21" t="s">
-        <v>489</v>
       </c>
       <c r="C48" s="21" t="s">
         <v>84</v>
@@ -11772,23 +11850,23 @@
         <v>85</v>
       </c>
       <c r="E48" s="17" t="s">
+        <v>521</v>
+      </c>
+      <c r="F48" s="22" t="s">
         <v>522</v>
-      </c>
-      <c r="F48" s="22" t="s">
-        <v>523</v>
       </c>
       <c r="G48" s="5" t="str">
         <f t="shared" si="0"/>
         <v>浏览杭州外围模特mini的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H48" s="17" t="s">
+        <v>523</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="J48" s="17" t="s">
         <v>524</v>
-      </c>
-      <c r="I48" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="J48" s="17" t="s">
-        <v>525</v>
       </c>
       <c r="K48" s="5" t="str">
         <f t="shared" si="1"/>
@@ -11798,28 +11876,28 @@
         <v>176</v>
       </c>
       <c r="M48" s="5" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="N48" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="O48" s="21" t="s">
         <v>526</v>
       </c>
-      <c r="O48" s="21" t="s">
+      <c r="P48" s="21" t="s">
         <v>527</v>
       </c>
-      <c r="P48" s="21" t="s">
+      <c r="Q48" s="21" t="s">
         <v>528</v>
       </c>
-      <c r="Q48" s="21" t="s">
+      <c r="R48" s="21" t="s">
         <v>529</v>
       </c>
-      <c r="R48" s="21" t="s">
+      <c r="S48" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="T48" s="21" t="s">
         <v>530</v>
-      </c>
-      <c r="S48" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="T48" s="21" t="s">
-        <v>531</v>
       </c>
       <c r="U48" s="5" t="s">
         <v>58</v>
@@ -11876,10 +11954,10 @@
     </row>
     <row r="49" ht="42" customHeight="1" spans="1:38">
       <c r="A49" s="20" t="s">
+        <v>487</v>
+      </c>
+      <c r="B49" s="21" t="s">
         <v>488</v>
-      </c>
-      <c r="B49" s="21" t="s">
-        <v>489</v>
       </c>
       <c r="C49" s="21" t="s">
         <v>96</v>
@@ -11888,23 +11966,23 @@
         <v>97</v>
       </c>
       <c r="E49" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="F49" s="22" t="s">
         <v>532</v>
-      </c>
-      <c r="F49" s="22" t="s">
-        <v>533</v>
       </c>
       <c r="G49" s="5" t="str">
         <f t="shared" si="0"/>
         <v>浏览杭州外围模特的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H49" s="17" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I49" s="5" t="s">
         <v>161</v>
       </c>
       <c r="J49" s="17" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="K49" s="5" t="str">
         <f t="shared" si="1"/>
@@ -11914,28 +11992,28 @@
         <v>176</v>
       </c>
       <c r="M49" s="5" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="N49" s="21" t="s">
+        <v>535</v>
+      </c>
+      <c r="O49" s="21" t="s">
         <v>536</v>
       </c>
-      <c r="O49" s="21" t="s">
+      <c r="P49" s="21" t="s">
         <v>537</v>
       </c>
-      <c r="P49" s="21" t="s">
+      <c r="Q49" s="21" t="s">
         <v>538</v>
       </c>
-      <c r="Q49" s="21" t="s">
+      <c r="R49" s="21" t="s">
         <v>539</v>
       </c>
-      <c r="R49" s="21" t="s">
+      <c r="S49" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="T49" s="21" t="s">
         <v>540</v>
-      </c>
-      <c r="S49" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="T49" s="21" t="s">
-        <v>541</v>
       </c>
       <c r="U49" s="5" t="s">
         <v>58</v>
@@ -11992,10 +12070,10 @@
     </row>
     <row r="50" ht="42" customHeight="1" spans="1:38">
       <c r="A50" s="20" t="s">
+        <v>487</v>
+      </c>
+      <c r="B50" s="21" t="s">
         <v>488</v>
-      </c>
-      <c r="B50" s="21" t="s">
-        <v>489</v>
       </c>
       <c r="C50" s="21" t="s">
         <v>108</v>
@@ -12004,23 +12082,23 @@
         <v>109</v>
       </c>
       <c r="E50" s="17" t="s">
+        <v>541</v>
+      </c>
+      <c r="F50" s="22" t="s">
         <v>542</v>
-      </c>
-      <c r="F50" s="22" t="s">
-        <v>543</v>
       </c>
       <c r="G50" s="5" t="str">
         <f t="shared" si="0"/>
         <v>浏览杭州外围模特可可的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H50" s="17" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="I50" s="5" t="s">
         <v>174</v>
       </c>
       <c r="J50" s="17" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="K50" s="5" t="str">
         <f t="shared" si="1"/>
@@ -12030,28 +12108,28 @@
         <v>176</v>
       </c>
       <c r="M50" s="5" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="N50" s="21" t="s">
+        <v>545</v>
+      </c>
+      <c r="O50" s="21" t="s">
         <v>546</v>
       </c>
-      <c r="O50" s="21" t="s">
+      <c r="P50" s="21" t="s">
         <v>547</v>
       </c>
-      <c r="P50" s="21" t="s">
+      <c r="Q50" s="21" t="s">
         <v>548</v>
       </c>
-      <c r="Q50" s="21" t="s">
+      <c r="R50" s="21" t="s">
         <v>549</v>
       </c>
-      <c r="R50" s="21" t="s">
+      <c r="S50" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="T50" s="21" t="s">
         <v>550</v>
-      </c>
-      <c r="S50" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="T50" s="21" t="s">
-        <v>551</v>
       </c>
       <c r="U50" s="5" t="s">
         <v>58</v>
@@ -12108,10 +12186,10 @@
     </row>
     <row r="51" ht="42" customHeight="1" spans="1:38">
       <c r="A51" s="20" t="s">
+        <v>487</v>
+      </c>
+      <c r="B51" s="21" t="s">
         <v>488</v>
-      </c>
-      <c r="B51" s="21" t="s">
-        <v>489</v>
       </c>
       <c r="C51" s="21" t="s">
         <v>120</v>
@@ -12120,23 +12198,23 @@
         <v>121</v>
       </c>
       <c r="E51" s="17" t="s">
+        <v>551</v>
+      </c>
+      <c r="F51" s="22" t="s">
         <v>552</v>
-      </c>
-      <c r="F51" s="22" t="s">
-        <v>553</v>
       </c>
       <c r="G51" s="5" t="str">
         <f t="shared" si="0"/>
         <v>浏览杭州外围模特卡卡的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H51" s="17" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="I51" s="5" t="s">
         <v>124</v>
       </c>
       <c r="J51" s="17" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="K51" s="5" t="str">
         <f t="shared" si="1"/>
@@ -12146,28 +12224,28 @@
         <v>176</v>
       </c>
       <c r="M51" s="5" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="N51" s="21" t="s">
+        <v>555</v>
+      </c>
+      <c r="O51" s="21" t="s">
         <v>556</v>
       </c>
-      <c r="O51" s="21" t="s">
+      <c r="P51" s="21" t="s">
         <v>557</v>
       </c>
-      <c r="P51" s="21" t="s">
+      <c r="Q51" s="21" t="s">
         <v>558</v>
       </c>
-      <c r="Q51" s="21" t="s">
+      <c r="R51" s="21" t="s">
         <v>559</v>
       </c>
-      <c r="R51" s="21" t="s">
+      <c r="S51" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="T51" s="21" t="s">
         <v>560</v>
-      </c>
-      <c r="S51" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="T51" s="21" t="s">
-        <v>561</v>
       </c>
       <c r="U51" s="5" t="s">
         <v>58</v>
@@ -12224,10 +12302,10 @@
     </row>
     <row r="52" ht="42" customHeight="1" spans="1:38">
       <c r="A52" s="20" t="s">
+        <v>487</v>
+      </c>
+      <c r="B52" s="21" t="s">
         <v>488</v>
-      </c>
-      <c r="B52" s="21" t="s">
-        <v>489</v>
       </c>
       <c r="C52" s="21" t="s">
         <v>132</v>
@@ -12236,23 +12314,23 @@
         <v>133</v>
       </c>
       <c r="E52" s="17" t="s">
+        <v>561</v>
+      </c>
+      <c r="F52" s="22" t="s">
         <v>562</v>
-      </c>
-      <c r="F52" s="22" t="s">
-        <v>563</v>
       </c>
       <c r="G52" s="5" t="str">
         <f t="shared" si="0"/>
         <v>浏览杭州外围模特橙橙 的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H52" s="17" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="I52" s="5" t="s">
         <v>136</v>
       </c>
       <c r="J52" s="17" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K52" s="5" t="str">
         <f t="shared" si="1"/>
@@ -12262,28 +12340,28 @@
         <v>176</v>
       </c>
       <c r="M52" s="5" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="N52" s="21" t="s">
+        <v>565</v>
+      </c>
+      <c r="O52" s="21" t="s">
         <v>566</v>
       </c>
-      <c r="O52" s="21" t="s">
+      <c r="P52" s="21" t="s">
         <v>567</v>
       </c>
-      <c r="P52" s="21" t="s">
+      <c r="Q52" s="21" t="s">
         <v>568</v>
       </c>
-      <c r="Q52" s="21" t="s">
+      <c r="R52" s="21" t="s">
         <v>569</v>
       </c>
-      <c r="R52" s="21" t="s">
+      <c r="S52" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="T52" s="21" t="s">
         <v>570</v>
-      </c>
-      <c r="S52" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="T52" s="21" t="s">
-        <v>571</v>
       </c>
       <c r="U52" s="5" t="s">
         <v>58</v>
@@ -12340,10 +12418,10 @@
     </row>
     <row r="53" ht="42" customHeight="1" spans="1:38">
       <c r="A53" s="20" t="s">
+        <v>487</v>
+      </c>
+      <c r="B53" s="21" t="s">
         <v>488</v>
-      </c>
-      <c r="B53" s="21" t="s">
-        <v>489</v>
       </c>
       <c r="C53" s="21" t="s">
         <v>144</v>
@@ -12352,23 +12430,23 @@
         <v>145</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F53" s="22" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G53" s="5" t="str">
         <f t="shared" si="0"/>
         <v>浏览杭州外围模特的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H53" s="17" t="s">
+        <v>572</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="J53" s="17" t="s">
         <v>573</v>
-      </c>
-      <c r="I53" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="J53" s="17" t="s">
-        <v>574</v>
       </c>
       <c r="K53" s="5" t="str">
         <f t="shared" si="1"/>
@@ -12378,28 +12456,28 @@
         <v>176</v>
       </c>
       <c r="M53" s="5" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="N53" s="21" t="s">
+        <v>574</v>
+      </c>
+      <c r="O53" s="21" t="s">
         <v>575</v>
       </c>
-      <c r="O53" s="21" t="s">
+      <c r="P53" s="21" t="s">
         <v>576</v>
       </c>
-      <c r="P53" s="21" t="s">
+      <c r="Q53" s="21" t="s">
         <v>577</v>
       </c>
-      <c r="Q53" s="21" t="s">
+      <c r="R53" s="21" t="s">
         <v>578</v>
       </c>
-      <c r="R53" s="21" t="s">
+      <c r="S53" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="T53" s="21" t="s">
         <v>579</v>
-      </c>
-      <c r="S53" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="T53" s="21" t="s">
-        <v>580</v>
       </c>
       <c r="U53" s="5" t="s">
         <v>58</v>
@@ -12456,10 +12534,10 @@
     </row>
     <row r="54" ht="42" customHeight="1" spans="1:38">
       <c r="A54" s="20" t="s">
+        <v>487</v>
+      </c>
+      <c r="B54" s="21" t="s">
         <v>488</v>
-      </c>
-      <c r="B54" s="21" t="s">
-        <v>489</v>
       </c>
       <c r="C54" s="21" t="s">
         <v>157</v>
@@ -12468,54 +12546,54 @@
         <v>158</v>
       </c>
       <c r="E54" s="17" t="s">
+        <v>580</v>
+      </c>
+      <c r="F54" s="22" t="s">
         <v>581</v>
-      </c>
-      <c r="F54" s="22" t="s">
-        <v>582</v>
       </c>
       <c r="G54" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>浏览杭州外围模特周的独立资料、图片说明、内容介绍与相关推荐。</v>
+        <v>浏览杭州外围模特周周的独立资料、图片说明、内容介绍与相关推荐。</v>
       </c>
       <c r="H54" s="17" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="I54" s="5" t="s">
         <v>161</v>
       </c>
       <c r="J54" s="17" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="K54" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>以上是杭州外围模特周的照片、资料、无需注册登录即可浏览。</v>
+        <v>以上是杭州外围模特周周的照片、资料、无需注册登录即可浏览。</v>
       </c>
       <c r="L54" s="5" t="s">
         <v>176</v>
       </c>
       <c r="M54" s="5" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="N54" s="21" t="s">
+        <v>584</v>
+      </c>
+      <c r="O54" s="21" t="s">
         <v>585</v>
       </c>
-      <c r="O54" s="21" t="s">
+      <c r="P54" s="21" t="s">
         <v>586</v>
       </c>
-      <c r="P54" s="21" t="s">
+      <c r="Q54" s="21" t="s">
         <v>587</v>
       </c>
-      <c r="Q54" s="21" t="s">
+      <c r="R54" s="21" t="s">
         <v>588</v>
       </c>
-      <c r="R54" s="21" t="s">
+      <c r="S54" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="T54" s="21" t="s">
         <v>589</v>
-      </c>
-      <c r="S54" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="T54" s="21" t="s">
-        <v>590</v>
       </c>
       <c r="U54" s="5" t="s">
         <v>58</v>
@@ -12533,35 +12611,35 @@
       <c r="Z54" s="18"/>
       <c r="AA54" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>杭州外围模特周主图</v>
+        <v>杭州外围模特周周主图</v>
       </c>
       <c r="AB54" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>杭州外围模特周资料主图</v>
+        <v>杭州外围模特周周资料主图</v>
       </c>
       <c r="AC54" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>杭州外围模特周细节图</v>
+        <v>杭州外围模特周周细节图</v>
       </c>
       <c r="AD54" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>杭州外围模特周资料细节</v>
+        <v>杭州外围模特周周资料细节</v>
       </c>
       <c r="AE54" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>杭州外围模特周展示图</v>
+        <v>杭州外围模特周周展示图</v>
       </c>
       <c r="AF54" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>杭州外围模特周资料展示</v>
+        <v>杭州外围模特周周资料展示</v>
       </c>
       <c r="AG54" s="5" t="str">
         <f t="shared" si="8"/>
-        <v>杭州外围模特周资料视频</v>
+        <v>杭州外围模特周周资料视频</v>
       </c>
       <c r="AH54" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>杭州外围模特周相关资料视频</v>
+        <v>杭州外围模特周周相关资料视频</v>
       </c>
       <c r="AI54" s="5"/>
       <c r="AJ54" s="18"/>
@@ -16621,7 +16699,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:5">
       <c r="A1" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -16630,7 +16708,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:5">
       <c r="A2" s="9" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -16646,500 +16724,500 @@
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:5">
       <c r="A4" s="11" t="s">
+        <v>592</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>593</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="C4" s="11" t="s">
         <v>594</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="D4" s="11" t="s">
         <v>595</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="E4" s="11" t="s">
         <v>596</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1" spans="1:5">
       <c r="A5" s="12" t="s">
+        <v>597</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>598</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="C5" s="12" t="s">
         <v>599</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="D5" s="13" t="s">
         <v>600</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="E5" s="14" t="s">
         <v>601</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1" spans="1:5">
       <c r="A6" s="12" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B6" s="12" t="s">
+        <v>602</v>
+      </c>
+      <c r="C6" s="12" t="s">
         <v>603</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="D6" s="13" t="s">
         <v>604</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="E6" s="14" t="s">
         <v>605</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1" spans="1:5">
       <c r="A7" s="12" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B7" s="12" t="s">
+        <v>606</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>607</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="D7" s="13" t="s">
         <v>608</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="E7" s="14" t="s">
         <v>609</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1" spans="1:5">
       <c r="A8" s="12" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B8" s="12" t="s">
+        <v>610</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>611</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="D8" s="13" t="s">
         <v>612</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="E8" s="14" t="s">
         <v>613</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1" spans="1:5">
       <c r="A9" s="12" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B9" s="12" t="s">
+        <v>614</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>615</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="D9" s="13" t="s">
         <v>616</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="E9" s="14" t="s">
         <v>617</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1" spans="1:5">
       <c r="A10" s="12" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B10" s="12" t="s">
+        <v>618</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>619</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="D10" s="13" t="s">
         <v>620</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="E10" s="14" t="s">
         <v>621</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1" spans="1:5">
       <c r="A11" s="12" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B11" s="12" t="s">
+        <v>622</v>
+      </c>
+      <c r="C11" s="12" t="s">
         <v>623</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="D11" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="D11" s="13" t="s">
-        <v>625</v>
-      </c>
       <c r="E11" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:5">
       <c r="A12" s="12" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B12" s="12" t="s">
+        <v>625</v>
+      </c>
+      <c r="C12" s="12" t="s">
         <v>626</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="D12" s="13" t="s">
         <v>627</v>
       </c>
-      <c r="D12" s="13" t="s">
-        <v>628</v>
-      </c>
       <c r="E12" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1" spans="1:5">
       <c r="A13" s="12" t="s">
+        <v>628</v>
+      </c>
+      <c r="B13" s="12" t="s">
         <v>629</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>630</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>7</v>
       </c>
       <c r="D13" s="13" t="s">
+        <v>630</v>
+      </c>
+      <c r="E13" s="14" t="s">
         <v>631</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1" spans="1:5">
       <c r="A14" s="12" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="13" t="s">
+        <v>633</v>
+      </c>
+      <c r="E14" s="14" t="s">
         <v>634</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1" spans="1:5">
       <c r="A15" s="12" t="s">
+        <v>635</v>
+      </c>
+      <c r="B15" s="12" t="s">
         <v>636</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="C15" s="12" t="s">
         <v>637</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="D15" s="13" t="s">
         <v>638</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="E15" s="14" t="s">
         <v>639</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1" spans="1:5">
       <c r="A16" s="12" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B16" s="12" t="s">
+        <v>640</v>
+      </c>
+      <c r="C16" s="12" t="s">
         <v>641</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="D16" s="13" t="s">
         <v>642</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="E16" s="14" t="s">
         <v>643</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1" spans="1:5">
       <c r="A17" s="12" t="s">
+        <v>644</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>645</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="C17" s="12" t="s">
         <v>646</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="D17" s="13" t="s">
         <v>647</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="E17" s="14" t="s">
         <v>648</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1" spans="1:5">
       <c r="A18" s="12" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B18" s="12" t="s">
+        <v>649</v>
+      </c>
+      <c r="C18" s="12" t="s">
         <v>650</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="D18" s="13" t="s">
         <v>651</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="E18" s="14" t="s">
         <v>652</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1" spans="1:5">
       <c r="A19" s="12" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B19" s="12" t="s">
+        <v>653</v>
+      </c>
+      <c r="C19" s="12" t="s">
         <v>654</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="D19" s="13" t="s">
         <v>655</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="E19" s="14" t="s">
         <v>656</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1" spans="1:5">
       <c r="A20" s="12" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B20" s="12" t="s">
+        <v>657</v>
+      </c>
+      <c r="C20" s="12" t="s">
         <v>658</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="D20" s="13" t="s">
         <v>659</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="E20" s="14" t="s">
         <v>660</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1" spans="1:5">
       <c r="A21" s="12" t="s">
+        <v>661</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>662</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="C21" s="12" t="s">
         <v>663</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="D21" s="13" t="s">
         <v>664</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="E21" s="14" t="s">
         <v>665</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="22" ht="42" customHeight="1" spans="1:5">
       <c r="A22" s="12" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B22" s="12" t="s">
+        <v>666</v>
+      </c>
+      <c r="C22" s="12" t="s">
         <v>667</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="D22" s="13" t="s">
         <v>668</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>669</v>
-      </c>
       <c r="E22" s="14" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1" spans="1:5">
       <c r="A23" s="12" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B23" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C23" s="12" t="s">
         <v>670</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="D23" s="13" t="s">
         <v>671</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="E23" s="14" t="s">
         <v>672</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="24" ht="42" customHeight="1" spans="1:5">
       <c r="A24" s="12" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B24" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="C24" s="12" t="s">
         <v>674</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="D24" s="13" t="s">
         <v>675</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="E24" s="14" t="s">
         <v>676</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="25" ht="42" customHeight="1" spans="1:5">
       <c r="A25" s="12" t="s">
+        <v>677</v>
+      </c>
+      <c r="B25" s="12" t="s">
         <v>678</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="C25" s="12" t="s">
         <v>679</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="D25" s="13" t="s">
         <v>680</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="E25" s="14" t="s">
         <v>681</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="26" ht="42" customHeight="1" spans="1:5">
       <c r="A26" s="12" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B26" s="12" t="s">
+        <v>682</v>
+      </c>
+      <c r="C26" s="12" t="s">
         <v>683</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="D26" s="13" t="s">
         <v>684</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="E26" s="14" t="s">
         <v>685</v>
-      </c>
-      <c r="E26" s="14" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="27" ht="42" customHeight="1" spans="1:5">
       <c r="A27" s="12" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B27" s="12" t="s">
+        <v>686</v>
+      </c>
+      <c r="C27" s="12" t="s">
         <v>687</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="D27" s="13" t="s">
         <v>688</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>689</v>
-      </c>
       <c r="E27" s="14" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="28" ht="42" customHeight="1" spans="1:5">
       <c r="A28" s="12" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B28" s="12" t="s">
+        <v>689</v>
+      </c>
+      <c r="C28" s="12" t="s">
         <v>690</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="D28" s="13" t="s">
         <v>691</v>
       </c>
-      <c r="D28" s="13" t="s">
+      <c r="E28" s="14" t="s">
         <v>692</v>
-      </c>
-      <c r="E28" s="14" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="29" ht="42" customHeight="1" spans="1:5">
       <c r="A29" s="12" t="s">
+        <v>693</v>
+      </c>
+      <c r="B29" s="12" t="s">
         <v>694</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="C29" s="12" t="s">
         <v>695</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="D29" s="13" t="s">
         <v>696</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>697</v>
-      </c>
       <c r="E29" s="14" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="30" ht="42" customHeight="1" spans="1:5">
       <c r="A30" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B30" s="12" t="s">
+        <v>697</v>
+      </c>
+      <c r="C30" s="12" t="s">
         <v>698</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="D30" s="13" t="s">
         <v>699</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>700</v>
-      </c>
       <c r="E30" s="14" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="31" ht="42" customHeight="1" spans="1:5">
       <c r="A31" s="12" t="s">
+        <v>700</v>
+      </c>
+      <c r="B31" s="12" t="s">
         <v>701</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="C31" s="12" t="s">
         <v>702</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="D31" s="13" t="s">
         <v>703</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="E31" s="14" t="s">
         <v>704</v>
-      </c>
-      <c r="E31" s="14" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="32" ht="42" customHeight="1" spans="1:5">
       <c r="A32" s="12" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B32" s="12" t="s">
+        <v>705</v>
+      </c>
+      <c r="C32" s="12" t="s">
         <v>706</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="D32" s="13" t="s">
         <v>707</v>
       </c>
-      <c r="D32" s="13" t="s">
-        <v>656</v>
-      </c>
       <c r="E32" s="14" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="33" ht="42" customHeight="1" spans="1:5">
       <c r="A33" s="12" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>708</v>
@@ -17151,12 +17229,12 @@
         <v>710</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="34" ht="42" customHeight="1" spans="1:5">
       <c r="A34" s="12" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>711</v>
@@ -17168,12 +17246,12 @@
         <v>713</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="35" ht="42" customHeight="1" spans="1:5">
       <c r="A35" s="12" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B35" s="12" t="s">
         <v>714</v>
@@ -17185,12 +17263,12 @@
         <v>716</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="36" ht="42" customHeight="1" spans="1:5">
       <c r="A36" s="12" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>717</v>
@@ -17202,12 +17280,12 @@
         <v>719</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="37" ht="42" customHeight="1" spans="1:5">
       <c r="A37" s="12" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B37" s="12" t="s">
         <v>720</v>
@@ -17219,12 +17297,12 @@
         <v>722</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="38" ht="42" customHeight="1" spans="1:5">
       <c r="A38" s="12" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>723</v>
@@ -17236,12 +17314,12 @@
         <v>725</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="39" ht="42" customHeight="1" spans="1:5">
       <c r="A39" s="12" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B39" s="12" t="s">
         <v>726</v>
@@ -17253,7 +17331,7 @@
         <v>728</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="40" ht="42" customHeight="1" spans="1:5">
@@ -17270,7 +17348,7 @@
         <v>732</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="41" ht="42" customHeight="1" spans="1:5">
@@ -17542,7 +17620,7 @@
         <v>796</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="57" ht="42" customHeight="1" spans="1:5">
@@ -17902,13 +17980,13 @@
         <v>8</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>852</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>853</v>
@@ -18120,7 +18198,7 @@
         <v>58</v>
       </c>
       <c r="AL5" s="5" t="s">
-        <v>183</v>
+        <v>909</v>
       </c>
       <c r="AM5" s="5">
         <v>1</v>
@@ -18137,22 +18215,22 @@
         <v>170</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>879</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>882</v>
@@ -18161,13 +18239,13 @@
         <v>883</v>
       </c>
       <c r="K6" s="17" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="L6" s="17" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="M6" s="17" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="N6" s="17" t="s">
         <v>887</v>
@@ -18179,19 +18257,19 @@
         <v>889</v>
       </c>
       <c r="Q6" s="17" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="R6" s="17" t="s">
         <v>891</v>
       </c>
       <c r="S6" s="17" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="T6" s="5" t="s">
         <v>893</v>
       </c>
       <c r="U6" s="5" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="V6" s="5" t="s">
         <v>895</v>
@@ -18200,7 +18278,7 @@
         <v>896</v>
       </c>
       <c r="X6" s="17" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="Y6" s="5" t="s">
         <v>898</v>
@@ -18209,13 +18287,13 @@
         <v>796</v>
       </c>
       <c r="AA6" s="5" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="AB6" s="17" t="s">
         <v>900</v>
       </c>
       <c r="AC6" s="17" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="AD6" s="17" t="s">
         <v>902</v>
@@ -18242,7 +18320,7 @@
         <v>58</v>
       </c>
       <c r="AL6" s="5" t="s">
-        <v>183</v>
+        <v>909</v>
       </c>
       <c r="AM6" s="5">
         <v>2</v>
@@ -18253,28 +18331,28 @@
     </row>
     <row r="7" ht="52" customHeight="1" spans="1:40">
       <c r="A7" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>278</v>
-      </c>
       <c r="C7" s="5" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>879</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>882</v>
@@ -18283,13 +18361,13 @@
         <v>883</v>
       </c>
       <c r="K7" s="17" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="L7" s="17" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="M7" s="17" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="N7" s="17" t="s">
         <v>887</v>
@@ -18301,19 +18379,19 @@
         <v>889</v>
       </c>
       <c r="Q7" s="17" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="R7" s="17" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="S7" s="17" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="T7" s="5" t="s">
         <v>893</v>
       </c>
       <c r="U7" s="5" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="V7" s="5" t="s">
         <v>895</v>
@@ -18322,7 +18400,7 @@
         <v>896</v>
       </c>
       <c r="X7" s="17" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="Y7" s="5" t="s">
         <v>898</v>
@@ -18331,13 +18409,13 @@
         <v>796</v>
       </c>
       <c r="AA7" s="5" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="AB7" s="17" t="s">
         <v>900</v>
       </c>
       <c r="AC7" s="17" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="AD7" s="17" t="s">
         <v>902</v>
@@ -18364,7 +18442,7 @@
         <v>58</v>
       </c>
       <c r="AL7" s="5" t="s">
-        <v>183</v>
+        <v>909</v>
       </c>
       <c r="AM7" s="5">
         <v>3</v>
@@ -18375,28 +18453,28 @@
     </row>
     <row r="8" ht="52" customHeight="1" spans="1:40">
       <c r="A8" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>381</v>
-      </c>
       <c r="C8" s="5" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>879</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>882</v>
@@ -18405,13 +18483,13 @@
         <v>883</v>
       </c>
       <c r="K8" s="17" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="L8" s="17" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="M8" s="17" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="N8" s="17" t="s">
         <v>887</v>
@@ -18423,19 +18501,19 @@
         <v>889</v>
       </c>
       <c r="Q8" s="17" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="R8" s="17" t="s">
         <v>891</v>
       </c>
       <c r="S8" s="17" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="T8" s="5" t="s">
         <v>893</v>
       </c>
       <c r="U8" s="5" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="V8" s="5" t="s">
         <v>895</v>
@@ -18444,7 +18522,7 @@
         <v>896</v>
       </c>
       <c r="X8" s="17" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="Y8" s="5" t="s">
         <v>898</v>
@@ -18453,13 +18531,13 @@
         <v>796</v>
       </c>
       <c r="AA8" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="AB8" s="17" t="s">
         <v>900</v>
       </c>
       <c r="AC8" s="17" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="AD8" s="17" t="s">
         <v>902</v>
@@ -18486,7 +18564,7 @@
         <v>58</v>
       </c>
       <c r="AL8" s="5" t="s">
-        <v>183</v>
+        <v>909</v>
       </c>
       <c r="AM8" s="5">
         <v>4</v>
@@ -18497,28 +18575,28 @@
     </row>
     <row r="9" ht="52" customHeight="1" spans="1:40">
       <c r="A9" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>488</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>489</v>
-      </c>
       <c r="C9" s="5" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>879</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>882</v>
@@ -18527,13 +18605,13 @@
         <v>883</v>
       </c>
       <c r="K9" s="17" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="L9" s="17" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="M9" s="17" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="N9" s="17" t="s">
         <v>887</v>
@@ -18545,19 +18623,19 @@
         <v>889</v>
       </c>
       <c r="Q9" s="17" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="R9" s="17" t="s">
         <v>891</v>
       </c>
       <c r="S9" s="17" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="T9" s="5" t="s">
         <v>893</v>
       </c>
       <c r="U9" s="5" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="V9" s="5" t="s">
         <v>895</v>
@@ -18566,7 +18644,7 @@
         <v>896</v>
       </c>
       <c r="X9" s="17" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="Y9" s="5" t="s">
         <v>898</v>
@@ -18575,13 +18653,13 @@
         <v>796</v>
       </c>
       <c r="AA9" s="5" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="AB9" s="17" t="s">
         <v>900</v>
       </c>
       <c r="AC9" s="17" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="AD9" s="17" t="s">
         <v>902</v>
@@ -18608,7 +18686,7 @@
         <v>58</v>
       </c>
       <c r="AL9" s="5" t="s">
-        <v>183</v>
+        <v>909</v>
       </c>
       <c r="AM9" s="5">
         <v>5</v>
@@ -19499,7 +19577,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -19509,7 +19587,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6">
       <c r="A2" s="9" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -19527,190 +19605,190 @@
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:6">
       <c r="A4" s="11" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="C4" s="11" t="s">
+        <v>593</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>594</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="E4" s="11" t="s">
         <v>595</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="F4" s="11" t="s">
         <v>596</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:6">
       <c r="A5" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>6</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:6">
       <c r="A6" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:6">
       <c r="A7" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="13" t="s">
+        <v>974</v>
+      </c>
+      <c r="F7" s="14" t="s">
         <v>973</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:6">
       <c r="A8" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C8" s="12" t="s">
+        <v>645</v>
+      </c>
+      <c r="D8" s="12" t="s">
         <v>646</v>
       </c>
-      <c r="D8" s="12" t="s">
-        <v>647</v>
-      </c>
       <c r="E8" s="13" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:6">
       <c r="A9" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>852</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:6">
       <c r="A10" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:6">
       <c r="A11" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:6">
       <c r="A12" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:6">
       <c r="A13" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>985</v>
@@ -19719,18 +19797,18 @@
         <v>986</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:6">
       <c r="A14" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>987</v>
@@ -19742,15 +19820,15 @@
         <v>989</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:6">
       <c r="A15" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>990</v>
@@ -19762,15 +19840,15 @@
         <v>992</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:6">
       <c r="A16" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>993</v>
@@ -19782,15 +19860,15 @@
         <v>995</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:6">
       <c r="A17" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>996</v>
@@ -19802,15 +19880,15 @@
         <v>998</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:6">
       <c r="A18" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>999</v>
@@ -19822,15 +19900,15 @@
         <v>1001</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:6">
       <c r="A19" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>1002</v>
@@ -19842,15 +19920,15 @@
         <v>1004</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:6">
       <c r="A20" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>1005</v>
@@ -19862,15 +19940,15 @@
         <v>1007</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:6">
       <c r="A21" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>1008</v>
@@ -19882,15 +19960,15 @@
         <v>1010</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:6">
       <c r="A22" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>1011</v>
@@ -19902,15 +19980,15 @@
         <v>1013</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:6">
       <c r="A23" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>1014</v>
@@ -19919,98 +19997,98 @@
         <v>1015</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>656</v>
+        <v>1016</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:6">
       <c r="A24" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:6">
       <c r="A25" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:6">
       <c r="A26" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="27" ht="48" customHeight="1" spans="1:6">
       <c r="A27" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>1027</v>
+        <v>722</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="28" ht="48" customHeight="1" spans="1:6">
       <c r="A28" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>1028</v>
@@ -20022,15 +20100,15 @@
         <v>1030</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="29" ht="48" customHeight="1" spans="1:6">
       <c r="A29" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>1031</v>
@@ -20042,38 +20120,38 @@
         <v>1033</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="30" ht="48" customHeight="1" spans="1:6">
       <c r="A30" s="12" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>1034</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="D30" s="12" t="s">
         <v>6</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="31" ht="48" customHeight="1" spans="1:6">
       <c r="A31" s="12" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B31" s="12" t="s">
         <v>1034</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D31" s="12" t="s">
         <v>7</v>
@@ -20082,18 +20160,18 @@
         <v>1035</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="32" ht="48" customHeight="1" spans="1:6">
       <c r="A32" s="12" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>1034</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D32" s="12" t="s">
         <v>8</v>
@@ -20102,38 +20180,38 @@
         <v>1036</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="33" ht="48" customHeight="1" spans="1:6">
       <c r="A33" s="12" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>1034</v>
       </c>
       <c r="C33" s="12" t="s">
+        <v>645</v>
+      </c>
+      <c r="D33" s="12" t="s">
         <v>646</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>647</v>
       </c>
       <c r="E33" s="13" t="s">
         <v>1037</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="34" ht="48" customHeight="1" spans="1:6">
       <c r="A34" s="12" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>1034</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="D34" s="12" t="s">
         <v>852</v>
@@ -20142,32 +20220,32 @@
         <v>1038</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="35" ht="48" customHeight="1" spans="1:6">
       <c r="A35" s="12" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B35" s="12" t="s">
         <v>1034</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="E35" s="13" t="s">
         <v>1036</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="36" ht="48" customHeight="1" spans="1:6">
       <c r="A36" s="12" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>1034</v>
@@ -20182,12 +20260,12 @@
         <v>1041</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="37" ht="48" customHeight="1" spans="1:6">
       <c r="A37" s="12" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B37" s="12" t="s">
         <v>1034</v>
@@ -20202,12 +20280,12 @@
         <v>1044</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="38" ht="48" customHeight="1" spans="1:6">
       <c r="A38" s="12" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>1034</v>
@@ -20222,12 +20300,12 @@
         <v>1047</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="39" ht="48" customHeight="1" spans="1:6">
       <c r="A39" s="12" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B39" s="12" t="s">
         <v>1034</v>
@@ -20242,12 +20320,12 @@
         <v>1050</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="40" ht="48" customHeight="1" spans="1:6">
       <c r="A40" s="12" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>1034</v>
@@ -20262,12 +20340,12 @@
         <v>1053</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="41" ht="48" customHeight="1" spans="1:6">
       <c r="A41" s="12" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B41" s="12" t="s">
         <v>1034</v>
@@ -20282,12 +20360,12 @@
         <v>1056</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="42" ht="48" customHeight="1" spans="1:6">
       <c r="A42" s="12" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B42" s="12" t="s">
         <v>1034</v>
@@ -20302,12 +20380,12 @@
         <v>1059</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="43" ht="48" customHeight="1" spans="1:6">
       <c r="A43" s="12" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B43" s="12" t="s">
         <v>1034</v>
@@ -20322,12 +20400,12 @@
         <v>1062</v>
       </c>
       <c r="F43" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="44" ht="48" customHeight="1" spans="1:6">
       <c r="A44" s="12" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>1034</v>
@@ -20342,12 +20420,12 @@
         <v>1065</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="45" ht="48" customHeight="1" spans="1:6">
       <c r="A45" s="12" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B45" s="12" t="s">
         <v>1034</v>
@@ -20362,12 +20440,12 @@
         <v>1068</v>
       </c>
       <c r="F45" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="46" ht="48" customHeight="1" spans="1:6">
       <c r="A46" s="12" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B46" s="12" t="s">
         <v>1034</v>
@@ -20382,7 +20460,7 @@
         <v>1041</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="47" ht="48" customHeight="1" spans="1:6">
@@ -20393,7 +20471,7 @@
         <v>1072</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="D47" s="12" t="s">
         <v>6</v>
@@ -20402,7 +20480,7 @@
         <v>1071</v>
       </c>
       <c r="F47" s="14" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="48" ht="48" customHeight="1" spans="1:6">
@@ -20413,7 +20491,7 @@
         <v>1072</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D48" s="12" t="s">
         <v>7</v>
@@ -20422,7 +20500,7 @@
         <v>1073</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="49" ht="48" customHeight="1" spans="1:6">
@@ -20433,7 +20511,7 @@
         <v>1072</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D49" s="12" t="s">
         <v>8</v>
@@ -20442,7 +20520,7 @@
         <v>1074</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="50" ht="48" customHeight="1" spans="1:6">
@@ -20453,16 +20531,16 @@
         <v>1072</v>
       </c>
       <c r="C50" s="12" t="s">
+        <v>645</v>
+      </c>
+      <c r="D50" s="12" t="s">
         <v>646</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>647</v>
       </c>
       <c r="E50" s="13" t="s">
         <v>1075</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="51" ht="48" customHeight="1" spans="1:6">
@@ -20473,7 +20551,7 @@
         <v>1072</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="D51" s="12" t="s">
         <v>852</v>
@@ -20482,7 +20560,7 @@
         <v>1071</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="52" ht="48" customHeight="1" spans="1:6">
@@ -20493,16 +20571,16 @@
         <v>1072</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="E52" s="13" t="s">
         <v>1074</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="53" ht="48" customHeight="1" spans="1:6">
@@ -20522,7 +20600,7 @@
         <v>1078</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="54" ht="48" customHeight="1" spans="1:6">
@@ -20533,16 +20611,16 @@
         <v>1072</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="E54" s="13" t="s">
         <v>1079</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="55" ht="48" customHeight="1" spans="1:6">
@@ -20553,16 +20631,16 @@
         <v>1072</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="E55" s="13" t="s">
         <v>1080</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="56" ht="48" customHeight="1" spans="1:6">
@@ -20582,7 +20660,7 @@
         <v>1081</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="57" ht="48" customHeight="1" spans="1:6">
@@ -20602,7 +20680,7 @@
         <v>1082</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="58" ht="48" customHeight="1" spans="1:6">
@@ -20622,7 +20700,7 @@
         <v>1085</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="59" ht="48" customHeight="1" spans="1:6">
@@ -20642,7 +20720,7 @@
         <v>1088</v>
       </c>
       <c r="F59" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="60" ht="48" customHeight="1" spans="1:6">
@@ -20662,7 +20740,7 @@
         <v>1091</v>
       </c>
       <c r="F60" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="61" ht="48" customHeight="1" spans="1:6">
@@ -20682,7 +20760,7 @@
         <v>1092</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="62" ht="48" customHeight="1" spans="1:6">
@@ -20702,7 +20780,7 @@
         <v>1093</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="63" ht="48" customHeight="1" spans="1:6">
@@ -20722,7 +20800,7 @@
         <v>1094</v>
       </c>
       <c r="F63" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="64" ht="48" customHeight="1" spans="1:6">
@@ -20742,7 +20820,7 @@
         <v>1095</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="65" ht="48" customHeight="1" spans="1:6">
@@ -20762,7 +20840,7 @@
         <v>1098</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="66" ht="48" customHeight="1" spans="1:6">
@@ -20779,10 +20857,10 @@
         <v>1100</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="67" ht="48" customHeight="1" spans="1:6">
@@ -20802,7 +20880,7 @@
         <v>1101</v>
       </c>
       <c r="F67" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="68" ht="48" customHeight="1" spans="1:6">
@@ -20822,7 +20900,7 @@
         <v>1104</v>
       </c>
       <c r="F68" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="69" ht="48" customHeight="1" spans="1:6">
@@ -20839,10 +20917,10 @@
         <v>1106</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="F69" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="70" ht="48" customHeight="1" spans="1:6">
@@ -20862,7 +20940,7 @@
         <v>1109</v>
       </c>
       <c r="F70" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="71" ht="48" customHeight="1" spans="1:6">
@@ -20882,7 +20960,7 @@
         <v>1112</v>
       </c>
       <c r="F71" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="72" ht="48" customHeight="1" spans="1:6">
@@ -20899,10 +20977,10 @@
         <v>1114</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="F72" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="73" ht="48" customHeight="1" spans="1:6">
@@ -20922,7 +21000,7 @@
         <v>1117</v>
       </c>
       <c r="F73" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="74" ht="48" customHeight="1" spans="1:6">
@@ -20942,7 +21020,7 @@
         <v>1120</v>
       </c>
       <c r="F74" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="75" ht="48" customHeight="1" spans="1:6">
@@ -20959,10 +21037,10 @@
         <v>1122</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="F75" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="76" ht="48" customHeight="1" spans="1:6">
@@ -20982,7 +21060,7 @@
         <v>1125</v>
       </c>
       <c r="F76" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="77" ht="48" customHeight="1" spans="1:6">
@@ -21002,7 +21080,7 @@
         <v>1128</v>
       </c>
       <c r="F77" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="78" ht="48" customHeight="1" spans="1:6">
@@ -21022,7 +21100,7 @@
         <v>1131</v>
       </c>
       <c r="F78" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="79" ht="48" customHeight="1" spans="1:6">
@@ -21033,7 +21111,7 @@
         <v>1133</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="D79" s="12" t="s">
         <v>6</v>
@@ -21042,7 +21120,7 @@
         <v>1132</v>
       </c>
       <c r="F79" s="14" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="80" ht="48" customHeight="1" spans="1:6">
@@ -21053,7 +21131,7 @@
         <v>1133</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D80" s="12" t="s">
         <v>7</v>
@@ -21062,7 +21140,7 @@
         <v>1134</v>
       </c>
       <c r="F80" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="81" ht="48" customHeight="1" spans="1:6">
@@ -21073,7 +21151,7 @@
         <v>1133</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D81" s="12" t="s">
         <v>8</v>
@@ -21082,7 +21160,7 @@
         <v>1135</v>
       </c>
       <c r="F81" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="82" ht="48" customHeight="1" spans="1:6">
@@ -21093,16 +21171,16 @@
         <v>1133</v>
       </c>
       <c r="C82" s="12" t="s">
+        <v>645</v>
+      </c>
+      <c r="D82" s="12" t="s">
         <v>646</v>
-      </c>
-      <c r="D82" s="12" t="s">
-        <v>647</v>
       </c>
       <c r="E82" s="13" t="s">
         <v>1136</v>
       </c>
       <c r="F82" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="83" ht="48" customHeight="1" spans="1:6">
@@ -21113,7 +21191,7 @@
         <v>1133</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="D83" s="12" t="s">
         <v>852</v>
@@ -21122,7 +21200,7 @@
         <v>1132</v>
       </c>
       <c r="F83" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="84" ht="48" customHeight="1" spans="1:6">
@@ -21133,16 +21211,16 @@
         <v>1133</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="E84" s="13" t="s">
         <v>1135</v>
       </c>
       <c r="F84" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="85" ht="48" customHeight="1" spans="1:6">
@@ -21162,7 +21240,7 @@
         <v>1078</v>
       </c>
       <c r="F85" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="86" ht="48" customHeight="1" spans="1:6">
@@ -21173,16 +21251,16 @@
         <v>1133</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="E86" s="13" t="s">
         <v>1137</v>
       </c>
       <c r="F86" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="87" ht="48" customHeight="1" spans="1:6">
@@ -21193,16 +21271,16 @@
         <v>1133</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="E87" s="13" t="s">
         <v>1138</v>
       </c>
       <c r="F87" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="88" ht="48" customHeight="1" spans="1:6">
@@ -21222,7 +21300,7 @@
         <v>1139</v>
       </c>
       <c r="F88" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="89" ht="48" customHeight="1" spans="1:6">
@@ -21242,7 +21320,7 @@
         <v>1140</v>
       </c>
       <c r="F89" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="90" ht="48" customHeight="1" spans="1:6">
@@ -21262,7 +21340,7 @@
         <v>1085</v>
       </c>
       <c r="F90" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="91" ht="48" customHeight="1" spans="1:6">
@@ -21282,7 +21360,7 @@
         <v>1141</v>
       </c>
       <c r="F91" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="92" ht="48" customHeight="1" spans="1:6">
@@ -21302,7 +21380,7 @@
         <v>1142</v>
       </c>
       <c r="F92" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="93" ht="48" customHeight="1" spans="1:6">
@@ -21322,7 +21400,7 @@
         <v>1143</v>
       </c>
       <c r="F93" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="94" ht="48" customHeight="1" spans="1:6">
@@ -21342,7 +21420,7 @@
         <v>1144</v>
       </c>
       <c r="F94" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="95" ht="48" customHeight="1" spans="1:6">
@@ -21359,10 +21437,10 @@
         <v>1000</v>
       </c>
       <c r="E95" s="13" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="F95" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="96" ht="48" customHeight="1" spans="1:6">
@@ -21382,7 +21460,7 @@
         <v>1145</v>
       </c>
       <c r="F96" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="97" ht="48" customHeight="1" spans="1:6">
@@ -21402,7 +21480,7 @@
         <v>1146</v>
       </c>
       <c r="F97" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="98" ht="48" customHeight="1" spans="1:6">
@@ -21419,10 +21497,10 @@
         <v>1100</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="F98" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="99" ht="48" customHeight="1" spans="1:6">
@@ -21442,7 +21520,7 @@
         <v>1147</v>
       </c>
       <c r="F99" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="100" ht="48" customHeight="1" spans="1:6">
@@ -21462,7 +21540,7 @@
         <v>1148</v>
       </c>
       <c r="F100" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="101" ht="48" customHeight="1" spans="1:6">
@@ -21479,10 +21557,10 @@
         <v>1106</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="F101" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="102" ht="48" customHeight="1" spans="1:6">
@@ -21502,7 +21580,7 @@
         <v>1149</v>
       </c>
       <c r="F102" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="103" ht="48" customHeight="1" spans="1:6">
@@ -21522,7 +21600,7 @@
         <v>1150</v>
       </c>
       <c r="F103" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="104" ht="48" customHeight="1" spans="1:6">
@@ -21539,10 +21617,10 @@
         <v>1114</v>
       </c>
       <c r="E104" s="13" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="F104" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="105" ht="48" customHeight="1" spans="1:6">
@@ -21562,7 +21640,7 @@
         <v>1151</v>
       </c>
       <c r="F105" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="106" ht="48" customHeight="1" spans="1:6">
@@ -21582,7 +21660,7 @@
         <v>1152</v>
       </c>
       <c r="F106" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="107" ht="48" customHeight="1" spans="1:6">
@@ -21599,10 +21677,10 @@
         <v>1122</v>
       </c>
       <c r="E107" s="13" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="F107" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="108" ht="48" customHeight="1" spans="1:6">
@@ -21622,7 +21700,7 @@
         <v>1153</v>
       </c>
       <c r="F108" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="109" ht="48" customHeight="1" spans="1:6">
@@ -21642,7 +21720,7 @@
         <v>1154</v>
       </c>
       <c r="F109" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="110" ht="48" customHeight="1" spans="1:6">
@@ -21659,10 +21737,10 @@
         <v>1130</v>
       </c>
       <c r="E110" s="13" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="F110" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="111" ht="48" customHeight="1" spans="1:6">
@@ -21673,7 +21751,7 @@
         <v>1156</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="D111" s="12" t="s">
         <v>6</v>
@@ -21682,7 +21760,7 @@
         <v>1155</v>
       </c>
       <c r="F111" s="14" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="112" ht="48" customHeight="1" spans="1:6">
@@ -21693,7 +21771,7 @@
         <v>1156</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D112" s="12" t="s">
         <v>7</v>
@@ -21702,7 +21780,7 @@
         <v>1157</v>
       </c>
       <c r="F112" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="113" ht="48" customHeight="1" spans="1:6">
@@ -21713,7 +21791,7 @@
         <v>1156</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D113" s="12" t="s">
         <v>8</v>
@@ -21722,7 +21800,7 @@
         <v>1158</v>
       </c>
       <c r="F113" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="114" ht="48" customHeight="1" spans="1:6">
@@ -21733,16 +21811,16 @@
         <v>1156</v>
       </c>
       <c r="C114" s="12" t="s">
+        <v>645</v>
+      </c>
+      <c r="D114" s="12" t="s">
         <v>646</v>
-      </c>
-      <c r="D114" s="12" t="s">
-        <v>647</v>
       </c>
       <c r="E114" s="13" t="s">
         <v>1159</v>
       </c>
       <c r="F114" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="115" ht="48" customHeight="1" spans="1:6">
@@ -21753,7 +21831,7 @@
         <v>1156</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="D115" s="12" t="s">
         <v>852</v>
@@ -21762,7 +21840,7 @@
         <v>1160</v>
       </c>
       <c r="F115" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="116" ht="48" customHeight="1" spans="1:6">
@@ -21773,16 +21851,16 @@
         <v>1156</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D116" s="12" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="E116" s="13" t="s">
         <v>1161</v>
       </c>
       <c r="F116" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="117" ht="48" customHeight="1" spans="1:6">
@@ -21802,7 +21880,7 @@
         <v>1164</v>
       </c>
       <c r="F117" s="14" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
   </sheetData>
@@ -21856,19 +21934,19 @@
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:5">
       <c r="A4" s="11" t="s">
+        <v>592</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>593</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="C4" s="11" t="s">
         <v>594</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="D4" s="11" t="s">
         <v>595</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="E4" s="11" t="s">
         <v>596</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1" spans="1:5">
@@ -21902,7 +21980,7 @@
         <v>1173</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1" spans="1:5">
@@ -21936,7 +22014,7 @@
         <v>1177</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1" spans="1:5">
@@ -21970,7 +22048,7 @@
         <v>1184</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1" spans="1:5">
@@ -21987,7 +22065,7 @@
         <v>1187</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:5">
@@ -22001,10 +22079,10 @@
         <v>1190</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1" spans="1:5">
@@ -22018,10 +22096,10 @@
         <v>1192</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1" spans="1:5">
@@ -22038,7 +22116,7 @@
         <v>1071</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1" spans="1:5">
@@ -22055,7 +22133,7 @@
         <v>1132</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1" spans="1:5">
@@ -22072,7 +22150,7 @@
         <v>1200</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1" spans="1:5">
@@ -22089,7 +22167,7 @@
         <v>1203</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1" spans="1:5">
@@ -22106,7 +22184,7 @@
         <v>1206</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1" spans="1:5">
@@ -22123,7 +22201,7 @@
         <v>1041</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
   </sheetData>

--- a/顶奢_整站资料批量编辑.xlsx
+++ b/顶奢_整站资料批量编辑.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16455" activeTab="4"/>
+    <workbookView windowHeight="16455" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="资料批量编辑" sheetId="1" r:id="rId1"/>
@@ -3842,7 +3842,7 @@
     <t>问答区说明</t>
   </si>
   <si>
-    <t>关于资料浏览、媒体更新和客服入口的说明。</t>
+    <t>关于模特挑选、媒体更新和客服入口的说明。</t>
   </si>
   <si>
     <t>首页问答简介</t>
@@ -4421,7 +4421,7 @@
     <t>第1段标题</t>
   </si>
   <si>
-    <t>让每套资料拥有清晰、可持续的页面</t>
+    <t>顶奢甄选  尊享非凡</t>
   </si>
   <si>
     <t>section_1_body_1</t>

--- a/顶奢_整站资料批量编辑.xlsx
+++ b/顶奢_整站资料批量编辑.xlsx
@@ -3326,7 +3326,7 @@
     <t>seo_title</t>
   </si>
   <si>
-    <t>顶奢｜城市精选资料展示</t>
+    <t>商务模特预约｜高端外围预约｜顶奢</t>
   </si>
   <si>
     <t>浏览器标题与搜索标题</t>

--- a/顶奢_整站资料批量编辑.xlsx
+++ b/顶奢_整站资料批量编辑.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16455" activeTab="4"/>
+    <workbookView windowHeight="16455" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="资料批量编辑" sheetId="1" r:id="rId1"/>
@@ -3437,7 +3437,7 @@
     <t>首屏简介</t>
   </si>
   <si>
-    <t>欢迎来到顶奢商务模特外围工作室！我们的服务覆盖全国一二线城市及热门城市，国外英法美日韩，欧洲等热门国家。，为您提供需要的外围商务模特。</t>
+    <t>欢迎来到顶奢商务模特外围工作室！我们的服务覆盖全国一二线城市及热门城市，国外英法美日韩，欧洲等热门国家，为您提供需要的外围商务模特。</t>
   </si>
   <si>
     <t>主标题下方文字</t>

--- a/顶奢_整站资料批量编辑.xlsx
+++ b/顶奢_整站资料批量编辑.xlsx
@@ -4091,10 +4091,10 @@
     <t>海派格调与都会精选</t>
   </si>
   <si>
-    <t>上海外围｜上海模特预约｜顶奢</t>
-  </si>
-  <si>
-    <t>顶奢上海资源库，集中展示上海城市精选资料、独立图片、视频、风格介绍与相关推荐。</t>
+    <t>上海外围｜上海模特预约｜上海高端外围｜顶奢</t>
+  </si>
+  <si>
+    <t>顶奢上海资源库，集中展示上海城市精选外围模特资料、独立图片、视频、风格介绍与相关推荐。</t>
   </si>
   <si>
     <t>CITY COLLECTION</t>
@@ -4187,10 +4187,10 @@
     <t>岭南风尚与城市精选</t>
   </si>
   <si>
-    <t>广州外围｜广州模特预约｜顶奢</t>
-  </si>
-  <si>
-    <t>顶奢广州资源库，浏览广州城市精选资料、专属图片、视频介绍及相关城市内容。</t>
+    <t>广州外围｜广州模特预约｜广州高端外围｜顶奢</t>
+  </si>
+  <si>
+    <t>顶奢广州资源库，浏览广州城市精选外围模特资料、专属图片、视频介绍及相关城市内容。</t>
   </si>
   <si>
     <t>广州外围模特</t>
@@ -4229,10 +4229,10 @@
     <t>湾区新锐与现代精选</t>
   </si>
   <si>
-    <t>深圳外围｜深圳模特预约｜顶奢</t>
-  </si>
-  <si>
-    <t>顶奢深圳资源库，查看深圳现代城市精选资料、图片展示、视频位置与相关推荐。</t>
+    <t>深圳外围｜深圳模特预约｜深圳高端外围｜顶奢</t>
+  </si>
+  <si>
+    <t>顶奢深圳资源库，查看深圳现代城市精选外围模特资料、图片展示、视频位置与相关推荐。</t>
   </si>
   <si>
     <t>深圳外围模特</t>
@@ -4274,10 +4274,10 @@
     <t>京华气韵与城市精选</t>
   </si>
   <si>
-    <t>北京外围｜北京模特预约｜顶奢</t>
-  </si>
-  <si>
-    <t>顶奢北京资源库，汇总北京城市精选资料、独立图片、视频、专题说明和相关推荐。</t>
+    <t>北京外围｜北京模特预约｜北京高端外围｜顶奢</t>
+  </si>
+  <si>
+    <t>顶奢北京资源库，汇总北京城市精选外围模特资料、独立图片、视频、专题说明和相关推荐。</t>
   </si>
   <si>
     <t>北京外围模特</t>
@@ -4313,10 +4313,10 @@
     <t>江南雅意与城市精选</t>
   </si>
   <si>
-    <t>杭州外围｜杭州模特预约｜顶奢</t>
-  </si>
-  <si>
-    <t>顶奢杭州资源库，浏览杭州城市精选资料、独立图片说明、视频信息、独立说明与站内推荐。</t>
+    <t>杭州外围｜杭州模特预约｜杭州高端外围｜顶奢</t>
+  </si>
+  <si>
+    <t>顶奢杭州资源库，浏览杭州城市精选外围模特资料、独立图片说明、视频信息、独立说明与站内推荐。</t>
   </si>
   <si>
     <t>杭州外围模特</t>
@@ -18316,7 +18316,7 @@
       <c r="D5" s="17" t="s">
         <v>885</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="17" t="s">
         <v>886</v>
       </c>
       <c r="F5" s="5" t="s">
@@ -18438,7 +18438,7 @@
       <c r="D6" s="17" t="s">
         <v>917</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="17" t="s">
         <v>918</v>
       </c>
       <c r="F6" s="5" t="s">
@@ -18560,7 +18560,7 @@
       <c r="D7" s="17" t="s">
         <v>931</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="17" t="s">
         <v>932</v>
       </c>
       <c r="F7" s="5" t="s">
@@ -18682,7 +18682,7 @@
       <c r="D8" s="17" t="s">
         <v>946</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="17" t="s">
         <v>947</v>
       </c>
       <c r="F8" s="5" t="s">
@@ -18804,7 +18804,7 @@
       <c r="D9" s="17" t="s">
         <v>959</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="17" t="s">
         <v>960</v>
       </c>
       <c r="F9" s="5" t="s">

--- a/顶奢_整站资料批量编辑.xlsx
+++ b/顶奢_整站资料批量编辑.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16455" activeTab="2"/>
+    <workbookView windowHeight="16455"/>
   </bookViews>
   <sheets>
     <sheet name="资料批量编辑" sheetId="1" r:id="rId1"/>
@@ -4100,7 +4100,7 @@
     <t>CITY COLLECTION</t>
   </si>
   <si>
-    <t>欢迎您来到顶奢上海精选，网页只展示部分女孩资料，更多资源请联系客服加入会员后解锁！</t>
+    <t>顶奢广州外围模特资源页面汇集上海静安区、徐汇区、闵行区、宝山区、普陀区、浦东区等区域外围商务模特资料，提供图片、视频及详细资料展示。并持续更新新的外围模特资料，更多资源请联系客服加入会员后解锁！</t>
   </si>
   <si>
     <t>套独立资料</t>
@@ -4196,7 +4196,7 @@
     <t>广州外围模特</t>
   </si>
   <si>
-    <t>欢迎您来到顶奢广州精选，网页只展示部分女孩资料，更多资源请联系客服加入会员后解锁！</t>
+    <t>顶奢广州外围模特资源页面汇集广州天河区、越秀区、海珠区、白云区等区域外围商务模特资料，提供图片、视频及详细资料展示。并持续更新新的外围模特资料，更多资源请联系客服加入会员后解锁！</t>
   </si>
   <si>
     <t>广州资料浏览指南</t>
@@ -4238,7 +4238,7 @@
     <t>深圳外围模特</t>
   </si>
   <si>
-    <t>欢迎您来到顶奢深圳精选，网页只展示部分女孩资料，更多资源请联系客服加入会员后解锁！</t>
+    <t>顶奢深圳外围模特资源页面汇集深圳福田区、南山区、罗湖区、宝安区、龙华区等区域外围商务模特资料，提供图片、视频及详细资料展示。并持续更新新的外围模特资料，更多资源请联系客服加入会员后解锁！</t>
   </si>
   <si>
     <t>深圳资料浏览指南</t>
@@ -4283,7 +4283,7 @@
     <t>北京外围模特</t>
   </si>
   <si>
-    <t>欢迎您来到顶奢北京精选，网页只展示部分女孩资料，更多资源请联系客服加入会员后解锁！</t>
+    <t>顶奢北京外围模特资源页面汇集北京朝阳区、东城区、海定区等区域外围商务模特资料，提供图片、视频及详细资料展示。并持续更新新的外围模特资料，更多资源请联系客服加入会员后解锁！</t>
   </si>
   <si>
     <t>北京资料浏览指南</t>
@@ -4322,7 +4322,7 @@
     <t>杭州外围模特</t>
   </si>
   <si>
-    <t>欢迎您来到顶奢杭州精选，网页只展示部分女孩资料，更多资源请联系客服加入会员后解锁！</t>
+    <t>顶奢杭州外围模特资源页面汇集杭州西湖区、上城区、滨江区、拱墅区、萧山区等区域外围商务模特资料，提供图片、视频及详细资料展示。并持续更新新的外围模特资料，更多资源请联系客服加入会员后解锁！</t>
   </si>
   <si>
     <t>杭州资料浏览指南</t>
@@ -18792,7 +18792,7 @@
       </c>
     </row>
     <row r="9" ht="52" customHeight="1" spans="1:40">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="17" t="s">
         <v>493</v>
       </c>
       <c r="B9" s="8" t="s">

--- a/顶奢_整站资料批量编辑.xlsx
+++ b/顶奢_整站资料批量编辑.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16455"/>
+    <workbookView windowHeight="16455" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="资料批量编辑" sheetId="1" r:id="rId1"/>
@@ -4100,7 +4100,7 @@
     <t>CITY COLLECTION</t>
   </si>
   <si>
-    <t>顶奢广州外围模特资源页面汇集上海静安区、徐汇区、闵行区、宝山区、普陀区、浦东区等区域外围商务模特资料，提供图片、视频及详细资料展示。并持续更新新的外围模特资料，更多资源请联系客服加入会员后解锁！</t>
+    <t>顶奢上海外围模特资源页面汇集上海静安区、徐汇区、闵行区、宝山区、普陀区、浦东区等区域外围商务模特资料，提供图片、视频及详细资料展示。并持续更新新的外围模特资料，更多资源请联系客服加入会员后解锁！</t>
   </si>
   <si>
     <t>套独立资料</t>
@@ -18422,7 +18422,7 @@
         <v>1</v>
       </c>
       <c r="AN5" s="18">
-        <v>46288</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="6" ht="52" customHeight="1" spans="1:40">
@@ -18544,7 +18544,7 @@
         <v>2</v>
       </c>
       <c r="AN6" s="18">
-        <v>46288</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="7" ht="52" customHeight="1" spans="1:40">
@@ -18666,7 +18666,7 @@
         <v>3</v>
       </c>
       <c r="AN7" s="18">
-        <v>46288</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="8" ht="52" customHeight="1" spans="1:40">
@@ -18788,7 +18788,7 @@
         <v>4</v>
       </c>
       <c r="AN8" s="18">
-        <v>46288</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="9" ht="52" customHeight="1" spans="1:40">
@@ -18910,7 +18910,7 @@
         <v>5</v>
       </c>
       <c r="AN9" s="18">
-        <v>46288</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="10" ht="52" customHeight="1" spans="1:40">

--- a/顶奢_整站资料批量编辑.xlsx
+++ b/顶奢_整站资料批量编辑.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16455" activeTab="2"/>
+    <workbookView windowHeight="16455" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="资料批量编辑" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2524" uniqueCount="1261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2523" uniqueCount="1260">
   <si>
     <t>顶奢 · 整站资料批量编辑</t>
   </si>
@@ -3437,7 +3437,7 @@
     <t>首屏简介</t>
   </si>
   <si>
-    <t>欢迎来到顶奢商务模特外围工作室！我们的服务覆盖全国一二线城市及热门城市，国外英法美日韩，欧洲等热门国家，为您提供需要的外围商务模特。</t>
+    <t>欢迎来到顶奢商务模特外围工作室！我们的服务覆盖北京、上海、广州、深圳、杭州等全国一二线城市及热门城市，国外英法美日韩泰国新加坡等热门国家，为您提供需要的外围商务模特。</t>
   </si>
   <si>
     <t>主标题下方文字</t>
@@ -3654,9 +3654,6 @@
   </si>
   <si>
     <t>流程区英文</t>
-  </si>
-  <si>
-    <t>CONSULTATION PROCESS</t>
   </si>
   <si>
     <t>process_title</t>
@@ -17562,9 +17559,7 @@
       <c r="C40" s="12" t="s">
         <v>739</v>
       </c>
-      <c r="D40" s="13" t="s">
-        <v>740</v>
-      </c>
+      <c r="D40" s="13"/>
       <c r="E40" s="14" t="s">
         <v>656</v>
       </c>
@@ -17574,16 +17569,16 @@
         <v>737</v>
       </c>
       <c r="B41" s="12" t="s">
+        <v>740</v>
+      </c>
+      <c r="C41" s="12" t="s">
         <v>741</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="D41" s="13" t="s">
         <v>742</v>
       </c>
-      <c r="D41" s="13" t="s">
+      <c r="E41" s="14" t="s">
         <v>743</v>
-      </c>
-      <c r="E41" s="14" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="42" ht="42" customHeight="1" spans="1:5">
@@ -17591,16 +17586,16 @@
         <v>737</v>
       </c>
       <c r="B42" s="12" t="s">
+        <v>744</v>
+      </c>
+      <c r="C42" s="12" t="s">
         <v>745</v>
       </c>
-      <c r="C42" s="12" t="s">
+      <c r="D42" s="13" t="s">
         <v>746</v>
       </c>
-      <c r="D42" s="13" t="s">
+      <c r="E42" s="14" t="s">
         <v>747</v>
-      </c>
-      <c r="E42" s="14" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="43" ht="42" customHeight="1" spans="1:5">
@@ -17608,16 +17603,16 @@
         <v>737</v>
       </c>
       <c r="B43" s="12" t="s">
+        <v>748</v>
+      </c>
+      <c r="C43" s="12" t="s">
         <v>749</v>
       </c>
-      <c r="C43" s="12" t="s">
+      <c r="D43" s="13" t="s">
         <v>750</v>
       </c>
-      <c r="D43" s="13" t="s">
+      <c r="E43" s="14" t="s">
         <v>751</v>
-      </c>
-      <c r="E43" s="14" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="44" ht="42" customHeight="1" spans="1:5">
@@ -17625,16 +17620,16 @@
         <v>737</v>
       </c>
       <c r="B44" s="12" t="s">
+        <v>752</v>
+      </c>
+      <c r="C44" s="12" t="s">
         <v>753</v>
       </c>
-      <c r="C44" s="12" t="s">
+      <c r="D44" s="13" t="s">
         <v>754</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="E44" s="14" t="s">
         <v>755</v>
-      </c>
-      <c r="E44" s="14" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="45" ht="42" customHeight="1" spans="1:5">
@@ -17642,16 +17637,16 @@
         <v>737</v>
       </c>
       <c r="B45" s="12" t="s">
+        <v>756</v>
+      </c>
+      <c r="C45" s="12" t="s">
         <v>757</v>
       </c>
-      <c r="C45" s="12" t="s">
+      <c r="D45" s="13" t="s">
         <v>758</v>
       </c>
-      <c r="D45" s="13" t="s">
+      <c r="E45" s="14" t="s">
         <v>759</v>
-      </c>
-      <c r="E45" s="14" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="46" ht="42" customHeight="1" spans="1:5">
@@ -17659,16 +17654,16 @@
         <v>737</v>
       </c>
       <c r="B46" s="12" t="s">
+        <v>760</v>
+      </c>
+      <c r="C46" s="12" t="s">
         <v>761</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="D46" s="13" t="s">
         <v>762</v>
       </c>
-      <c r="D46" s="13" t="s">
+      <c r="E46" s="14" t="s">
         <v>763</v>
-      </c>
-      <c r="E46" s="14" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="47" ht="42" customHeight="1" spans="1:5">
@@ -17676,16 +17671,16 @@
         <v>737</v>
       </c>
       <c r="B47" s="12" t="s">
+        <v>764</v>
+      </c>
+      <c r="C47" s="12" t="s">
         <v>765</v>
       </c>
-      <c r="C47" s="12" t="s">
+      <c r="D47" s="13" t="s">
         <v>766</v>
       </c>
-      <c r="D47" s="13" t="s">
+      <c r="E47" s="14" t="s">
         <v>767</v>
-      </c>
-      <c r="E47" s="14" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="48" ht="42" customHeight="1" spans="1:5">
@@ -17693,16 +17688,16 @@
         <v>737</v>
       </c>
       <c r="B48" s="12" t="s">
+        <v>768</v>
+      </c>
+      <c r="C48" s="12" t="s">
         <v>769</v>
       </c>
-      <c r="C48" s="12" t="s">
+      <c r="D48" s="13" t="s">
         <v>770</v>
       </c>
-      <c r="D48" s="13" t="s">
+      <c r="E48" s="14" t="s">
         <v>771</v>
-      </c>
-      <c r="E48" s="14" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="49" ht="42" customHeight="1" spans="1:5">
@@ -17710,16 +17705,16 @@
         <v>737</v>
       </c>
       <c r="B49" s="12" t="s">
+        <v>772</v>
+      </c>
+      <c r="C49" s="12" t="s">
         <v>773</v>
       </c>
-      <c r="C49" s="12" t="s">
+      <c r="D49" s="13" t="s">
         <v>774</v>
       </c>
-      <c r="D49" s="13" t="s">
+      <c r="E49" s="14" t="s">
         <v>775</v>
-      </c>
-      <c r="E49" s="14" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="50" ht="42" customHeight="1" spans="1:5">
@@ -17727,16 +17722,16 @@
         <v>737</v>
       </c>
       <c r="B50" s="12" t="s">
+        <v>776</v>
+      </c>
+      <c r="C50" s="12" t="s">
         <v>777</v>
       </c>
-      <c r="C50" s="12" t="s">
+      <c r="D50" s="13" t="s">
         <v>778</v>
       </c>
-      <c r="D50" s="13" t="s">
+      <c r="E50" s="14" t="s">
         <v>779</v>
-      </c>
-      <c r="E50" s="14" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="51" ht="42" customHeight="1" spans="1:5">
@@ -17744,98 +17739,98 @@
         <v>737</v>
       </c>
       <c r="B51" s="12" t="s">
+        <v>780</v>
+      </c>
+      <c r="C51" s="12" t="s">
         <v>781</v>
       </c>
-      <c r="C51" s="12" t="s">
+      <c r="D51" s="13" t="s">
         <v>782</v>
       </c>
-      <c r="D51" s="13" t="s">
+      <c r="E51" s="14" t="s">
         <v>783</v>
-      </c>
-      <c r="E51" s="14" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="52" ht="42" customHeight="1" spans="1:5">
       <c r="A52" s="12" t="s">
+        <v>784</v>
+      </c>
+      <c r="B52" s="12" t="s">
         <v>785</v>
       </c>
-      <c r="B52" s="12" t="s">
+      <c r="C52" s="12" t="s">
         <v>786</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="D52" s="13" t="s">
         <v>787</v>
       </c>
-      <c r="D52" s="13" t="s">
+      <c r="E52" s="14" t="s">
         <v>788</v>
-      </c>
-      <c r="E52" s="14" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="53" ht="42" customHeight="1" spans="1:5">
       <c r="A53" s="12" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B53" s="12" t="s">
+        <v>789</v>
+      </c>
+      <c r="C53" s="12" t="s">
         <v>790</v>
       </c>
-      <c r="C53" s="12" t="s">
+      <c r="D53" s="13" t="s">
         <v>791</v>
       </c>
-      <c r="D53" s="13" t="s">
+      <c r="E53" s="14" t="s">
         <v>792</v>
-      </c>
-      <c r="E53" s="14" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="54" ht="42" customHeight="1" spans="1:5">
       <c r="A54" s="12" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B54" s="12" t="s">
+        <v>793</v>
+      </c>
+      <c r="C54" s="12" t="s">
         <v>794</v>
       </c>
-      <c r="C54" s="12" t="s">
+      <c r="D54" s="13" t="s">
         <v>795</v>
       </c>
-      <c r="D54" s="13" t="s">
+      <c r="E54" s="14" t="s">
         <v>796</v>
-      </c>
-      <c r="E54" s="14" t="s">
-        <v>797</v>
       </c>
     </row>
     <row r="55" ht="42" customHeight="1" spans="1:5">
       <c r="A55" s="12" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B55" s="12" t="s">
+        <v>797</v>
+      </c>
+      <c r="C55" s="12" t="s">
         <v>798</v>
-      </c>
-      <c r="C55" s="12" t="s">
-        <v>799</v>
       </c>
       <c r="D55" s="19">
         <v>8</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="56" ht="42" customHeight="1" spans="1:5">
       <c r="A56" s="12" t="s">
+        <v>800</v>
+      </c>
+      <c r="B56" s="12" t="s">
         <v>801</v>
       </c>
-      <c r="B56" s="12" t="s">
+      <c r="C56" s="12" t="s">
         <v>802</v>
       </c>
-      <c r="C56" s="12" t="s">
+      <c r="D56" s="13" t="s">
         <v>803</v>
-      </c>
-      <c r="D56" s="13" t="s">
-        <v>804</v>
       </c>
       <c r="E56" s="14" t="s">
         <v>656</v>
@@ -17843,240 +17838,240 @@
     </row>
     <row r="57" ht="42" customHeight="1" spans="1:5">
       <c r="A57" s="12" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B57" s="12" t="s">
+        <v>804</v>
+      </c>
+      <c r="C57" s="12" t="s">
         <v>805</v>
       </c>
-      <c r="C57" s="12" t="s">
+      <c r="D57" s="13" t="s">
+        <v>800</v>
+      </c>
+      <c r="E57" s="14" t="s">
         <v>806</v>
-      </c>
-      <c r="D57" s="13" t="s">
-        <v>801</v>
-      </c>
-      <c r="E57" s="14" t="s">
-        <v>807</v>
       </c>
     </row>
     <row r="58" ht="42" customHeight="1" spans="1:5">
       <c r="A58" s="12" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B58" s="12" t="s">
+        <v>807</v>
+      </c>
+      <c r="C58" s="12" t="s">
         <v>808</v>
       </c>
-      <c r="C58" s="12" t="s">
+      <c r="D58" s="13" t="s">
         <v>809</v>
       </c>
-      <c r="D58" s="13" t="s">
+      <c r="E58" s="14" t="s">
         <v>810</v>
-      </c>
-      <c r="E58" s="14" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="59" ht="42" customHeight="1" spans="1:5">
       <c r="A59" s="12" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B59" s="12" t="s">
+        <v>811</v>
+      </c>
+      <c r="C59" s="12" t="s">
         <v>812</v>
       </c>
-      <c r="C59" s="12" t="s">
+      <c r="D59" s="13" t="s">
         <v>813</v>
       </c>
-      <c r="D59" s="13" t="s">
+      <c r="E59" s="14" t="s">
         <v>814</v>
-      </c>
-      <c r="E59" s="14" t="s">
-        <v>815</v>
       </c>
     </row>
     <row r="60" ht="42" customHeight="1" spans="1:5">
       <c r="A60" s="12" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B60" s="12" t="s">
+        <v>815</v>
+      </c>
+      <c r="C60" s="12" t="s">
         <v>816</v>
       </c>
-      <c r="C60" s="12" t="s">
+      <c r="D60" s="13" t="s">
         <v>817</v>
       </c>
-      <c r="D60" s="13" t="s">
+      <c r="E60" s="14" t="s">
         <v>818</v>
-      </c>
-      <c r="E60" s="14" t="s">
-        <v>819</v>
       </c>
     </row>
     <row r="61" ht="42" customHeight="1" spans="1:5">
       <c r="A61" s="12" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B61" s="12" t="s">
+        <v>819</v>
+      </c>
+      <c r="C61" s="12" t="s">
         <v>820</v>
       </c>
-      <c r="C61" s="12" t="s">
+      <c r="D61" s="13" t="s">
         <v>821</v>
       </c>
-      <c r="D61" s="13" t="s">
-        <v>822</v>
-      </c>
       <c r="E61" s="14" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="62" ht="42" customHeight="1" spans="1:5">
       <c r="A62" s="12" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B62" s="12" t="s">
+        <v>822</v>
+      </c>
+      <c r="C62" s="12" t="s">
         <v>823</v>
       </c>
-      <c r="C62" s="12" t="s">
+      <c r="D62" s="13" t="s">
         <v>824</v>
       </c>
-      <c r="D62" s="13" t="s">
+      <c r="E62" s="14" t="s">
         <v>825</v>
-      </c>
-      <c r="E62" s="14" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="63" ht="42" customHeight="1" spans="1:5">
       <c r="A63" s="12" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B63" s="12" t="s">
+        <v>826</v>
+      </c>
+      <c r="C63" s="12" t="s">
         <v>827</v>
       </c>
-      <c r="C63" s="12" t="s">
+      <c r="D63" s="13" t="s">
         <v>828</v>
       </c>
-      <c r="D63" s="13" t="s">
-        <v>829</v>
-      </c>
       <c r="E63" s="14" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="64" ht="42" customHeight="1" spans="1:5">
       <c r="A64" s="12" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B64" s="12" t="s">
+        <v>829</v>
+      </c>
+      <c r="C64" s="12" t="s">
         <v>830</v>
       </c>
-      <c r="C64" s="12" t="s">
+      <c r="D64" s="13" t="s">
         <v>831</v>
       </c>
-      <c r="D64" s="13" t="s">
+      <c r="E64" s="14" t="s">
         <v>832</v>
-      </c>
-      <c r="E64" s="14" t="s">
-        <v>833</v>
       </c>
     </row>
     <row r="65" ht="42" customHeight="1" spans="1:5">
       <c r="A65" s="12" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B65" s="12" t="s">
+        <v>833</v>
+      </c>
+      <c r="C65" s="12" t="s">
         <v>834</v>
       </c>
-      <c r="C65" s="12" t="s">
+      <c r="D65" s="13" t="s">
         <v>835</v>
       </c>
-      <c r="D65" s="13" t="s">
-        <v>836</v>
-      </c>
       <c r="E65" s="14" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="66" ht="42" customHeight="1" spans="1:5">
       <c r="A66" s="12" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B66" s="12" t="s">
+        <v>836</v>
+      </c>
+      <c r="C66" s="12" t="s">
         <v>837</v>
       </c>
-      <c r="C66" s="12" t="s">
+      <c r="D66" s="13" t="s">
         <v>838</v>
       </c>
-      <c r="D66" s="13" t="s">
+      <c r="E66" s="14" t="s">
         <v>839</v>
-      </c>
-      <c r="E66" s="14" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="67" ht="42" customHeight="1" spans="1:5">
       <c r="A67" s="12" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B67" s="12" t="s">
+        <v>840</v>
+      </c>
+      <c r="C67" s="12" t="s">
         <v>841</v>
       </c>
-      <c r="C67" s="12" t="s">
+      <c r="D67" s="13" t="s">
         <v>842</v>
       </c>
-      <c r="D67" s="13" t="s">
-        <v>843</v>
-      </c>
       <c r="E67" s="14" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="68" ht="42" customHeight="1" spans="1:5">
       <c r="A68" s="12" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B68" s="12" t="s">
+        <v>843</v>
+      </c>
+      <c r="C68" s="12" t="s">
         <v>844</v>
       </c>
-      <c r="C68" s="12" t="s">
+      <c r="D68" s="13" t="s">
         <v>845</v>
       </c>
-      <c r="D68" s="13" t="s">
+      <c r="E68" s="14" t="s">
         <v>846</v>
-      </c>
-      <c r="E68" s="14" t="s">
-        <v>847</v>
       </c>
     </row>
     <row r="69" ht="42" customHeight="1" spans="1:5">
       <c r="A69" s="12" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B69" s="12" t="s">
+        <v>847</v>
+      </c>
+      <c r="C69" s="12" t="s">
         <v>848</v>
       </c>
-      <c r="C69" s="12" t="s">
+      <c r="D69" s="13" t="s">
         <v>849</v>
       </c>
-      <c r="D69" s="13" t="s">
-        <v>850</v>
-      </c>
       <c r="E69" s="14" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="70" ht="42" customHeight="1" spans="1:5">
       <c r="A70" s="12" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B70" s="12" t="s">
+        <v>850</v>
+      </c>
+      <c r="C70" s="12" t="s">
         <v>851</v>
       </c>
-      <c r="C70" s="12" t="s">
+      <c r="D70" s="13" t="s">
         <v>852</v>
       </c>
-      <c r="D70" s="13" t="s">
+      <c r="E70" s="14" t="s">
         <v>853</v>
-      </c>
-      <c r="E70" s="14" t="s">
-        <v>854</v>
       </c>
     </row>
   </sheetData>
@@ -18135,12 +18130,12 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:40">
       <c r="A1" s="15" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:40">
       <c r="A2" s="16" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="3" ht="8" customHeight="1" spans="1:40">
@@ -18183,13 +18178,13 @@
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:40">
       <c r="A4" s="4" t="s">
+        <v>856</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>857</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="4" t="s">
         <v>858</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>859</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>7</v>
@@ -18201,19 +18196,19 @@
         <v>654</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>666</v>
       </c>
       <c r="I4" s="4" t="s">
+        <v>860</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>861</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="K4" s="4" t="s">
         <v>862</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>863</v>
       </c>
       <c r="L4" s="4" t="s">
         <v>12</v>
@@ -18222,73 +18217,73 @@
         <v>13</v>
       </c>
       <c r="N4" s="4" t="s">
+        <v>863</v>
+      </c>
+      <c r="O4" s="4" t="s">
         <v>864</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="P4" s="4" t="s">
         <v>865</v>
       </c>
-      <c r="P4" s="4" t="s">
+      <c r="Q4" s="4" t="s">
         <v>866</v>
       </c>
-      <c r="Q4" s="4" t="s">
+      <c r="R4" s="4" t="s">
         <v>867</v>
       </c>
-      <c r="R4" s="4" t="s">
+      <c r="S4" s="4" t="s">
         <v>868</v>
       </c>
-      <c r="S4" s="4" t="s">
+      <c r="T4" s="4" t="s">
         <v>869</v>
       </c>
-      <c r="T4" s="4" t="s">
+      <c r="U4" s="4" t="s">
         <v>870</v>
       </c>
-      <c r="U4" s="4" t="s">
+      <c r="V4" s="4" t="s">
         <v>871</v>
       </c>
-      <c r="V4" s="4" t="s">
+      <c r="W4" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="W4" s="4" t="s">
+      <c r="X4" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="X4" s="4" t="s">
+      <c r="Y4" s="4" t="s">
         <v>874</v>
       </c>
-      <c r="Y4" s="4" t="s">
+      <c r="Z4" s="4" t="s">
         <v>875</v>
       </c>
-      <c r="Z4" s="4" t="s">
+      <c r="AA4" s="4" t="s">
         <v>876</v>
       </c>
-      <c r="AA4" s="4" t="s">
+      <c r="AB4" s="4" t="s">
         <v>877</v>
       </c>
-      <c r="AB4" s="4" t="s">
+      <c r="AC4" s="4" t="s">
+        <v>812</v>
+      </c>
+      <c r="AD4" s="4" t="s">
         <v>878</v>
       </c>
-      <c r="AC4" s="4" t="s">
-        <v>813</v>
-      </c>
-      <c r="AD4" s="4" t="s">
+      <c r="AE4" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="AF4" s="4" t="s">
         <v>879</v>
       </c>
-      <c r="AE4" s="4" t="s">
-        <v>821</v>
-      </c>
-      <c r="AF4" s="4" t="s">
+      <c r="AG4" s="4" t="s">
+        <v>827</v>
+      </c>
+      <c r="AH4" s="4" t="s">
         <v>880</v>
       </c>
-      <c r="AG4" s="4" t="s">
-        <v>828</v>
-      </c>
-      <c r="AH4" s="4" t="s">
+      <c r="AI4" s="4" t="s">
         <v>881</v>
       </c>
-      <c r="AI4" s="4" t="s">
+      <c r="AJ4" s="4" t="s">
         <v>882</v>
-      </c>
-      <c r="AJ4" s="4" t="s">
-        <v>883</v>
       </c>
       <c r="AK4" s="4" t="s">
         <v>22</v>
@@ -18311,106 +18306,106 @@
         <v>41</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>883</v>
+      </c>
+      <c r="D5" s="17" t="s">
         <v>884</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="E5" s="17" t="s">
         <v>885</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="F5" s="5" t="s">
         <v>886</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>887</v>
       </c>
       <c r="G5" s="17" t="s">
         <v>136</v>
       </c>
       <c r="H5" s="17" t="s">
+        <v>887</v>
+      </c>
+      <c r="I5" s="5" t="s">
         <v>888</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="J5" s="5" t="s">
         <v>889</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="K5" s="17" t="s">
         <v>890</v>
       </c>
-      <c r="K5" s="17" t="s">
+      <c r="L5" s="17" t="s">
         <v>891</v>
       </c>
-      <c r="L5" s="17" t="s">
+      <c r="M5" s="17" t="s">
         <v>892</v>
       </c>
-      <c r="M5" s="17" t="s">
+      <c r="N5" s="17" t="s">
         <v>893</v>
       </c>
-      <c r="N5" s="17" t="s">
+      <c r="O5" s="17" t="s">
         <v>894</v>
       </c>
-      <c r="O5" s="17" t="s">
+      <c r="P5" s="17" t="s">
         <v>895</v>
       </c>
-      <c r="P5" s="17" t="s">
+      <c r="Q5" s="17" t="s">
         <v>896</v>
       </c>
-      <c r="Q5" s="17" t="s">
+      <c r="R5" s="17" t="s">
         <v>897</v>
       </c>
-      <c r="R5" s="17" t="s">
+      <c r="S5" s="17" t="s">
         <v>898</v>
       </c>
-      <c r="S5" s="17" t="s">
+      <c r="T5" s="5" t="s">
         <v>899</v>
       </c>
-      <c r="T5" s="5" t="s">
+      <c r="U5" s="5" t="s">
         <v>900</v>
       </c>
-      <c r="U5" s="5" t="s">
+      <c r="V5" s="5" t="s">
         <v>901</v>
       </c>
-      <c r="V5" s="5" t="s">
+      <c r="W5" s="5" t="s">
         <v>902</v>
       </c>
-      <c r="W5" s="5" t="s">
+      <c r="X5" s="17" t="s">
         <v>903</v>
       </c>
-      <c r="X5" s="17" t="s">
+      <c r="Y5" s="5" t="s">
         <v>904</v>
       </c>
-      <c r="Y5" s="5" t="s">
+      <c r="Z5" s="5" t="s">
+        <v>803</v>
+      </c>
+      <c r="AA5" s="5" t="s">
         <v>905</v>
       </c>
-      <c r="Z5" s="5" t="s">
-        <v>804</v>
-      </c>
-      <c r="AA5" s="5" t="s">
+      <c r="AB5" s="17" t="s">
         <v>906</v>
       </c>
-      <c r="AB5" s="17" t="s">
+      <c r="AC5" s="17" t="s">
         <v>907</v>
       </c>
-      <c r="AC5" s="17" t="s">
+      <c r="AD5" s="17" t="s">
         <v>908</v>
       </c>
-      <c r="AD5" s="17" t="s">
+      <c r="AE5" s="17" t="s">
         <v>909</v>
       </c>
-      <c r="AE5" s="17" t="s">
+      <c r="AF5" s="17" t="s">
         <v>910</v>
       </c>
-      <c r="AF5" s="17" t="s">
+      <c r="AG5" s="17" t="s">
         <v>911</v>
       </c>
-      <c r="AG5" s="17" t="s">
+      <c r="AH5" s="17" t="s">
         <v>912</v>
       </c>
-      <c r="AH5" s="17" t="s">
+      <c r="AI5" s="5" t="s">
         <v>913</v>
       </c>
-      <c r="AI5" s="5" t="s">
+      <c r="AJ5" s="5" t="s">
         <v>914</v>
-      </c>
-      <c r="AJ5" s="5" t="s">
-        <v>915</v>
       </c>
       <c r="AK5" s="5" t="s">
         <v>58</v>
@@ -18433,106 +18428,106 @@
         <v>175</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>915</v>
+      </c>
+      <c r="D6" s="17" t="s">
         <v>916</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="E6" s="17" t="s">
         <v>917</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="F6" s="5" t="s">
+        <v>886</v>
+      </c>
+      <c r="G6" s="17" t="s">
         <v>918</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>887</v>
-      </c>
-      <c r="G6" s="17" t="s">
+      <c r="H6" s="17" t="s">
         <v>919</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="I6" s="5" t="s">
+        <v>888</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>889</v>
+      </c>
+      <c r="K6" s="17" t="s">
         <v>920</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>889</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>890</v>
-      </c>
-      <c r="K6" s="17" t="s">
+      <c r="L6" s="17" t="s">
         <v>921</v>
       </c>
-      <c r="L6" s="17" t="s">
+      <c r="M6" s="17" t="s">
         <v>922</v>
       </c>
-      <c r="M6" s="17" t="s">
+      <c r="N6" s="17" t="s">
+        <v>893</v>
+      </c>
+      <c r="O6" s="17" t="s">
+        <v>894</v>
+      </c>
+      <c r="P6" s="17" t="s">
+        <v>895</v>
+      </c>
+      <c r="Q6" s="17" t="s">
         <v>923</v>
       </c>
-      <c r="N6" s="17" t="s">
-        <v>894</v>
-      </c>
-      <c r="O6" s="17" t="s">
-        <v>895</v>
-      </c>
-      <c r="P6" s="17" t="s">
-        <v>896</v>
-      </c>
-      <c r="Q6" s="17" t="s">
+      <c r="R6" s="17" t="s">
+        <v>897</v>
+      </c>
+      <c r="S6" s="17" t="s">
         <v>924</v>
       </c>
-      <c r="R6" s="17" t="s">
-        <v>898</v>
-      </c>
-      <c r="S6" s="17" t="s">
+      <c r="T6" s="5" t="s">
+        <v>899</v>
+      </c>
+      <c r="U6" s="5" t="s">
         <v>925</v>
       </c>
-      <c r="T6" s="5" t="s">
-        <v>900</v>
-      </c>
-      <c r="U6" s="5" t="s">
+      <c r="V6" s="5" t="s">
+        <v>901</v>
+      </c>
+      <c r="W6" s="5" t="s">
+        <v>902</v>
+      </c>
+      <c r="X6" s="17" t="s">
         <v>926</v>
       </c>
-      <c r="V6" s="5" t="s">
-        <v>902</v>
-      </c>
-      <c r="W6" s="5" t="s">
-        <v>903</v>
-      </c>
-      <c r="X6" s="17" t="s">
+      <c r="Y6" s="5" t="s">
+        <v>904</v>
+      </c>
+      <c r="Z6" s="5" t="s">
+        <v>803</v>
+      </c>
+      <c r="AA6" s="5" t="s">
         <v>927</v>
       </c>
-      <c r="Y6" s="5" t="s">
-        <v>905</v>
-      </c>
-      <c r="Z6" s="5" t="s">
-        <v>804</v>
-      </c>
-      <c r="AA6" s="5" t="s">
+      <c r="AB6" s="17" t="s">
+        <v>906</v>
+      </c>
+      <c r="AC6" s="17" t="s">
         <v>928</v>
       </c>
-      <c r="AB6" s="17" t="s">
-        <v>907</v>
-      </c>
-      <c r="AC6" s="17" t="s">
-        <v>929</v>
-      </c>
       <c r="AD6" s="17" t="s">
+        <v>908</v>
+      </c>
+      <c r="AE6" s="17" t="s">
         <v>909</v>
       </c>
-      <c r="AE6" s="17" t="s">
+      <c r="AF6" s="17" t="s">
         <v>910</v>
       </c>
-      <c r="AF6" s="17" t="s">
+      <c r="AG6" s="17" t="s">
         <v>911</v>
       </c>
-      <c r="AG6" s="17" t="s">
+      <c r="AH6" s="5" t="s">
         <v>912</v>
       </c>
-      <c r="AH6" s="5" t="s">
+      <c r="AI6" s="5" t="s">
         <v>913</v>
       </c>
-      <c r="AI6" s="5" t="s">
+      <c r="AJ6" s="5" t="s">
         <v>914</v>
-      </c>
-      <c r="AJ6" s="5" t="s">
-        <v>915</v>
       </c>
       <c r="AK6" s="5" t="s">
         <v>58</v>
@@ -18555,106 +18550,106 @@
         <v>281</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>929</v>
+      </c>
+      <c r="D7" s="17" t="s">
         <v>930</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="E7" s="17" t="s">
         <v>931</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="F7" s="5" t="s">
+        <v>886</v>
+      </c>
+      <c r="G7" s="17" t="s">
         <v>932</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>887</v>
-      </c>
-      <c r="G7" s="17" t="s">
+      <c r="H7" s="17" t="s">
         <v>933</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="I7" s="5" t="s">
+        <v>888</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>889</v>
+      </c>
+      <c r="K7" s="17" t="s">
         <v>934</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>889</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>890</v>
-      </c>
-      <c r="K7" s="17" t="s">
+      <c r="L7" s="17" t="s">
         <v>935</v>
       </c>
-      <c r="L7" s="17" t="s">
+      <c r="M7" s="17" t="s">
         <v>936</v>
       </c>
-      <c r="M7" s="17" t="s">
+      <c r="N7" s="17" t="s">
+        <v>893</v>
+      </c>
+      <c r="O7" s="17" t="s">
+        <v>894</v>
+      </c>
+      <c r="P7" s="17" t="s">
+        <v>895</v>
+      </c>
+      <c r="Q7" s="17" t="s">
         <v>937</v>
       </c>
-      <c r="N7" s="17" t="s">
-        <v>894</v>
-      </c>
-      <c r="O7" s="17" t="s">
-        <v>895</v>
-      </c>
-      <c r="P7" s="17" t="s">
-        <v>896</v>
-      </c>
-      <c r="Q7" s="17" t="s">
+      <c r="R7" s="17" t="s">
         <v>938</v>
       </c>
-      <c r="R7" s="17" t="s">
+      <c r="S7" s="17" t="s">
         <v>939</v>
       </c>
-      <c r="S7" s="17" t="s">
+      <c r="T7" s="5" t="s">
+        <v>899</v>
+      </c>
+      <c r="U7" s="5" t="s">
         <v>940</v>
       </c>
-      <c r="T7" s="5" t="s">
-        <v>900</v>
-      </c>
-      <c r="U7" s="5" t="s">
+      <c r="V7" s="5" t="s">
+        <v>901</v>
+      </c>
+      <c r="W7" s="5" t="s">
+        <v>902</v>
+      </c>
+      <c r="X7" s="17" t="s">
         <v>941</v>
       </c>
-      <c r="V7" s="5" t="s">
-        <v>902</v>
-      </c>
-      <c r="W7" s="5" t="s">
-        <v>903</v>
-      </c>
-      <c r="X7" s="17" t="s">
+      <c r="Y7" s="5" t="s">
+        <v>904</v>
+      </c>
+      <c r="Z7" s="5" t="s">
+        <v>803</v>
+      </c>
+      <c r="AA7" s="5" t="s">
         <v>942</v>
       </c>
-      <c r="Y7" s="5" t="s">
-        <v>905</v>
-      </c>
-      <c r="Z7" s="5" t="s">
-        <v>804</v>
-      </c>
-      <c r="AA7" s="5" t="s">
+      <c r="AB7" s="17" t="s">
+        <v>906</v>
+      </c>
+      <c r="AC7" s="17" t="s">
         <v>943</v>
       </c>
-      <c r="AB7" s="17" t="s">
-        <v>907</v>
-      </c>
-      <c r="AC7" s="17" t="s">
-        <v>944</v>
-      </c>
       <c r="AD7" s="17" t="s">
+        <v>908</v>
+      </c>
+      <c r="AE7" s="17" t="s">
         <v>909</v>
       </c>
-      <c r="AE7" s="17" t="s">
+      <c r="AF7" s="17" t="s">
         <v>910</v>
       </c>
-      <c r="AF7" s="17" t="s">
+      <c r="AG7" s="17" t="s">
         <v>911</v>
       </c>
-      <c r="AG7" s="17" t="s">
+      <c r="AH7" s="5" t="s">
         <v>912</v>
       </c>
-      <c r="AH7" s="5" t="s">
+      <c r="AI7" s="5" t="s">
         <v>913</v>
       </c>
-      <c r="AI7" s="5" t="s">
+      <c r="AJ7" s="5" t="s">
         <v>914</v>
-      </c>
-      <c r="AJ7" s="5" t="s">
-        <v>915</v>
       </c>
       <c r="AK7" s="5" t="s">
         <v>58</v>
@@ -18677,106 +18672,106 @@
         <v>386</v>
       </c>
       <c r="C8" s="5" t="s">
+        <v>944</v>
+      </c>
+      <c r="D8" s="17" t="s">
         <v>945</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="E8" s="17" t="s">
         <v>946</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="F8" s="5" t="s">
+        <v>886</v>
+      </c>
+      <c r="G8" s="17" t="s">
         <v>947</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>887</v>
-      </c>
-      <c r="G8" s="17" t="s">
+      <c r="H8" s="17" t="s">
         <v>948</v>
       </c>
-      <c r="H8" s="17" t="s">
+      <c r="I8" s="5" t="s">
+        <v>888</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>889</v>
+      </c>
+      <c r="K8" s="17" t="s">
         <v>949</v>
       </c>
-      <c r="I8" s="5" t="s">
-        <v>889</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>890</v>
-      </c>
-      <c r="K8" s="17" t="s">
+      <c r="L8" s="17" t="s">
         <v>950</v>
       </c>
-      <c r="L8" s="17" t="s">
+      <c r="M8" s="17" t="s">
         <v>951</v>
       </c>
-      <c r="M8" s="17" t="s">
+      <c r="N8" s="17" t="s">
+        <v>893</v>
+      </c>
+      <c r="O8" s="17" t="s">
+        <v>894</v>
+      </c>
+      <c r="P8" s="17" t="s">
+        <v>895</v>
+      </c>
+      <c r="Q8" s="17" t="s">
         <v>952</v>
       </c>
-      <c r="N8" s="17" t="s">
-        <v>894</v>
-      </c>
-      <c r="O8" s="17" t="s">
-        <v>895</v>
-      </c>
-      <c r="P8" s="17" t="s">
-        <v>896</v>
-      </c>
-      <c r="Q8" s="17" t="s">
+      <c r="R8" s="17" t="s">
+        <v>897</v>
+      </c>
+      <c r="S8" s="17" t="s">
+        <v>939</v>
+      </c>
+      <c r="T8" s="5" t="s">
+        <v>899</v>
+      </c>
+      <c r="U8" s="5" t="s">
         <v>953</v>
       </c>
-      <c r="R8" s="17" t="s">
-        <v>898</v>
-      </c>
-      <c r="S8" s="17" t="s">
-        <v>940</v>
-      </c>
-      <c r="T8" s="5" t="s">
-        <v>900</v>
-      </c>
-      <c r="U8" s="5" t="s">
+      <c r="V8" s="5" t="s">
+        <v>901</v>
+      </c>
+      <c r="W8" s="5" t="s">
+        <v>902</v>
+      </c>
+      <c r="X8" s="17" t="s">
         <v>954</v>
       </c>
-      <c r="V8" s="5" t="s">
-        <v>902</v>
-      </c>
-      <c r="W8" s="5" t="s">
-        <v>903</v>
-      </c>
-      <c r="X8" s="17" t="s">
+      <c r="Y8" s="5" t="s">
+        <v>904</v>
+      </c>
+      <c r="Z8" s="5" t="s">
+        <v>803</v>
+      </c>
+      <c r="AA8" s="5" t="s">
         <v>955</v>
       </c>
-      <c r="Y8" s="5" t="s">
-        <v>905</v>
-      </c>
-      <c r="Z8" s="5" t="s">
-        <v>804</v>
-      </c>
-      <c r="AA8" s="5" t="s">
+      <c r="AB8" s="17" t="s">
+        <v>906</v>
+      </c>
+      <c r="AC8" s="17" t="s">
         <v>956</v>
       </c>
-      <c r="AB8" s="17" t="s">
-        <v>907</v>
-      </c>
-      <c r="AC8" s="17" t="s">
-        <v>957</v>
-      </c>
       <c r="AD8" s="17" t="s">
+        <v>908</v>
+      </c>
+      <c r="AE8" s="17" t="s">
         <v>909</v>
       </c>
-      <c r="AE8" s="17" t="s">
+      <c r="AF8" s="17" t="s">
         <v>910</v>
       </c>
-      <c r="AF8" s="17" t="s">
+      <c r="AG8" s="17" t="s">
         <v>911</v>
       </c>
-      <c r="AG8" s="17" t="s">
+      <c r="AH8" s="5" t="s">
         <v>912</v>
       </c>
-      <c r="AH8" s="5" t="s">
+      <c r="AI8" s="5" t="s">
         <v>913</v>
       </c>
-      <c r="AI8" s="5" t="s">
+      <c r="AJ8" s="5" t="s">
         <v>914</v>
-      </c>
-      <c r="AJ8" s="5" t="s">
-        <v>915</v>
       </c>
       <c r="AK8" s="5" t="s">
         <v>58</v>
@@ -18799,106 +18794,106 @@
         <v>494</v>
       </c>
       <c r="C9" s="5" t="s">
+        <v>957</v>
+      </c>
+      <c r="D9" s="17" t="s">
         <v>958</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="E9" s="17" t="s">
         <v>959</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="F9" s="5" t="s">
+        <v>886</v>
+      </c>
+      <c r="G9" s="17" t="s">
         <v>960</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>887</v>
-      </c>
-      <c r="G9" s="17" t="s">
+      <c r="H9" s="17" t="s">
         <v>961</v>
       </c>
-      <c r="H9" s="17" t="s">
+      <c r="I9" s="5" t="s">
+        <v>888</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>889</v>
+      </c>
+      <c r="K9" s="17" t="s">
         <v>962</v>
       </c>
-      <c r="I9" s="5" t="s">
-        <v>889</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>890</v>
-      </c>
-      <c r="K9" s="17" t="s">
+      <c r="L9" s="17" t="s">
         <v>963</v>
       </c>
-      <c r="L9" s="17" t="s">
+      <c r="M9" s="17" t="s">
         <v>964</v>
       </c>
-      <c r="M9" s="17" t="s">
+      <c r="N9" s="17" t="s">
+        <v>893</v>
+      </c>
+      <c r="O9" s="17" t="s">
+        <v>894</v>
+      </c>
+      <c r="P9" s="17" t="s">
+        <v>895</v>
+      </c>
+      <c r="Q9" s="17" t="s">
         <v>965</v>
       </c>
-      <c r="N9" s="17" t="s">
-        <v>894</v>
-      </c>
-      <c r="O9" s="17" t="s">
-        <v>895</v>
-      </c>
-      <c r="P9" s="17" t="s">
-        <v>896</v>
-      </c>
-      <c r="Q9" s="17" t="s">
+      <c r="R9" s="17" t="s">
+        <v>897</v>
+      </c>
+      <c r="S9" s="17" t="s">
+        <v>924</v>
+      </c>
+      <c r="T9" s="5" t="s">
+        <v>899</v>
+      </c>
+      <c r="U9" s="5" t="s">
         <v>966</v>
       </c>
-      <c r="R9" s="17" t="s">
-        <v>898</v>
-      </c>
-      <c r="S9" s="17" t="s">
-        <v>925</v>
-      </c>
-      <c r="T9" s="5" t="s">
-        <v>900</v>
-      </c>
-      <c r="U9" s="5" t="s">
+      <c r="V9" s="5" t="s">
+        <v>901</v>
+      </c>
+      <c r="W9" s="5" t="s">
+        <v>902</v>
+      </c>
+      <c r="X9" s="17" t="s">
         <v>967</v>
       </c>
-      <c r="V9" s="5" t="s">
-        <v>902</v>
-      </c>
-      <c r="W9" s="5" t="s">
-        <v>903</v>
-      </c>
-      <c r="X9" s="17" t="s">
+      <c r="Y9" s="5" t="s">
+        <v>904</v>
+      </c>
+      <c r="Z9" s="5" t="s">
+        <v>803</v>
+      </c>
+      <c r="AA9" s="5" t="s">
         <v>968</v>
       </c>
-      <c r="Y9" s="5" t="s">
-        <v>905</v>
-      </c>
-      <c r="Z9" s="5" t="s">
-        <v>804</v>
-      </c>
-      <c r="AA9" s="5" t="s">
+      <c r="AB9" s="17" t="s">
+        <v>906</v>
+      </c>
+      <c r="AC9" s="17" t="s">
         <v>969</v>
       </c>
-      <c r="AB9" s="17" t="s">
-        <v>907</v>
-      </c>
-      <c r="AC9" s="17" t="s">
-        <v>970</v>
-      </c>
       <c r="AD9" s="17" t="s">
+        <v>908</v>
+      </c>
+      <c r="AE9" s="17" t="s">
         <v>909</v>
       </c>
-      <c r="AE9" s="17" t="s">
+      <c r="AF9" s="17" t="s">
         <v>910</v>
       </c>
-      <c r="AF9" s="17" t="s">
+      <c r="AG9" s="17" t="s">
         <v>911</v>
       </c>
-      <c r="AG9" s="17" t="s">
+      <c r="AH9" s="5" t="s">
         <v>912</v>
       </c>
-      <c r="AH9" s="5" t="s">
+      <c r="AI9" s="5" t="s">
         <v>913</v>
       </c>
-      <c r="AI9" s="5" t="s">
+      <c r="AJ9" s="5" t="s">
         <v>914</v>
-      </c>
-      <c r="AJ9" s="5" t="s">
-        <v>915</v>
       </c>
       <c r="AK9" s="5" t="s">
         <v>58</v>
@@ -19795,7 +19790,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -19805,7 +19800,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6">
       <c r="A2" s="9" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -19823,10 +19818,10 @@
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:6">
       <c r="A4" s="11" t="s">
+        <v>972</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>973</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>974</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>601</v>
@@ -19846,10 +19841,10 @@
         <v>632</v>
       </c>
       <c r="B5" s="12" t="s">
+        <v>974</v>
+      </c>
+      <c r="C5" s="12" t="s">
         <v>975</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>976</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>6</v>
@@ -19858,7 +19853,7 @@
         <v>632</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:6">
@@ -19866,7 +19861,7 @@
         <v>632</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>637</v>
@@ -19875,10 +19870,10 @@
         <v>7</v>
       </c>
       <c r="E6" s="13" t="s">
+        <v>977</v>
+      </c>
+      <c r="F6" s="14" t="s">
         <v>978</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>979</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:6">
@@ -19886,7 +19881,7 @@
         <v>632</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>640</v>
@@ -19895,10 +19890,10 @@
         <v>8</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:6">
@@ -19906,7 +19901,7 @@
         <v>632</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>653</v>
@@ -19915,10 +19910,10 @@
         <v>654</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:6">
@@ -19926,19 +19921,19 @@
         <v>632</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C9" s="12" t="s">
+        <v>981</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>859</v>
+      </c>
+      <c r="E9" s="13" t="s">
         <v>982</v>
       </c>
-      <c r="D9" s="12" t="s">
-        <v>860</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>983</v>
-      </c>
       <c r="F9" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:6">
@@ -19946,19 +19941,19 @@
         <v>632</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>665</v>
       </c>
       <c r="D10" s="12" t="s">
+        <v>983</v>
+      </c>
+      <c r="E10" s="13" t="s">
         <v>984</v>
       </c>
-      <c r="E10" s="13" t="s">
-        <v>985</v>
-      </c>
       <c r="F10" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:6">
@@ -19966,19 +19961,19 @@
         <v>632</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C11" s="12" t="s">
+        <v>985</v>
+      </c>
+      <c r="D11" s="12" t="s">
         <v>986</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="E11" s="13" t="s">
         <v>987</v>
       </c>
-      <c r="E11" s="13" t="s">
-        <v>988</v>
-      </c>
       <c r="F11" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:6">
@@ -19986,19 +19981,19 @@
         <v>632</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C12" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="D12" s="12" t="s">
         <v>989</v>
       </c>
-      <c r="D12" s="12" t="s">
-        <v>990</v>
-      </c>
       <c r="E12" s="13" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:6">
@@ -20006,19 +20001,19 @@
         <v>632</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C13" s="12" t="s">
+        <v>990</v>
+      </c>
+      <c r="D13" s="12" t="s">
         <v>991</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>992</v>
       </c>
       <c r="E13" s="13" t="s">
         <v>685</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:6">
@@ -20026,19 +20021,19 @@
         <v>632</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C14" s="12" t="s">
+        <v>992</v>
+      </c>
+      <c r="D14" s="12" t="s">
         <v>993</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="E14" s="13" t="s">
         <v>994</v>
       </c>
-      <c r="E14" s="13" t="s">
-        <v>995</v>
-      </c>
       <c r="F14" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:6">
@@ -20046,19 +20041,19 @@
         <v>632</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C15" s="12" t="s">
+        <v>995</v>
+      </c>
+      <c r="D15" s="12" t="s">
         <v>996</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="E15" s="13" t="s">
         <v>997</v>
       </c>
-      <c r="E15" s="13" t="s">
-        <v>998</v>
-      </c>
       <c r="F15" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:6">
@@ -20066,19 +20061,19 @@
         <v>632</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C16" s="12" t="s">
+        <v>998</v>
+      </c>
+      <c r="D16" s="12" t="s">
         <v>999</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="E16" s="13" t="s">
         <v>1000</v>
       </c>
-      <c r="E16" s="13" t="s">
-        <v>1001</v>
-      </c>
       <c r="F16" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:6">
@@ -20086,19 +20081,19 @@
         <v>632</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C17" s="12" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D17" s="12" t="s">
         <v>1002</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="E17" s="13" t="s">
         <v>1003</v>
       </c>
-      <c r="E17" s="13" t="s">
-        <v>1004</v>
-      </c>
       <c r="F17" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:6">
@@ -20106,19 +20101,19 @@
         <v>632</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C18" s="12" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D18" s="12" t="s">
         <v>1005</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="E18" s="13" t="s">
         <v>1006</v>
       </c>
-      <c r="E18" s="13" t="s">
-        <v>1007</v>
-      </c>
       <c r="F18" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:6">
@@ -20126,19 +20121,19 @@
         <v>632</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C19" s="12" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D19" s="12" t="s">
         <v>1008</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="E19" s="13" t="s">
         <v>1009</v>
       </c>
-      <c r="E19" s="13" t="s">
-        <v>1010</v>
-      </c>
       <c r="F19" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:6">
@@ -20146,19 +20141,19 @@
         <v>632</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C20" s="12" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D20" s="12" t="s">
         <v>1011</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="E20" s="13" t="s">
         <v>1012</v>
       </c>
-      <c r="E20" s="13" t="s">
-        <v>1013</v>
-      </c>
       <c r="F20" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:6">
@@ -20166,19 +20161,19 @@
         <v>632</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C21" s="12" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D21" s="12" t="s">
         <v>1014</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="E21" s="13" t="s">
         <v>1015</v>
       </c>
-      <c r="E21" s="13" t="s">
-        <v>1016</v>
-      </c>
       <c r="F21" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:6">
@@ -20186,19 +20181,19 @@
         <v>632</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C22" s="12" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D22" s="12" t="s">
         <v>1017</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="E22" s="13" t="s">
         <v>1018</v>
       </c>
-      <c r="E22" s="13" t="s">
-        <v>1019</v>
-      </c>
       <c r="F22" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:6">
@@ -20206,19 +20201,19 @@
         <v>632</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C23" s="12" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D23" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="E23" s="13" t="s">
         <v>1021</v>
       </c>
-      <c r="E23" s="13" t="s">
-        <v>1022</v>
-      </c>
       <c r="F23" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:6">
@@ -20226,19 +20221,19 @@
         <v>632</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C24" s="12" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D24" s="12" t="s">
         <v>1023</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="E24" s="13" t="s">
         <v>1024</v>
       </c>
-      <c r="E24" s="13" t="s">
-        <v>1025</v>
-      </c>
       <c r="F24" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:6">
@@ -20246,19 +20241,19 @@
         <v>632</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C25" s="12" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D25" s="12" t="s">
         <v>1026</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="E25" s="13" t="s">
         <v>1027</v>
       </c>
-      <c r="E25" s="13" t="s">
-        <v>1028</v>
-      </c>
       <c r="F25" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:6">
@@ -20266,19 +20261,19 @@
         <v>632</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C26" s="12" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D26" s="12" t="s">
         <v>1029</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="E26" s="13" t="s">
         <v>1030</v>
       </c>
-      <c r="E26" s="13" t="s">
-        <v>1031</v>
-      </c>
       <c r="F26" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="27" ht="48" customHeight="1" spans="1:6">
@@ -20286,19 +20281,19 @@
         <v>632</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C27" s="12" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D27" s="12" t="s">
         <v>1032</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>1033</v>
       </c>
       <c r="E27" s="13" t="s">
         <v>730</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="28" ht="48" customHeight="1" spans="1:6">
@@ -20306,19 +20301,19 @@
         <v>632</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C28" s="12" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D28" s="12" t="s">
         <v>1034</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="E28" s="13" t="s">
         <v>1035</v>
       </c>
-      <c r="E28" s="13" t="s">
-        <v>1036</v>
-      </c>
       <c r="F28" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="29" ht="48" customHeight="1" spans="1:6">
@@ -20326,19 +20321,19 @@
         <v>632</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C29" s="12" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D29" s="12" t="s">
         <v>1037</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="E29" s="13" t="s">
         <v>1038</v>
       </c>
-      <c r="E29" s="13" t="s">
-        <v>1039</v>
-      </c>
       <c r="F29" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="30" ht="48" customHeight="1" spans="1:6">
@@ -20346,10 +20341,10 @@
         <v>635</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D30" s="12" t="s">
         <v>6</v>
@@ -20358,7 +20353,7 @@
         <v>635</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="31" ht="48" customHeight="1" spans="1:6">
@@ -20366,7 +20361,7 @@
         <v>635</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>637</v>
@@ -20375,10 +20370,10 @@
         <v>7</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="32" ht="48" customHeight="1" spans="1:6">
@@ -20386,7 +20381,7 @@
         <v>635</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C32" s="12" t="s">
         <v>640</v>
@@ -20395,10 +20390,10 @@
         <v>8</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="33" ht="48" customHeight="1" spans="1:6">
@@ -20406,7 +20401,7 @@
         <v>635</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>653</v>
@@ -20415,10 +20410,10 @@
         <v>654</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="34" ht="48" customHeight="1" spans="1:6">
@@ -20426,19 +20421,19 @@
         <v>635</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="35" ht="48" customHeight="1" spans="1:6">
@@ -20446,19 +20441,19 @@
         <v>635</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>665</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="36" ht="48" customHeight="1" spans="1:6">
@@ -20466,19 +20461,19 @@
         <v>635</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C36" s="12" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D36" s="12" t="s">
         <v>1045</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="E36" s="13" t="s">
         <v>1046</v>
       </c>
-      <c r="E36" s="13" t="s">
-        <v>1047</v>
-      </c>
       <c r="F36" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="37" ht="48" customHeight="1" spans="1:6">
@@ -20486,19 +20481,19 @@
         <v>635</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C37" s="12" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D37" s="12" t="s">
         <v>1048</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="E37" s="13" t="s">
         <v>1049</v>
       </c>
-      <c r="E37" s="13" t="s">
-        <v>1050</v>
-      </c>
       <c r="F37" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="38" ht="48" customHeight="1" spans="1:6">
@@ -20506,19 +20501,19 @@
         <v>635</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C38" s="12" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D38" s="12" t="s">
         <v>1051</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="E38" s="13" t="s">
         <v>1052</v>
       </c>
-      <c r="E38" s="13" t="s">
-        <v>1053</v>
-      </c>
       <c r="F38" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="39" ht="48" customHeight="1" spans="1:6">
@@ -20526,19 +20521,19 @@
         <v>635</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C39" s="12" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D39" s="12" t="s">
         <v>1054</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="E39" s="13" t="s">
         <v>1055</v>
       </c>
-      <c r="E39" s="13" t="s">
-        <v>1056</v>
-      </c>
       <c r="F39" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="40" ht="48" customHeight="1" spans="1:6">
@@ -20546,19 +20541,19 @@
         <v>635</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C40" s="12" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D40" s="12" t="s">
         <v>1057</v>
       </c>
-      <c r="D40" s="12" t="s">
+      <c r="E40" s="13" t="s">
         <v>1058</v>
       </c>
-      <c r="E40" s="13" t="s">
-        <v>1059</v>
-      </c>
       <c r="F40" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="41" ht="48" customHeight="1" spans="1:6">
@@ -20566,19 +20561,19 @@
         <v>635</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C41" s="12" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D41" s="12" t="s">
         <v>1060</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="E41" s="13" t="s">
         <v>1061</v>
       </c>
-      <c r="E41" s="13" t="s">
-        <v>1062</v>
-      </c>
       <c r="F41" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="42" ht="48" customHeight="1" spans="1:6">
@@ -20586,19 +20581,19 @@
         <v>635</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C42" s="12" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D42" s="12" t="s">
         <v>1063</v>
       </c>
-      <c r="D42" s="12" t="s">
+      <c r="E42" s="13" t="s">
         <v>1064</v>
       </c>
-      <c r="E42" s="13" t="s">
-        <v>1065</v>
-      </c>
       <c r="F42" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="43" ht="48" customHeight="1" spans="1:6">
@@ -20606,19 +20601,19 @@
         <v>635</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C43" s="12" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D43" s="12" t="s">
         <v>1066</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="E43" s="13" t="s">
         <v>1067</v>
       </c>
-      <c r="E43" s="13" t="s">
-        <v>1068</v>
-      </c>
       <c r="F43" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="44" ht="48" customHeight="1" spans="1:6">
@@ -20626,19 +20621,19 @@
         <v>635</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C44" s="12" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D44" s="12" t="s">
         <v>1069</v>
       </c>
-      <c r="D44" s="12" t="s">
+      <c r="E44" s="13" t="s">
         <v>1070</v>
       </c>
-      <c r="E44" s="13" t="s">
-        <v>1071</v>
-      </c>
       <c r="F44" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="45" ht="48" customHeight="1" spans="1:6">
@@ -20646,19 +20641,19 @@
         <v>635</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C45" s="12" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D45" s="12" t="s">
         <v>1072</v>
       </c>
-      <c r="D45" s="12" t="s">
+      <c r="E45" s="13" t="s">
         <v>1073</v>
       </c>
-      <c r="E45" s="13" t="s">
-        <v>1074</v>
-      </c>
       <c r="F45" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="46" ht="48" customHeight="1" spans="1:6">
@@ -20666,47 +20661,47 @@
         <v>635</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C46" s="12" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D46" s="12" t="s">
         <v>1075</v>
       </c>
-      <c r="D46" s="12" t="s">
-        <v>1076</v>
-      </c>
       <c r="E46" s="13" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="47" ht="48" customHeight="1" spans="1:6">
       <c r="A47" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B47" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="B47" s="12" t="s">
-        <v>1078</v>
-      </c>
       <c r="C47" s="12" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D47" s="12" t="s">
         <v>6</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="F47" s="14" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="48" ht="48" customHeight="1" spans="1:6">
       <c r="A48" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B48" s="12" t="s">
         <v>1077</v>
-      </c>
-      <c r="B48" s="12" t="s">
-        <v>1078</v>
       </c>
       <c r="C48" s="12" t="s">
         <v>637</v>
@@ -20715,18 +20710,18 @@
         <v>7</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="49" ht="48" customHeight="1" spans="1:6">
       <c r="A49" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B49" s="12" t="s">
         <v>1077</v>
-      </c>
-      <c r="B49" s="12" t="s">
-        <v>1078</v>
       </c>
       <c r="C49" s="12" t="s">
         <v>640</v>
@@ -20735,18 +20730,18 @@
         <v>8</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="50" ht="48" customHeight="1" spans="1:6">
       <c r="A50" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B50" s="12" t="s">
         <v>1077</v>
-      </c>
-      <c r="B50" s="12" t="s">
-        <v>1078</v>
       </c>
       <c r="C50" s="12" t="s">
         <v>653</v>
@@ -20755,598 +20750,598 @@
         <v>654</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="51" ht="48" customHeight="1" spans="1:6">
       <c r="A51" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B51" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="B51" s="12" t="s">
-        <v>1078</v>
-      </c>
       <c r="C51" s="12" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="52" ht="48" customHeight="1" spans="1:6">
       <c r="A52" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B52" s="12" t="s">
         <v>1077</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>1078</v>
       </c>
       <c r="C52" s="12" t="s">
         <v>665</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="53" ht="48" customHeight="1" spans="1:6">
       <c r="A53" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B53" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="B53" s="12" t="s">
-        <v>1078</v>
-      </c>
       <c r="C53" s="12" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D53" s="12" t="s">
         <v>1082</v>
       </c>
-      <c r="D53" s="12" t="s">
+      <c r="E53" s="13" t="s">
         <v>1083</v>
       </c>
-      <c r="E53" s="13" t="s">
-        <v>1084</v>
-      </c>
       <c r="F53" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="54" ht="48" customHeight="1" spans="1:6">
       <c r="A54" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B54" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="B54" s="12" t="s">
-        <v>1078</v>
-      </c>
       <c r="C54" s="12" t="s">
+        <v>985</v>
+      </c>
+      <c r="D54" s="12" t="s">
         <v>986</v>
       </c>
-      <c r="D54" s="12" t="s">
-        <v>987</v>
-      </c>
       <c r="E54" s="13" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="55" ht="48" customHeight="1" spans="1:6">
       <c r="A55" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B55" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="B55" s="12" t="s">
-        <v>1078</v>
-      </c>
       <c r="C55" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="D55" s="12" t="s">
         <v>989</v>
       </c>
-      <c r="D55" s="12" t="s">
-        <v>990</v>
-      </c>
       <c r="E55" s="13" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="56" ht="48" customHeight="1" spans="1:6">
       <c r="A56" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B56" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="B56" s="12" t="s">
-        <v>1078</v>
-      </c>
       <c r="C56" s="12" t="s">
+        <v>990</v>
+      </c>
+      <c r="D56" s="12" t="s">
         <v>991</v>
       </c>
-      <c r="D56" s="12" t="s">
-        <v>992</v>
-      </c>
       <c r="E56" s="13" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="57" ht="48" customHeight="1" spans="1:6">
       <c r="A57" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B57" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="B57" s="12" t="s">
-        <v>1078</v>
-      </c>
       <c r="C57" s="12" t="s">
+        <v>992</v>
+      </c>
+      <c r="D57" s="12" t="s">
         <v>993</v>
       </c>
-      <c r="D57" s="12" t="s">
-        <v>994</v>
-      </c>
       <c r="E57" s="13" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="58" ht="48" customHeight="1" spans="1:6">
       <c r="A58" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B58" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="B58" s="12" t="s">
-        <v>1078</v>
-      </c>
       <c r="C58" s="12" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D58" s="12" t="s">
         <v>1089</v>
       </c>
-      <c r="D58" s="12" t="s">
+      <c r="E58" s="13" t="s">
         <v>1090</v>
       </c>
-      <c r="E58" s="13" t="s">
-        <v>1091</v>
-      </c>
       <c r="F58" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="59" ht="48" customHeight="1" spans="1:6">
       <c r="A59" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B59" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="B59" s="12" t="s">
-        <v>1078</v>
-      </c>
       <c r="C59" s="12" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D59" s="12" t="s">
         <v>1092</v>
       </c>
-      <c r="D59" s="12" t="s">
+      <c r="E59" s="13" t="s">
         <v>1093</v>
       </c>
-      <c r="E59" s="13" t="s">
-        <v>1094</v>
-      </c>
       <c r="F59" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="60" ht="48" customHeight="1" spans="1:6">
       <c r="A60" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B60" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="B60" s="12" t="s">
-        <v>1078</v>
-      </c>
       <c r="C60" s="12" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D60" s="12" t="s">
         <v>1095</v>
       </c>
-      <c r="D60" s="12" t="s">
+      <c r="E60" s="13" t="s">
         <v>1096</v>
       </c>
-      <c r="E60" s="13" t="s">
-        <v>1097</v>
-      </c>
       <c r="F60" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="61" ht="48" customHeight="1" spans="1:6">
       <c r="A61" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B61" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="B61" s="12" t="s">
-        <v>1078</v>
-      </c>
       <c r="C61" s="12" t="s">
+        <v>998</v>
+      </c>
+      <c r="D61" s="12" t="s">
         <v>999</v>
       </c>
-      <c r="D61" s="12" t="s">
-        <v>1000</v>
-      </c>
       <c r="E61" s="13" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="62" ht="48" customHeight="1" spans="1:6">
       <c r="A62" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B62" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="B62" s="12" t="s">
-        <v>1078</v>
-      </c>
       <c r="C62" s="12" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D62" s="12" t="s">
         <v>1002</v>
       </c>
-      <c r="D62" s="12" t="s">
-        <v>1003</v>
-      </c>
       <c r="E62" s="13" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="63" ht="48" customHeight="1" spans="1:6">
       <c r="A63" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B63" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="B63" s="12" t="s">
-        <v>1078</v>
-      </c>
       <c r="C63" s="12" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D63" s="12" t="s">
         <v>1005</v>
       </c>
-      <c r="D63" s="12" t="s">
-        <v>1006</v>
-      </c>
       <c r="E63" s="13" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="F63" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="64" ht="48" customHeight="1" spans="1:6">
       <c r="A64" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B64" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="B64" s="12" t="s">
-        <v>1078</v>
-      </c>
       <c r="C64" s="12" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D64" s="12" t="s">
         <v>1011</v>
       </c>
-      <c r="D64" s="12" t="s">
-        <v>1012</v>
-      </c>
       <c r="E64" s="13" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="65" ht="48" customHeight="1" spans="1:6">
       <c r="A65" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B65" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="B65" s="12" t="s">
-        <v>1078</v>
-      </c>
       <c r="C65" s="12" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D65" s="12" t="s">
         <v>1102</v>
       </c>
-      <c r="D65" s="12" t="s">
+      <c r="E65" s="13" t="s">
         <v>1103</v>
       </c>
-      <c r="E65" s="13" t="s">
-        <v>1104</v>
-      </c>
       <c r="F65" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="66" ht="48" customHeight="1" spans="1:6">
       <c r="A66" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B66" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="B66" s="12" t="s">
-        <v>1078</v>
-      </c>
       <c r="C66" s="12" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D66" s="12" t="s">
         <v>1105</v>
-      </c>
-      <c r="D66" s="12" t="s">
-        <v>1106</v>
       </c>
       <c r="E66" s="13" t="s">
         <v>693</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="67" ht="48" customHeight="1" spans="1:6">
       <c r="A67" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B67" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="B67" s="12" t="s">
-        <v>1078</v>
-      </c>
       <c r="C67" s="12" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D67" s="12" t="s">
         <v>1017</v>
       </c>
-      <c r="D67" s="12" t="s">
-        <v>1018</v>
-      </c>
       <c r="E67" s="13" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="F67" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="68" ht="48" customHeight="1" spans="1:6">
       <c r="A68" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B68" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="B68" s="12" t="s">
-        <v>1078</v>
-      </c>
       <c r="C68" s="12" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D68" s="12" t="s">
         <v>1108</v>
       </c>
-      <c r="D68" s="12" t="s">
+      <c r="E68" s="13" t="s">
         <v>1109</v>
       </c>
-      <c r="E68" s="13" t="s">
-        <v>1110</v>
-      </c>
       <c r="F68" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="69" ht="48" customHeight="1" spans="1:6">
       <c r="A69" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B69" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="B69" s="12" t="s">
-        <v>1078</v>
-      </c>
       <c r="C69" s="12" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D69" s="12" t="s">
         <v>1111</v>
-      </c>
-      <c r="D69" s="12" t="s">
-        <v>1112</v>
       </c>
       <c r="E69" s="13" t="s">
         <v>693</v>
       </c>
       <c r="F69" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="70" ht="48" customHeight="1" spans="1:6">
       <c r="A70" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B70" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="B70" s="12" t="s">
-        <v>1078</v>
-      </c>
       <c r="C70" s="12" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D70" s="12" t="s">
         <v>1113</v>
       </c>
-      <c r="D70" s="12" t="s">
+      <c r="E70" s="13" t="s">
         <v>1114</v>
       </c>
-      <c r="E70" s="13" t="s">
-        <v>1115</v>
-      </c>
       <c r="F70" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="71" ht="48" customHeight="1" spans="1:6">
       <c r="A71" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B71" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="B71" s="12" t="s">
-        <v>1078</v>
-      </c>
       <c r="C71" s="12" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D71" s="12" t="s">
         <v>1116</v>
       </c>
-      <c r="D71" s="12" t="s">
+      <c r="E71" s="13" t="s">
         <v>1117</v>
       </c>
-      <c r="E71" s="13" t="s">
-        <v>1118</v>
-      </c>
       <c r="F71" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="72" ht="48" customHeight="1" spans="1:6">
       <c r="A72" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B72" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="B72" s="12" t="s">
-        <v>1078</v>
-      </c>
       <c r="C72" s="12" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D72" s="12" t="s">
         <v>1119</v>
-      </c>
-      <c r="D72" s="12" t="s">
-        <v>1120</v>
       </c>
       <c r="E72" s="13" t="s">
         <v>693</v>
       </c>
       <c r="F72" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="73" ht="48" customHeight="1" spans="1:6">
       <c r="A73" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B73" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="B73" s="12" t="s">
-        <v>1078</v>
-      </c>
       <c r="C73" s="12" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D73" s="12" t="s">
         <v>1121</v>
       </c>
-      <c r="D73" s="12" t="s">
+      <c r="E73" s="13" t="s">
         <v>1122</v>
       </c>
-      <c r="E73" s="13" t="s">
-        <v>1123</v>
-      </c>
       <c r="F73" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="74" ht="48" customHeight="1" spans="1:6">
       <c r="A74" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B74" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="B74" s="12" t="s">
-        <v>1078</v>
-      </c>
       <c r="C74" s="12" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D74" s="12" t="s">
         <v>1124</v>
       </c>
-      <c r="D74" s="12" t="s">
+      <c r="E74" s="13" t="s">
         <v>1125</v>
       </c>
-      <c r="E74" s="13" t="s">
-        <v>1126</v>
-      </c>
       <c r="F74" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="75" ht="48" customHeight="1" spans="1:6">
       <c r="A75" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B75" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="B75" s="12" t="s">
-        <v>1078</v>
-      </c>
       <c r="C75" s="12" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D75" s="12" t="s">
         <v>1127</v>
-      </c>
-      <c r="D75" s="12" t="s">
-        <v>1128</v>
       </c>
       <c r="E75" s="13" t="s">
         <v>693</v>
       </c>
       <c r="F75" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="76" ht="48" customHeight="1" spans="1:6">
       <c r="A76" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B76" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="B76" s="12" t="s">
-        <v>1078</v>
-      </c>
       <c r="C76" s="12" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D76" s="12" t="s">
         <v>1129</v>
       </c>
-      <c r="D76" s="12" t="s">
+      <c r="E76" s="13" t="s">
         <v>1130</v>
       </c>
-      <c r="E76" s="13" t="s">
-        <v>1131</v>
-      </c>
       <c r="F76" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="77" ht="48" customHeight="1" spans="1:6">
       <c r="A77" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B77" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="B77" s="12" t="s">
-        <v>1078</v>
-      </c>
       <c r="C77" s="12" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D77" s="12" t="s">
         <v>1132</v>
       </c>
-      <c r="D77" s="12" t="s">
+      <c r="E77" s="13" t="s">
         <v>1133</v>
       </c>
-      <c r="E77" s="13" t="s">
-        <v>1134</v>
-      </c>
       <c r="F77" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="78" ht="48" customHeight="1" spans="1:6">
       <c r="A78" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B78" s="12" t="s">
         <v>1077</v>
       </c>
-      <c r="B78" s="12" t="s">
-        <v>1078</v>
-      </c>
       <c r="C78" s="12" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D78" s="12" t="s">
         <v>1135</v>
       </c>
-      <c r="D78" s="12" t="s">
+      <c r="E78" s="13" t="s">
         <v>1136</v>
       </c>
-      <c r="E78" s="13" t="s">
-        <v>1137</v>
-      </c>
       <c r="F78" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="79" ht="48" customHeight="1" spans="1:6">
       <c r="A79" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B79" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="B79" s="12" t="s">
-        <v>1139</v>
-      </c>
       <c r="C79" s="12" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D79" s="12" t="s">
         <v>6</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="F79" s="14" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="80" ht="48" customHeight="1" spans="1:6">
       <c r="A80" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B80" s="12" t="s">
         <v>1138</v>
-      </c>
-      <c r="B80" s="12" t="s">
-        <v>1139</v>
       </c>
       <c r="C80" s="12" t="s">
         <v>637</v>
@@ -21355,18 +21350,18 @@
         <v>7</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="F80" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="81" ht="48" customHeight="1" spans="1:6">
       <c r="A81" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B81" s="12" t="s">
         <v>1138</v>
-      </c>
-      <c r="B81" s="12" t="s">
-        <v>1139</v>
       </c>
       <c r="C81" s="12" t="s">
         <v>640</v>
@@ -21375,18 +21370,18 @@
         <v>8</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="F81" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="82" ht="48" customHeight="1" spans="1:6">
       <c r="A82" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B82" s="12" t="s">
         <v>1138</v>
-      </c>
-      <c r="B82" s="12" t="s">
-        <v>1139</v>
       </c>
       <c r="C82" s="12" t="s">
         <v>653</v>
@@ -21395,598 +21390,598 @@
         <v>654</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="F82" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="83" ht="48" customHeight="1" spans="1:6">
       <c r="A83" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B83" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="B83" s="12" t="s">
-        <v>1139</v>
-      </c>
       <c r="C83" s="12" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="F83" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="84" ht="48" customHeight="1" spans="1:6">
       <c r="A84" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B84" s="12" t="s">
         <v>1138</v>
-      </c>
-      <c r="B84" s="12" t="s">
-        <v>1139</v>
       </c>
       <c r="C84" s="12" t="s">
         <v>665</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="F84" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="85" ht="48" customHeight="1" spans="1:6">
       <c r="A85" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B85" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="B85" s="12" t="s">
-        <v>1139</v>
-      </c>
       <c r="C85" s="12" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D85" s="12" t="s">
         <v>1082</v>
       </c>
-      <c r="D85" s="12" t="s">
+      <c r="E85" s="13" t="s">
         <v>1083</v>
       </c>
-      <c r="E85" s="13" t="s">
-        <v>1084</v>
-      </c>
       <c r="F85" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="86" ht="48" customHeight="1" spans="1:6">
       <c r="A86" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B86" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="B86" s="12" t="s">
-        <v>1139</v>
-      </c>
       <c r="C86" s="12" t="s">
+        <v>985</v>
+      </c>
+      <c r="D86" s="12" t="s">
         <v>986</v>
       </c>
-      <c r="D86" s="12" t="s">
-        <v>987</v>
-      </c>
       <c r="E86" s="13" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="F86" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="87" ht="48" customHeight="1" spans="1:6">
       <c r="A87" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B87" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="B87" s="12" t="s">
-        <v>1139</v>
-      </c>
       <c r="C87" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="D87" s="12" t="s">
         <v>989</v>
       </c>
-      <c r="D87" s="12" t="s">
-        <v>990</v>
-      </c>
       <c r="E87" s="13" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="F87" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="88" ht="48" customHeight="1" spans="1:6">
       <c r="A88" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B88" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="B88" s="12" t="s">
-        <v>1139</v>
-      </c>
       <c r="C88" s="12" t="s">
+        <v>990</v>
+      </c>
+      <c r="D88" s="12" t="s">
         <v>991</v>
       </c>
-      <c r="D88" s="12" t="s">
-        <v>992</v>
-      </c>
       <c r="E88" s="13" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="F88" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="89" ht="48" customHeight="1" spans="1:6">
       <c r="A89" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B89" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="B89" s="12" t="s">
-        <v>1139</v>
-      </c>
       <c r="C89" s="12" t="s">
+        <v>992</v>
+      </c>
+      <c r="D89" s="12" t="s">
         <v>993</v>
       </c>
-      <c r="D89" s="12" t="s">
-        <v>994</v>
-      </c>
       <c r="E89" s="13" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="F89" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="90" ht="48" customHeight="1" spans="1:6">
       <c r="A90" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B90" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="B90" s="12" t="s">
-        <v>1139</v>
-      </c>
       <c r="C90" s="12" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D90" s="12" t="s">
         <v>1089</v>
       </c>
-      <c r="D90" s="12" t="s">
+      <c r="E90" s="13" t="s">
         <v>1090</v>
       </c>
-      <c r="E90" s="13" t="s">
-        <v>1091</v>
-      </c>
       <c r="F90" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="91" ht="48" customHeight="1" spans="1:6">
       <c r="A91" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B91" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="B91" s="12" t="s">
-        <v>1139</v>
-      </c>
       <c r="C91" s="12" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D91" s="12" t="s">
         <v>1092</v>
       </c>
-      <c r="D91" s="12" t="s">
-        <v>1093</v>
-      </c>
       <c r="E91" s="13" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="F91" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="92" ht="48" customHeight="1" spans="1:6">
       <c r="A92" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B92" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="B92" s="12" t="s">
-        <v>1139</v>
-      </c>
       <c r="C92" s="12" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D92" s="12" t="s">
         <v>1095</v>
       </c>
-      <c r="D92" s="12" t="s">
-        <v>1096</v>
-      </c>
       <c r="E92" s="13" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="F92" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="93" ht="48" customHeight="1" spans="1:6">
       <c r="A93" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B93" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="B93" s="12" t="s">
-        <v>1139</v>
-      </c>
       <c r="C93" s="12" t="s">
+        <v>998</v>
+      </c>
+      <c r="D93" s="12" t="s">
         <v>999</v>
       </c>
-      <c r="D93" s="12" t="s">
-        <v>1000</v>
-      </c>
       <c r="E93" s="13" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="F93" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="94" ht="48" customHeight="1" spans="1:6">
       <c r="A94" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B94" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="B94" s="12" t="s">
-        <v>1139</v>
-      </c>
       <c r="C94" s="12" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D94" s="12" t="s">
         <v>1002</v>
       </c>
-      <c r="D94" s="12" t="s">
-        <v>1003</v>
-      </c>
       <c r="E94" s="13" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="F94" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="95" ht="48" customHeight="1" spans="1:6">
       <c r="A95" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B95" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="B95" s="12" t="s">
-        <v>1139</v>
-      </c>
       <c r="C95" s="12" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D95" s="12" t="s">
         <v>1005</v>
-      </c>
-      <c r="D95" s="12" t="s">
-        <v>1006</v>
       </c>
       <c r="E95" s="13" t="s">
         <v>693</v>
       </c>
       <c r="F95" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="96" ht="48" customHeight="1" spans="1:6">
       <c r="A96" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B96" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="B96" s="12" t="s">
-        <v>1139</v>
-      </c>
       <c r="C96" s="12" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D96" s="12" t="s">
         <v>1011</v>
       </c>
-      <c r="D96" s="12" t="s">
-        <v>1012</v>
-      </c>
       <c r="E96" s="13" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F96" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="97" ht="48" customHeight="1" spans="1:6">
       <c r="A97" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B97" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="B97" s="12" t="s">
-        <v>1139</v>
-      </c>
       <c r="C97" s="12" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D97" s="12" t="s">
         <v>1102</v>
       </c>
-      <c r="D97" s="12" t="s">
-        <v>1103</v>
-      </c>
       <c r="E97" s="13" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="F97" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="98" ht="48" customHeight="1" spans="1:6">
       <c r="A98" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B98" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="B98" s="12" t="s">
-        <v>1139</v>
-      </c>
       <c r="C98" s="12" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D98" s="12" t="s">
         <v>1105</v>
-      </c>
-      <c r="D98" s="12" t="s">
-        <v>1106</v>
       </c>
       <c r="E98" s="13" t="s">
         <v>693</v>
       </c>
       <c r="F98" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="99" ht="48" customHeight="1" spans="1:6">
       <c r="A99" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B99" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="B99" s="12" t="s">
-        <v>1139</v>
-      </c>
       <c r="C99" s="12" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D99" s="12" t="s">
         <v>1017</v>
       </c>
-      <c r="D99" s="12" t="s">
-        <v>1018</v>
-      </c>
       <c r="E99" s="13" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="F99" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="100" ht="48" customHeight="1" spans="1:6">
       <c r="A100" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B100" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="B100" s="12" t="s">
-        <v>1139</v>
-      </c>
       <c r="C100" s="12" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D100" s="12" t="s">
         <v>1108</v>
       </c>
-      <c r="D100" s="12" t="s">
-        <v>1109</v>
-      </c>
       <c r="E100" s="13" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="F100" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="101" ht="48" customHeight="1" spans="1:6">
       <c r="A101" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B101" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="B101" s="12" t="s">
-        <v>1139</v>
-      </c>
       <c r="C101" s="12" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D101" s="12" t="s">
         <v>1111</v>
-      </c>
-      <c r="D101" s="12" t="s">
-        <v>1112</v>
       </c>
       <c r="E101" s="13" t="s">
         <v>693</v>
       </c>
       <c r="F101" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="102" ht="48" customHeight="1" spans="1:6">
       <c r="A102" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B102" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="B102" s="12" t="s">
-        <v>1139</v>
-      </c>
       <c r="C102" s="12" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D102" s="12" t="s">
         <v>1113</v>
       </c>
-      <c r="D102" s="12" t="s">
-        <v>1114</v>
-      </c>
       <c r="E102" s="13" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="F102" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="103" ht="48" customHeight="1" spans="1:6">
       <c r="A103" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B103" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="B103" s="12" t="s">
-        <v>1139</v>
-      </c>
       <c r="C103" s="12" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D103" s="12" t="s">
         <v>1116</v>
       </c>
-      <c r="D103" s="12" t="s">
-        <v>1117</v>
-      </c>
       <c r="E103" s="13" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="F103" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="104" ht="48" customHeight="1" spans="1:6">
       <c r="A104" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B104" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="B104" s="12" t="s">
-        <v>1139</v>
-      </c>
       <c r="C104" s="12" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D104" s="12" t="s">
         <v>1119</v>
-      </c>
-      <c r="D104" s="12" t="s">
-        <v>1120</v>
       </c>
       <c r="E104" s="13" t="s">
         <v>693</v>
       </c>
       <c r="F104" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="105" ht="48" customHeight="1" spans="1:6">
       <c r="A105" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B105" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="B105" s="12" t="s">
-        <v>1139</v>
-      </c>
       <c r="C105" s="12" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D105" s="12" t="s">
         <v>1121</v>
       </c>
-      <c r="D105" s="12" t="s">
-        <v>1122</v>
-      </c>
       <c r="E105" s="13" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="F105" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="106" ht="48" customHeight="1" spans="1:6">
       <c r="A106" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B106" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="B106" s="12" t="s">
-        <v>1139</v>
-      </c>
       <c r="C106" s="12" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D106" s="12" t="s">
         <v>1124</v>
       </c>
-      <c r="D106" s="12" t="s">
-        <v>1125</v>
-      </c>
       <c r="E106" s="13" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="F106" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="107" ht="48" customHeight="1" spans="1:6">
       <c r="A107" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B107" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="B107" s="12" t="s">
-        <v>1139</v>
-      </c>
       <c r="C107" s="12" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D107" s="12" t="s">
         <v>1127</v>
-      </c>
-      <c r="D107" s="12" t="s">
-        <v>1128</v>
       </c>
       <c r="E107" s="13" t="s">
         <v>693</v>
       </c>
       <c r="F107" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="108" ht="48" customHeight="1" spans="1:6">
       <c r="A108" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B108" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="B108" s="12" t="s">
-        <v>1139</v>
-      </c>
       <c r="C108" s="12" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D108" s="12" t="s">
         <v>1129</v>
       </c>
-      <c r="D108" s="12" t="s">
-        <v>1130</v>
-      </c>
       <c r="E108" s="13" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="F108" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="109" ht="48" customHeight="1" spans="1:6">
       <c r="A109" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B109" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="B109" s="12" t="s">
-        <v>1139</v>
-      </c>
       <c r="C109" s="12" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D109" s="12" t="s">
         <v>1132</v>
       </c>
-      <c r="D109" s="12" t="s">
-        <v>1133</v>
-      </c>
       <c r="E109" s="13" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="F109" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="110" ht="48" customHeight="1" spans="1:6">
       <c r="A110" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B110" s="12" t="s">
         <v>1138</v>
       </c>
-      <c r="B110" s="12" t="s">
-        <v>1139</v>
-      </c>
       <c r="C110" s="12" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D110" s="12" t="s">
         <v>1135</v>
-      </c>
-      <c r="D110" s="12" t="s">
-        <v>1136</v>
       </c>
       <c r="E110" s="13" t="s">
         <v>693</v>
       </c>
       <c r="F110" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="111" ht="48" customHeight="1" spans="1:6">
       <c r="A111" s="12" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B111" s="12" t="s">
         <v>1161</v>
       </c>
-      <c r="B111" s="12" t="s">
-        <v>1162</v>
-      </c>
       <c r="C111" s="12" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D111" s="12" t="s">
         <v>6</v>
       </c>
       <c r="E111" s="13" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="F111" s="14" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="112" ht="48" customHeight="1" spans="1:6">
       <c r="A112" s="12" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B112" s="12" t="s">
         <v>1161</v>
-      </c>
-      <c r="B112" s="12" t="s">
-        <v>1162</v>
       </c>
       <c r="C112" s="12" t="s">
         <v>637</v>
@@ -21995,18 +21990,18 @@
         <v>7</v>
       </c>
       <c r="E112" s="13" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="F112" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="113" ht="48" customHeight="1" spans="1:6">
       <c r="A113" s="12" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B113" s="12" t="s">
         <v>1161</v>
-      </c>
-      <c r="B113" s="12" t="s">
-        <v>1162</v>
       </c>
       <c r="C113" s="12" t="s">
         <v>640</v>
@@ -22015,18 +22010,18 @@
         <v>8</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="F113" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="114" ht="48" customHeight="1" spans="1:6">
       <c r="A114" s="12" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B114" s="12" t="s">
         <v>1161</v>
-      </c>
-      <c r="B114" s="12" t="s">
-        <v>1162</v>
       </c>
       <c r="C114" s="12" t="s">
         <v>653</v>
@@ -22035,70 +22030,70 @@
         <v>654</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="F114" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="115" ht="48" customHeight="1" spans="1:6">
       <c r="A115" s="12" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B115" s="12" t="s">
         <v>1161</v>
       </c>
-      <c r="B115" s="12" t="s">
-        <v>1162</v>
-      </c>
       <c r="C115" s="12" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="D115" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="F115" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="116" ht="48" customHeight="1" spans="1:6">
       <c r="A116" s="12" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B116" s="12" t="s">
         <v>1161</v>
-      </c>
-      <c r="B116" s="12" t="s">
-        <v>1162</v>
       </c>
       <c r="C116" s="12" t="s">
         <v>665</v>
       </c>
       <c r="D116" s="12" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="E116" s="13" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="F116" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="117" ht="48" customHeight="1" spans="1:6">
       <c r="A117" s="12" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B117" s="12" t="s">
         <v>1161</v>
       </c>
-      <c r="B117" s="12" t="s">
-        <v>1162</v>
-      </c>
       <c r="C117" s="12" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D117" s="12" t="s">
         <v>1168</v>
       </c>
-      <c r="D117" s="12" t="s">
+      <c r="E117" s="13" t="s">
         <v>1169</v>
       </c>
-      <c r="E117" s="13" t="s">
-        <v>1170</v>
-      </c>
       <c r="F117" s="14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
   </sheetData>
@@ -22127,7 +22122,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:5">
       <c r="A1" s="2" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -22136,7 +22131,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:5">
       <c r="A2" s="9" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -22169,33 +22164,33 @@
     </row>
     <row r="5" ht="42" customHeight="1" spans="1:5">
       <c r="A5" s="12" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>1173</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="C5" s="12" t="s">
         <v>1174</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="D5" s="13" t="s">
         <v>1175</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="E5" s="14" t="s">
         <v>1176</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>1177</v>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1" spans="1:5">
       <c r="A6" s="12" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D6" s="13" t="s">
         <v>1178</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>1054</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>1055</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>1179</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>693</v>
@@ -22203,33 +22198,33 @@
     </row>
     <row r="7" ht="42" customHeight="1" spans="1:5">
       <c r="A7" s="12" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>1178</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="D7" s="13" t="s">
         <v>1180</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>1179</v>
-      </c>
-      <c r="D7" s="13" t="s">
+      <c r="E7" s="14" t="s">
         <v>1181</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>1182</v>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1" spans="1:5">
       <c r="A8" s="12" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B8" s="12" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>1057</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>1058</v>
-      </c>
       <c r="D8" s="13" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="E8" s="14" t="s">
         <v>693</v>
@@ -22237,33 +22232,33 @@
     </row>
     <row r="9" ht="42" customHeight="1" spans="1:5">
       <c r="A9" s="12" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B9" s="12" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>1184</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="D9" s="13" t="s">
         <v>1185</v>
       </c>
-      <c r="D9" s="13" t="s">
-        <v>1186</v>
-      </c>
       <c r="E9" s="14" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1" spans="1:5">
       <c r="A10" s="12" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B10" s="12" t="s">
         <v>1187</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="C10" s="12" t="s">
         <v>1188</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="D10" s="13" t="s">
         <v>1189</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>1190</v>
       </c>
       <c r="E10" s="14" t="s">
         <v>693</v>
@@ -22271,16 +22266,16 @@
     </row>
     <row r="11" ht="42" customHeight="1" spans="1:5">
       <c r="A11" s="12" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="B11" s="12" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C11" s="12" t="s">
         <v>1191</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="D11" s="13" t="s">
         <v>1192</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>1193</v>
       </c>
       <c r="E11" s="14" t="s">
         <v>693</v>
@@ -22288,13 +22283,13 @@
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:5">
       <c r="A12" s="12" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B12" s="12" t="s">
         <v>1194</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="C12" s="12" t="s">
         <v>1195</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>1196</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>632</v>
@@ -22305,13 +22300,13 @@
     </row>
     <row r="13" ht="42" customHeight="1" spans="1:5">
       <c r="A13" s="12" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B13" s="12" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>1197</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>1198</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>635</v>
@@ -22322,16 +22317,16 @@
     </row>
     <row r="14" ht="42" customHeight="1" spans="1:5">
       <c r="A14" s="12" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B14" s="12" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C14" s="12" t="s">
         <v>1199</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>1200</v>
-      </c>
       <c r="D14" s="13" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="E14" s="14" t="s">
         <v>693</v>
@@ -22339,16 +22334,16 @@
     </row>
     <row r="15" ht="42" customHeight="1" spans="1:5">
       <c r="A15" s="12" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B15" s="12" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>1201</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>1202</v>
-      </c>
       <c r="D15" s="13" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E15" s="14" t="s">
         <v>693</v>
@@ -22356,16 +22351,16 @@
     </row>
     <row r="16" ht="42" customHeight="1" spans="1:5">
       <c r="A16" s="12" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B16" s="12" t="s">
         <v>1203</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="C16" s="12" t="s">
         <v>1204</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="D16" s="13" t="s">
         <v>1205</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>1206</v>
       </c>
       <c r="E16" s="14" t="s">
         <v>693</v>
@@ -22373,16 +22368,16 @@
     </row>
     <row r="17" ht="42" customHeight="1" spans="1:5">
       <c r="A17" s="12" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B17" s="12" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C17" s="12" t="s">
         <v>1207</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="D17" s="13" t="s">
         <v>1208</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>1209</v>
       </c>
       <c r="E17" s="14" t="s">
         <v>693</v>
@@ -22390,16 +22385,16 @@
     </row>
     <row r="18" ht="42" customHeight="1" spans="1:5">
       <c r="A18" s="12" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B18" s="12" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C18" s="12" t="s">
         <v>1210</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="D18" s="13" t="s">
         <v>1211</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>1212</v>
       </c>
       <c r="E18" s="14" t="s">
         <v>693</v>
@@ -22407,16 +22402,16 @@
     </row>
     <row r="19" ht="42" customHeight="1" spans="1:5">
       <c r="A19" s="12" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B19" s="12" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C19" s="12" t="s">
         <v>1213</v>
       </c>
-      <c r="C19" s="12" t="s">
-        <v>1214</v>
-      </c>
       <c r="D19" s="13" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="E19" s="14" t="s">
         <v>693</v>
@@ -22446,7 +22441,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:8">
       <c r="A1" s="2" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -22458,7 +22453,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -22470,50 +22465,50 @@
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:8">
       <c r="A4" s="4" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>1217</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>1218</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:8">
       <c r="A5" s="5" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>1219</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>1220</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:8">
       <c r="A6" s="5" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>1221</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>1222</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:8">
       <c r="A7" s="5" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>1223</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>1224</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:8">
       <c r="A8" s="5" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>1225</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>1226</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:8">
       <c r="A9" s="5" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>1227</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>1228</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:8">
@@ -22521,10 +22516,10 @@
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:8">
       <c r="A11" s="4" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>1229</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>1230</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:8">
@@ -22532,7 +22527,7 @@
         <v>22</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:8">
@@ -22540,47 +22535,47 @@
         <v>23</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:8">
       <c r="A14" s="5" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>1233</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>1234</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:8">
       <c r="A15" s="5" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>1235</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:8">
       <c r="A16" s="5" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>1237</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2">
       <c r="A17" s="5" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>1239</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>1240</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:2">
       <c r="A18" s="5" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>1241</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>1242</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:2">
@@ -22588,10 +22583,10 @@
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:2">
       <c r="A20" s="4" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>1243</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>1244</v>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:2">
@@ -22599,7 +22594,7 @@
         <v>1</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:2">
@@ -22607,7 +22602,7 @@
         <v>2</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:2">
@@ -22615,7 +22610,7 @@
         <v>3</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1" spans="1:2">
@@ -22623,7 +22618,7 @@
         <v>4</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:2">
@@ -22631,7 +22626,7 @@
         <v>5</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1" spans="1:2">
@@ -22639,7 +22634,7 @@
         <v>6</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1" spans="1:2">
@@ -22647,7 +22642,7 @@
         <v>7</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1" spans="1:2">
@@ -22655,7 +22650,7 @@
         <v>8</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1" spans="1:2">
@@ -22663,7 +22658,7 @@
         <v>9</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1" spans="1:2">
@@ -22671,7 +22666,7 @@
         <v>10</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1" spans="1:2">
@@ -22679,26 +22674,26 @@
     </row>
     <row r="32" ht="28" customHeight="1" spans="1:2">
       <c r="A32" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>1255</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>1256</v>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1" spans="1:2">
       <c r="A33" s="5" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B33" s="7" t="s">
         <v>1257</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>1258</v>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1" spans="1:2">
       <c r="A34" s="8" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B34" s="7" t="s">
         <v>1259</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>1260</v>
       </c>
     </row>
   </sheetData>

--- a/顶奢_整站资料批量编辑.xlsx
+++ b/顶奢_整站资料批量编辑.xlsx
@@ -3437,7 +3437,7 @@
     <t>首屏简介</t>
   </si>
   <si>
-    <t>欢迎来到顶奢商务模特外围工作室！我们的服务覆盖北京、上海、广州、深圳、杭州等全国一二线城市及热门城市，国外英法美日韩泰国新加坡等热门国家，为您提供需要的外围商务模特。</t>
+    <t>欢迎来到顶奢商务模特外围工作室！我们的服务覆盖北京、上海、广州、深圳、杭州等全国一二线城市及热门城市，国外英法美日韩泰国新加坡等热门国家，为您提供需要的外围商务模特预约。</t>
   </si>
   <si>
     <t>主标题下方文字</t>

--- a/顶奢_整站资料批量编辑.xlsx
+++ b/顶奢_整站资料批量编辑.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16455" activeTab="1"/>
+    <workbookView windowHeight="16455" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="资料批量编辑" sheetId="1" r:id="rId1"/>
@@ -269,7 +269,7 @@
     <t>上海外围模特Lisa</t>
   </si>
   <si>
-    <t>上海外围｜上海朝阳区外围｜上海外围上门</t>
+    <t>上海外围｜上海高端外围｜上海外围上门</t>
   </si>
   <si>
     <t>176高百醇  纯欲天花板 </t>
@@ -326,7 +326,7 @@
     </r>
   </si>
   <si>
-    <t>上海外围｜上海朝阳区外围上门｜上海上门服务</t>
+    <t>上海外围｜上海外围预约｜上海上门服务</t>
   </si>
   <si>
     <t>身高/175
@@ -622,7 +622,7 @@
     <t>上海外围模特丸子</t>
   </si>
   <si>
-    <t>上海外围｜上海外围女｜上海高端模特预约</t>
+    <t>上海外围｜上海外围女｜上海学生上门</t>
   </si>
   <si>
     <t>05 175  真胸c </t>
@@ -706,7 +706,7 @@
     <t>上海外围模特蝶语</t>
   </si>
   <si>
-    <t>上海外围｜上海外围经纪｜上海外围资源</t>
+    <t>上海外围｜上海外围经纪人｜上海外围资源</t>
   </si>
   <si>
     <t>🐻34c 170cm 43kg 05年</t>
@@ -790,7 +790,7 @@
     <t>上海外围模特西西</t>
   </si>
   <si>
-    <t>上海外围｜上海女大学生外围｜上海高端外围</t>
+    <t>上海外围｜上海大学生外围｜上海高端外围</t>
   </si>
   <si>
     <r>
@@ -1037,7 +1037,7 @@
     <t>广州外围模特喵喵</t>
   </si>
   <si>
-    <t>广州外围｜广州朝阳区外围｜广州外围上门</t>
+    <t>广州外围｜广州天河外围｜广州外围上门</t>
   </si>
   <si>
     <t>175cm 47KG 胸D 03年 </t>
@@ -1070,7 +1070,7 @@
     <t>广州外围模特凯莉</t>
   </si>
   <si>
-    <t>广州外围｜广州朝阳区外围上门｜广州上门服务</t>
+    <t>广州外围｜广州高端外围｜广州上门服务</t>
   </si>
   <si>
     <t>身高178 胸c</t>
@@ -1681,7 +1681,7 @@
     <t>深圳外围模特汤晨</t>
   </si>
   <si>
-    <t>深圳外围｜深圳朝阳区外围｜深圳外围上门</t>
+    <t>深圳外围｜深圳福田区外围｜深圳外围上门</t>
   </si>
   <si>
     <r>
@@ -1766,7 +1766,7 @@
     <t>深圳外围模特鹿鹿</t>
   </si>
   <si>
-    <t>深圳外围｜深圳朝阳区外围上门｜深圳上门服务</t>
+    <t>深圳外围｜深圳南山区外围｜深圳上门服务</t>
   </si>
   <si>
     <t>身高/净高170 体重/95 胸围/E 年龄/02</t>
@@ -2593,7 +2593,7 @@
     <t>杭州外围模特楚楚</t>
   </si>
   <si>
-    <t>杭州外围｜杭州朝阳区外围｜杭州外围上门</t>
+    <t>杭州外围｜杭州拱墅区外围｜杭州外围上门</t>
   </si>
   <si>
     <t>170 D   ╸真 实 03</t>
@@ -2731,7 +2731,7 @@
     </r>
   </si>
   <si>
-    <t>杭州外围｜杭州朝阳区外围上门｜杭州上门服务</t>
+    <t>杭州外围｜杭州高端外围｜杭州上门服务</t>
   </si>
   <si>
     <t>04年  171cm C</t>
@@ -3120,7 +3120,7 @@
     <t>杭州外围模特周周</t>
   </si>
   <si>
-    <t>杭州外围｜杭州女大学生外围｜杭州高端外围</t>
+    <t>杭州外围｜杭州同城上门｜杭州高端外围</t>
   </si>
   <si>
     <t>172D</t>
@@ -4091,7 +4091,7 @@
     <t>上海外围｜上海模特预约｜上海高端外围｜顶奢</t>
   </si>
   <si>
-    <t>顶奢上海资源库，集中展示上海城市精选外围模特资料、独立图片、视频、风格介绍与相关推荐。</t>
+    <t>顶奢上海外围，集中展示上海精选外围模特，上海高端外围，上海外围女资料、独立图片、视频、风格介绍与相关推荐。</t>
   </si>
   <si>
     <t>CITY COLLECTION</t>
@@ -4187,7 +4187,7 @@
     <t>广州外围｜广州模特预约｜广州高端外围｜顶奢</t>
   </si>
   <si>
-    <t>顶奢广州资源库，浏览广州城市精选外围模特资料、专属图片、视频介绍及相关城市内容。</t>
+    <t>顶奢广州外围，集中展示广州精选外围模特，广州高端外围，广州外围女资料、独立图片、视频、风格介绍与相关推荐。</t>
   </si>
   <si>
     <t>广州外围模特</t>
@@ -4229,7 +4229,7 @@
     <t>深圳外围｜深圳模特预约｜深圳高端外围｜顶奢</t>
   </si>
   <si>
-    <t>顶奢深圳资源库，查看深圳现代城市精选外围模特资料、图片展示、视频位置与相关推荐。</t>
+    <t>顶奢深圳外围，集中展示深圳精选外围模特，深圳高端外围，深圳外围女资料、独立图片、视频、风格介绍与相关推荐。</t>
   </si>
   <si>
     <t>深圳外围模特</t>
@@ -4274,7 +4274,7 @@
     <t>北京外围｜北京模特预约｜北京高端外围｜顶奢</t>
   </si>
   <si>
-    <t>顶奢北京资源库，汇总北京城市精选外围模特资料、独立图片、视频、专题说明和相关推荐。</t>
+    <t>顶奢北京外围，集中展示北京精选外围模特，北京高端外围，北京外围女资料、独立图片、视频、风格介绍与相关推荐。</t>
   </si>
   <si>
     <t>北京外围模特</t>
@@ -4313,7 +4313,7 @@
     <t>杭州外围｜杭州模特预约｜杭州高端外围｜顶奢</t>
   </si>
   <si>
-    <t>顶奢杭州资源库，浏览杭州城市精选外围模特资料、独立图片说明、视频信息、独立说明与站内推荐。</t>
+    <t>顶奢杭州外围，集中展示杭州精选外围模特，杭州高端外围，杭州外围女资料、独立图片、视频、风格介绍与相关推荐。</t>
   </si>
   <si>
     <t>杭州外围模特</t>
@@ -4961,7 +4961,7 @@
     <t>页脚品牌说明</t>
   </si>
   <si>
-    <t>顶奢平台专业为社会名流高端人士提供高端靠谱商务外围服务，找全球伴游、兼职外围女模特、高端商务陪同、极品外围女请与我们联系。资源覆盖国内一二线城市以及海外各大主流城市，规范化服务流程，注重客户隐私保护。</t>
+    <t>顶奢平台专业为社会名流高端人士提供高端靠谱商务外围服务，商务伴游、兼职外围女模特、高端商务陪同、极品外围女请与我们联系。资源覆盖国内一二线城市以及海外各大主流城市，规范化服务流程，注重客户隐私保护。</t>
   </si>
   <si>
     <t>全站每个页面都会显示</t>

--- a/顶奢_整站资料批量编辑.xlsx
+++ b/顶奢_整站资料批量编辑.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16455" activeTab="4"/>
+    <workbookView windowHeight="16455" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="资料批量编辑" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2523" uniqueCount="1260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2523" uniqueCount="1261">
   <si>
     <t>顶奢 · 整站资料批量编辑</t>
   </si>
@@ -3359,7 +3359,7 @@
     <t>seo_description</t>
   </si>
   <si>
-    <t>上海、广州、深圳、北京、杭州城市资料展示与独立详情页。</t>
+    <t>上海外围、广州外围、深圳外围、北京外围、杭州外围城市资料展示与独立详情页。</t>
   </si>
   <si>
     <t>首页搜索摘要</t>
@@ -4085,19 +4085,22 @@
     <t>更多城市标题</t>
   </si>
   <si>
-    <t>海派格调与都会精选</t>
+    <t>海派格调上海外围精选</t>
   </si>
   <si>
     <t>上海外围｜上海模特预约｜上海高端外围｜顶奢</t>
   </si>
   <si>
-    <t>顶奢上海外围，集中展示上海精选外围模特，上海高端外围，上海外围女资料、独立图片、视频、风格介绍与相关推荐。</t>
+    <t>顶奢外围模特预约平台，集中展示上海外围，上海外围模特，上海包养，上海伴游，上海空姐，上海学生兼职，上海高端外围，上海外围女资料、上海外围预约，上海上门服务，上海同城上门，上海嫩模独立图片、视频、介绍与价格相关推荐。</t>
   </si>
   <si>
     <t>CITY COLLECTION</t>
   </si>
   <si>
-    <t>顶奢上海外围模特资源页面汇集上海静安区、徐汇区、闵行区、宝山区、普陀区、浦东区等区域外围商务模特资料，提供图片、视频及详细资料展示。并持续更新新的外围模特资料，更多资源请联系客服加入会员后解锁！</t>
+    <t>上海外围</t>
+  </si>
+  <si>
+    <t>顶奢上海外围模特资源页面汇集上海静安区、徐汇区、闵行区、宝山区、普陀区、浦东区等区域外围商务模特资料，提供图片、视频及详细资料展示。并持续更新新的外围模特资料，更多高端外围资源请联系客服加入会员后解锁！</t>
   </si>
   <si>
     <t>套独立资料</t>
@@ -4181,19 +4184,19 @@
     <t>继续浏览其他城市</t>
   </si>
   <si>
-    <t>岭南风尚与城市精选</t>
+    <t>岭南风尚广州外围精选</t>
   </si>
   <si>
     <t>广州外围｜广州模特预约｜广州高端外围｜顶奢</t>
   </si>
   <si>
-    <t>顶奢广州外围，集中展示广州精选外围模特，广州高端外围，广州外围女资料、独立图片、视频、风格介绍与相关推荐。</t>
-  </si>
-  <si>
-    <t>广州外围模特</t>
-  </si>
-  <si>
-    <t>顶奢广州外围模特资源页面汇集广州天河区、越秀区、海珠区、白云区等区域外围商务模特资料，提供图片、视频及详细资料展示。并持续更新新的外围模特资料，更多资源请联系客服加入会员后解锁！</t>
+    <t>顶奢外围模特预约平台，集中展示广州外围，广州外围模特，广州包养，广州伴游，广州空姐，广州学生兼职，广州高端外围，广州外围女资料、广州外围预约，广州上门服务，广州同城上门，广州嫩模独立图片、视频、介绍与价格相关推荐。</t>
+  </si>
+  <si>
+    <t>广州外围</t>
+  </si>
+  <si>
+    <t>顶奢广州外围模特资源页面汇集广州天河区、越秀区、海珠区、白云区等区域外围商务模特资料，提供图片、视频及详细资料展示。并持续更新新的外围模特资料，更多高端外围资源请联系客服加入会员后解锁！</t>
   </si>
   <si>
     <t>广州资料浏览指南</t>
@@ -4223,19 +4226,19 @@
     <t>怎样查看广州全部资料？</t>
   </si>
   <si>
-    <t>湾区新锐与现代精选</t>
+    <t>湾区新锐深圳外围精选</t>
   </si>
   <si>
     <t>深圳外围｜深圳模特预约｜深圳高端外围｜顶奢</t>
   </si>
   <si>
-    <t>顶奢深圳外围，集中展示深圳精选外围模特，深圳高端外围，深圳外围女资料、独立图片、视频、风格介绍与相关推荐。</t>
-  </si>
-  <si>
-    <t>深圳外围模特</t>
-  </si>
-  <si>
-    <t>顶奢深圳外围模特资源页面汇集深圳福田区、南山区、罗湖区、宝安区、龙华区等区域外围商务模特资料，提供图片、视频及详细资料展示。并持续更新新的外围模特资料，更多资源请联系客服加入会员后解锁！</t>
+    <t>顶奢外围模特预约平台，集中展示深圳外围，深圳外围模特，深圳包养，深圳伴游，深圳空姐，深圳学生兼职，深圳高端外围，深圳外围女资料、深圳外围预约，深圳上门服务，深圳同城上门，深圳嫩模独立图片、视频、介绍与价格相关推荐。</t>
+  </si>
+  <si>
+    <t>深圳外围</t>
+  </si>
+  <si>
+    <t>顶奢深圳外围模特资源页面汇集深圳福田区、南山区、罗湖区、宝安区、龙华区等区域外围商务模特资料，提供图片、视频及详细资料展示。并持续更新新的外围模特资料，更多高端外围资源请联系客服加入会员后解锁！</t>
   </si>
   <si>
     <t>深圳资料浏览指南</t>
@@ -4268,19 +4271,19 @@
     <t>怎样查看深圳全部资料？</t>
   </si>
   <si>
-    <t>京华气韵与城市精选</t>
+    <t>京华气韵北京外围精选</t>
   </si>
   <si>
     <t>北京外围｜北京模特预约｜北京高端外围｜顶奢</t>
   </si>
   <si>
-    <t>顶奢北京外围，集中展示北京精选外围模特，北京高端外围，北京外围女资料、独立图片、视频、风格介绍与相关推荐。</t>
-  </si>
-  <si>
-    <t>北京外围模特</t>
-  </si>
-  <si>
-    <t>顶奢北京外围模特资源页面汇集北京朝阳区、东城区、海定区等区域外围商务模特资料，提供图片、视频及详细资料展示。并持续更新新的外围模特资料，更多资源请联系客服加入会员后解锁！</t>
+    <t>顶奢外围模特预约平台，集中展示北京外围，北京外围模特，北京包养，北京伴游，北京空姐，北京学生兼职，北京高端外围，北京外围女资料、北京外围预约，北京上门服务，北京同城上门，北京嫩模独立图片、视频、介绍与价格相关推荐。</t>
+  </si>
+  <si>
+    <t>北京外围</t>
+  </si>
+  <si>
+    <t>顶奢北京外围模特资源页面汇集北京朝阳区、东城区、海定区等区域外围商务模特资料，提供图片、视频及详细资料展示。并持续更新新的外围模特资料，更多高端外围资源请联系客服加入会员后解锁！</t>
   </si>
   <si>
     <t>北京资料浏览指南</t>
@@ -4307,19 +4310,19 @@
     <t>怎样查看北京全部资料？</t>
   </si>
   <si>
-    <t>江南雅意与城市精选</t>
+    <t>江南雅意杭州外围精选</t>
   </si>
   <si>
     <t>杭州外围｜杭州模特预约｜杭州高端外围｜顶奢</t>
   </si>
   <si>
-    <t>顶奢杭州外围，集中展示杭州精选外围模特，杭州高端外围，杭州外围女资料、独立图片、视频、风格介绍与相关推荐。</t>
-  </si>
-  <si>
-    <t>杭州外围模特</t>
-  </si>
-  <si>
-    <t>顶奢杭州外围模特资源页面汇集杭州西湖区、上城区、滨江区、拱墅区、萧山区等区域外围商务模特资料，提供图片、视频及详细资料展示。并持续更新新的外围模特资料，更多资源请联系客服加入会员后解锁！</t>
+    <t>顶奢外围模特预约平台，集中展示杭州外围，杭州外围模特，杭州包养，杭州伴游，杭州空姐，杭州学生兼职，杭州高端外围，杭州外围女资料、杭州外围预约，杭州上门服务，杭州同城上门，杭州嫩模独立图片、视频、介绍与价格相关推荐。</t>
+  </si>
+  <si>
+    <t>杭州外围</t>
+  </si>
+  <si>
+    <t>顶奢杭州外围模特资源页面汇集杭州西湖区、上城区、滨江区、拱墅区、萧山区等区域外围商务模特资料，提供图片、视频及详细资料展示。并持续更新新的外围模特资料，更多高端资源请联系客服加入会员后解锁！</t>
   </si>
   <si>
     <t>杭州资料浏览指南</t>
@@ -18305,7 +18308,7 @@
       <c r="B5" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="17" t="s">
         <v>883</v>
       </c>
       <c r="D5" s="17" t="s">
@@ -18318,94 +18321,94 @@
         <v>886</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>136</v>
+        <v>887</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="K5" s="17" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="L5" s="17" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="M5" s="17" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="N5" s="17" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="O5" s="17" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="Q5" s="17" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="R5" s="17" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="S5" s="17" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="T5" s="5" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="U5" s="5" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="V5" s="5" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="W5" s="5" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="X5" s="17" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="Y5" s="5" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="Z5" s="5" t="s">
         <v>803</v>
       </c>
       <c r="AA5" s="5" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="AB5" s="17" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="AC5" s="17" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="AD5" s="17" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="AE5" s="17" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="AF5" s="17" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="AG5" s="17" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="AH5" s="17" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="AI5" s="5" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="AJ5" s="5" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="AK5" s="5" t="s">
         <v>58</v>
@@ -18427,107 +18430,107 @@
       <c r="B6" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>915</v>
+      <c r="C6" s="17" t="s">
+        <v>916</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>886</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="K6" s="17" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="L6" s="17" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="M6" s="17" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="N6" s="17" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="O6" s="17" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="P6" s="17" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="Q6" s="17" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="R6" s="17" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="S6" s="17" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="T6" s="5" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="U6" s="5" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="V6" s="5" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="W6" s="5" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="X6" s="17" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="Y6" s="5" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="Z6" s="5" t="s">
         <v>803</v>
       </c>
       <c r="AA6" s="5" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="AB6" s="17" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="AC6" s="17" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="AD6" s="17" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="AE6" s="17" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="AF6" s="17" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="AG6" s="17" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="AH6" s="5" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="AI6" s="5" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="AJ6" s="5" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="AK6" s="5" t="s">
         <v>58</v>
@@ -18549,107 +18552,107 @@
       <c r="B7" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>929</v>
+      <c r="C7" s="17" t="s">
+        <v>930</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>886</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="K7" s="17" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="L7" s="17" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="M7" s="17" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="O7" s="17" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="P7" s="17" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="Q7" s="17" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="R7" s="17" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="S7" s="17" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="T7" s="5" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="U7" s="5" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="V7" s="5" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="W7" s="5" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="X7" s="17" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="Y7" s="5" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="Z7" s="5" t="s">
         <v>803</v>
       </c>
       <c r="AA7" s="5" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="AB7" s="17" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="AC7" s="17" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="AD7" s="17" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="AE7" s="17" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="AF7" s="17" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="AG7" s="17" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="AH7" s="5" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="AI7" s="5" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="AJ7" s="5" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="AK7" s="5" t="s">
         <v>58</v>
@@ -18671,107 +18674,107 @@
       <c r="B8" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>944</v>
+      <c r="C8" s="17" t="s">
+        <v>945</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>886</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="K8" s="17" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="L8" s="17" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M8" s="17" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="O8" s="17" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="Q8" s="17" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="R8" s="17" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="S8" s="17" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="T8" s="5" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="U8" s="5" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="V8" s="5" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="W8" s="5" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="X8" s="17" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="Y8" s="5" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="Z8" s="5" t="s">
         <v>803</v>
       </c>
       <c r="AA8" s="5" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="AB8" s="17" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="AC8" s="17" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="AD8" s="17" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="AE8" s="17" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="AF8" s="17" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="AG8" s="17" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="AH8" s="5" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="AI8" s="5" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="AJ8" s="5" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="AK8" s="5" t="s">
         <v>58</v>
@@ -18793,107 +18796,107 @@
       <c r="B9" s="8" t="s">
         <v>494</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>957</v>
+      <c r="C9" s="17" t="s">
+        <v>958</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>886</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="K9" s="17" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="L9" s="17" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="M9" s="17" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="P9" s="17" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="Q9" s="17" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="R9" s="17" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="S9" s="17" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="T9" s="5" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="U9" s="5" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="V9" s="5" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="W9" s="5" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="X9" s="17" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="Y9" s="5" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="Z9" s="5" t="s">
         <v>803</v>
       </c>
       <c r="AA9" s="5" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="AB9" s="17" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="AC9" s="17" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="AD9" s="17" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="AE9" s="17" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="AF9" s="17" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="AG9" s="17" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="AH9" s="5" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="AI9" s="5" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="AJ9" s="5" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="AK9" s="5" t="s">
         <v>58</v>
@@ -19790,7 +19793,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -19800,7 +19803,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6">
       <c r="A2" s="9" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -19818,10 +19821,10 @@
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:6">
       <c r="A4" s="11" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>601</v>
@@ -19841,10 +19844,10 @@
         <v>632</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>6</v>
@@ -19853,7 +19856,7 @@
         <v>632</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:6">
@@ -19861,7 +19864,7 @@
         <v>632</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>637</v>
@@ -19870,10 +19873,10 @@
         <v>7</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:6">
@@ -19881,7 +19884,7 @@
         <v>632</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>640</v>
@@ -19890,10 +19893,10 @@
         <v>8</v>
       </c>
       <c r="E7" s="13" t="s">
+        <v>980</v>
+      </c>
+      <c r="F7" s="14" t="s">
         <v>979</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>978</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:6">
@@ -19901,7 +19904,7 @@
         <v>632</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>653</v>
@@ -19910,10 +19913,10 @@
         <v>654</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:6">
@@ -19921,19 +19924,19 @@
         <v>632</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>859</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:6">
@@ -19941,19 +19944,19 @@
         <v>632</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>665</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:6">
@@ -19961,19 +19964,19 @@
         <v>632</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:6">
@@ -19981,19 +19984,19 @@
         <v>632</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:6">
@@ -20001,19 +20004,19 @@
         <v>632</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="E13" s="13" t="s">
         <v>685</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:6">
@@ -20021,19 +20024,19 @@
         <v>632</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:6">
@@ -20041,19 +20044,19 @@
         <v>632</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:6">
@@ -20061,19 +20064,19 @@
         <v>632</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:6">
@@ -20081,19 +20084,19 @@
         <v>632</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:6">
@@ -20101,19 +20104,19 @@
         <v>632</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:6">
@@ -20121,19 +20124,19 @@
         <v>632</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:6">
@@ -20141,19 +20144,19 @@
         <v>632</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:6">
@@ -20161,19 +20164,19 @@
         <v>632</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:6">
@@ -20181,19 +20184,19 @@
         <v>632</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:6">
@@ -20201,19 +20204,19 @@
         <v>632</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:6">
@@ -20221,19 +20224,19 @@
         <v>632</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:6">
@@ -20241,19 +20244,19 @@
         <v>632</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:6">
@@ -20261,19 +20264,19 @@
         <v>632</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="27" ht="48" customHeight="1" spans="1:6">
@@ -20281,19 +20284,19 @@
         <v>632</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="E27" s="13" t="s">
         <v>730</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="28" ht="48" customHeight="1" spans="1:6">
@@ -20301,19 +20304,19 @@
         <v>632</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="29" ht="48" customHeight="1" spans="1:6">
@@ -20321,19 +20324,19 @@
         <v>632</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="30" ht="48" customHeight="1" spans="1:6">
@@ -20341,10 +20344,10 @@
         <v>635</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="D30" s="12" t="s">
         <v>6</v>
@@ -20353,7 +20356,7 @@
         <v>635</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="31" ht="48" customHeight="1" spans="1:6">
@@ -20361,7 +20364,7 @@
         <v>635</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>637</v>
@@ -20370,10 +20373,10 @@
         <v>7</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="32" ht="48" customHeight="1" spans="1:6">
@@ -20381,7 +20384,7 @@
         <v>635</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C32" s="12" t="s">
         <v>640</v>
@@ -20390,10 +20393,10 @@
         <v>8</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="33" ht="48" customHeight="1" spans="1:6">
@@ -20401,7 +20404,7 @@
         <v>635</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>653</v>
@@ -20410,10 +20413,10 @@
         <v>654</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="34" ht="48" customHeight="1" spans="1:6">
@@ -20421,19 +20424,19 @@
         <v>635</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="D34" s="12" t="s">
         <v>859</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="35" ht="48" customHeight="1" spans="1:6">
@@ -20441,19 +20444,19 @@
         <v>635</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>665</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="36" ht="48" customHeight="1" spans="1:6">
@@ -20461,19 +20464,19 @@
         <v>635</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="37" ht="48" customHeight="1" spans="1:6">
@@ -20481,19 +20484,19 @@
         <v>635</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="38" ht="48" customHeight="1" spans="1:6">
@@ -20501,19 +20504,19 @@
         <v>635</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="39" ht="48" customHeight="1" spans="1:6">
@@ -20521,19 +20524,19 @@
         <v>635</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="40" ht="48" customHeight="1" spans="1:6">
@@ -20541,19 +20544,19 @@
         <v>635</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="41" ht="48" customHeight="1" spans="1:6">
@@ -20561,19 +20564,19 @@
         <v>635</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="42" ht="48" customHeight="1" spans="1:6">
@@ -20581,19 +20584,19 @@
         <v>635</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="43" ht="48" customHeight="1" spans="1:6">
@@ -20601,19 +20604,19 @@
         <v>635</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="F43" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="44" ht="48" customHeight="1" spans="1:6">
@@ -20621,19 +20624,19 @@
         <v>635</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="45" ht="48" customHeight="1" spans="1:6">
@@ -20641,19 +20644,19 @@
         <v>635</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="F45" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="46" ht="48" customHeight="1" spans="1:6">
@@ -20661,47 +20664,47 @@
         <v>635</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="47" ht="48" customHeight="1" spans="1:6">
       <c r="A47" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="D47" s="12" t="s">
         <v>6</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="F47" s="14" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="48" ht="48" customHeight="1" spans="1:6">
       <c r="A48" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C48" s="12" t="s">
         <v>637</v>
@@ -20710,18 +20713,18 @@
         <v>7</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="49" ht="48" customHeight="1" spans="1:6">
       <c r="A49" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C49" s="12" t="s">
         <v>640</v>
@@ -20730,18 +20733,18 @@
         <v>8</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="50" ht="48" customHeight="1" spans="1:6">
       <c r="A50" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C50" s="12" t="s">
         <v>653</v>
@@ -20750,598 +20753,598 @@
         <v>654</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="51" ht="48" customHeight="1" spans="1:6">
       <c r="A51" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="D51" s="12" t="s">
         <v>859</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="52" ht="48" customHeight="1" spans="1:6">
       <c r="A52" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C52" s="12" t="s">
         <v>665</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="53" ht="48" customHeight="1" spans="1:6">
       <c r="A53" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="54" ht="48" customHeight="1" spans="1:6">
       <c r="A54" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="55" ht="48" customHeight="1" spans="1:6">
       <c r="A55" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="56" ht="48" customHeight="1" spans="1:6">
       <c r="A56" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="57" ht="48" customHeight="1" spans="1:6">
       <c r="A57" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="58" ht="48" customHeight="1" spans="1:6">
       <c r="A58" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="59" ht="48" customHeight="1" spans="1:6">
       <c r="A59" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="F59" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="60" ht="48" customHeight="1" spans="1:6">
       <c r="A60" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="F60" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="61" ht="48" customHeight="1" spans="1:6">
       <c r="A61" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="62" ht="48" customHeight="1" spans="1:6">
       <c r="A62" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="63" ht="48" customHeight="1" spans="1:6">
       <c r="A63" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="F63" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="64" ht="48" customHeight="1" spans="1:6">
       <c r="A64" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="65" ht="48" customHeight="1" spans="1:6">
       <c r="A65" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="66" ht="48" customHeight="1" spans="1:6">
       <c r="A66" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="E66" s="13" t="s">
         <v>693</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="67" ht="48" customHeight="1" spans="1:6">
       <c r="A67" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="F67" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="68" ht="48" customHeight="1" spans="1:6">
       <c r="A68" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="F68" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="69" ht="48" customHeight="1" spans="1:6">
       <c r="A69" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="E69" s="13" t="s">
         <v>693</v>
       </c>
       <c r="F69" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="70" ht="48" customHeight="1" spans="1:6">
       <c r="A70" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="F70" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="71" ht="48" customHeight="1" spans="1:6">
       <c r="A71" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="F71" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="72" ht="48" customHeight="1" spans="1:6">
       <c r="A72" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="E72" s="13" t="s">
         <v>693</v>
       </c>
       <c r="F72" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="73" ht="48" customHeight="1" spans="1:6">
       <c r="A73" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="F73" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="74" ht="48" customHeight="1" spans="1:6">
       <c r="A74" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="F74" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="75" ht="48" customHeight="1" spans="1:6">
       <c r="A75" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E75" s="13" t="s">
         <v>693</v>
       </c>
       <c r="F75" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="76" ht="48" customHeight="1" spans="1:6">
       <c r="A76" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="F76" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="77" ht="48" customHeight="1" spans="1:6">
       <c r="A77" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="F77" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="78" ht="48" customHeight="1" spans="1:6">
       <c r="A78" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="D78" s="12" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="F78" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="79" ht="48" customHeight="1" spans="1:6">
       <c r="A79" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="D79" s="12" t="s">
         <v>6</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="F79" s="14" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="80" ht="48" customHeight="1" spans="1:6">
       <c r="A80" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C80" s="12" t="s">
         <v>637</v>
@@ -21350,18 +21353,18 @@
         <v>7</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="F80" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="81" ht="48" customHeight="1" spans="1:6">
       <c r="A81" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C81" s="12" t="s">
         <v>640</v>
@@ -21370,18 +21373,18 @@
         <v>8</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="F81" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="82" ht="48" customHeight="1" spans="1:6">
       <c r="A82" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C82" s="12" t="s">
         <v>653</v>
@@ -21390,598 +21393,598 @@
         <v>654</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="F82" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="83" ht="48" customHeight="1" spans="1:6">
       <c r="A83" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="D83" s="12" t="s">
         <v>859</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="F83" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="84" ht="48" customHeight="1" spans="1:6">
       <c r="A84" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C84" s="12" t="s">
         <v>665</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="F84" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="85" ht="48" customHeight="1" spans="1:6">
       <c r="A85" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="F85" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="86" ht="48" customHeight="1" spans="1:6">
       <c r="A86" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="F86" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="87" ht="48" customHeight="1" spans="1:6">
       <c r="A87" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="F87" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="88" ht="48" customHeight="1" spans="1:6">
       <c r="A88" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B88" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="F88" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="89" ht="48" customHeight="1" spans="1:6">
       <c r="A89" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="F89" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="90" ht="48" customHeight="1" spans="1:6">
       <c r="A90" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="D90" s="12" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="F90" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="91" ht="48" customHeight="1" spans="1:6">
       <c r="A91" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B91" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="F91" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="92" ht="48" customHeight="1" spans="1:6">
       <c r="A92" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B92" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="F92" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="93" ht="48" customHeight="1" spans="1:6">
       <c r="A93" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B93" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="F93" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="94" ht="48" customHeight="1" spans="1:6">
       <c r="A94" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B94" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="E94" s="13" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="F94" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="95" ht="48" customHeight="1" spans="1:6">
       <c r="A95" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="E95" s="13" t="s">
         <v>693</v>
       </c>
       <c r="F95" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="96" ht="48" customHeight="1" spans="1:6">
       <c r="A96" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="D96" s="12" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="E96" s="13" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F96" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="97" ht="48" customHeight="1" spans="1:6">
       <c r="A97" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="D97" s="12" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="E97" s="13" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="F97" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="98" ht="48" customHeight="1" spans="1:6">
       <c r="A98" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B98" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="D98" s="12" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="E98" s="13" t="s">
         <v>693</v>
       </c>
       <c r="F98" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="99" ht="48" customHeight="1" spans="1:6">
       <c r="A99" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B99" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="D99" s="12" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="F99" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="100" ht="48" customHeight="1" spans="1:6">
       <c r="A100" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B100" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="D100" s="12" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="F100" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="101" ht="48" customHeight="1" spans="1:6">
       <c r="A101" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B101" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D101" s="12" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="E101" s="13" t="s">
         <v>693</v>
       </c>
       <c r="F101" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="102" ht="48" customHeight="1" spans="1:6">
       <c r="A102" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B102" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D102" s="12" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="F102" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="103" ht="48" customHeight="1" spans="1:6">
       <c r="A103" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B103" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D103" s="12" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="F103" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="104" ht="48" customHeight="1" spans="1:6">
       <c r="A104" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B104" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="E104" s="13" t="s">
         <v>693</v>
       </c>
       <c r="F104" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="105" ht="48" customHeight="1" spans="1:6">
       <c r="A105" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B105" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="D105" s="12" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="E105" s="13" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="F105" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="106" ht="48" customHeight="1" spans="1:6">
       <c r="A106" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B106" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="D106" s="12" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="E106" s="13" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="F106" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="107" ht="48" customHeight="1" spans="1:6">
       <c r="A107" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B107" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D107" s="12" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E107" s="13" t="s">
         <v>693</v>
       </c>
       <c r="F107" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="108" ht="48" customHeight="1" spans="1:6">
       <c r="A108" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B108" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="D108" s="12" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="E108" s="13" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="F108" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="109" ht="48" customHeight="1" spans="1:6">
       <c r="A109" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B109" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="D109" s="12" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="F109" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="110" ht="48" customHeight="1" spans="1:6">
       <c r="A110" s="12" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B110" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="D110" s="12" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="E110" s="13" t="s">
         <v>693</v>
       </c>
       <c r="F110" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="111" ht="48" customHeight="1" spans="1:6">
       <c r="A111" s="12" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B111" s="12" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="D111" s="12" t="s">
         <v>6</v>
       </c>
       <c r="E111" s="13" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="F111" s="14" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="112" ht="48" customHeight="1" spans="1:6">
       <c r="A112" s="12" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B112" s="12" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="C112" s="12" t="s">
         <v>637</v>
@@ -21990,18 +21993,18 @@
         <v>7</v>
       </c>
       <c r="E112" s="13" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="F112" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="113" ht="48" customHeight="1" spans="1:6">
       <c r="A113" s="12" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B113" s="12" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="C113" s="12" t="s">
         <v>640</v>
@@ -22010,18 +22013,18 @@
         <v>8</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="F113" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="114" ht="48" customHeight="1" spans="1:6">
       <c r="A114" s="12" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B114" s="12" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="C114" s="12" t="s">
         <v>653</v>
@@ -22030,70 +22033,70 @@
         <v>654</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="F114" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="115" ht="48" customHeight="1" spans="1:6">
       <c r="A115" s="12" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="D115" s="12" t="s">
         <v>859</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="F115" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="116" ht="48" customHeight="1" spans="1:6">
       <c r="A116" s="12" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B116" s="12" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="C116" s="12" t="s">
         <v>665</v>
       </c>
       <c r="D116" s="12" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="E116" s="13" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="F116" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="117" ht="48" customHeight="1" spans="1:6">
       <c r="A117" s="12" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B117" s="12" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="E117" s="13" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="F117" s="14" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
   </sheetData>
@@ -22122,7 +22125,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:5">
       <c r="A1" s="2" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -22131,7 +22134,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:5">
       <c r="A2" s="9" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -22164,33 +22167,33 @@
     </row>
     <row r="5" ht="42" customHeight="1" spans="1:5">
       <c r="A5" s="12" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1" spans="1:5">
       <c r="A6" s="12" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>693</v>
@@ -22198,33 +22201,33 @@
     </row>
     <row r="7" ht="42" customHeight="1" spans="1:5">
       <c r="A7" s="12" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B7" s="12" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>1179</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>1178</v>
-      </c>
       <c r="D7" s="13" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1" spans="1:5">
       <c r="A8" s="12" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="E8" s="14" t="s">
         <v>693</v>
@@ -22232,33 +22235,33 @@
     </row>
     <row r="9" ht="42" customHeight="1" spans="1:5">
       <c r="A9" s="12" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1" spans="1:5">
       <c r="A10" s="12" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="E10" s="14" t="s">
         <v>693</v>
@@ -22266,16 +22269,16 @@
     </row>
     <row r="11" ht="42" customHeight="1" spans="1:5">
       <c r="A11" s="12" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="E11" s="14" t="s">
         <v>693</v>
@@ -22283,13 +22286,13 @@
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:5">
       <c r="A12" s="12" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>632</v>
@@ -22300,13 +22303,13 @@
     </row>
     <row r="13" ht="42" customHeight="1" spans="1:5">
       <c r="A13" s="12" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>635</v>
@@ -22317,16 +22320,16 @@
     </row>
     <row r="14" ht="42" customHeight="1" spans="1:5">
       <c r="A14" s="12" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="E14" s="14" t="s">
         <v>693</v>
@@ -22334,16 +22337,16 @@
     </row>
     <row r="15" ht="42" customHeight="1" spans="1:5">
       <c r="A15" s="12" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="E15" s="14" t="s">
         <v>693</v>
@@ -22351,16 +22354,16 @@
     </row>
     <row r="16" ht="42" customHeight="1" spans="1:5">
       <c r="A16" s="12" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="E16" s="14" t="s">
         <v>693</v>
@@ -22368,16 +22371,16 @@
     </row>
     <row r="17" ht="42" customHeight="1" spans="1:5">
       <c r="A17" s="12" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="E17" s="14" t="s">
         <v>693</v>
@@ -22385,16 +22388,16 @@
     </row>
     <row r="18" ht="42" customHeight="1" spans="1:5">
       <c r="A18" s="12" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="E18" s="14" t="s">
         <v>693</v>
@@ -22402,16 +22405,16 @@
     </row>
     <row r="19" ht="42" customHeight="1" spans="1:5">
       <c r="A19" s="12" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="E19" s="14" t="s">
         <v>693</v>
@@ -22441,7 +22444,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:8">
       <c r="A1" s="2" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -22453,7 +22456,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -22465,50 +22468,50 @@
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:8">
       <c r="A4" s="4" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:8">
       <c r="A5" s="5" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:8">
       <c r="A6" s="5" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:8">
       <c r="A7" s="5" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:8">
       <c r="A8" s="5" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:8">
       <c r="A9" s="5" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:8">
@@ -22516,10 +22519,10 @@
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:8">
       <c r="A11" s="4" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:8">
@@ -22527,7 +22530,7 @@
         <v>22</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:8">
@@ -22535,47 +22538,47 @@
         <v>23</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:8">
       <c r="A14" s="5" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:8">
       <c r="A15" s="5" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:8">
       <c r="A16" s="5" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2">
       <c r="A17" s="5" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:2">
       <c r="A18" s="5" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:2">
@@ -22583,10 +22586,10 @@
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:2">
       <c r="A20" s="4" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:2">
@@ -22594,7 +22597,7 @@
         <v>1</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:2">
@@ -22602,7 +22605,7 @@
         <v>2</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:2">
@@ -22610,7 +22613,7 @@
         <v>3</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1" spans="1:2">
@@ -22618,7 +22621,7 @@
         <v>4</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:2">
@@ -22626,7 +22629,7 @@
         <v>5</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1" spans="1:2">
@@ -22634,7 +22637,7 @@
         <v>6</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1" spans="1:2">
@@ -22642,7 +22645,7 @@
         <v>7</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1" spans="1:2">
@@ -22650,7 +22653,7 @@
         <v>8</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1" spans="1:2">
@@ -22658,7 +22661,7 @@
         <v>9</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1" spans="1:2">
@@ -22666,7 +22669,7 @@
         <v>10</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1" spans="1:2">
@@ -22674,26 +22677,26 @@
     </row>
     <row r="32" ht="28" customHeight="1" spans="1:2">
       <c r="A32" s="4" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1" spans="1:2">
       <c r="A33" s="5" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1" spans="1:2">
       <c r="A34" s="8" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
     </row>
   </sheetData>

--- a/顶奢_整站资料批量编辑.xlsx
+++ b/顶奢_整站资料批量编辑.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16455" activeTab="2"/>
+    <workbookView windowHeight="16455" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="资料批量编辑" sheetId="1" r:id="rId1"/>
@@ -3359,7 +3359,7 @@
     <t>seo_description</t>
   </si>
   <si>
-    <t>上海外围、广州外围、深圳外围、北京外围、杭州外围城市资料展示与独立详情页。</t>
+    <t>顶奢平台专业为社会名流高端人士提供高端靠谱上海外围、广州外围、深圳外围、北京外围、杭州外围等一二线城市资料展示与价格外围经纪人联系方式。商务外围，商务伴游、上门服务、桑拿品茶、高端外围、兼职外围女模特、极品外围女请与我们联系。资源覆盖国内一二线城市以及海外各大主流城市，规范化服务流程，注重客户隐私保护。</t>
   </si>
   <si>
     <t>首页搜索摘要</t>
@@ -4091,7 +4091,7 @@
     <t>上海外围｜上海模特预约｜上海高端外围｜顶奢</t>
   </si>
   <si>
-    <t>顶奢外围模特预约平台，集中展示上海外围，上海外围模特，上海包养，上海伴游，上海空姐，上海学生兼职，上海高端外围，上海外围女资料、上海外围预约，上海上门服务，上海同城上门，上海嫩模独立图片、视频、介绍与价格相关推荐。</t>
+    <t>顶奢外围模特预约平台，展示上海外围，上海外围模特，上海包养，上海伴游，上海空姐，上海学生兼职，上海高端外围，上海外围女资料、上海外围预约，上海上门服务，上海同城上门，上海嫩模独立图片、视频、介绍与价格相关推荐。</t>
   </si>
   <si>
     <t>CITY COLLECTION</t>
@@ -4232,7 +4232,7 @@
     <t>深圳外围｜深圳模特预约｜深圳高端外围｜顶奢</t>
   </si>
   <si>
-    <t>顶奢外围模特预约平台，集中展示深圳外围，深圳外围模特，深圳包养，深圳伴游，深圳空姐，深圳学生兼职，深圳高端外围，深圳外围女资料、深圳外围预约，深圳上门服务，深圳同城上门，深圳嫩模独立图片、视频、介绍与价格相关推荐。</t>
+    <t>顶奢外围模特预约平台，展示深圳外围，深圳外围模特，深圳包养，深圳伴游，深圳空姐，深圳学生兼职，深圳高端外围，深圳外围女资料、深圳外围预约，深圳上门服务，深圳同城上门，深圳嫩模独立图片、视频、介绍与价格相关推荐。</t>
   </si>
   <si>
     <t>深圳外围</t>
@@ -4277,7 +4277,7 @@
     <t>北京外围｜北京模特预约｜北京高端外围｜顶奢</t>
   </si>
   <si>
-    <t>顶奢外围模特预约平台，集中展示北京外围，北京外围模特，北京包养，北京伴游，北京空姐，北京学生兼职，北京高端外围，北京外围女资料、北京外围预约，北京上门服务，北京同城上门，北京嫩模独立图片、视频、介绍与价格相关推荐。</t>
+    <t>顶奢外围模特预约平台，展示北京外围，北京外围模特，北京包养，北京伴游，北京空姐，北京学生兼职，北京高端外围，北京外围女资料、北京外围预约，北京上门服务，北京同城上门，北京嫩模独立图片、视频、介绍与价格相关推荐。</t>
   </si>
   <si>
     <t>北京外围</t>
@@ -4316,7 +4316,7 @@
     <t>杭州外围｜杭州模特预约｜杭州高端外围｜顶奢</t>
   </si>
   <si>
-    <t>顶奢外围模特预约平台，集中展示杭州外围，杭州外围模特，杭州包养，杭州伴游，杭州空姐，杭州学生兼职，杭州高端外围，杭州外围女资料、杭州外围预约，杭州上门服务，杭州同城上门，杭州嫩模独立图片、视频、介绍与价格相关推荐。</t>
+    <t>顶奢外围模特预约平台，展示杭州外围，杭州外围模特，杭州包养，杭州伴游，杭州空姐，杭州学生兼职，杭州高端外围，杭州外围女资料、杭州外围预约，杭州上门服务，杭州同城上门，杭州嫩模独立图片、视频、介绍与价格相关推荐。</t>
   </si>
   <si>
     <t>杭州外围</t>
@@ -4457,7 +4457,7 @@
     <t>第1段正文2</t>
   </si>
   <si>
-    <t>、以及国内主流城市和国外主流城市的高端外围模特、平面模特、商务模特、网红模特、车模、泳装模特、内衣模特、兼职空姐、coser、洛丽塔等高端资源。平台专业为社会名流高端人士提供高端靠谱商务外围服务，找全球伴游、兼职外围女模特、高端商务陪同、极品外围女请与我们联系。覆盖国内各大城市，规范化服务流程，注重客户隐私保护。</t>
+    <t>以及国内主流城市和国外主流城市的高端外围模特、平面模特、商务模特、网红模特、车模、泳装模特、内衣模特、兼职空姐、coser、洛丽塔等高端资源。平台专业为社会名流高端人士提供高端靠谱商务外围服务，找全球伴游、兼职外围女模特、高端商务陪同、极品外围女请与我们联系。覆盖国内各大城市，规范化服务流程，注重客户隐私保护。</t>
   </si>
   <si>
     <t>section_2_kicker</t>
